--- a/input/lista/1 LISTA PDV ENI 2.xlsx
+++ b/input/lista/1 LISTA PDV ENI 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nadir\Desktop\APP TELEPASS\FILE FISSI\lista\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A3AE8BC-1B48-42C4-9759-EA78F669B0A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80D1C2A0-0396-4067-AE4B-C399FBEC8622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{D320C423-4B98-4D55-B6E8-3ABF0EE22191}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2136" uniqueCount="1472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2119" uniqueCount="1462">
   <si>
     <t>ALESSANDRIA</t>
   </si>
@@ -711,9 +711,6 @@
     <t>ALBA</t>
   </si>
   <si>
-    <t>C.SO M. COPPINO N° 54</t>
-  </si>
-  <si>
     <t>FERMO</t>
   </si>
   <si>
@@ -3600,9 +3597,6 @@
     <t>215</t>
   </si>
   <si>
-    <t>10241</t>
-  </si>
-  <si>
     <t>350</t>
   </si>
   <si>
@@ -3966,18 +3960,9 @@
     <t>3775</t>
   </si>
   <si>
-    <t>51318</t>
-  </si>
-  <si>
     <t>1858</t>
   </si>
   <si>
-    <t>607</t>
-  </si>
-  <si>
-    <t>1923</t>
-  </si>
-  <si>
     <t>7224</t>
   </si>
   <si>
@@ -3996,9 +3981,6 @@
     <t>1007</t>
   </si>
   <si>
-    <t>'1480</t>
-  </si>
-  <si>
     <t>259</t>
   </si>
   <si>
@@ -4116,9 +4098,6 @@
     <t>BREGNANO</t>
   </si>
   <si>
-    <t>CANTÙ</t>
-  </si>
-  <si>
     <t>PORTO SAN GIORGIO</t>
   </si>
   <si>
@@ -4296,16 +4275,7 @@
     <t>VIA NOVARA</t>
   </si>
   <si>
-    <t>C.SO CASALE 292A</t>
-  </si>
-  <si>
     <t>STRADA PROVINC.LE 31</t>
-  </si>
-  <si>
-    <t>CORSO FRANCIA 6</t>
-  </si>
-  <si>
-    <t>RONCO VIA VERGANI</t>
   </si>
   <si>
     <t>Via Casilina, 1423</t>
@@ -4811,7 +4781,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{175EF563-0873-44BA-ACAF-2DC290E6A803}">
-  <dimension ref="A1:J534"/>
+  <dimension ref="A1:J530"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="29.44140625" bestFit="1" customWidth="1"/>
@@ -4821,13 +4791,13 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="G1" t="s">
+        <v>514</v>
+      </c>
+      <c r="H1" t="s">
         <v>515</v>
-      </c>
-      <c r="H1" t="s">
-        <v>516</v>
       </c>
       <c r="J1" t="s">
         <v>34</v>
@@ -4835,13 +4805,13 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="G2" t="s">
+        <v>502</v>
+      </c>
+      <c r="H2" t="s">
         <v>503</v>
-      </c>
-      <c r="H2" t="s">
-        <v>504</v>
       </c>
       <c r="J2" t="s">
         <v>34</v>
@@ -4849,13 +4819,13 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="G3" t="s">
+        <v>231</v>
+      </c>
+      <c r="H3" t="s">
         <v>232</v>
-      </c>
-      <c r="H3" t="s">
-        <v>233</v>
       </c>
       <c r="J3" t="s">
         <v>34</v>
@@ -4863,7 +4833,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="G4" t="s">
         <v>98</v>
@@ -4877,13 +4847,13 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="G5" t="s">
+        <v>328</v>
+      </c>
+      <c r="H5" t="s">
         <v>329</v>
-      </c>
-      <c r="H5" t="s">
-        <v>330</v>
       </c>
       <c r="J5" t="s">
         <v>34</v>
@@ -4891,13 +4861,13 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="G6" t="s">
+        <v>236</v>
+      </c>
+      <c r="H6" t="s">
         <v>237</v>
-      </c>
-      <c r="H6" t="s">
-        <v>238</v>
       </c>
       <c r="J6" t="s">
         <v>34</v>
@@ -4905,13 +4875,13 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="G7" t="s">
+        <v>399</v>
+      </c>
+      <c r="H7" t="s">
         <v>400</v>
-      </c>
-      <c r="H7" t="s">
-        <v>401</v>
       </c>
       <c r="J7" t="s">
         <v>34</v>
@@ -4919,13 +4889,13 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="G8" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H8" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="J8" t="s">
         <v>34</v>
@@ -4933,13 +4903,13 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="G9" t="s">
+        <v>541</v>
+      </c>
+      <c r="H9" t="s">
         <v>542</v>
-      </c>
-      <c r="H9" t="s">
-        <v>543</v>
       </c>
       <c r="J9" t="s">
         <v>34</v>
@@ -4947,13 +4917,13 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="G10" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H10" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="J10" t="s">
         <v>34</v>
@@ -4961,13 +4931,13 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="G11" t="s">
+        <v>396</v>
+      </c>
+      <c r="H11" t="s">
         <v>397</v>
-      </c>
-      <c r="H11" t="s">
-        <v>398</v>
       </c>
       <c r="J11" t="s">
         <v>34</v>
@@ -4975,13 +4945,13 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="G12" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H12" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="J12" t="s">
         <v>34</v>
@@ -4989,13 +4959,13 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="G13" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H13" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="J13" t="s">
         <v>34</v>
@@ -5003,13 +4973,13 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="G14" t="s">
+        <v>243</v>
+      </c>
+      <c r="H14" t="s">
         <v>244</v>
-      </c>
-      <c r="H14" t="s">
-        <v>245</v>
       </c>
       <c r="J14" t="s">
         <v>34</v>
@@ -5017,13 +4987,13 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="G15" t="s">
+        <v>495</v>
+      </c>
+      <c r="H15" t="s">
         <v>496</v>
-      </c>
-      <c r="H15" t="s">
-        <v>497</v>
       </c>
       <c r="J15" t="s">
         <v>34</v>
@@ -5031,13 +5001,13 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="G16" t="s">
+        <v>519</v>
+      </c>
+      <c r="H16" t="s">
         <v>520</v>
-      </c>
-      <c r="H16" t="s">
-        <v>521</v>
       </c>
       <c r="J16" t="s">
         <v>34</v>
@@ -5045,13 +5015,13 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="G17" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H17" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J17" t="s">
         <v>34</v>
@@ -5059,7 +5029,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="G18" t="s">
         <v>98</v>
@@ -5073,13 +5043,13 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="G19" t="s">
+        <v>544</v>
+      </c>
+      <c r="H19" t="s">
         <v>545</v>
-      </c>
-      <c r="H19" t="s">
-        <v>546</v>
       </c>
       <c r="J19" t="s">
         <v>34</v>
@@ -5087,13 +5057,13 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="G20" t="s">
+        <v>255</v>
+      </c>
+      <c r="H20" t="s">
         <v>256</v>
-      </c>
-      <c r="H20" t="s">
-        <v>257</v>
       </c>
       <c r="J20" t="s">
         <v>34</v>
@@ -5101,13 +5071,13 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="G21" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H21" t="s">
-        <v>1404</v>
+        <v>1397</v>
       </c>
       <c r="J21" t="s">
         <v>34</v>
@@ -5115,7 +5085,7 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="G22" t="s">
         <v>108</v>
@@ -5129,7 +5099,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="G23" t="s">
         <v>35</v>
@@ -5143,13 +5113,13 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="G24" t="s">
+        <v>245</v>
+      </c>
+      <c r="H24" t="s">
         <v>246</v>
-      </c>
-      <c r="H24" t="s">
-        <v>247</v>
       </c>
       <c r="J24" t="s">
         <v>34</v>
@@ -5157,13 +5127,13 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="G25" t="s">
+        <v>539</v>
+      </c>
+      <c r="H25" t="s">
         <v>540</v>
-      </c>
-      <c r="H25" t="s">
-        <v>541</v>
       </c>
       <c r="J25" t="s">
         <v>34</v>
@@ -5171,13 +5141,13 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="G26" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H26" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="J26" t="s">
         <v>34</v>
@@ -5185,13 +5155,13 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="G27" t="s">
+        <v>394</v>
+      </c>
+      <c r="H27" t="s">
         <v>395</v>
-      </c>
-      <c r="H27" t="s">
-        <v>396</v>
       </c>
       <c r="J27" t="s">
         <v>34</v>
@@ -5199,13 +5169,13 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="G28" t="s">
+        <v>493</v>
+      </c>
+      <c r="H28" t="s">
         <v>494</v>
-      </c>
-      <c r="H28" t="s">
-        <v>495</v>
       </c>
       <c r="J28" t="s">
         <v>34</v>
@@ -5213,13 +5183,13 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="G29" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H29" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="J29" t="s">
         <v>34</v>
@@ -5227,7 +5197,7 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="G30" t="s">
         <v>98</v>
@@ -5241,13 +5211,13 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="G31" t="s">
+        <v>318</v>
+      </c>
+      <c r="H31" t="s">
         <v>319</v>
-      </c>
-      <c r="H31" t="s">
-        <v>320</v>
       </c>
       <c r="J31" t="s">
         <v>34</v>
@@ -5255,13 +5225,13 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="G32" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H32" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="J32" t="s">
         <v>34</v>
@@ -5269,13 +5239,13 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="G33" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="H33" t="s">
-        <v>1405</v>
+        <v>1398</v>
       </c>
       <c r="J33" t="s">
         <v>34</v>
@@ -5283,7 +5253,7 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="G34" t="s">
         <v>104</v>
@@ -5297,7 +5267,7 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="G35" t="s">
         <v>98</v>
@@ -5311,13 +5281,13 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="G36" t="s">
+        <v>344</v>
+      </c>
+      <c r="H36" t="s">
         <v>345</v>
-      </c>
-      <c r="H36" t="s">
-        <v>346</v>
       </c>
       <c r="J36" t="s">
         <v>34</v>
@@ -5325,7 +5295,7 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="G37" t="s">
         <v>101</v>
@@ -5339,13 +5309,13 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="G38" t="s">
+        <v>257</v>
+      </c>
+      <c r="H38" t="s">
         <v>258</v>
-      </c>
-      <c r="H38" t="s">
-        <v>259</v>
       </c>
       <c r="J38" t="s">
         <v>34</v>
@@ -5353,13 +5323,13 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="G39" t="s">
+        <v>240</v>
+      </c>
+      <c r="H39" t="s">
         <v>241</v>
-      </c>
-      <c r="H39" t="s">
-        <v>242</v>
       </c>
       <c r="J39" t="s">
         <v>34</v>
@@ -5367,13 +5337,13 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="G40" t="s">
+        <v>404</v>
+      </c>
+      <c r="H40" t="s">
         <v>405</v>
-      </c>
-      <c r="H40" t="s">
-        <v>406</v>
       </c>
       <c r="J40" t="s">
         <v>34</v>
@@ -5381,7 +5351,7 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="G41" t="s">
         <v>98</v>
@@ -5395,13 +5365,13 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="G42" t="s">
+        <v>286</v>
+      </c>
+      <c r="H42" t="s">
         <v>287</v>
-      </c>
-      <c r="H42" t="s">
-        <v>288</v>
       </c>
       <c r="J42" t="s">
         <v>34</v>
@@ -5409,13 +5379,13 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="G43" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H43" t="s">
-        <v>1406</v>
+        <v>1399</v>
       </c>
       <c r="J43" t="s">
         <v>34</v>
@@ -5423,13 +5393,13 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="G44" t="s">
+        <v>497</v>
+      </c>
+      <c r="H44" t="s">
         <v>498</v>
-      </c>
-      <c r="H44" t="s">
-        <v>499</v>
       </c>
       <c r="J44" t="s">
         <v>34</v>
@@ -5437,7 +5407,7 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="G45" t="s">
         <v>98</v>
@@ -5451,13 +5421,13 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="G46" t="s">
         <v>32</v>
       </c>
       <c r="H46" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="J46" t="s">
         <v>34</v>
@@ -5465,7 +5435,7 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="G47" t="s">
         <v>98</v>
@@ -5479,13 +5449,13 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="G48" t="s">
+        <v>613</v>
+      </c>
+      <c r="H48" t="s">
         <v>614</v>
-      </c>
-      <c r="H48" t="s">
-        <v>615</v>
       </c>
       <c r="J48" t="s">
         <v>34</v>
@@ -5493,13 +5463,13 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="G49" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H49" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="J49" t="s">
         <v>34</v>
@@ -5507,13 +5477,13 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="G50" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H50" t="s">
-        <v>1370</v>
+        <v>1363</v>
       </c>
       <c r="J50" t="s">
         <v>34</v>
@@ -5521,13 +5491,13 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="G51" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H51" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J51" t="s">
         <v>34</v>
@@ -5535,13 +5505,13 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="G52" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H52" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="J52" t="s">
         <v>34</v>
@@ -5549,13 +5519,13 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="G53" t="s">
         <v>98</v>
       </c>
       <c r="H53" t="s">
-        <v>1407</v>
+        <v>1400</v>
       </c>
       <c r="J53" t="s">
         <v>34</v>
@@ -5563,13 +5533,13 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="G54" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H54" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="J54" t="s">
         <v>34</v>
@@ -5577,7 +5547,7 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="G55" t="s">
         <v>37</v>
@@ -5591,7 +5561,7 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="G56" t="s">
         <v>98</v>
@@ -5605,7 +5575,7 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="G57" t="s">
         <v>106</v>
@@ -5619,7 +5589,7 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="G58" t="s">
         <v>119</v>
@@ -5633,13 +5603,13 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="G59" t="s">
         <v>98</v>
       </c>
       <c r="H59" t="s">
-        <v>1408</v>
+        <v>1401</v>
       </c>
       <c r="J59" t="s">
         <v>34</v>
@@ -5647,13 +5617,13 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G60" t="s">
+        <v>500</v>
+      </c>
+      <c r="H60" t="s">
         <v>501</v>
-      </c>
-      <c r="H60" t="s">
-        <v>502</v>
       </c>
       <c r="J60" t="s">
         <v>34</v>
@@ -5661,7 +5631,7 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="G61" t="s">
         <v>32</v>
@@ -5675,13 +5645,13 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="G62" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H62" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="J62" t="s">
         <v>34</v>
@@ -5689,13 +5659,13 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="G63" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H63" t="s">
-        <v>1409</v>
+        <v>1402</v>
       </c>
       <c r="J63" t="s">
         <v>34</v>
@@ -5703,13 +5673,13 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="G64" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H64" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="J64" t="s">
         <v>34</v>
@@ -5717,13 +5687,13 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="G65" t="s">
+        <v>316</v>
+      </c>
+      <c r="H65" t="s">
         <v>317</v>
-      </c>
-      <c r="H65" t="s">
-        <v>318</v>
       </c>
       <c r="J65" t="s">
         <v>34</v>
@@ -5731,7 +5701,7 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="G66" t="s">
         <v>32</v>
@@ -5745,13 +5715,13 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="G67" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H67" t="s">
-        <v>1410</v>
+        <v>1403</v>
       </c>
       <c r="J67" t="s">
         <v>34</v>
@@ -5759,13 +5729,13 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="G68" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H68" t="s">
-        <v>1371</v>
+        <v>1364</v>
       </c>
       <c r="J68" t="s">
         <v>34</v>
@@ -5773,13 +5743,13 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="G69" t="s">
+        <v>332</v>
+      </c>
+      <c r="H69" t="s">
         <v>333</v>
-      </c>
-      <c r="H69" t="s">
-        <v>334</v>
       </c>
       <c r="J69" t="s">
         <v>34</v>
@@ -5787,13 +5757,13 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="G70" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H70" t="s">
-        <v>1411</v>
+        <v>1404</v>
       </c>
       <c r="J70" t="s">
         <v>34</v>
@@ -5801,13 +5771,13 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="G71" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="H71" t="s">
-        <v>1372</v>
+        <v>1365</v>
       </c>
       <c r="J71" t="s">
         <v>34</v>
@@ -5815,13 +5785,13 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="G72" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H72" t="s">
-        <v>1373</v>
+        <v>1366</v>
       </c>
       <c r="J72" t="s">
         <v>34</v>
@@ -5829,7 +5799,7 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="G73" t="s">
         <v>114</v>
@@ -5843,13 +5813,13 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="G74" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H74" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="J74" t="s">
         <v>34</v>
@@ -5857,7 +5827,7 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="G75" t="s">
         <v>99</v>
@@ -5871,13 +5841,13 @@
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="G76" t="s">
+        <v>330</v>
+      </c>
+      <c r="H76" t="s">
         <v>331</v>
-      </c>
-      <c r="H76" t="s">
-        <v>332</v>
       </c>
       <c r="J76" t="s">
         <v>34</v>
@@ -5885,13 +5855,13 @@
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="G77" t="s">
-        <v>1351</v>
+        <v>1345</v>
       </c>
       <c r="H77" t="s">
-        <v>1409</v>
+        <v>1402</v>
       </c>
       <c r="J77" t="s">
         <v>34</v>
@@ -5899,13 +5869,13 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="G78" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H78" t="s">
-        <v>1409</v>
+        <v>1402</v>
       </c>
       <c r="J78" t="s">
         <v>34</v>
@@ -5913,13 +5883,13 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="G79" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H79" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="J79" t="s">
         <v>34</v>
@@ -5927,13 +5897,13 @@
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="G80" t="s">
+        <v>234</v>
+      </c>
+      <c r="H80" t="s">
         <v>235</v>
-      </c>
-      <c r="H80" t="s">
-        <v>236</v>
       </c>
       <c r="J80" t="s">
         <v>34</v>
@@ -5941,13 +5911,13 @@
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="G81" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H81" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="J81" t="s">
         <v>34</v>
@@ -5955,13 +5925,13 @@
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="G82" t="s">
+        <v>525</v>
+      </c>
+      <c r="H82" t="s">
         <v>526</v>
-      </c>
-      <c r="H82" t="s">
-        <v>527</v>
       </c>
       <c r="J82" t="s">
         <v>34</v>
@@ -5969,13 +5939,13 @@
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="G83" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H83" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="J83" t="s">
         <v>34</v>
@@ -5983,7 +5953,7 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G84" t="s">
         <v>108</v>
@@ -5997,7 +5967,7 @@
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="G85" t="s">
         <v>111</v>
@@ -6011,13 +5981,13 @@
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="G86" t="s">
+        <v>288</v>
+      </c>
+      <c r="H86" t="s">
         <v>289</v>
-      </c>
-      <c r="H86" t="s">
-        <v>290</v>
       </c>
       <c r="J86" t="s">
         <v>34</v>
@@ -6025,13 +5995,13 @@
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="G87" t="s">
+        <v>1128</v>
+      </c>
+      <c r="H87" t="s">
         <v>1129</v>
-      </c>
-      <c r="H87" t="s">
-        <v>1130</v>
       </c>
       <c r="J87" t="s">
         <v>34</v>
@@ -6039,41 +6009,41 @@
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="G88" t="s">
+        <v>534</v>
+      </c>
+      <c r="H88" t="s">
         <v>535</v>
       </c>
-      <c r="H88" t="s">
+      <c r="J88" t="s">
         <v>536</v>
-      </c>
-      <c r="J88" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="G89" t="s">
+        <v>537</v>
+      </c>
+      <c r="H89" t="s">
         <v>538</v>
       </c>
-      <c r="H89" t="s">
-        <v>539</v>
-      </c>
       <c r="J89" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="G90" t="s">
+        <v>462</v>
+      </c>
+      <c r="H90" t="s">
         <v>463</v>
-      </c>
-      <c r="H90" t="s">
-        <v>464</v>
       </c>
       <c r="J90" t="s">
         <v>31</v>
@@ -6081,13 +6051,13 @@
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="G91" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H91" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="J91" t="s">
         <v>31</v>
@@ -6095,13 +6065,13 @@
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="G92" t="s">
+        <v>527</v>
+      </c>
+      <c r="H92" t="s">
         <v>528</v>
-      </c>
-      <c r="H92" t="s">
-        <v>529</v>
       </c>
       <c r="J92" t="s">
         <v>31</v>
@@ -6109,13 +6079,13 @@
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="G93" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H93" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="J93" t="s">
         <v>31</v>
@@ -6123,13 +6093,13 @@
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="G94" t="s">
+        <v>523</v>
+      </c>
+      <c r="H94" t="s">
         <v>524</v>
-      </c>
-      <c r="H94" t="s">
-        <v>525</v>
       </c>
       <c r="J94" t="s">
         <v>31</v>
@@ -6137,13 +6107,13 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="G95" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H95" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="J95" t="s">
         <v>31</v>
@@ -6151,13 +6121,13 @@
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="G96" t="s">
+        <v>531</v>
+      </c>
+      <c r="H96" t="s">
         <v>532</v>
-      </c>
-      <c r="H96" t="s">
-        <v>533</v>
       </c>
       <c r="J96" t="s">
         <v>31</v>
@@ -6165,13 +6135,13 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="G97" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H97" t="s">
-        <v>1412</v>
+        <v>1405</v>
       </c>
       <c r="J97" t="s">
         <v>31</v>
@@ -6179,13 +6149,13 @@
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="G98" t="s">
+        <v>529</v>
+      </c>
+      <c r="H98" t="s">
         <v>530</v>
-      </c>
-      <c r="H98" t="s">
-        <v>531</v>
       </c>
       <c r="J98" t="s">
         <v>31</v>
@@ -6193,13 +6163,13 @@
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="G99" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="H99" t="s">
-        <v>1374</v>
+        <v>1367</v>
       </c>
       <c r="J99" t="s">
         <v>31</v>
@@ -6207,13 +6177,13 @@
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="G100" t="s">
+        <v>406</v>
+      </c>
+      <c r="H100" t="s">
         <v>407</v>
-      </c>
-      <c r="H100" t="s">
-        <v>408</v>
       </c>
       <c r="J100" t="s">
         <v>31</v>
@@ -6221,13 +6191,13 @@
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="G101" t="s">
+        <v>692</v>
+      </c>
+      <c r="H101" t="s">
         <v>693</v>
-      </c>
-      <c r="H101" t="s">
-        <v>694</v>
       </c>
       <c r="J101" t="s">
         <v>31</v>
@@ -6235,13 +6205,13 @@
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="G102" t="s">
+        <v>409</v>
+      </c>
+      <c r="H102" t="s">
         <v>410</v>
-      </c>
-      <c r="H102" t="s">
-        <v>411</v>
       </c>
       <c r="J102" t="s">
         <v>31</v>
@@ -6249,13 +6219,13 @@
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="G103" t="s">
+        <v>470</v>
+      </c>
+      <c r="H103" t="s">
         <v>471</v>
-      </c>
-      <c r="H103" t="s">
-        <v>472</v>
       </c>
       <c r="J103" t="s">
         <v>31</v>
@@ -6263,7 +6233,7 @@
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="G104" t="s">
         <v>194</v>
@@ -6277,13 +6247,13 @@
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="G105" t="s">
+        <v>685</v>
+      </c>
+      <c r="H105" t="s">
         <v>686</v>
-      </c>
-      <c r="H105" t="s">
-        <v>687</v>
       </c>
       <c r="J105" t="s">
         <v>31</v>
@@ -6291,13 +6261,13 @@
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="G106" t="s">
+        <v>391</v>
+      </c>
+      <c r="H106" t="s">
         <v>392</v>
-      </c>
-      <c r="H106" t="s">
-        <v>393</v>
       </c>
       <c r="J106" t="s">
         <v>31</v>
@@ -6305,13 +6275,13 @@
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="G107" t="s">
+        <v>363</v>
+      </c>
+      <c r="H107" t="s">
         <v>364</v>
-      </c>
-      <c r="H107" t="s">
-        <v>365</v>
       </c>
       <c r="J107" t="s">
         <v>31</v>
@@ -6319,13 +6289,13 @@
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="G108" t="s">
+        <v>708</v>
+      </c>
+      <c r="H108" t="s">
         <v>709</v>
-      </c>
-      <c r="H108" t="s">
-        <v>710</v>
       </c>
       <c r="J108" t="s">
         <v>31</v>
@@ -6333,13 +6303,13 @@
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="G109" t="s">
+        <v>361</v>
+      </c>
+      <c r="H109" t="s">
         <v>362</v>
-      </c>
-      <c r="H109" t="s">
-        <v>363</v>
       </c>
       <c r="J109" t="s">
         <v>31</v>
@@ -6347,7 +6317,7 @@
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="G110" t="s">
         <v>196</v>
@@ -6361,13 +6331,13 @@
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G111" t="s">
+        <v>644</v>
+      </c>
+      <c r="H111" t="s">
         <v>645</v>
-      </c>
-      <c r="H111" t="s">
-        <v>646</v>
       </c>
       <c r="J111" t="s">
         <v>31</v>
@@ -6375,13 +6345,13 @@
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="G112" t="s">
-        <v>1352</v>
+        <v>1346</v>
       </c>
       <c r="H112" t="s">
-        <v>1375</v>
+        <v>1368</v>
       </c>
       <c r="J112" t="s">
         <v>31</v>
@@ -6389,13 +6359,13 @@
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="G113" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H113" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="J113" t="s">
         <v>31</v>
@@ -6403,13 +6373,13 @@
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="G114" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H114" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="J114" t="s">
         <v>31</v>
@@ -6417,7 +6387,7 @@
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="G115" t="s">
         <v>201</v>
@@ -6431,13 +6401,13 @@
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="G116" t="s">
+        <v>365</v>
+      </c>
+      <c r="H116" t="s">
         <v>366</v>
-      </c>
-      <c r="H116" t="s">
-        <v>367</v>
       </c>
       <c r="J116" t="s">
         <v>31</v>
@@ -6445,13 +6415,13 @@
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="G117" t="s">
+        <v>683</v>
+      </c>
+      <c r="H117" t="s">
         <v>684</v>
-      </c>
-      <c r="H117" t="s">
-        <v>685</v>
       </c>
       <c r="J117" t="s">
         <v>31</v>
@@ -6459,7 +6429,7 @@
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="G118" t="s">
         <v>193</v>
@@ -6473,13 +6443,13 @@
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="G119" t="s">
         <v>97</v>
       </c>
       <c r="H119" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="J119" t="s">
         <v>31</v>
@@ -6487,13 +6457,13 @@
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="G120" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H120" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="J120" t="s">
         <v>31</v>
@@ -6501,13 +6471,13 @@
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="G121" t="s">
+        <v>490</v>
+      </c>
+      <c r="H121" t="s">
         <v>491</v>
-      </c>
-      <c r="H121" t="s">
-        <v>492</v>
       </c>
       <c r="J121" t="s">
         <v>31</v>
@@ -6515,13 +6485,13 @@
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="G122" t="s">
+        <v>657</v>
+      </c>
+      <c r="H122" t="s">
         <v>658</v>
-      </c>
-      <c r="H122" t="s">
-        <v>659</v>
       </c>
       <c r="J122" t="s">
         <v>31</v>
@@ -6529,13 +6499,13 @@
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="G123" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H123" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="J123" t="s">
         <v>31</v>
@@ -6543,13 +6513,13 @@
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="G124" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H124" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="J124" t="s">
         <v>31</v>
@@ -6557,13 +6527,13 @@
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="G125" t="s">
+        <v>411</v>
+      </c>
+      <c r="H125" t="s">
         <v>412</v>
-      </c>
-      <c r="H125" t="s">
-        <v>413</v>
       </c>
       <c r="J125" t="s">
         <v>31</v>
@@ -6571,13 +6541,13 @@
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="G126" t="s">
+        <v>312</v>
+      </c>
+      <c r="H126" t="s">
         <v>313</v>
-      </c>
-      <c r="H126" t="s">
-        <v>314</v>
       </c>
       <c r="J126" t="s">
         <v>31</v>
@@ -6585,13 +6555,13 @@
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="G127" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H127" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="J127" t="s">
         <v>31</v>
@@ -6599,13 +6569,13 @@
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="G128" t="s">
+        <v>640</v>
+      </c>
+      <c r="H128" t="s">
         <v>641</v>
-      </c>
-      <c r="H128" t="s">
-        <v>642</v>
       </c>
       <c r="J128" t="s">
         <v>31</v>
@@ -6613,13 +6583,13 @@
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="G129" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H129" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="J129" t="s">
         <v>31</v>
@@ -6627,13 +6597,13 @@
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="G130" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H130" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J130" t="s">
         <v>31</v>
@@ -6641,13 +6611,13 @@
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="G131" t="s">
+        <v>706</v>
+      </c>
+      <c r="H131" t="s">
         <v>707</v>
-      </c>
-      <c r="H131" t="s">
-        <v>708</v>
       </c>
       <c r="J131" t="s">
         <v>31</v>
@@ -6655,13 +6625,13 @@
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="G132" t="s">
+        <v>690</v>
+      </c>
+      <c r="H132" t="s">
         <v>691</v>
-      </c>
-      <c r="H132" t="s">
-        <v>692</v>
       </c>
       <c r="J132" t="s">
         <v>31</v>
@@ -6669,13 +6639,13 @@
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="G133" t="s">
+        <v>655</v>
+      </c>
+      <c r="H133" t="s">
         <v>656</v>
-      </c>
-      <c r="H133" t="s">
-        <v>657</v>
       </c>
       <c r="J133" t="s">
         <v>31</v>
@@ -6683,13 +6653,13 @@
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="G134" t="s">
+        <v>367</v>
+      </c>
+      <c r="H134" t="s">
         <v>368</v>
-      </c>
-      <c r="H134" t="s">
-        <v>369</v>
       </c>
       <c r="J134" t="s">
         <v>31</v>
@@ -6697,13 +6667,13 @@
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="G135" t="s">
+        <v>487</v>
+      </c>
+      <c r="H135" t="s">
         <v>488</v>
-      </c>
-      <c r="H135" t="s">
-        <v>489</v>
       </c>
       <c r="J135" t="s">
         <v>31</v>
@@ -6711,13 +6681,13 @@
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="G136" t="s">
+        <v>389</v>
+      </c>
+      <c r="H136" t="s">
         <v>390</v>
-      </c>
-      <c r="H136" t="s">
-        <v>391</v>
       </c>
       <c r="J136" t="s">
         <v>31</v>
@@ -6725,13 +6695,13 @@
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="G137" t="s">
+        <v>680</v>
+      </c>
+      <c r="H137" t="s">
         <v>681</v>
-      </c>
-      <c r="H137" t="s">
-        <v>682</v>
       </c>
       <c r="J137" t="s">
         <v>31</v>
@@ -6739,13 +6709,13 @@
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="G138" t="s">
+        <v>687</v>
+      </c>
+      <c r="H138" t="s">
         <v>688</v>
-      </c>
-      <c r="H138" t="s">
-        <v>689</v>
       </c>
       <c r="J138" t="s">
         <v>31</v>
@@ -6753,7 +6723,7 @@
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="G139" t="s">
         <v>193</v>
@@ -6767,13 +6737,13 @@
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="G140" t="s">
+        <v>636</v>
+      </c>
+      <c r="H140" t="s">
         <v>637</v>
-      </c>
-      <c r="H140" t="s">
-        <v>638</v>
       </c>
       <c r="J140" t="s">
         <v>31</v>
@@ -6781,13 +6751,13 @@
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="G141" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H141" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="J141" t="s">
         <v>31</v>
@@ -6795,13 +6765,13 @@
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="G142" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H142" t="s">
-        <v>1413</v>
+        <v>1406</v>
       </c>
       <c r="J142" t="s">
         <v>31</v>
@@ -6809,13 +6779,13 @@
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="G143" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H143" t="s">
-        <v>1376</v>
+        <v>1369</v>
       </c>
       <c r="J143" t="s">
         <v>31</v>
@@ -6823,13 +6793,13 @@
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="G144" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H144" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="J144" t="s">
         <v>31</v>
@@ -6837,13 +6807,13 @@
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="G145" t="s">
+        <v>437</v>
+      </c>
+      <c r="H145" t="s">
         <v>438</v>
-      </c>
-      <c r="H145" t="s">
-        <v>439</v>
       </c>
       <c r="J145" t="s">
         <v>31</v>
@@ -6851,13 +6821,13 @@
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="G146" t="s">
+        <v>325</v>
+      </c>
+      <c r="H146" t="s">
         <v>326</v>
-      </c>
-      <c r="H146" t="s">
-        <v>327</v>
       </c>
       <c r="J146" t="s">
         <v>31</v>
@@ -6865,13 +6835,13 @@
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="G147" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H147" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="J147" t="s">
         <v>31</v>
@@ -6879,13 +6849,13 @@
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="G148" t="s">
-        <v>1353</v>
+        <v>1347</v>
       </c>
       <c r="H148" t="s">
-        <v>1377</v>
+        <v>1370</v>
       </c>
       <c r="J148" t="s">
         <v>31</v>
@@ -6893,13 +6863,13 @@
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="G149" t="s">
+        <v>384</v>
+      </c>
+      <c r="H149" t="s">
         <v>385</v>
-      </c>
-      <c r="H149" t="s">
-        <v>386</v>
       </c>
       <c r="J149" t="s">
         <v>31</v>
@@ -6907,13 +6877,13 @@
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="G150" t="s">
+        <v>323</v>
+      </c>
+      <c r="H150" t="s">
         <v>324</v>
-      </c>
-      <c r="H150" t="s">
-        <v>325</v>
       </c>
       <c r="J150" t="s">
         <v>31</v>
@@ -6921,13 +6891,13 @@
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="G151" t="s">
+        <v>376</v>
+      </c>
+      <c r="H151" t="s">
         <v>377</v>
-      </c>
-      <c r="H151" t="s">
-        <v>378</v>
       </c>
       <c r="J151" t="s">
         <v>31</v>
@@ -6935,13 +6905,13 @@
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="G152" t="s">
+        <v>382</v>
+      </c>
+      <c r="H152" t="s">
         <v>383</v>
-      </c>
-      <c r="H152" t="s">
-        <v>384</v>
       </c>
       <c r="J152" t="s">
         <v>31</v>
@@ -6949,13 +6919,13 @@
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="G153" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J153" t="s">
         <v>31</v>
@@ -6963,13 +6933,13 @@
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="G154" t="s">
+        <v>650</v>
+      </c>
+      <c r="H154" t="s">
         <v>651</v>
-      </c>
-      <c r="H154" t="s">
-        <v>652</v>
       </c>
       <c r="J154" t="s">
         <v>31</v>
@@ -6977,13 +6947,13 @@
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="G155" t="s">
+        <v>467</v>
+      </c>
+      <c r="H155" t="s">
         <v>468</v>
-      </c>
-      <c r="H155" t="s">
-        <v>469</v>
       </c>
       <c r="J155" t="s">
         <v>31</v>
@@ -6991,13 +6961,13 @@
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="G156" t="s">
+        <v>370</v>
+      </c>
+      <c r="H156" t="s">
         <v>371</v>
-      </c>
-      <c r="H156" t="s">
-        <v>372</v>
       </c>
       <c r="J156" t="s">
         <v>31</v>
@@ -7005,13 +6975,13 @@
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="G157" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H157" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="J157" t="s">
         <v>31</v>
@@ -7019,13 +6989,13 @@
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="G158" t="s">
-        <v>1354</v>
+        <v>1348</v>
       </c>
       <c r="H158" t="s">
-        <v>1378</v>
+        <v>1371</v>
       </c>
       <c r="J158" t="s">
         <v>31</v>
@@ -7033,7 +7003,7 @@
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="G159" t="s">
         <v>198</v>
@@ -7047,13 +7017,13 @@
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="G160" t="s">
+        <v>359</v>
+      </c>
+      <c r="H160" t="s">
         <v>360</v>
-      </c>
-      <c r="H160" t="s">
-        <v>361</v>
       </c>
       <c r="J160" t="s">
         <v>31</v>
@@ -7061,13 +7031,13 @@
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="G161" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H161" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="J161" t="s">
         <v>31</v>
@@ -7075,13 +7045,13 @@
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="G162" t="s">
+        <v>642</v>
+      </c>
+      <c r="H162" t="s">
         <v>643</v>
-      </c>
-      <c r="H162" t="s">
-        <v>644</v>
       </c>
       <c r="J162" t="s">
         <v>31</v>
@@ -7089,13 +7059,13 @@
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="G163" t="s">
+        <v>712</v>
+      </c>
+      <c r="H163" t="s">
         <v>713</v>
-      </c>
-      <c r="H163" t="s">
-        <v>714</v>
       </c>
       <c r="J163" t="s">
         <v>31</v>
@@ -7103,13 +7073,13 @@
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="G164" t="s">
+        <v>634</v>
+      </c>
+      <c r="H164" t="s">
         <v>635</v>
-      </c>
-      <c r="H164" t="s">
-        <v>636</v>
       </c>
       <c r="J164" t="s">
         <v>31</v>
@@ -7117,13 +7087,13 @@
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="G165" t="s">
+        <v>652</v>
+      </c>
+      <c r="H165" t="s">
         <v>653</v>
-      </c>
-      <c r="H165" t="s">
-        <v>654</v>
       </c>
       <c r="J165" t="s">
         <v>31</v>
@@ -7131,13 +7101,13 @@
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="G166" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H166" t="s">
-        <v>1414</v>
+        <v>1407</v>
       </c>
       <c r="J166" t="s">
         <v>31</v>
@@ -7145,13 +7115,13 @@
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="G167" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H167" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="J167" t="s">
         <v>31</v>
@@ -7159,13 +7129,13 @@
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="G168" t="s">
+        <v>472</v>
+      </c>
+      <c r="H168" t="s">
         <v>473</v>
-      </c>
-      <c r="H168" t="s">
-        <v>474</v>
       </c>
       <c r="J168" t="s">
         <v>31</v>
@@ -7173,13 +7143,13 @@
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="G169" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H169" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="J169" t="s">
         <v>31</v>
@@ -7187,13 +7157,13 @@
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="G170" t="s">
+        <v>648</v>
+      </c>
+      <c r="H170" t="s">
         <v>649</v>
-      </c>
-      <c r="H170" t="s">
-        <v>650</v>
       </c>
       <c r="J170" t="s">
         <v>31</v>
@@ -7201,13 +7171,13 @@
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="G171" t="s">
-        <v>1355</v>
+        <v>1349</v>
       </c>
       <c r="H171" t="s">
-        <v>1379</v>
+        <v>1372</v>
       </c>
       <c r="J171" t="s">
         <v>31</v>
@@ -7215,13 +7185,13 @@
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="G172" t="s">
+        <v>646</v>
+      </c>
+      <c r="H172" t="s">
         <v>647</v>
-      </c>
-      <c r="H172" t="s">
-        <v>648</v>
       </c>
       <c r="J172" t="s">
         <v>31</v>
@@ -7229,13 +7199,13 @@
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="G173" t="s">
+        <v>710</v>
+      </c>
+      <c r="H173" t="s">
         <v>711</v>
-      </c>
-      <c r="H173" t="s">
-        <v>712</v>
       </c>
       <c r="J173" t="s">
         <v>31</v>
@@ -7243,13 +7213,13 @@
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="G174" t="s">
+        <v>374</v>
+      </c>
+      <c r="H174" t="s">
         <v>375</v>
-      </c>
-      <c r="H174" t="s">
-        <v>376</v>
       </c>
       <c r="J174" t="s">
         <v>31</v>
@@ -7257,13 +7227,13 @@
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="G175" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H175" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="J175" t="s">
         <v>31</v>
@@ -7271,13 +7241,13 @@
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="G176" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H176" t="s">
-        <v>1380</v>
+        <v>1373</v>
       </c>
       <c r="J176" t="s">
         <v>31</v>
@@ -7285,13 +7255,13 @@
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="G177" t="s">
+        <v>378</v>
+      </c>
+      <c r="H177" t="s">
         <v>379</v>
-      </c>
-      <c r="H177" t="s">
-        <v>380</v>
       </c>
       <c r="J177" t="s">
         <v>31</v>
@@ -7299,13 +7269,13 @@
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="G178" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H178" t="s">
-        <v>1415</v>
+        <v>1408</v>
       </c>
       <c r="J178" t="s">
         <v>31</v>
@@ -7313,7 +7283,7 @@
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="G179" t="s">
         <v>29</v>
@@ -7327,13 +7297,13 @@
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="G180" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H180" t="s">
-        <v>1381</v>
+        <v>1374</v>
       </c>
       <c r="J180" t="s">
         <v>31</v>
@@ -7341,13 +7311,13 @@
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="G181" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H181" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J181" t="s">
         <v>31</v>
@@ -7355,13 +7325,13 @@
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="G182" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H182" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="J182" t="s">
         <v>31</v>
@@ -7369,13 +7339,13 @@
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G183" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H183" t="s">
-        <v>1416</v>
+        <v>1409</v>
       </c>
       <c r="J183" t="s">
         <v>31</v>
@@ -7383,13 +7353,13 @@
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="G184" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H184" t="s">
-        <v>1417</v>
+        <v>1410</v>
       </c>
       <c r="J184" t="s">
         <v>31</v>
@@ -7397,13 +7367,13 @@
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G185" t="s">
         <v>224</v>
       </c>
       <c r="H185" t="s">
-        <v>1418</v>
+        <v>1411</v>
       </c>
       <c r="J185" t="s">
         <v>31</v>
@@ -7411,13 +7381,13 @@
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="G186" t="s">
+        <v>714</v>
+      </c>
+      <c r="H186" t="s">
         <v>715</v>
-      </c>
-      <c r="H186" t="s">
-        <v>716</v>
       </c>
       <c r="J186" t="s">
         <v>31</v>
@@ -7425,13 +7395,13 @@
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A187" s="1" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="G187" t="s">
-        <v>1356</v>
+        <v>1350</v>
       </c>
       <c r="H187" t="s">
-        <v>1382</v>
+        <v>1375</v>
       </c>
       <c r="J187" t="s">
         <v>31</v>
@@ -7439,13 +7409,13 @@
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="G188" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H188" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="J188" t="s">
         <v>31</v>
@@ -7453,13 +7423,13 @@
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A189" s="1" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="G189" t="s">
-        <v>1357</v>
+        <v>1351</v>
       </c>
       <c r="H189" t="s">
-        <v>1419</v>
+        <v>1412</v>
       </c>
       <c r="J189" t="s">
         <v>31</v>
@@ -7467,13 +7437,13 @@
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="G190" t="s">
-        <v>1358</v>
+        <v>1352</v>
       </c>
       <c r="H190" t="s">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="J190" t="s">
         <v>31</v>
@@ -7481,13 +7451,13 @@
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A191" s="1" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="G191" t="s">
-        <v>635</v>
+        <v>1353</v>
       </c>
       <c r="H191" t="s">
-        <v>1420</v>
+        <v>1413</v>
       </c>
       <c r="J191" t="s">
         <v>31</v>
@@ -7495,55 +7465,55 @@
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
-        <v>1311</v>
+        <v>1218</v>
       </c>
       <c r="G192" t="s">
-        <v>1359</v>
+        <v>547</v>
       </c>
       <c r="H192" t="s">
-        <v>1421</v>
+        <v>560</v>
       </c>
       <c r="J192" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A193" s="1" t="s">
-        <v>1312</v>
+        <v>1209</v>
       </c>
       <c r="G193" t="s">
-        <v>640</v>
+        <v>565</v>
       </c>
       <c r="H193" t="s">
-        <v>1422</v>
+        <v>566</v>
       </c>
       <c r="J193" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
-        <v>1313</v>
+        <v>1228</v>
       </c>
       <c r="G194" t="s">
-        <v>1360</v>
+        <v>547</v>
       </c>
       <c r="H194" t="s">
-        <v>1423</v>
+        <v>572</v>
       </c>
       <c r="J194" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A195" s="1" t="s">
-        <v>1220</v>
+        <v>1246</v>
       </c>
       <c r="G195" t="s">
-        <v>548</v>
+        <v>188</v>
       </c>
       <c r="H195" t="s">
-        <v>561</v>
+        <v>189</v>
       </c>
       <c r="J195" t="s">
         <v>14</v>
@@ -7551,13 +7521,13 @@
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
-        <v>1211</v>
+        <v>1237</v>
       </c>
       <c r="G196" t="s">
-        <v>566</v>
+        <v>484</v>
       </c>
       <c r="H196" t="s">
-        <v>567</v>
+        <v>485</v>
       </c>
       <c r="J196" t="s">
         <v>14</v>
@@ -7565,13 +7535,13 @@
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="s">
-        <v>1230</v>
+        <v>1220</v>
       </c>
       <c r="G197" t="s">
-        <v>548</v>
+        <v>561</v>
       </c>
       <c r="H197" t="s">
-        <v>573</v>
+        <v>562</v>
       </c>
       <c r="J197" t="s">
         <v>14</v>
@@ -7579,13 +7549,13 @@
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="s">
-        <v>1248</v>
+        <v>1258</v>
       </c>
       <c r="G198" t="s">
-        <v>188</v>
+        <v>27</v>
       </c>
       <c r="H198" t="s">
-        <v>189</v>
+        <v>28</v>
       </c>
       <c r="J198" t="s">
         <v>14</v>
@@ -7593,13 +7563,13 @@
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A199" s="1" t="s">
-        <v>1239</v>
+        <v>1271</v>
       </c>
       <c r="G199" t="s">
-        <v>485</v>
+        <v>225</v>
       </c>
       <c r="H199" t="s">
-        <v>486</v>
+        <v>226</v>
       </c>
       <c r="J199" t="s">
         <v>14</v>
@@ -7607,13 +7577,13 @@
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
-        <v>1222</v>
+        <v>1233</v>
       </c>
       <c r="G200" t="s">
-        <v>562</v>
+        <v>547</v>
       </c>
       <c r="H200" t="s">
-        <v>563</v>
+        <v>578</v>
       </c>
       <c r="J200" t="s">
         <v>14</v>
@@ -7621,13 +7591,13 @@
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A201" s="1" t="s">
-        <v>1260</v>
+        <v>1268</v>
       </c>
       <c r="G201" t="s">
-        <v>27</v>
+        <v>478</v>
       </c>
       <c r="H201" t="s">
-        <v>28</v>
+        <v>479</v>
       </c>
       <c r="J201" t="s">
         <v>14</v>
@@ -7635,13 +7605,13 @@
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
-        <v>1273</v>
+        <v>1234</v>
       </c>
       <c r="G202" t="s">
-        <v>226</v>
+        <v>547</v>
       </c>
       <c r="H202" t="s">
-        <v>227</v>
+        <v>580</v>
       </c>
       <c r="J202" t="s">
         <v>14</v>
@@ -7649,13 +7619,13 @@
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A203" s="1" t="s">
-        <v>1235</v>
+        <v>1210</v>
       </c>
       <c r="G203" t="s">
-        <v>548</v>
+        <v>585</v>
       </c>
       <c r="H203" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="J203" t="s">
         <v>14</v>
@@ -7663,13 +7633,13 @@
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
-        <v>1270</v>
+        <v>1219</v>
       </c>
       <c r="G204" t="s">
-        <v>479</v>
+        <v>547</v>
       </c>
       <c r="H204" t="s">
-        <v>480</v>
+        <v>556</v>
       </c>
       <c r="J204" t="s">
         <v>14</v>
@@ -7677,13 +7647,13 @@
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A205" s="1" t="s">
-        <v>1236</v>
+        <v>1261</v>
       </c>
       <c r="G205" t="s">
-        <v>548</v>
+        <v>23</v>
       </c>
       <c r="H205" t="s">
-        <v>581</v>
+        <v>24</v>
       </c>
       <c r="J205" t="s">
         <v>14</v>
@@ -7691,13 +7661,13 @@
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
-        <v>1212</v>
+        <v>1269</v>
       </c>
       <c r="G206" t="s">
-        <v>586</v>
+        <v>335</v>
       </c>
       <c r="H206" t="s">
-        <v>587</v>
+        <v>336</v>
       </c>
       <c r="J206" t="s">
         <v>14</v>
@@ -7705,13 +7675,13 @@
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A207" s="1" t="s">
-        <v>1221</v>
+        <v>1259</v>
       </c>
       <c r="G207" t="s">
-        <v>548</v>
+        <v>482</v>
       </c>
       <c r="H207" t="s">
-        <v>557</v>
+        <v>483</v>
       </c>
       <c r="J207" t="s">
         <v>14</v>
@@ -7719,13 +7689,13 @@
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
-        <v>1263</v>
+        <v>1249</v>
       </c>
       <c r="G208" t="s">
-        <v>23</v>
+        <v>261</v>
       </c>
       <c r="H208" t="s">
-        <v>24</v>
+        <v>262</v>
       </c>
       <c r="J208" t="s">
         <v>14</v>
@@ -7733,13 +7703,13 @@
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="s">
-        <v>1271</v>
+        <v>1243</v>
       </c>
       <c r="G209" t="s">
-        <v>336</v>
+        <v>300</v>
       </c>
       <c r="H209" t="s">
-        <v>337</v>
+        <v>301</v>
       </c>
       <c r="J209" t="s">
         <v>14</v>
@@ -7747,13 +7717,13 @@
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
-        <v>1261</v>
+        <v>1248</v>
       </c>
       <c r="G210" t="s">
-        <v>483</v>
+        <v>154</v>
       </c>
       <c r="H210" t="s">
-        <v>484</v>
+        <v>155</v>
       </c>
       <c r="J210" t="s">
         <v>14</v>
@@ -7761,13 +7731,13 @@
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A211" s="1" t="s">
-        <v>1251</v>
+        <v>1216</v>
       </c>
       <c r="G211" t="s">
-        <v>262</v>
+        <v>549</v>
       </c>
       <c r="H211" t="s">
-        <v>263</v>
+        <v>550</v>
       </c>
       <c r="J211" t="s">
         <v>14</v>
@@ -7775,13 +7745,13 @@
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="s">
-        <v>1245</v>
+        <v>1238</v>
       </c>
       <c r="G212" t="s">
-        <v>301</v>
+        <v>626</v>
       </c>
       <c r="H212" t="s">
-        <v>302</v>
+        <v>627</v>
       </c>
       <c r="J212" t="s">
         <v>14</v>
@@ -7792,10 +7762,10 @@
         <v>1250</v>
       </c>
       <c r="G213" t="s">
-        <v>154</v>
+        <v>269</v>
       </c>
       <c r="H213" t="s">
-        <v>155</v>
+        <v>270</v>
       </c>
       <c r="J213" t="s">
         <v>14</v>
@@ -7803,13 +7773,13 @@
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
-        <v>1218</v>
+        <v>1239</v>
       </c>
       <c r="G214" t="s">
-        <v>550</v>
+        <v>628</v>
       </c>
       <c r="H214" t="s">
-        <v>551</v>
+        <v>629</v>
       </c>
       <c r="J214" t="s">
         <v>14</v>
@@ -7817,13 +7787,13 @@
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A215" s="1" t="s">
-        <v>1240</v>
+        <v>1247</v>
       </c>
       <c r="G215" t="s">
-        <v>627</v>
+        <v>186</v>
       </c>
       <c r="H215" t="s">
-        <v>628</v>
+        <v>187</v>
       </c>
       <c r="J215" t="s">
         <v>14</v>
@@ -7831,13 +7801,13 @@
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="G216" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="H216" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="J216" t="s">
         <v>14</v>
@@ -7845,13 +7815,13 @@
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A217" s="1" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="G217" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="H217" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="J217" t="s">
         <v>14</v>
@@ -7859,13 +7829,13 @@
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
-        <v>1249</v>
+        <v>1215</v>
       </c>
       <c r="G218" t="s">
-        <v>186</v>
+        <v>746</v>
       </c>
       <c r="H218" t="s">
-        <v>187</v>
+        <v>747</v>
       </c>
       <c r="J218" t="s">
         <v>14</v>
@@ -7873,13 +7843,13 @@
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A219" s="1" t="s">
-        <v>1275</v>
+        <v>1241</v>
       </c>
       <c r="G219" t="s">
-        <v>335</v>
+        <v>185</v>
       </c>
       <c r="H219" t="s">
-        <v>281</v>
+        <v>192</v>
       </c>
       <c r="J219" t="s">
         <v>14</v>
@@ -7887,13 +7857,13 @@
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
-        <v>1244</v>
+        <v>1224</v>
       </c>
       <c r="G220" t="s">
-        <v>624</v>
+        <v>547</v>
       </c>
       <c r="H220" t="s">
-        <v>625</v>
+        <v>571</v>
       </c>
       <c r="J220" t="s">
         <v>14</v>
@@ -7901,13 +7871,13 @@
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A221" s="1" t="s">
-        <v>1217</v>
+        <v>1223</v>
       </c>
       <c r="G221" t="s">
-        <v>747</v>
+        <v>569</v>
       </c>
       <c r="H221" t="s">
-        <v>748</v>
+        <v>570</v>
       </c>
       <c r="J221" t="s">
         <v>14</v>
@@ -7915,13 +7885,13 @@
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="s">
-        <v>1243</v>
+        <v>1236</v>
       </c>
       <c r="G222" t="s">
-        <v>185</v>
+        <v>474</v>
       </c>
       <c r="H222" t="s">
-        <v>192</v>
+        <v>477</v>
       </c>
       <c r="J222" t="s">
         <v>14</v>
@@ -7929,13 +7899,13 @@
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A223" s="1" t="s">
-        <v>1226</v>
+        <v>1222</v>
       </c>
       <c r="G223" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H223" t="s">
-        <v>572</v>
+        <v>592</v>
       </c>
       <c r="J223" t="s">
         <v>14</v>
@@ -7943,13 +7913,13 @@
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="s">
-        <v>1225</v>
+        <v>1244</v>
       </c>
       <c r="G224" t="s">
-        <v>570</v>
+        <v>153</v>
       </c>
       <c r="H224" t="s">
-        <v>571</v>
+        <v>156</v>
       </c>
       <c r="J224" t="s">
         <v>14</v>
@@ -7957,13 +7927,13 @@
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A225" s="1" t="s">
-        <v>1238</v>
+        <v>1221</v>
       </c>
       <c r="G225" t="s">
-        <v>475</v>
+        <v>547</v>
       </c>
       <c r="H225" t="s">
-        <v>478</v>
+        <v>567</v>
       </c>
       <c r="J225" t="s">
         <v>14</v>
@@ -7971,13 +7941,13 @@
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
-        <v>1224</v>
+        <v>1287</v>
       </c>
       <c r="G226" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H226" t="s">
-        <v>593</v>
+        <v>1414</v>
       </c>
       <c r="J226" t="s">
         <v>14</v>
@@ -7985,13 +7955,13 @@
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="s">
-        <v>1246</v>
+        <v>1276</v>
       </c>
       <c r="G227" t="s">
-        <v>153</v>
+        <v>1290</v>
       </c>
       <c r="H227" t="s">
-        <v>156</v>
+        <v>1415</v>
       </c>
       <c r="J227" t="s">
         <v>14</v>
@@ -7999,13 +7969,13 @@
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
-        <v>1223</v>
+        <v>1240</v>
       </c>
       <c r="G228" t="s">
-        <v>548</v>
+        <v>622</v>
       </c>
       <c r="H228" t="s">
-        <v>568</v>
+        <v>625</v>
       </c>
       <c r="J228" t="s">
         <v>14</v>
@@ -8013,13 +7983,13 @@
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A229" s="1" t="s">
-        <v>1289</v>
+        <v>1260</v>
       </c>
       <c r="G229" t="s">
-        <v>548</v>
+        <v>12</v>
       </c>
       <c r="H229" t="s">
-        <v>1424</v>
+        <v>13</v>
       </c>
       <c r="J229" t="s">
         <v>14</v>
@@ -8027,13 +7997,13 @@
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="s">
-        <v>1278</v>
+        <v>1245</v>
       </c>
       <c r="G230" t="s">
-        <v>1292</v>
+        <v>302</v>
       </c>
       <c r="H230" t="s">
-        <v>1425</v>
+        <v>303</v>
       </c>
       <c r="J230" t="s">
         <v>14</v>
@@ -8041,13 +8011,13 @@
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A231" s="1" t="s">
-        <v>1242</v>
+        <v>1214</v>
       </c>
       <c r="G231" t="s">
-        <v>623</v>
+        <v>573</v>
       </c>
       <c r="H231" t="s">
-        <v>626</v>
+        <v>574</v>
       </c>
       <c r="J231" t="s">
         <v>14</v>
@@ -8055,13 +8025,13 @@
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="s">
-        <v>1262</v>
+        <v>1309</v>
       </c>
       <c r="G232" t="s">
-        <v>12</v>
+        <v>547</v>
       </c>
       <c r="H232" t="s">
-        <v>13</v>
+        <v>1377</v>
       </c>
       <c r="J232" t="s">
         <v>14</v>
@@ -8069,13 +8039,13 @@
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A233" s="1" t="s">
-        <v>1247</v>
+        <v>1254</v>
       </c>
       <c r="G233" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H233" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="J233" t="s">
         <v>14</v>
@@ -8083,13 +8053,13 @@
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="s">
-        <v>1216</v>
+        <v>1262</v>
       </c>
       <c r="G234" t="s">
-        <v>574</v>
+        <v>17</v>
       </c>
       <c r="H234" t="s">
-        <v>575</v>
+        <v>18</v>
       </c>
       <c r="J234" t="s">
         <v>14</v>
@@ -8097,13 +8067,13 @@
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A235" s="1" t="s">
-        <v>1314</v>
+        <v>1253</v>
       </c>
       <c r="G235" t="s">
-        <v>548</v>
+        <v>263</v>
       </c>
       <c r="H235" t="s">
-        <v>1384</v>
+        <v>264</v>
       </c>
       <c r="J235" t="s">
         <v>14</v>
@@ -8111,13 +8081,13 @@
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="s">
-        <v>1256</v>
+        <v>1270</v>
       </c>
       <c r="G236" t="s">
-        <v>305</v>
+        <v>41</v>
       </c>
       <c r="H236" t="s">
-        <v>308</v>
+        <v>42</v>
       </c>
       <c r="J236" t="s">
         <v>14</v>
@@ -8125,13 +8095,13 @@
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A237" s="1" t="s">
-        <v>1264</v>
+        <v>1212</v>
       </c>
       <c r="G237" t="s">
-        <v>17</v>
+        <v>563</v>
       </c>
       <c r="H237" t="s">
-        <v>18</v>
+        <v>564</v>
       </c>
       <c r="J237" t="s">
         <v>14</v>
@@ -8139,13 +8109,13 @@
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="s">
-        <v>1255</v>
+        <v>1274</v>
       </c>
       <c r="G238" t="s">
-        <v>264</v>
+        <v>40</v>
       </c>
       <c r="H238" t="s">
-        <v>265</v>
+        <v>43</v>
       </c>
       <c r="J238" t="s">
         <v>14</v>
@@ -8153,13 +8123,13 @@
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A239" s="1" t="s">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="G239" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="H239" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="J239" t="s">
         <v>14</v>
@@ -8167,13 +8137,13 @@
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A240" s="1" t="s">
-        <v>1214</v>
+        <v>1217</v>
       </c>
       <c r="G240" t="s">
-        <v>564</v>
+        <v>748</v>
       </c>
       <c r="H240" t="s">
-        <v>565</v>
+        <v>749</v>
       </c>
       <c r="J240" t="s">
         <v>14</v>
@@ -8181,13 +8151,13 @@
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A241" s="1" t="s">
-        <v>1276</v>
+        <v>1252</v>
       </c>
       <c r="G241" t="s">
-        <v>40</v>
+        <v>265</v>
       </c>
       <c r="H241" t="s">
-        <v>43</v>
+        <v>266</v>
       </c>
       <c r="J241" t="s">
         <v>14</v>
@@ -8195,13 +8165,13 @@
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="s">
-        <v>1268</v>
+        <v>1211</v>
       </c>
       <c r="G242" t="s">
-        <v>25</v>
+        <v>547</v>
       </c>
       <c r="H242" t="s">
-        <v>26</v>
+        <v>587</v>
       </c>
       <c r="J242" t="s">
         <v>14</v>
@@ -8209,13 +8179,13 @@
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A243" s="1" t="s">
-        <v>1219</v>
+        <v>1251</v>
       </c>
       <c r="G243" t="s">
-        <v>749</v>
+        <v>267</v>
       </c>
       <c r="H243" t="s">
-        <v>750</v>
+        <v>268</v>
       </c>
       <c r="J243" t="s">
         <v>14</v>
@@ -8223,13 +8193,13 @@
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="s">
-        <v>1254</v>
+        <v>1282</v>
       </c>
       <c r="G244" t="s">
-        <v>266</v>
+        <v>764</v>
       </c>
       <c r="H244" t="s">
-        <v>267</v>
+        <v>1416</v>
       </c>
       <c r="J244" t="s">
         <v>14</v>
@@ -8237,13 +8207,13 @@
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A245" s="1" t="s">
-        <v>1213</v>
+        <v>1265</v>
       </c>
       <c r="G245" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="H245" t="s">
-        <v>588</v>
+        <v>20</v>
       </c>
       <c r="J245" t="s">
         <v>14</v>
@@ -8251,13 +8221,13 @@
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="s">
-        <v>1253</v>
+        <v>1229</v>
       </c>
       <c r="G246" t="s">
-        <v>268</v>
+        <v>547</v>
       </c>
       <c r="H246" t="s">
-        <v>269</v>
+        <v>589</v>
       </c>
       <c r="J246" t="s">
         <v>14</v>
@@ -8265,13 +8235,13 @@
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A247" s="1" t="s">
-        <v>1284</v>
+        <v>1264</v>
       </c>
       <c r="G247" t="s">
-        <v>765</v>
+        <v>15</v>
       </c>
       <c r="H247" t="s">
-        <v>1426</v>
+        <v>16</v>
       </c>
       <c r="J247" t="s">
         <v>14</v>
@@ -8279,13 +8249,13 @@
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
-        <v>1267</v>
+        <v>1310</v>
       </c>
       <c r="G248" t="s">
-        <v>19</v>
+        <v>764</v>
       </c>
       <c r="H248" t="s">
-        <v>20</v>
+        <v>1378</v>
       </c>
       <c r="J248" t="s">
         <v>14</v>
@@ -8293,13 +8263,13 @@
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
       <c r="G249" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H249" t="s">
-        <v>590</v>
+        <v>577</v>
       </c>
       <c r="J249" t="s">
         <v>14</v>
@@ -8307,13 +8277,13 @@
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
-        <v>1266</v>
+        <v>1235</v>
       </c>
       <c r="G250" t="s">
-        <v>15</v>
+        <v>547</v>
       </c>
       <c r="H250" t="s">
-        <v>16</v>
+        <v>581</v>
       </c>
       <c r="J250" t="s">
         <v>14</v>
@@ -8321,13 +8291,13 @@
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A251" s="1" t="s">
-        <v>1315</v>
+        <v>1263</v>
       </c>
       <c r="G251" t="s">
-        <v>765</v>
+        <v>480</v>
       </c>
       <c r="H251" t="s">
-        <v>1385</v>
+        <v>481</v>
       </c>
       <c r="J251" t="s">
         <v>14</v>
@@ -8335,13 +8305,13 @@
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
-        <v>1227</v>
+        <v>1272</v>
       </c>
       <c r="G252" t="s">
-        <v>548</v>
+        <v>225</v>
       </c>
       <c r="H252" t="s">
-        <v>578</v>
+        <v>227</v>
       </c>
       <c r="J252" t="s">
         <v>14</v>
@@ -8349,13 +8319,13 @@
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A253" s="1" t="s">
-        <v>1237</v>
+        <v>1255</v>
       </c>
       <c r="G253" t="s">
-        <v>548</v>
+        <v>632</v>
       </c>
       <c r="H253" t="s">
-        <v>582</v>
+        <v>633</v>
       </c>
       <c r="J253" t="s">
         <v>14</v>
@@ -8363,13 +8333,13 @@
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
-        <v>1265</v>
+        <v>1278</v>
       </c>
       <c r="G254" t="s">
-        <v>481</v>
+        <v>547</v>
       </c>
       <c r="H254" t="s">
-        <v>482</v>
+        <v>1417</v>
       </c>
       <c r="J254" t="s">
         <v>14</v>
@@ -8377,13 +8347,13 @@
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A255" s="1" t="s">
-        <v>1274</v>
+        <v>1227</v>
       </c>
       <c r="G255" t="s">
-        <v>226</v>
+        <v>582</v>
       </c>
       <c r="H255" t="s">
-        <v>228</v>
+        <v>583</v>
       </c>
       <c r="J255" t="s">
         <v>14</v>
@@ -8391,13 +8361,13 @@
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
-        <v>1257</v>
+        <v>1226</v>
       </c>
       <c r="G256" t="s">
-        <v>633</v>
+        <v>547</v>
       </c>
       <c r="H256" t="s">
-        <v>634</v>
+        <v>579</v>
       </c>
       <c r="J256" t="s">
         <v>14</v>
@@ -8405,13 +8375,13 @@
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A257" s="1" t="s">
-        <v>1280</v>
+        <v>1285</v>
       </c>
       <c r="G257" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H257" t="s">
-        <v>1427</v>
+        <v>1418</v>
       </c>
       <c r="J257" t="s">
         <v>14</v>
@@ -8419,13 +8389,13 @@
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="s">
-        <v>1229</v>
+        <v>1256</v>
       </c>
       <c r="G258" t="s">
-        <v>583</v>
+        <v>475</v>
       </c>
       <c r="H258" t="s">
-        <v>584</v>
+        <v>476</v>
       </c>
       <c r="J258" t="s">
         <v>14</v>
@@ -8433,13 +8403,13 @@
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A259" s="1" t="s">
-        <v>1228</v>
+        <v>1267</v>
       </c>
       <c r="G259" t="s">
-        <v>548</v>
+        <v>21</v>
       </c>
       <c r="H259" t="s">
-        <v>580</v>
+        <v>22</v>
       </c>
       <c r="J259" t="s">
         <v>14</v>
@@ -8447,13 +8417,13 @@
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="s">
-        <v>1287</v>
+        <v>1231</v>
       </c>
       <c r="G260" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H260" t="s">
-        <v>1428</v>
+        <v>568</v>
       </c>
       <c r="J260" t="s">
         <v>14</v>
@@ -8461,13 +8431,13 @@
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A261" s="1" t="s">
-        <v>1258</v>
+        <v>880</v>
       </c>
       <c r="G261" t="s">
-        <v>476</v>
+        <v>252</v>
       </c>
       <c r="H261" t="s">
-        <v>477</v>
+        <v>253</v>
       </c>
       <c r="J261" t="s">
         <v>14</v>
@@ -8475,13 +8445,13 @@
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="s">
-        <v>1269</v>
+        <v>1280</v>
       </c>
       <c r="G262" t="s">
-        <v>21</v>
+        <v>334</v>
       </c>
       <c r="H262" t="s">
-        <v>22</v>
+        <v>1419</v>
       </c>
       <c r="J262" t="s">
         <v>14</v>
@@ -8489,13 +8459,13 @@
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A263" s="1" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G263" t="s">
-        <v>548</v>
+        <v>630</v>
       </c>
       <c r="H263" t="s">
-        <v>569</v>
+        <v>631</v>
       </c>
       <c r="J263" t="s">
         <v>14</v>
@@ -8503,13 +8473,13 @@
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A264" s="1" t="s">
-        <v>881</v>
+        <v>1257</v>
       </c>
       <c r="G264" t="s">
-        <v>253</v>
+        <v>190</v>
       </c>
       <c r="H264" t="s">
-        <v>254</v>
+        <v>191</v>
       </c>
       <c r="J264" t="s">
         <v>14</v>
@@ -8517,13 +8487,13 @@
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A265" s="1" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="G265" t="s">
-        <v>335</v>
+        <v>768</v>
       </c>
       <c r="H265" t="s">
-        <v>1429</v>
+        <v>1420</v>
       </c>
       <c r="J265" t="s">
         <v>14</v>
@@ -8531,13 +8501,13 @@
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A266" s="1" t="s">
-        <v>1234</v>
+        <v>1289</v>
       </c>
       <c r="G266" t="s">
-        <v>631</v>
+        <v>1292</v>
       </c>
       <c r="H266" t="s">
-        <v>632</v>
+        <v>1421</v>
       </c>
       <c r="J266" t="s">
         <v>14</v>
@@ -8545,13 +8515,13 @@
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A267" s="1" t="s">
-        <v>1259</v>
+        <v>1284</v>
       </c>
       <c r="G267" t="s">
-        <v>190</v>
+        <v>1354</v>
       </c>
       <c r="H267" t="s">
-        <v>191</v>
+        <v>1422</v>
       </c>
       <c r="J267" t="s">
         <v>14</v>
@@ -8559,13 +8529,13 @@
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A268" s="1" t="s">
-        <v>1285</v>
+        <v>1213</v>
       </c>
       <c r="G268" t="s">
-        <v>769</v>
+        <v>547</v>
       </c>
       <c r="H268" t="s">
-        <v>1430</v>
+        <v>555</v>
       </c>
       <c r="J268" t="s">
         <v>14</v>
@@ -8573,13 +8543,13 @@
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A269" s="1" t="s">
+        <v>1288</v>
+      </c>
+      <c r="G269" t="s">
         <v>1291</v>
       </c>
-      <c r="G269" t="s">
-        <v>1294</v>
-      </c>
       <c r="H269" t="s">
-        <v>1431</v>
+        <v>1423</v>
       </c>
       <c r="J269" t="s">
         <v>14</v>
@@ -8587,13 +8557,13 @@
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A270" s="1" t="s">
-        <v>1286</v>
+        <v>1275</v>
       </c>
       <c r="G270" t="s">
-        <v>1361</v>
+        <v>1355</v>
       </c>
       <c r="H270" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="J270" t="s">
         <v>14</v>
@@ -8601,13 +8571,13 @@
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A271" s="1" t="s">
-        <v>1215</v>
+        <v>1311</v>
       </c>
       <c r="G271" t="s">
-        <v>548</v>
+        <v>575</v>
       </c>
       <c r="H271" t="s">
-        <v>556</v>
+        <v>1379</v>
       </c>
       <c r="J271" t="s">
         <v>14</v>
@@ -8615,13 +8585,13 @@
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A272" s="1" t="s">
-        <v>1290</v>
+        <v>1286</v>
       </c>
       <c r="G272" t="s">
-        <v>1293</v>
+        <v>547</v>
       </c>
       <c r="H272" t="s">
-        <v>1433</v>
+        <v>1425</v>
       </c>
       <c r="J272" t="s">
         <v>14</v>
@@ -8629,13 +8599,13 @@
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A273" s="1" t="s">
-        <v>1277</v>
+        <v>1312</v>
       </c>
       <c r="G273" t="s">
-        <v>1362</v>
+        <v>1293</v>
       </c>
       <c r="H273" t="s">
-        <v>1434</v>
+        <v>1380</v>
       </c>
       <c r="J273" t="s">
         <v>14</v>
@@ -8643,13 +8613,13 @@
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A274" s="1" t="s">
-        <v>1316</v>
+        <v>1277</v>
       </c>
       <c r="G274" t="s">
-        <v>576</v>
+        <v>547</v>
       </c>
       <c r="H274" t="s">
-        <v>1386</v>
+        <v>1426</v>
       </c>
       <c r="J274" t="s">
         <v>14</v>
@@ -8657,13 +8627,13 @@
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A275" s="1" t="s">
-        <v>1288</v>
+        <v>1281</v>
       </c>
       <c r="G275" t="s">
-        <v>548</v>
+        <v>763</v>
       </c>
       <c r="H275" t="s">
-        <v>1435</v>
+        <v>1427</v>
       </c>
       <c r="J275" t="s">
         <v>14</v>
@@ -8671,13 +8641,13 @@
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A276" s="1" t="s">
-        <v>1317</v>
+        <v>1279</v>
       </c>
       <c r="G276" t="s">
-        <v>1295</v>
+        <v>478</v>
       </c>
       <c r="H276" t="s">
-        <v>1387</v>
+        <v>1422</v>
       </c>
       <c r="J276" t="s">
         <v>14</v>
@@ -8685,13 +8655,13 @@
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A277" s="1" t="s">
-        <v>1279</v>
+        <v>1230</v>
       </c>
       <c r="G277" t="s">
+        <v>547</v>
+      </c>
+      <c r="H277" t="s">
         <v>548</v>
-      </c>
-      <c r="H277" t="s">
-        <v>1436</v>
       </c>
       <c r="J277" t="s">
         <v>14</v>
@@ -8699,55 +8669,55 @@
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A278" s="1" t="s">
-        <v>1283</v>
+        <v>1154</v>
       </c>
       <c r="G278" t="s">
-        <v>764</v>
+        <v>126</v>
       </c>
       <c r="H278" t="s">
-        <v>1437</v>
+        <v>148</v>
       </c>
       <c r="J278" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A279" s="1" t="s">
-        <v>1281</v>
+        <v>1162</v>
       </c>
       <c r="G279" t="s">
-        <v>479</v>
+        <v>126</v>
       </c>
       <c r="H279" t="s">
-        <v>1432</v>
+        <v>151</v>
       </c>
       <c r="J279" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A280" s="1" t="s">
-        <v>1232</v>
+        <v>1149</v>
       </c>
       <c r="G280" t="s">
-        <v>548</v>
+        <v>138</v>
       </c>
       <c r="H280" t="s">
-        <v>549</v>
+        <v>139</v>
       </c>
       <c r="J280" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A281" s="1" t="s">
-        <v>1155</v>
+        <v>1148</v>
       </c>
       <c r="G281" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="H281" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J281" t="s">
         <v>3</v>
@@ -8755,13 +8725,13 @@
     </row>
     <row r="282" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A282" s="1" t="s">
-        <v>1163</v>
+        <v>1188</v>
       </c>
       <c r="G282" t="s">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="H282" t="s">
-        <v>151</v>
+        <v>4</v>
       </c>
       <c r="J282" t="s">
         <v>3</v>
@@ -8769,13 +8739,13 @@
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A283" s="1" t="s">
-        <v>1150</v>
+        <v>1170</v>
       </c>
       <c r="G283" t="s">
-        <v>138</v>
+        <v>273</v>
       </c>
       <c r="H283" t="s">
-        <v>139</v>
+        <v>275</v>
       </c>
       <c r="J283" t="s">
         <v>3</v>
@@ -8783,13 +8753,13 @@
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A284" s="1" t="s">
-        <v>1149</v>
+        <v>1155</v>
       </c>
       <c r="G284" t="s">
-        <v>146</v>
+        <v>70</v>
       </c>
       <c r="H284" t="s">
-        <v>147</v>
+        <v>71</v>
       </c>
       <c r="J284" t="s">
         <v>3</v>
@@ -8797,13 +8767,13 @@
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A285" s="1" t="s">
-        <v>1190</v>
+        <v>1133</v>
       </c>
       <c r="G285" t="s">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="H285" t="s">
-        <v>4</v>
+        <v>1200</v>
       </c>
       <c r="J285" t="s">
         <v>3</v>
@@ -8811,13 +8781,13 @@
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="s">
-        <v>1171</v>
+        <v>1185</v>
       </c>
       <c r="G286" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
       <c r="H286" t="s">
-        <v>276</v>
+        <v>221</v>
       </c>
       <c r="J286" t="s">
         <v>3</v>
@@ -8825,27 +8795,27 @@
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A287" s="1" t="s">
-        <v>1156</v>
+        <v>1189</v>
       </c>
       <c r="G287" t="s">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="H287" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="J287" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A288" s="1" t="s">
-        <v>1134</v>
+        <v>975</v>
       </c>
       <c r="G288" t="s">
-        <v>126</v>
+        <v>505</v>
       </c>
       <c r="H288" t="s">
-        <v>1202</v>
+        <v>506</v>
       </c>
       <c r="J288" t="s">
         <v>3</v>
@@ -8853,27 +8823,27 @@
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A289" s="1" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="G289" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="H289" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="J289" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="s">
-        <v>1191</v>
+        <v>1159</v>
       </c>
       <c r="G290" t="s">
-        <v>44</v>
+        <v>136</v>
       </c>
       <c r="H290" t="s">
-        <v>48</v>
+        <v>137</v>
       </c>
       <c r="J290" t="s">
         <v>3</v>
@@ -8881,13 +8851,13 @@
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A291" s="1" t="s">
-        <v>976</v>
+        <v>1134</v>
       </c>
       <c r="G291" t="s">
-        <v>506</v>
+        <v>91</v>
       </c>
       <c r="H291" t="s">
-        <v>507</v>
+        <v>92</v>
       </c>
       <c r="J291" t="s">
         <v>3</v>
@@ -8895,13 +8865,13 @@
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A292" s="1" t="s">
-        <v>1185</v>
+        <v>1158</v>
       </c>
       <c r="G292" t="s">
-        <v>216</v>
+        <v>78</v>
       </c>
       <c r="H292" t="s">
-        <v>217</v>
+        <v>79</v>
       </c>
       <c r="J292" t="s">
         <v>3</v>
@@ -8909,13 +8879,13 @@
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A293" s="1" t="s">
-        <v>1160</v>
+        <v>1132</v>
       </c>
       <c r="G293" t="s">
-        <v>136</v>
+        <v>87</v>
       </c>
       <c r="H293" t="s">
-        <v>137</v>
+        <v>88</v>
       </c>
       <c r="J293" t="s">
         <v>3</v>
@@ -8923,13 +8893,13 @@
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="s">
-        <v>1135</v>
+        <v>1165</v>
       </c>
       <c r="G294" t="s">
-        <v>91</v>
+        <v>603</v>
       </c>
       <c r="H294" t="s">
-        <v>92</v>
+        <v>608</v>
       </c>
       <c r="J294" t="s">
         <v>3</v>
@@ -8937,13 +8907,13 @@
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A295" s="1" t="s">
-        <v>1159</v>
+        <v>836</v>
       </c>
       <c r="G295" t="s">
-        <v>78</v>
+        <v>310</v>
       </c>
       <c r="H295" t="s">
-        <v>79</v>
+        <v>311</v>
       </c>
       <c r="J295" t="s">
         <v>3</v>
@@ -8951,13 +8921,13 @@
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="s">
-        <v>1133</v>
+        <v>1171</v>
       </c>
       <c r="G296" t="s">
-        <v>87</v>
+        <v>273</v>
       </c>
       <c r="H296" t="s">
-        <v>88</v>
+        <v>276</v>
       </c>
       <c r="J296" t="s">
         <v>3</v>
@@ -8965,13 +8935,13 @@
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A297" s="1" t="s">
-        <v>1166</v>
+        <v>1139</v>
       </c>
       <c r="G297" t="s">
-        <v>604</v>
+        <v>206</v>
       </c>
       <c r="H297" t="s">
-        <v>609</v>
+        <v>209</v>
       </c>
       <c r="J297" t="s">
         <v>3</v>
@@ -8979,13 +8949,13 @@
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A298" s="1" t="s">
-        <v>837</v>
+        <v>1135</v>
       </c>
       <c r="G298" t="s">
-        <v>311</v>
+        <v>76</v>
       </c>
       <c r="H298" t="s">
-        <v>312</v>
+        <v>77</v>
       </c>
       <c r="J298" t="s">
         <v>3</v>
@@ -8996,10 +8966,10 @@
         <v>1172</v>
       </c>
       <c r="G299" t="s">
+        <v>273</v>
+      </c>
+      <c r="H299" t="s">
         <v>274</v>
-      </c>
-      <c r="H299" t="s">
-        <v>277</v>
       </c>
       <c r="J299" t="s">
         <v>3</v>
@@ -9007,13 +8977,13 @@
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="s">
-        <v>1140</v>
+        <v>1156</v>
       </c>
       <c r="G300" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H300" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J300" t="s">
         <v>3</v>
@@ -9021,13 +8991,13 @@
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A301" s="1" t="s">
-        <v>1136</v>
+        <v>1157</v>
       </c>
       <c r="G301" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="H301" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="J301" t="s">
         <v>3</v>
@@ -9035,13 +9005,13 @@
     </row>
     <row r="302" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A302" s="1" t="s">
-        <v>1173</v>
+        <v>1141</v>
       </c>
       <c r="G302" t="s">
-        <v>274</v>
+        <v>206</v>
       </c>
       <c r="H302" t="s">
-        <v>275</v>
+        <v>215</v>
       </c>
       <c r="J302" t="s">
         <v>3</v>
@@ -9049,13 +9019,13 @@
     </row>
     <row r="303" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A303" s="1" t="s">
-        <v>1157</v>
+        <v>1150</v>
       </c>
       <c r="G303" t="s">
-        <v>207</v>
+        <v>95</v>
       </c>
       <c r="H303" t="s">
-        <v>208</v>
+        <v>96</v>
       </c>
       <c r="J303" t="s">
         <v>3</v>
@@ -9063,13 +9033,13 @@
     </row>
     <row r="304" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A304" s="1" t="s">
-        <v>1158</v>
+        <v>1177</v>
       </c>
       <c r="G304" t="s">
-        <v>93</v>
+        <v>273</v>
       </c>
       <c r="H304" t="s">
-        <v>94</v>
+        <v>277</v>
       </c>
       <c r="J304" t="s">
         <v>3</v>
@@ -9077,13 +9047,13 @@
     </row>
     <row r="305" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A305" s="1" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="G305" t="s">
-        <v>206</v>
+        <v>134</v>
       </c>
       <c r="H305" t="s">
-        <v>215</v>
+        <v>135</v>
       </c>
       <c r="J305" t="s">
         <v>3</v>
@@ -9091,13 +9061,13 @@
     </row>
     <row r="306" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A306" s="1" t="s">
-        <v>1151</v>
+        <v>1313</v>
       </c>
       <c r="G306" t="s">
-        <v>95</v>
+        <v>787</v>
       </c>
       <c r="H306" t="s">
-        <v>96</v>
+        <v>1381</v>
       </c>
       <c r="J306" t="s">
         <v>3</v>
@@ -9105,10 +9075,10 @@
     </row>
     <row r="307" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A307" s="1" t="s">
-        <v>1178</v>
+        <v>1174</v>
       </c>
       <c r="G307" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H307" t="s">
         <v>278</v>
@@ -9119,27 +9089,27 @@
     </row>
     <row r="308" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A308" s="1" t="s">
-        <v>1141</v>
+        <v>1186</v>
       </c>
       <c r="G308" t="s">
-        <v>134</v>
+        <v>218</v>
       </c>
       <c r="H308" t="s">
-        <v>135</v>
+        <v>219</v>
       </c>
       <c r="J308" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="309" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A309" s="1" t="s">
-        <v>1318</v>
+        <v>1314</v>
       </c>
       <c r="G309" t="s">
         <v>788</v>
       </c>
       <c r="H309" t="s">
-        <v>1388</v>
+        <v>789</v>
       </c>
       <c r="J309" t="s">
         <v>3</v>
@@ -9147,13 +9117,13 @@
     </row>
     <row r="310" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A310" s="1" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="G310" t="s">
-        <v>274</v>
+        <v>610</v>
       </c>
       <c r="H310" t="s">
-        <v>279</v>
+        <v>611</v>
       </c>
       <c r="J310" t="s">
         <v>3</v>
@@ -9161,13 +9131,13 @@
     </row>
     <row r="311" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A311" s="1" t="s">
-        <v>1187</v>
+        <v>1191</v>
       </c>
       <c r="G311" t="s">
-        <v>218</v>
+        <v>8</v>
       </c>
       <c r="H311" t="s">
-        <v>219</v>
+        <v>9</v>
       </c>
       <c r="J311" t="s">
         <v>3</v>
@@ -9175,13 +9145,13 @@
     </row>
     <row r="312" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A312" s="1" t="s">
-        <v>1319</v>
+        <v>1164</v>
       </c>
       <c r="G312" t="s">
-        <v>789</v>
+        <v>603</v>
       </c>
       <c r="H312" t="s">
-        <v>790</v>
+        <v>609</v>
       </c>
       <c r="J312" t="s">
         <v>3</v>
@@ -9189,13 +9159,13 @@
     </row>
     <row r="313" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A313" s="1" t="s">
-        <v>1174</v>
+        <v>1160</v>
       </c>
       <c r="G313" t="s">
-        <v>611</v>
+        <v>82</v>
       </c>
       <c r="H313" t="s">
-        <v>612</v>
+        <v>83</v>
       </c>
       <c r="J313" t="s">
         <v>3</v>
@@ -9203,27 +9173,27 @@
     </row>
     <row r="314" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A314" s="1" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="G314" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H314" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J314" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="315" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A315" s="1" t="s">
-        <v>1165</v>
+        <v>1143</v>
       </c>
       <c r="G315" t="s">
-        <v>604</v>
+        <v>337</v>
       </c>
       <c r="H315" t="s">
-        <v>610</v>
+        <v>342</v>
       </c>
       <c r="J315" t="s">
         <v>3</v>
@@ -9231,41 +9201,41 @@
     </row>
     <row r="316" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A316" s="1" t="s">
-        <v>1161</v>
+        <v>1190</v>
       </c>
       <c r="G316" t="s">
-        <v>82</v>
+        <v>5</v>
       </c>
       <c r="H316" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="J316" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="317" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A317" s="1" t="s">
-        <v>1194</v>
+      <c r="A317">
+        <v>1480</v>
       </c>
       <c r="G317" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="H317" t="s">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="J317" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="318" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A318" s="1" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="G318" t="s">
-        <v>338</v>
+        <v>206</v>
       </c>
       <c r="H318" t="s">
-        <v>343</v>
+        <v>210</v>
       </c>
       <c r="J318" t="s">
         <v>3</v>
@@ -9273,27 +9243,27 @@
     </row>
     <row r="319" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A319" s="1" t="s">
-        <v>1192</v>
+        <v>1167</v>
       </c>
       <c r="G319" t="s">
-        <v>5</v>
+        <v>291</v>
       </c>
       <c r="H319" t="s">
-        <v>7</v>
+        <v>292</v>
       </c>
       <c r="J319" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="320" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A320" t="s">
-        <v>1320</v>
+      <c r="A320" s="1" t="s">
+        <v>1151</v>
       </c>
       <c r="G320" t="s">
-        <v>44</v>
+        <v>86</v>
       </c>
       <c r="H320" t="s">
-        <v>45</v>
+        <v>1201</v>
       </c>
       <c r="J320" t="s">
         <v>3</v>
@@ -9301,13 +9271,13 @@
     </row>
     <row r="321" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A321" s="1" t="s">
-        <v>1143</v>
+        <v>1182</v>
       </c>
       <c r="G321" t="s">
-        <v>206</v>
+        <v>10</v>
       </c>
       <c r="H321" t="s">
-        <v>210</v>
+        <v>11</v>
       </c>
       <c r="J321" t="s">
         <v>3</v>
@@ -9315,13 +9285,13 @@
     </row>
     <row r="322" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A322" s="1" t="s">
-        <v>1168</v>
+        <v>1163</v>
       </c>
       <c r="G322" t="s">
-        <v>292</v>
+        <v>126</v>
       </c>
       <c r="H322" t="s">
-        <v>293</v>
+        <v>152</v>
       </c>
       <c r="J322" t="s">
         <v>3</v>
@@ -9329,13 +9299,13 @@
     </row>
     <row r="323" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A323" s="1" t="s">
-        <v>1152</v>
+        <v>1168</v>
       </c>
       <c r="G323" t="s">
-        <v>86</v>
+        <v>604</v>
       </c>
       <c r="H323" t="s">
-        <v>1203</v>
+        <v>605</v>
       </c>
       <c r="J323" t="s">
         <v>3</v>
@@ -9343,13 +9313,13 @@
     </row>
     <row r="324" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A324" s="1" t="s">
-        <v>1183</v>
+        <v>1175</v>
       </c>
       <c r="G324" t="s">
-        <v>10</v>
+        <v>273</v>
       </c>
       <c r="H324" t="s">
-        <v>11</v>
+        <v>281</v>
       </c>
       <c r="J324" t="s">
         <v>3</v>
@@ -9357,13 +9327,13 @@
     </row>
     <row r="325" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A325" s="1" t="s">
-        <v>1164</v>
+        <v>1176</v>
       </c>
       <c r="G325" t="s">
-        <v>126</v>
+        <v>282</v>
       </c>
       <c r="H325" t="s">
-        <v>152</v>
+        <v>283</v>
       </c>
       <c r="J325" t="s">
         <v>3</v>
@@ -9371,13 +9341,13 @@
     </row>
     <row r="326" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A326" s="1" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="G326" t="s">
-        <v>605</v>
+        <v>290</v>
       </c>
       <c r="H326" t="s">
-        <v>606</v>
+        <v>293</v>
       </c>
       <c r="J326" t="s">
         <v>3</v>
@@ -9385,27 +9355,27 @@
     </row>
     <row r="327" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A327" s="1" t="s">
-        <v>1176</v>
+        <v>1315</v>
       </c>
       <c r="G327" t="s">
-        <v>274</v>
+        <v>1207</v>
       </c>
       <c r="H327" t="s">
-        <v>282</v>
+        <v>1382</v>
       </c>
       <c r="J327" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="328" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A328" s="1" t="s">
-        <v>1177</v>
+        <v>1144</v>
       </c>
       <c r="G328" t="s">
-        <v>283</v>
+        <v>340</v>
       </c>
       <c r="H328" t="s">
-        <v>284</v>
+        <v>341</v>
       </c>
       <c r="J328" t="s">
         <v>3</v>
@@ -9413,13 +9383,13 @@
     </row>
     <row r="329" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A329" s="1" t="s">
-        <v>1167</v>
+        <v>1153</v>
       </c>
       <c r="G329" t="s">
-        <v>291</v>
+        <v>80</v>
       </c>
       <c r="H329" t="s">
-        <v>294</v>
+        <v>81</v>
       </c>
       <c r="J329" t="s">
         <v>3</v>
@@ -9427,13 +9397,13 @@
     </row>
     <row r="330" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A330" s="1" t="s">
-        <v>1321</v>
+        <v>1181</v>
       </c>
       <c r="G330" t="s">
-        <v>1209</v>
+        <v>296</v>
       </c>
       <c r="H330" t="s">
-        <v>1389</v>
+        <v>297</v>
       </c>
       <c r="J330" t="s">
         <v>3</v>
@@ -9441,13 +9411,13 @@
     </row>
     <row r="331" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A331" s="1" t="s">
-        <v>1145</v>
+        <v>1199</v>
       </c>
       <c r="G331" t="s">
-        <v>341</v>
+        <v>781</v>
       </c>
       <c r="H331" t="s">
-        <v>342</v>
+        <v>1428</v>
       </c>
       <c r="J331" t="s">
         <v>3</v>
@@ -9455,13 +9425,13 @@
     </row>
     <row r="332" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A332" s="1" t="s">
-        <v>1154</v>
+        <v>1146</v>
       </c>
       <c r="G332" t="s">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="H332" t="s">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="J332" t="s">
         <v>3</v>
@@ -9469,13 +9439,13 @@
     </row>
     <row r="333" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A333" s="1" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="G333" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="H333" t="s">
-        <v>298</v>
+        <v>280</v>
       </c>
       <c r="J333" t="s">
         <v>3</v>
@@ -9483,13 +9453,13 @@
     </row>
     <row r="334" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A334" s="1" t="s">
-        <v>1201</v>
+        <v>1023</v>
       </c>
       <c r="G334" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="H334" t="s">
-        <v>1438</v>
+        <v>1429</v>
       </c>
       <c r="J334" t="s">
         <v>3</v>
@@ -9497,13 +9467,13 @@
     </row>
     <row r="335" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A335" s="1" t="s">
-        <v>1147</v>
+        <v>1195</v>
       </c>
       <c r="G335" t="s">
-        <v>140</v>
+        <v>754</v>
       </c>
       <c r="H335" t="s">
-        <v>141</v>
+        <v>1430</v>
       </c>
       <c r="J335" t="s">
         <v>3</v>
@@ -9511,27 +9481,27 @@
     </row>
     <row r="336" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A336" s="1" t="s">
-        <v>1180</v>
+        <v>1193</v>
       </c>
       <c r="G336" t="s">
-        <v>280</v>
+        <v>46</v>
       </c>
       <c r="H336" t="s">
-        <v>281</v>
+        <v>47</v>
       </c>
       <c r="J336" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="337" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A337" s="1" t="s">
-        <v>1024</v>
+        <v>1145</v>
       </c>
       <c r="G337" t="s">
-        <v>787</v>
+        <v>213</v>
       </c>
       <c r="H337" t="s">
-        <v>1439</v>
+        <v>214</v>
       </c>
       <c r="J337" t="s">
         <v>3</v>
@@ -9539,13 +9509,13 @@
     </row>
     <row r="338" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A338" s="1" t="s">
-        <v>1197</v>
+        <v>1161</v>
       </c>
       <c r="G338" t="s">
-        <v>755</v>
+        <v>211</v>
       </c>
       <c r="H338" t="s">
-        <v>1440</v>
+        <v>212</v>
       </c>
       <c r="J338" t="s">
         <v>3</v>
@@ -9553,13 +9523,13 @@
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A339" s="1" t="s">
-        <v>1195</v>
+        <v>1180</v>
       </c>
       <c r="G339" t="s">
-        <v>46</v>
+        <v>294</v>
       </c>
       <c r="H339" t="s">
-        <v>47</v>
+        <v>295</v>
       </c>
       <c r="J339" t="s">
         <v>3</v>
@@ -9567,13 +9537,13 @@
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A340" s="1" t="s">
-        <v>1146</v>
+        <v>1196</v>
       </c>
       <c r="G340" t="s">
-        <v>213</v>
+        <v>1356</v>
       </c>
       <c r="H340" t="s">
-        <v>214</v>
+        <v>1431</v>
       </c>
       <c r="J340" t="s">
         <v>3</v>
@@ -9581,13 +9551,13 @@
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A341" s="1" t="s">
-        <v>1162</v>
+        <v>1197</v>
       </c>
       <c r="G341" t="s">
-        <v>211</v>
+        <v>273</v>
       </c>
       <c r="H341" t="s">
-        <v>212</v>
+        <v>1432</v>
       </c>
       <c r="J341" t="s">
         <v>3</v>
@@ -9595,27 +9565,27 @@
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A342" s="1" t="s">
-        <v>1181</v>
+        <v>1187</v>
       </c>
       <c r="G342" t="s">
-        <v>295</v>
+        <v>222</v>
       </c>
       <c r="H342" t="s">
-        <v>296</v>
+        <v>223</v>
       </c>
       <c r="J342" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="343" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A343" s="1" t="s">
-        <v>1198</v>
+        <v>1183</v>
       </c>
       <c r="G343" t="s">
-        <v>1363</v>
+        <v>298</v>
       </c>
       <c r="H343" t="s">
-        <v>1441</v>
+        <v>299</v>
       </c>
       <c r="J343" t="s">
         <v>3</v>
@@ -9623,13 +9593,13 @@
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A344" s="1" t="s">
-        <v>1199</v>
+        <v>1152</v>
       </c>
       <c r="G344" t="s">
-        <v>274</v>
+        <v>84</v>
       </c>
       <c r="H344" t="s">
-        <v>1442</v>
+        <v>85</v>
       </c>
       <c r="J344" t="s">
         <v>3</v>
@@ -9637,13 +9607,13 @@
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A345" s="1" t="s">
-        <v>1189</v>
+        <v>1138</v>
       </c>
       <c r="G345" t="s">
-        <v>222</v>
+        <v>126</v>
       </c>
       <c r="H345" t="s">
-        <v>223</v>
+        <v>127</v>
       </c>
       <c r="J345" t="s">
         <v>3</v>
@@ -9651,13 +9621,13 @@
     </row>
     <row r="346" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A346" s="1" t="s">
-        <v>1184</v>
+        <v>1316</v>
       </c>
       <c r="G346" t="s">
-        <v>299</v>
+        <v>773</v>
       </c>
       <c r="H346" t="s">
-        <v>300</v>
+        <v>1383</v>
       </c>
       <c r="J346" t="s">
         <v>3</v>
@@ -9665,13 +9635,13 @@
     </row>
     <row r="347" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A347" s="1" t="s">
-        <v>1153</v>
+        <v>1198</v>
       </c>
       <c r="G347" t="s">
-        <v>84</v>
+        <v>780</v>
       </c>
       <c r="H347" t="s">
-        <v>85</v>
+        <v>1433</v>
       </c>
       <c r="J347" t="s">
         <v>3</v>
@@ -9679,13 +9649,13 @@
     </row>
     <row r="348" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A348" s="1" t="s">
-        <v>1139</v>
+        <v>1317</v>
       </c>
       <c r="G348" t="s">
-        <v>126</v>
+        <v>1208</v>
       </c>
       <c r="H348" t="s">
-        <v>127</v>
+        <v>1384</v>
       </c>
       <c r="J348" t="s">
         <v>3</v>
@@ -9693,13 +9663,13 @@
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A349" s="1" t="s">
-        <v>1322</v>
+        <v>1169</v>
       </c>
       <c r="G349" t="s">
-        <v>774</v>
+        <v>606</v>
       </c>
       <c r="H349" t="s">
-        <v>1390</v>
+        <v>607</v>
       </c>
       <c r="J349" t="s">
         <v>3</v>
@@ -9707,27 +9677,27 @@
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A350" s="1" t="s">
-        <v>1200</v>
+        <v>1178</v>
       </c>
       <c r="G350" t="s">
-        <v>781</v>
+        <v>1</v>
       </c>
       <c r="H350" t="s">
-        <v>1443</v>
+        <v>2</v>
       </c>
       <c r="J350" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A351" s="1" t="s">
-        <v>1323</v>
+        <v>1137</v>
       </c>
       <c r="G351" t="s">
-        <v>1210</v>
+        <v>72</v>
       </c>
       <c r="H351" t="s">
-        <v>1391</v>
+        <v>73</v>
       </c>
       <c r="J351" t="s">
         <v>3</v>
@@ -9735,13 +9705,13 @@
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A352" s="1" t="s">
-        <v>1170</v>
+        <v>1136</v>
       </c>
       <c r="G352" t="s">
-        <v>607</v>
+        <v>89</v>
       </c>
       <c r="H352" t="s">
-        <v>608</v>
+        <v>90</v>
       </c>
       <c r="J352" t="s">
         <v>3</v>
@@ -9749,13 +9719,13 @@
     </row>
     <row r="353" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A353" s="1" t="s">
-        <v>1179</v>
+        <v>1147</v>
       </c>
       <c r="G353" t="s">
-        <v>1</v>
+        <v>338</v>
       </c>
       <c r="H353" t="s">
-        <v>2</v>
+        <v>339</v>
       </c>
       <c r="J353" t="s">
         <v>3</v>
@@ -9763,13 +9733,13 @@
     </row>
     <row r="354" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A354" s="1" t="s">
-        <v>1138</v>
+        <v>1318</v>
       </c>
       <c r="G354" t="s">
-        <v>72</v>
+        <v>1202</v>
       </c>
       <c r="H354" t="s">
-        <v>73</v>
+        <v>1203</v>
       </c>
       <c r="J354" t="s">
         <v>3</v>
@@ -9777,13 +9747,13 @@
     </row>
     <row r="355" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A355" s="1" t="s">
-        <v>1137</v>
+        <v>1319</v>
       </c>
       <c r="G355" t="s">
-        <v>89</v>
+        <v>1204</v>
       </c>
       <c r="H355" t="s">
-        <v>90</v>
+        <v>1205</v>
       </c>
       <c r="J355" t="s">
         <v>3</v>
@@ -9791,13 +9761,13 @@
     </row>
     <row r="356" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A356" s="1" t="s">
-        <v>1148</v>
+        <v>1194</v>
       </c>
       <c r="G356" t="s">
-        <v>339</v>
+        <v>1206</v>
       </c>
       <c r="H356" t="s">
-        <v>340</v>
+        <v>1434</v>
       </c>
       <c r="J356" t="s">
         <v>3</v>
@@ -9805,13 +9775,13 @@
     </row>
     <row r="357" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A357" s="1" t="s">
-        <v>1324</v>
+        <v>1320</v>
       </c>
       <c r="G357" t="s">
-        <v>1204</v>
+        <v>1357</v>
       </c>
       <c r="H357" t="s">
-        <v>1205</v>
+        <v>1385</v>
       </c>
       <c r="J357" t="s">
         <v>3</v>
@@ -9819,237 +9789,237 @@
     </row>
     <row r="358" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A358" s="1" t="s">
-        <v>1325</v>
+        <v>1321</v>
       </c>
       <c r="G358" t="s">
-        <v>1206</v>
+        <v>547</v>
       </c>
       <c r="H358" t="s">
-        <v>1207</v>
+        <v>584</v>
       </c>
       <c r="J358" t="s">
-        <v>3</v>
+        <v>553</v>
       </c>
     </row>
     <row r="359" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A359" s="1" t="s">
-        <v>1188</v>
+        <v>1322</v>
       </c>
       <c r="G359" t="s">
-        <v>224</v>
+        <v>551</v>
       </c>
       <c r="H359" t="s">
-        <v>225</v>
+        <v>552</v>
       </c>
       <c r="J359" t="s">
-        <v>3</v>
+        <v>553</v>
       </c>
     </row>
     <row r="360" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A360" s="1" t="s">
-        <v>1196</v>
+        <v>1323</v>
       </c>
       <c r="G360" t="s">
-        <v>1208</v>
+        <v>557</v>
       </c>
       <c r="H360" t="s">
-        <v>1444</v>
+        <v>558</v>
       </c>
       <c r="J360" t="s">
-        <v>3</v>
+        <v>553</v>
       </c>
     </row>
     <row r="361" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A361" s="1" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="G361" t="s">
-        <v>1364</v>
+        <v>575</v>
       </c>
       <c r="H361" t="s">
-        <v>1392</v>
+        <v>576</v>
       </c>
       <c r="J361" t="s">
-        <v>3</v>
+        <v>553</v>
       </c>
     </row>
     <row r="362" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A362" s="1" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="G362" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H362" t="s">
-        <v>585</v>
+        <v>559</v>
       </c>
       <c r="J362" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="363" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A363" s="1" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="G363" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="H363" t="s">
+        <v>588</v>
+      </c>
+      <c r="J363" t="s">
         <v>553</v>
-      </c>
-      <c r="J363" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="364" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A364" s="1" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="G364" t="s">
-        <v>558</v>
+        <v>260</v>
       </c>
       <c r="H364" t="s">
-        <v>559</v>
+        <v>771</v>
       </c>
       <c r="J364" t="s">
-        <v>554</v>
+        <v>272</v>
       </c>
     </row>
     <row r="365" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A365" s="1" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="G365" t="s">
-        <v>576</v>
+        <v>554</v>
       </c>
       <c r="H365" t="s">
-        <v>577</v>
+        <v>1435</v>
       </c>
       <c r="J365" t="s">
-        <v>554</v>
+        <v>272</v>
       </c>
     </row>
     <row r="366" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A366" s="1" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="G366" t="s">
-        <v>548</v>
+        <v>260</v>
       </c>
       <c r="H366" t="s">
-        <v>560</v>
+        <v>271</v>
       </c>
       <c r="J366" t="s">
-        <v>554</v>
+        <v>272</v>
       </c>
     </row>
     <row r="367" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A367" s="1" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="G367" t="s">
-        <v>548</v>
+        <v>308</v>
       </c>
       <c r="H367" t="s">
-        <v>589</v>
+        <v>309</v>
       </c>
       <c r="J367" t="s">
-        <v>554</v>
+        <v>272</v>
       </c>
     </row>
     <row r="368" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A368" s="1" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="G368" t="s">
-        <v>261</v>
+        <v>305</v>
       </c>
       <c r="H368" t="s">
-        <v>772</v>
+        <v>306</v>
       </c>
       <c r="J368" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="369" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A369" s="1" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="G369" t="s">
-        <v>555</v>
+        <v>590</v>
       </c>
       <c r="H369" t="s">
-        <v>1445</v>
+        <v>591</v>
       </c>
       <c r="J369" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="370" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A370" s="1" t="s">
-        <v>1335</v>
+        <v>973</v>
       </c>
       <c r="G370" t="s">
-        <v>261</v>
+        <v>671</v>
       </c>
       <c r="H370" t="s">
-        <v>272</v>
+        <v>672</v>
       </c>
       <c r="J370" t="s">
-        <v>273</v>
+        <v>67</v>
       </c>
     </row>
     <row r="371" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A371" s="1" t="s">
-        <v>1336</v>
+        <v>981</v>
       </c>
       <c r="G371" t="s">
-        <v>309</v>
+        <v>667</v>
       </c>
       <c r="H371" t="s">
-        <v>310</v>
+        <v>668</v>
       </c>
       <c r="J371" t="s">
-        <v>273</v>
+        <v>67</v>
       </c>
     </row>
     <row r="372" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A372" s="1" t="s">
-        <v>1337</v>
+        <v>1008</v>
       </c>
       <c r="G372" t="s">
-        <v>306</v>
+        <v>128</v>
       </c>
       <c r="H372" t="s">
-        <v>307</v>
+        <v>129</v>
       </c>
       <c r="J372" t="s">
-        <v>273</v>
+        <v>67</v>
       </c>
     </row>
     <row r="373" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A373" s="1" t="s">
-        <v>1338</v>
+        <v>965</v>
       </c>
       <c r="G373" t="s">
-        <v>591</v>
+        <v>445</v>
       </c>
       <c r="H373" t="s">
-        <v>592</v>
+        <v>446</v>
       </c>
       <c r="J373" t="s">
-        <v>273</v>
+        <v>67</v>
       </c>
     </row>
     <row r="374" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A374" s="1" t="s">
-        <v>974</v>
+        <v>952</v>
       </c>
       <c r="G374" t="s">
-        <v>672</v>
+        <v>517</v>
       </c>
       <c r="H374" t="s">
-        <v>673</v>
+        <v>518</v>
       </c>
       <c r="J374" t="s">
         <v>67</v>
@@ -10057,13 +10027,13 @@
     </row>
     <row r="375" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A375" s="1" t="s">
-        <v>982</v>
+        <v>990</v>
       </c>
       <c r="G375" t="s">
-        <v>668</v>
+        <v>228</v>
       </c>
       <c r="H375" t="s">
-        <v>669</v>
+        <v>229</v>
       </c>
       <c r="J375" t="s">
         <v>67</v>
@@ -10071,13 +10041,13 @@
     </row>
     <row r="376" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A376" s="1" t="s">
-        <v>1009</v>
+        <v>982</v>
       </c>
       <c r="G376" t="s">
-        <v>128</v>
+        <v>65</v>
       </c>
       <c r="H376" t="s">
-        <v>129</v>
+        <v>66</v>
       </c>
       <c r="J376" t="s">
         <v>67</v>
@@ -10085,13 +10055,13 @@
     </row>
     <row r="377" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A377" s="1" t="s">
-        <v>966</v>
+        <v>991</v>
       </c>
       <c r="G377" t="s">
-        <v>446</v>
+        <v>740</v>
       </c>
       <c r="H377" t="s">
-        <v>447</v>
+        <v>741</v>
       </c>
       <c r="J377" t="s">
         <v>67</v>
@@ -10099,13 +10069,13 @@
     </row>
     <row r="378" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A378" s="1" t="s">
-        <v>953</v>
+        <v>966</v>
       </c>
       <c r="G378" t="s">
-        <v>518</v>
+        <v>593</v>
       </c>
       <c r="H378" t="s">
-        <v>519</v>
+        <v>594</v>
       </c>
       <c r="J378" t="s">
         <v>67</v>
@@ -10113,13 +10083,13 @@
     </row>
     <row r="379" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A379" s="1" t="s">
-        <v>991</v>
+        <v>956</v>
       </c>
       <c r="G379" t="s">
-        <v>229</v>
+        <v>452</v>
       </c>
       <c r="H379" t="s">
-        <v>230</v>
+        <v>453</v>
       </c>
       <c r="J379" t="s">
         <v>67</v>
@@ -10127,13 +10097,13 @@
     </row>
     <row r="380" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A380" s="1" t="s">
-        <v>983</v>
+        <v>958</v>
       </c>
       <c r="G380" t="s">
-        <v>65</v>
+        <v>441</v>
       </c>
       <c r="H380" t="s">
-        <v>66</v>
+        <v>449</v>
       </c>
       <c r="J380" t="s">
         <v>67</v>
@@ -10141,13 +10111,13 @@
     </row>
     <row r="381" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A381" s="1" t="s">
-        <v>992</v>
+        <v>960</v>
       </c>
       <c r="G381" t="s">
-        <v>741</v>
+        <v>441</v>
       </c>
       <c r="H381" t="s">
-        <v>742</v>
+        <v>448</v>
       </c>
       <c r="J381" t="s">
         <v>67</v>
@@ -10155,13 +10125,13 @@
     </row>
     <row r="382" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A382" s="1" t="s">
-        <v>967</v>
+        <v>977</v>
       </c>
       <c r="G382" t="s">
-        <v>594</v>
+        <v>669</v>
       </c>
       <c r="H382" t="s">
-        <v>595</v>
+        <v>670</v>
       </c>
       <c r="J382" t="s">
         <v>67</v>
@@ -10169,13 +10139,13 @@
     </row>
     <row r="383" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A383" s="1" t="s">
-        <v>957</v>
+        <v>974</v>
       </c>
       <c r="G383" t="s">
-        <v>453</v>
+        <v>505</v>
       </c>
       <c r="H383" t="s">
-        <v>454</v>
+        <v>509</v>
       </c>
       <c r="J383" t="s">
         <v>67</v>
@@ -10183,13 +10153,13 @@
     </row>
     <row r="384" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A384" s="1" t="s">
-        <v>959</v>
+        <v>998</v>
       </c>
       <c r="G384" t="s">
-        <v>442</v>
+        <v>734</v>
       </c>
       <c r="H384" t="s">
-        <v>450</v>
+        <v>735</v>
       </c>
       <c r="J384" t="s">
         <v>67</v>
@@ -10197,13 +10167,13 @@
     </row>
     <row r="385" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A385" s="1" t="s">
-        <v>961</v>
+        <v>984</v>
       </c>
       <c r="G385" t="s">
-        <v>442</v>
+        <v>694</v>
       </c>
       <c r="H385" t="s">
-        <v>449</v>
+        <v>697</v>
       </c>
       <c r="J385" t="s">
         <v>67</v>
@@ -10211,13 +10181,13 @@
     </row>
     <row r="386" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A386" s="1" t="s">
-        <v>978</v>
+        <v>955</v>
       </c>
       <c r="G386" t="s">
-        <v>670</v>
+        <v>441</v>
       </c>
       <c r="H386" t="s">
-        <v>671</v>
+        <v>442</v>
       </c>
       <c r="J386" t="s">
         <v>67</v>
@@ -10225,13 +10195,13 @@
     </row>
     <row r="387" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A387" s="1" t="s">
-        <v>975</v>
+        <v>1333</v>
       </c>
       <c r="G387" t="s">
-        <v>506</v>
+        <v>675</v>
       </c>
       <c r="H387" t="s">
-        <v>510</v>
+        <v>1386</v>
       </c>
       <c r="J387" t="s">
         <v>67</v>
@@ -10239,13 +10209,13 @@
     </row>
     <row r="388" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A388" s="1" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="G388" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="H388" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="J388" t="s">
         <v>67</v>
@@ -10253,13 +10223,13 @@
     </row>
     <row r="389" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A389" s="1" t="s">
-        <v>985</v>
+        <v>957</v>
       </c>
       <c r="G389" t="s">
-        <v>695</v>
+        <v>443</v>
       </c>
       <c r="H389" t="s">
-        <v>698</v>
+        <v>444</v>
       </c>
       <c r="J389" t="s">
         <v>67</v>
@@ -10267,13 +10237,13 @@
     </row>
     <row r="390" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A390" s="1" t="s">
-        <v>956</v>
+        <v>1000</v>
       </c>
       <c r="G390" t="s">
-        <v>442</v>
+        <v>716</v>
       </c>
       <c r="H390" t="s">
-        <v>443</v>
+        <v>723</v>
       </c>
       <c r="J390" t="s">
         <v>67</v>
@@ -10281,13 +10251,13 @@
     </row>
     <row r="391" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A391" s="1" t="s">
-        <v>1339</v>
+        <v>993</v>
       </c>
       <c r="G391" t="s">
-        <v>676</v>
+        <v>736</v>
       </c>
       <c r="H391" t="s">
-        <v>1393</v>
+        <v>738</v>
       </c>
       <c r="J391" t="s">
         <v>67</v>
@@ -10295,13 +10265,13 @@
     </row>
     <row r="392" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A392" s="1" t="s">
-        <v>998</v>
+        <v>1334</v>
       </c>
       <c r="G392" t="s">
-        <v>743</v>
+        <v>694</v>
       </c>
       <c r="H392" t="s">
-        <v>744</v>
+        <v>1032</v>
       </c>
       <c r="J392" t="s">
         <v>67</v>
@@ -10309,13 +10279,13 @@
     </row>
     <row r="393" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A393" s="1" t="s">
-        <v>958</v>
+        <v>978</v>
       </c>
       <c r="G393" t="s">
-        <v>444</v>
+        <v>704</v>
       </c>
       <c r="H393" t="s">
-        <v>445</v>
+        <v>705</v>
       </c>
       <c r="J393" t="s">
         <v>67</v>
@@ -10323,13 +10293,13 @@
     </row>
     <row r="394" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A394" s="1" t="s">
-        <v>1001</v>
+        <v>992</v>
       </c>
       <c r="G394" t="s">
-        <v>717</v>
+        <v>736</v>
       </c>
       <c r="H394" t="s">
-        <v>724</v>
+        <v>737</v>
       </c>
       <c r="J394" t="s">
         <v>67</v>
@@ -10337,13 +10307,13 @@
     </row>
     <row r="395" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A395" s="1" t="s">
-        <v>994</v>
+        <v>1335</v>
       </c>
       <c r="G395" t="s">
-        <v>737</v>
+        <v>716</v>
       </c>
       <c r="H395" t="s">
-        <v>739</v>
+        <v>1387</v>
       </c>
       <c r="J395" t="s">
         <v>67</v>
@@ -10351,13 +10321,13 @@
     </row>
     <row r="396" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A396" s="1" t="s">
-        <v>1340</v>
+        <v>959</v>
       </c>
       <c r="G396" t="s">
-        <v>695</v>
+        <v>456</v>
       </c>
       <c r="H396" t="s">
-        <v>1033</v>
+        <v>457</v>
       </c>
       <c r="J396" t="s">
         <v>67</v>
@@ -10365,13 +10335,13 @@
     </row>
     <row r="397" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A397" s="1" t="s">
-        <v>979</v>
+        <v>967</v>
       </c>
       <c r="G397" t="s">
-        <v>705</v>
+        <v>124</v>
       </c>
       <c r="H397" t="s">
-        <v>706</v>
+        <v>125</v>
       </c>
       <c r="J397" t="s">
         <v>67</v>
@@ -10379,13 +10349,13 @@
     </row>
     <row r="398" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A398" s="1" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="G398" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="H398" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="J398" t="s">
         <v>67</v>
@@ -10393,13 +10363,13 @@
     </row>
     <row r="399" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A399" s="1" t="s">
-        <v>1341</v>
+        <v>976</v>
       </c>
       <c r="G399" t="s">
-        <v>717</v>
+        <v>673</v>
       </c>
       <c r="H399" t="s">
-        <v>1394</v>
+        <v>674</v>
       </c>
       <c r="J399" t="s">
         <v>67</v>
@@ -10407,13 +10377,13 @@
     </row>
     <row r="400" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A400" s="1" t="s">
-        <v>960</v>
+        <v>985</v>
       </c>
       <c r="G400" t="s">
-        <v>457</v>
+        <v>698</v>
       </c>
       <c r="H400" t="s">
-        <v>458</v>
+        <v>699</v>
       </c>
       <c r="J400" t="s">
         <v>67</v>
@@ -10421,13 +10391,13 @@
     </row>
     <row r="401" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A401" s="1" t="s">
-        <v>968</v>
+        <v>1017</v>
       </c>
       <c r="G401" t="s">
-        <v>124</v>
+        <v>750</v>
       </c>
       <c r="H401" t="s">
-        <v>125</v>
+        <v>1436</v>
       </c>
       <c r="J401" t="s">
         <v>67</v>
@@ -10435,13 +10405,13 @@
     </row>
     <row r="402" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A402" s="1" t="s">
-        <v>997</v>
+        <v>983</v>
       </c>
       <c r="G402" t="s">
-        <v>745</v>
+        <v>700</v>
       </c>
       <c r="H402" t="s">
-        <v>746</v>
+        <v>701</v>
       </c>
       <c r="J402" t="s">
         <v>67</v>
@@ -10449,13 +10419,13 @@
     </row>
     <row r="403" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A403" s="1" t="s">
-        <v>977</v>
+        <v>962</v>
       </c>
       <c r="G403" t="s">
-        <v>674</v>
+        <v>441</v>
       </c>
       <c r="H403" t="s">
-        <v>675</v>
+        <v>450</v>
       </c>
       <c r="J403" t="s">
         <v>67</v>
@@ -10463,13 +10433,13 @@
     </row>
     <row r="404" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A404" s="1" t="s">
-        <v>986</v>
+        <v>1020</v>
       </c>
       <c r="G404" t="s">
-        <v>699</v>
+        <v>228</v>
       </c>
       <c r="H404" t="s">
-        <v>700</v>
+        <v>1437</v>
       </c>
       <c r="J404" t="s">
         <v>67</v>
@@ -10477,13 +10447,13 @@
     </row>
     <row r="405" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A405" s="1" t="s">
-        <v>1018</v>
+        <v>1024</v>
       </c>
       <c r="G405" t="s">
-        <v>751</v>
+        <v>517</v>
       </c>
       <c r="H405" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="J405" t="s">
         <v>67</v>
@@ -10491,13 +10461,13 @@
     </row>
     <row r="406" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A406" s="1" t="s">
-        <v>984</v>
+        <v>999</v>
       </c>
       <c r="G406" t="s">
-        <v>701</v>
+        <v>739</v>
       </c>
       <c r="H406" t="s">
-        <v>702</v>
+        <v>1031</v>
       </c>
       <c r="J406" t="s">
         <v>67</v>
@@ -10505,13 +10475,13 @@
     </row>
     <row r="407" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A407" s="1" t="s">
-        <v>963</v>
+        <v>1003</v>
       </c>
       <c r="G407" t="s">
-        <v>442</v>
+        <v>716</v>
       </c>
       <c r="H407" t="s">
-        <v>451</v>
+        <v>724</v>
       </c>
       <c r="J407" t="s">
         <v>67</v>
@@ -10519,13 +10489,13 @@
     </row>
     <row r="408" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A408" s="1" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="G408" t="s">
-        <v>229</v>
+        <v>761</v>
       </c>
       <c r="H408" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="J408" t="s">
         <v>67</v>
@@ -10533,13 +10503,13 @@
     </row>
     <row r="409" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A409" s="1" t="s">
-        <v>1025</v>
+        <v>963</v>
       </c>
       <c r="G409" t="s">
-        <v>518</v>
+        <v>441</v>
       </c>
       <c r="H409" t="s">
-        <v>1448</v>
+        <v>447</v>
       </c>
       <c r="J409" t="s">
         <v>67</v>
@@ -10547,13 +10517,13 @@
     </row>
     <row r="410" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A410" s="1" t="s">
-        <v>1000</v>
+        <v>1025</v>
       </c>
       <c r="G410" t="s">
-        <v>740</v>
+        <v>677</v>
       </c>
       <c r="H410" t="s">
-        <v>1032</v>
+        <v>1440</v>
       </c>
       <c r="J410" t="s">
         <v>67</v>
@@ -10561,13 +10531,13 @@
     </row>
     <row r="411" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A411" s="1" t="s">
-        <v>1004</v>
+        <v>980</v>
       </c>
       <c r="G411" t="s">
-        <v>717</v>
+        <v>702</v>
       </c>
       <c r="H411" t="s">
-        <v>725</v>
+        <v>703</v>
       </c>
       <c r="J411" t="s">
         <v>67</v>
@@ -10575,13 +10545,13 @@
     </row>
     <row r="412" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A412" s="1" t="s">
-        <v>1020</v>
+        <v>1336</v>
       </c>
       <c r="G412" t="s">
-        <v>762</v>
+        <v>1358</v>
       </c>
       <c r="H412" t="s">
-        <v>1449</v>
+        <v>1388</v>
       </c>
       <c r="J412" t="s">
         <v>67</v>
@@ -10589,13 +10559,13 @@
     </row>
     <row r="413" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A413" s="1" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="G413" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H413" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="J413" t="s">
         <v>67</v>
@@ -10603,13 +10573,13 @@
     </row>
     <row r="414" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A414" s="1" t="s">
-        <v>1026</v>
+        <v>979</v>
       </c>
       <c r="G414" t="s">
-        <v>678</v>
+        <v>507</v>
       </c>
       <c r="H414" t="s">
-        <v>1450</v>
+        <v>508</v>
       </c>
       <c r="J414" t="s">
         <v>67</v>
@@ -10617,13 +10587,13 @@
     </row>
     <row r="415" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A415" s="1" t="s">
-        <v>981</v>
+        <v>1005</v>
       </c>
       <c r="G415" t="s">
-        <v>703</v>
+        <v>721</v>
       </c>
       <c r="H415" t="s">
-        <v>704</v>
+        <v>722</v>
       </c>
       <c r="J415" t="s">
         <v>67</v>
@@ -10631,13 +10601,13 @@
     </row>
     <row r="416" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A416" s="1" t="s">
-        <v>1342</v>
+        <v>964</v>
       </c>
       <c r="G416" t="s">
-        <v>1365</v>
+        <v>454</v>
       </c>
       <c r="H416" t="s">
-        <v>1395</v>
+        <v>455</v>
       </c>
       <c r="J416" t="s">
         <v>67</v>
@@ -10645,13 +10615,13 @@
     </row>
     <row r="417" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A417" s="1" t="s">
-        <v>962</v>
+        <v>1015</v>
       </c>
       <c r="G417" t="s">
-        <v>442</v>
+        <v>616</v>
       </c>
       <c r="H417" t="s">
-        <v>452</v>
+        <v>617</v>
       </c>
       <c r="J417" t="s">
         <v>67</v>
@@ -10659,13 +10629,13 @@
     </row>
     <row r="418" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A418" s="1" t="s">
-        <v>980</v>
+        <v>968</v>
       </c>
       <c r="G418" t="s">
-        <v>508</v>
+        <v>665</v>
       </c>
       <c r="H418" t="s">
-        <v>509</v>
+        <v>666</v>
       </c>
       <c r="J418" t="s">
         <v>67</v>
@@ -10673,13 +10643,13 @@
     </row>
     <row r="419" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A419" s="1" t="s">
-        <v>1006</v>
+        <v>1021</v>
       </c>
       <c r="G419" t="s">
-        <v>722</v>
+        <v>783</v>
       </c>
       <c r="H419" t="s">
-        <v>723</v>
+        <v>1441</v>
       </c>
       <c r="J419" t="s">
         <v>67</v>
@@ -10687,13 +10657,13 @@
     </row>
     <row r="420" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A420" s="1" t="s">
-        <v>965</v>
+        <v>989</v>
       </c>
       <c r="G420" t="s">
-        <v>455</v>
+        <v>284</v>
       </c>
       <c r="H420" t="s">
-        <v>456</v>
+        <v>285</v>
       </c>
       <c r="J420" t="s">
         <v>67</v>
@@ -10701,13 +10671,13 @@
     </row>
     <row r="421" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A421" s="1" t="s">
-        <v>1016</v>
+        <v>1002</v>
       </c>
       <c r="G421" t="s">
-        <v>617</v>
+        <v>717</v>
       </c>
       <c r="H421" t="s">
-        <v>618</v>
+        <v>718</v>
       </c>
       <c r="J421" t="s">
         <v>67</v>
@@ -10715,13 +10685,13 @@
     </row>
     <row r="422" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A422" s="1" t="s">
-        <v>969</v>
+        <v>953</v>
       </c>
       <c r="G422" t="s">
-        <v>666</v>
+        <v>521</v>
       </c>
       <c r="H422" t="s">
-        <v>667</v>
+        <v>522</v>
       </c>
       <c r="J422" t="s">
         <v>67</v>
@@ -10729,13 +10699,13 @@
     </row>
     <row r="423" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A423" s="1" t="s">
-        <v>1022</v>
+        <v>1011</v>
       </c>
       <c r="G423" t="s">
-        <v>784</v>
+        <v>130</v>
       </c>
       <c r="H423" t="s">
-        <v>1451</v>
+        <v>131</v>
       </c>
       <c r="J423" t="s">
         <v>67</v>
@@ -10743,13 +10713,13 @@
     </row>
     <row r="424" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A424" s="1" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="G424" t="s">
-        <v>285</v>
+        <v>695</v>
       </c>
       <c r="H424" t="s">
-        <v>286</v>
+        <v>696</v>
       </c>
       <c r="J424" t="s">
         <v>67</v>
@@ -10757,13 +10727,13 @@
     </row>
     <row r="425" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A425" s="1" t="s">
-        <v>1003</v>
+        <v>1014</v>
       </c>
       <c r="G425" t="s">
-        <v>718</v>
+        <v>618</v>
       </c>
       <c r="H425" t="s">
-        <v>719</v>
+        <v>619</v>
       </c>
       <c r="J425" t="s">
         <v>67</v>
@@ -10771,13 +10741,13 @@
     </row>
     <row r="426" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A426" s="1" t="s">
-        <v>954</v>
+        <v>1337</v>
       </c>
       <c r="G426" t="s">
-        <v>522</v>
+        <v>774</v>
       </c>
       <c r="H426" t="s">
-        <v>523</v>
+        <v>1389</v>
       </c>
       <c r="J426" t="s">
         <v>67</v>
@@ -10785,13 +10755,13 @@
     </row>
     <row r="427" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A427" s="1" t="s">
-        <v>1012</v>
+        <v>994</v>
       </c>
       <c r="G427" t="s">
-        <v>130</v>
+        <v>727</v>
       </c>
       <c r="H427" t="s">
-        <v>131</v>
+        <v>728</v>
       </c>
       <c r="J427" t="s">
         <v>67</v>
@@ -10799,13 +10769,13 @@
     </row>
     <row r="428" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A428" s="1" t="s">
-        <v>987</v>
+        <v>1029</v>
       </c>
       <c r="G428" t="s">
-        <v>696</v>
+        <v>1359</v>
       </c>
       <c r="H428" t="s">
-        <v>697</v>
+        <v>1442</v>
       </c>
       <c r="J428" t="s">
         <v>67</v>
@@ -10813,13 +10783,13 @@
     </row>
     <row r="429" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A429" s="1" t="s">
-        <v>1015</v>
+        <v>1022</v>
       </c>
       <c r="G429" t="s">
-        <v>619</v>
+        <v>731</v>
       </c>
       <c r="H429" t="s">
-        <v>620</v>
+        <v>1443</v>
       </c>
       <c r="J429" t="s">
         <v>67</v>
@@ -10827,13 +10797,13 @@
     </row>
     <row r="430" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A430" s="1" t="s">
-        <v>1343</v>
+        <v>954</v>
       </c>
       <c r="G430" t="s">
-        <v>775</v>
+        <v>517</v>
       </c>
       <c r="H430" t="s">
-        <v>1396</v>
+        <v>1030</v>
       </c>
       <c r="J430" t="s">
         <v>67</v>
@@ -10841,13 +10811,13 @@
     </row>
     <row r="431" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A431" s="1" t="s">
-        <v>995</v>
+        <v>1338</v>
       </c>
       <c r="G431" t="s">
-        <v>728</v>
+        <v>734</v>
       </c>
       <c r="H431" t="s">
-        <v>729</v>
+        <v>1390</v>
       </c>
       <c r="J431" t="s">
         <v>67</v>
@@ -10855,13 +10825,13 @@
     </row>
     <row r="432" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A432" s="1" t="s">
-        <v>1030</v>
+        <v>1018</v>
       </c>
       <c r="G432" t="s">
-        <v>1366</v>
+        <v>716</v>
       </c>
       <c r="H432" t="s">
-        <v>1452</v>
+        <v>1444</v>
       </c>
       <c r="J432" t="s">
         <v>67</v>
@@ -10869,13 +10839,13 @@
     </row>
     <row r="433" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A433" s="1" t="s">
-        <v>1023</v>
+        <v>971</v>
       </c>
       <c r="G433" t="s">
-        <v>732</v>
+        <v>660</v>
       </c>
       <c r="H433" t="s">
-        <v>1453</v>
+        <v>663</v>
       </c>
       <c r="J433" t="s">
         <v>67</v>
@@ -10883,13 +10853,13 @@
     </row>
     <row r="434" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A434" s="1" t="s">
-        <v>955</v>
+        <v>1339</v>
       </c>
       <c r="G434" t="s">
-        <v>518</v>
+        <v>734</v>
       </c>
       <c r="H434" t="s">
-        <v>1031</v>
+        <v>1391</v>
       </c>
       <c r="J434" t="s">
         <v>67</v>
@@ -10897,13 +10867,13 @@
     </row>
     <row r="435" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A435" s="1" t="s">
-        <v>1344</v>
+        <v>995</v>
       </c>
       <c r="G435" t="s">
-        <v>735</v>
+        <v>725</v>
       </c>
       <c r="H435" t="s">
-        <v>1397</v>
+        <v>726</v>
       </c>
       <c r="J435" t="s">
         <v>67</v>
@@ -10911,13 +10881,13 @@
     </row>
     <row r="436" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A436" s="1" t="s">
-        <v>1019</v>
+        <v>987</v>
       </c>
       <c r="G436" t="s">
-        <v>717</v>
+        <v>677</v>
       </c>
       <c r="H436" t="s">
-        <v>1454</v>
+        <v>678</v>
       </c>
       <c r="J436" t="s">
         <v>67</v>
@@ -10925,13 +10895,13 @@
     </row>
     <row r="437" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A437" s="1" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="G437" t="s">
         <v>661</v>
       </c>
       <c r="H437" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="J437" t="s">
         <v>67</v>
@@ -10939,13 +10909,13 @@
     </row>
     <row r="438" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A438" s="1" t="s">
-        <v>1345</v>
+        <v>970</v>
       </c>
       <c r="G438" t="s">
-        <v>735</v>
+        <v>660</v>
       </c>
       <c r="H438" t="s">
-        <v>1398</v>
+        <v>664</v>
       </c>
       <c r="J438" t="s">
         <v>67</v>
@@ -10953,13 +10923,13 @@
     </row>
     <row r="439" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A439" s="1" t="s">
-        <v>996</v>
+        <v>1006</v>
       </c>
       <c r="G439" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
       <c r="H439" t="s">
-        <v>727</v>
+        <v>720</v>
       </c>
       <c r="J439" t="s">
         <v>67</v>
@@ -10967,13 +10937,13 @@
     </row>
     <row r="440" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A440" s="1" t="s">
-        <v>988</v>
+        <v>1004</v>
       </c>
       <c r="G440" t="s">
-        <v>678</v>
+        <v>729</v>
       </c>
       <c r="H440" t="s">
-        <v>679</v>
+        <v>730</v>
       </c>
       <c r="J440" t="s">
         <v>67</v>
@@ -10981,13 +10951,13 @@
     </row>
     <row r="441" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A441" s="1" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="G441" t="s">
-        <v>662</v>
+        <v>510</v>
       </c>
       <c r="H441" t="s">
-        <v>663</v>
+        <v>511</v>
       </c>
       <c r="J441" t="s">
         <v>67</v>
@@ -10995,13 +10965,13 @@
     </row>
     <row r="442" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A442" s="1" t="s">
-        <v>971</v>
+        <v>1001</v>
       </c>
       <c r="G442" t="s">
-        <v>661</v>
+        <v>716</v>
       </c>
       <c r="H442" t="s">
-        <v>665</v>
+        <v>733</v>
       </c>
       <c r="J442" t="s">
         <v>67</v>
@@ -11009,13 +10979,13 @@
     </row>
     <row r="443" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A443" s="1" t="s">
-        <v>1007</v>
+        <v>988</v>
       </c>
       <c r="G443" t="s">
-        <v>720</v>
+        <v>675</v>
       </c>
       <c r="H443" t="s">
-        <v>721</v>
+        <v>676</v>
       </c>
       <c r="J443" t="s">
         <v>67</v>
@@ -11023,13 +10993,13 @@
     </row>
     <row r="444" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A444" s="1" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="G444" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H444" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="J444" t="s">
         <v>67</v>
@@ -11037,13 +11007,13 @@
     </row>
     <row r="445" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A445" s="1" t="s">
-        <v>973</v>
+        <v>1026</v>
       </c>
       <c r="G445" t="s">
-        <v>511</v>
+        <v>1360</v>
       </c>
       <c r="H445" t="s">
-        <v>512</v>
+        <v>1445</v>
       </c>
       <c r="J445" t="s">
         <v>67</v>
@@ -11051,13 +11021,13 @@
     </row>
     <row r="446" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A446" s="1" t="s">
-        <v>1002</v>
+        <v>1027</v>
       </c>
       <c r="G446" t="s">
-        <v>717</v>
+        <v>1361</v>
       </c>
       <c r="H446" t="s">
-        <v>734</v>
+        <v>1446</v>
       </c>
       <c r="J446" t="s">
         <v>67</v>
@@ -11065,13 +11035,13 @@
     </row>
     <row r="447" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A447" s="1" t="s">
-        <v>989</v>
+        <v>1028</v>
       </c>
       <c r="G447" t="s">
-        <v>676</v>
+        <v>441</v>
       </c>
       <c r="H447" t="s">
-        <v>677</v>
+        <v>1447</v>
       </c>
       <c r="J447" t="s">
         <v>67</v>
@@ -11079,139 +11049,139 @@
     </row>
     <row r="448" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A448" s="1" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="G448" t="s">
-        <v>732</v>
+        <v>132</v>
       </c>
       <c r="H448" t="s">
-        <v>733</v>
+        <v>133</v>
       </c>
       <c r="J448" t="s">
-        <v>67</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="449" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A449" s="1" t="s">
-        <v>1027</v>
+        <v>1012</v>
       </c>
       <c r="G449" t="s">
-        <v>1367</v>
+        <v>149</v>
       </c>
       <c r="H449" t="s">
-        <v>1455</v>
+        <v>150</v>
       </c>
       <c r="J449" t="s">
-        <v>67</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="450" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A450" s="1" t="s">
-        <v>1028</v>
+        <v>1010</v>
       </c>
       <c r="G450" t="s">
-        <v>1368</v>
+        <v>144</v>
       </c>
       <c r="H450" t="s">
-        <v>1456</v>
+        <v>145</v>
       </c>
       <c r="J450" t="s">
-        <v>67</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="451" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A451" s="1" t="s">
-        <v>1029</v>
+        <v>1013</v>
       </c>
       <c r="G451" t="s">
-        <v>442</v>
+        <v>142</v>
       </c>
       <c r="H451" t="s">
-        <v>1457</v>
+        <v>143</v>
       </c>
       <c r="J451" t="s">
-        <v>67</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="452" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A452" s="1" t="s">
-        <v>1010</v>
+        <v>1016</v>
       </c>
       <c r="G452" t="s">
-        <v>132</v>
+        <v>74</v>
       </c>
       <c r="H452" t="s">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="J452" t="s">
-        <v>1471</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="453" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A453" s="1" t="s">
-        <v>1013</v>
+        <v>899</v>
       </c>
       <c r="G453" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="H453" t="s">
-        <v>150</v>
+        <v>951</v>
       </c>
       <c r="J453" t="s">
-        <v>1471</v>
+        <v>51</v>
       </c>
     </row>
     <row r="454" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A454" s="1" t="s">
-        <v>1011</v>
+        <v>922</v>
       </c>
       <c r="G454" t="s">
-        <v>144</v>
+        <v>173</v>
       </c>
       <c r="H454" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="J454" t="s">
-        <v>1471</v>
+        <v>51</v>
       </c>
     </row>
     <row r="455" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A455" s="1" t="s">
-        <v>1014</v>
+        <v>893</v>
       </c>
       <c r="G455" t="s">
-        <v>142</v>
+        <v>427</v>
       </c>
       <c r="H455" t="s">
-        <v>143</v>
+        <v>428</v>
       </c>
       <c r="J455" t="s">
-        <v>1471</v>
+        <v>51</v>
       </c>
     </row>
     <row r="456" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A456" s="1" t="s">
-        <v>1017</v>
+        <v>886</v>
       </c>
       <c r="G456" t="s">
-        <v>74</v>
+        <v>423</v>
       </c>
       <c r="H456" t="s">
-        <v>75</v>
+        <v>424</v>
       </c>
       <c r="J456" t="s">
-        <v>1471</v>
+        <v>51</v>
       </c>
     </row>
     <row r="457" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A457" s="1" t="s">
-        <v>900</v>
+        <v>927</v>
       </c>
       <c r="G457" t="s">
-        <v>157</v>
+        <v>351</v>
       </c>
       <c r="H457" t="s">
-        <v>952</v>
+        <v>352</v>
       </c>
       <c r="J457" t="s">
         <v>51</v>
@@ -11219,13 +11189,13 @@
     </row>
     <row r="458" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A458" s="1" t="s">
-        <v>923</v>
+        <v>887</v>
       </c>
       <c r="G458" t="s">
-        <v>173</v>
+        <v>596</v>
       </c>
       <c r="H458" t="s">
-        <v>174</v>
+        <v>597</v>
       </c>
       <c r="J458" t="s">
         <v>51</v>
@@ -11233,13 +11203,13 @@
     </row>
     <row r="459" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A459" s="1" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="G459" t="s">
-        <v>428</v>
+        <v>49</v>
       </c>
       <c r="H459" t="s">
-        <v>429</v>
+        <v>50</v>
       </c>
       <c r="J459" t="s">
         <v>51</v>
@@ -11247,13 +11217,13 @@
     </row>
     <row r="460" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A460" s="1" t="s">
-        <v>887</v>
+        <v>904</v>
       </c>
       <c r="G460" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="H460" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="J460" t="s">
         <v>51</v>
@@ -11261,13 +11231,13 @@
     </row>
     <row r="461" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A461" s="1" t="s">
-        <v>928</v>
+        <v>905</v>
       </c>
       <c r="G461" t="s">
-        <v>352</v>
+        <v>413</v>
       </c>
       <c r="H461" t="s">
-        <v>353</v>
+        <v>414</v>
       </c>
       <c r="J461" t="s">
         <v>51</v>
@@ -11278,10 +11248,10 @@
         <v>888</v>
       </c>
       <c r="G462" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="H462" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="J462" t="s">
         <v>51</v>
@@ -11289,13 +11259,13 @@
     </row>
     <row r="463" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A463" s="1" t="s">
-        <v>893</v>
+        <v>882</v>
       </c>
       <c r="G463" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="H463" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="J463" t="s">
         <v>51</v>
@@ -11303,13 +11273,13 @@
     </row>
     <row r="464" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A464" s="1" t="s">
-        <v>905</v>
+        <v>895</v>
       </c>
       <c r="G464" t="s">
-        <v>417</v>
+        <v>433</v>
       </c>
       <c r="H464" t="s">
-        <v>418</v>
+        <v>434</v>
       </c>
       <c r="J464" t="s">
         <v>51</v>
@@ -11317,13 +11287,13 @@
     </row>
     <row r="465" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A465" s="1" t="s">
-        <v>906</v>
+        <v>889</v>
       </c>
       <c r="G465" t="s">
-        <v>414</v>
+        <v>600</v>
       </c>
       <c r="H465" t="s">
-        <v>415</v>
+        <v>601</v>
       </c>
       <c r="J465" t="s">
         <v>51</v>
@@ -11331,13 +11301,13 @@
     </row>
     <row r="466" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A466" s="1" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="G466" t="s">
-        <v>596</v>
+        <v>418</v>
       </c>
       <c r="H466" t="s">
-        <v>603</v>
+        <v>419</v>
       </c>
       <c r="J466" t="s">
         <v>51</v>
@@ -11345,13 +11315,13 @@
     </row>
     <row r="467" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A467" s="1" t="s">
-        <v>883</v>
+        <v>928</v>
       </c>
       <c r="G467" t="s">
-        <v>61</v>
+        <v>355</v>
       </c>
       <c r="H467" t="s">
-        <v>62</v>
+        <v>356</v>
       </c>
       <c r="J467" t="s">
         <v>51</v>
@@ -11359,13 +11329,13 @@
     </row>
     <row r="468" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A468" s="1" t="s">
-        <v>896</v>
+        <v>907</v>
       </c>
       <c r="G468" t="s">
-        <v>434</v>
+        <v>413</v>
       </c>
       <c r="H468" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="J468" t="s">
         <v>51</v>
@@ -11373,13 +11343,13 @@
     </row>
     <row r="469" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A469" s="1" t="s">
-        <v>890</v>
+        <v>921</v>
       </c>
       <c r="G469" t="s">
-        <v>601</v>
+        <v>181</v>
       </c>
       <c r="H469" t="s">
-        <v>602</v>
+        <v>182</v>
       </c>
       <c r="J469" t="s">
         <v>51</v>
@@ -11387,13 +11357,13 @@
     </row>
     <row r="470" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A470" s="1" t="s">
-        <v>886</v>
+        <v>906</v>
       </c>
       <c r="G470" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="H470" t="s">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="J470" t="s">
         <v>51</v>
@@ -11401,13 +11371,13 @@
     </row>
     <row r="471" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A471" s="1" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="G471" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="H471" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="J471" t="s">
         <v>51</v>
@@ -11415,13 +11385,13 @@
     </row>
     <row r="472" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A472" s="1" t="s">
-        <v>908</v>
+        <v>920</v>
       </c>
       <c r="G472" t="s">
-        <v>414</v>
+        <v>183</v>
       </c>
       <c r="H472" t="s">
-        <v>433</v>
+        <v>184</v>
       </c>
       <c r="J472" t="s">
         <v>51</v>
@@ -11429,13 +11399,13 @@
     </row>
     <row r="473" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A473" s="1" t="s">
-        <v>922</v>
+        <v>908</v>
       </c>
       <c r="G473" t="s">
-        <v>181</v>
+        <v>413</v>
       </c>
       <c r="H473" t="s">
-        <v>182</v>
+        <v>429</v>
       </c>
       <c r="J473" t="s">
         <v>51</v>
@@ -11443,13 +11413,13 @@
     </row>
     <row r="474" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A474" s="1" t="s">
-        <v>907</v>
+        <v>900</v>
       </c>
       <c r="G474" t="s">
-        <v>414</v>
+        <v>162</v>
       </c>
       <c r="H474" t="s">
-        <v>436</v>
+        <v>163</v>
       </c>
       <c r="J474" t="s">
         <v>51</v>
@@ -11457,13 +11427,13 @@
     </row>
     <row r="475" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A475" s="1" t="s">
-        <v>931</v>
+        <v>897</v>
       </c>
       <c r="G475" t="s">
-        <v>348</v>
+        <v>68</v>
       </c>
       <c r="H475" t="s">
-        <v>349</v>
+        <v>69</v>
       </c>
       <c r="J475" t="s">
         <v>51</v>
@@ -11471,13 +11441,13 @@
     </row>
     <row r="476" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A476" s="1" t="s">
-        <v>921</v>
+        <v>936</v>
       </c>
       <c r="G476" t="s">
-        <v>183</v>
+        <v>458</v>
       </c>
       <c r="H476" t="s">
-        <v>184</v>
+        <v>1448</v>
       </c>
       <c r="J476" t="s">
         <v>51</v>
@@ -11485,13 +11455,13 @@
     </row>
     <row r="477" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A477" s="1" t="s">
-        <v>909</v>
+        <v>894</v>
       </c>
       <c r="G477" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
       <c r="H477" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="J477" t="s">
         <v>51</v>
@@ -11499,13 +11469,13 @@
     </row>
     <row r="478" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A478" s="1" t="s">
-        <v>901</v>
+        <v>933</v>
       </c>
       <c r="G478" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="H478" t="s">
-        <v>163</v>
+        <v>129</v>
       </c>
       <c r="J478" t="s">
         <v>51</v>
@@ -11513,13 +11483,13 @@
     </row>
     <row r="479" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A479" s="1" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="G479" t="s">
-        <v>68</v>
+        <v>164</v>
       </c>
       <c r="H479" t="s">
-        <v>69</v>
+        <v>165</v>
       </c>
       <c r="J479" t="s">
         <v>51</v>
@@ -11527,13 +11497,13 @@
     </row>
     <row r="480" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A480" s="1" t="s">
-        <v>937</v>
+        <v>896</v>
       </c>
       <c r="G480" t="s">
-        <v>459</v>
+        <v>421</v>
       </c>
       <c r="H480" t="s">
-        <v>1458</v>
+        <v>422</v>
       </c>
       <c r="J480" t="s">
         <v>51</v>
@@ -11541,13 +11511,13 @@
     </row>
     <row r="481" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A481" s="1" t="s">
-        <v>895</v>
+        <v>940</v>
       </c>
       <c r="G481" t="s">
-        <v>431</v>
+        <v>758</v>
       </c>
       <c r="H481" t="s">
-        <v>432</v>
+        <v>1449</v>
       </c>
       <c r="J481" t="s">
         <v>51</v>
@@ -11555,13 +11525,13 @@
     </row>
     <row r="482" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A482" s="1" t="s">
-        <v>934</v>
+        <v>912</v>
       </c>
       <c r="G482" t="s">
-        <v>170</v>
+        <v>512</v>
       </c>
       <c r="H482" t="s">
-        <v>129</v>
+        <v>513</v>
       </c>
       <c r="J482" t="s">
         <v>51</v>
@@ -11572,10 +11542,10 @@
         <v>902</v>
       </c>
       <c r="G483" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="H483" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="J483" t="s">
         <v>51</v>
@@ -11583,13 +11553,13 @@
     </row>
     <row r="484" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A484" s="1" t="s">
-        <v>897</v>
+        <v>948</v>
       </c>
       <c r="G484" t="s">
-        <v>422</v>
+        <v>179</v>
       </c>
       <c r="H484" t="s">
-        <v>423</v>
+        <v>1450</v>
       </c>
       <c r="J484" t="s">
         <v>51</v>
@@ -11597,13 +11567,13 @@
     </row>
     <row r="485" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A485" s="1" t="s">
-        <v>941</v>
+        <v>909</v>
       </c>
       <c r="G485" t="s">
-        <v>759</v>
+        <v>413</v>
       </c>
       <c r="H485" t="s">
-        <v>1459</v>
+        <v>415</v>
       </c>
       <c r="J485" t="s">
         <v>51</v>
@@ -11611,13 +11581,13 @@
     </row>
     <row r="486" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A486" s="1" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="G486" t="s">
-        <v>513</v>
+        <v>63</v>
       </c>
       <c r="H486" t="s">
-        <v>514</v>
+        <v>64</v>
       </c>
       <c r="J486" t="s">
         <v>51</v>
@@ -11625,13 +11595,13 @@
     </row>
     <row r="487" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A487" s="1" t="s">
-        <v>903</v>
+        <v>932</v>
       </c>
       <c r="G487" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="H487" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="J487" t="s">
         <v>51</v>
@@ -11639,13 +11609,13 @@
     </row>
     <row r="488" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A488" s="1" t="s">
-        <v>949</v>
+        <v>903</v>
       </c>
       <c r="G488" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="H488" t="s">
-        <v>1460</v>
+        <v>168</v>
       </c>
       <c r="J488" t="s">
         <v>51</v>
@@ -11653,13 +11623,13 @@
     </row>
     <row r="489" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A489" s="1" t="s">
-        <v>910</v>
+        <v>946</v>
       </c>
       <c r="G489" t="s">
-        <v>414</v>
+        <v>183</v>
       </c>
       <c r="H489" t="s">
-        <v>416</v>
+        <v>1451</v>
       </c>
       <c r="J489" t="s">
         <v>51</v>
@@ -11667,13 +11637,13 @@
     </row>
     <row r="490" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A490" s="1" t="s">
-        <v>915</v>
+        <v>935</v>
       </c>
       <c r="G490" t="s">
-        <v>63</v>
+        <v>346</v>
       </c>
       <c r="H490" t="s">
-        <v>64</v>
+        <v>358</v>
       </c>
       <c r="J490" t="s">
         <v>51</v>
@@ -11681,13 +11651,13 @@
     </row>
     <row r="491" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A491" s="1" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="G491" t="s">
-        <v>179</v>
+        <v>353</v>
       </c>
       <c r="H491" t="s">
-        <v>180</v>
+        <v>354</v>
       </c>
       <c r="J491" t="s">
         <v>51</v>
@@ -11695,13 +11665,13 @@
     </row>
     <row r="492" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A492" s="1" t="s">
-        <v>904</v>
+        <v>934</v>
       </c>
       <c r="G492" t="s">
-        <v>166</v>
+        <v>346</v>
       </c>
       <c r="H492" t="s">
-        <v>168</v>
+        <v>357</v>
       </c>
       <c r="J492" t="s">
         <v>51</v>
@@ -11709,13 +11679,13 @@
     </row>
     <row r="493" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A493" s="1" t="s">
-        <v>947</v>
+        <v>891</v>
       </c>
       <c r="G493" t="s">
-        <v>183</v>
+        <v>425</v>
       </c>
       <c r="H493" t="s">
-        <v>1461</v>
+        <v>426</v>
       </c>
       <c r="J493" t="s">
         <v>51</v>
@@ -11723,13 +11693,13 @@
     </row>
     <row r="494" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A494" s="1" t="s">
-        <v>936</v>
+        <v>890</v>
       </c>
       <c r="G494" t="s">
-        <v>347</v>
+        <v>598</v>
       </c>
       <c r="H494" t="s">
-        <v>359</v>
+        <v>599</v>
       </c>
       <c r="J494" t="s">
         <v>51</v>
@@ -11737,13 +11707,13 @@
     </row>
     <row r="495" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A495" s="1" t="s">
-        <v>930</v>
+        <v>924</v>
       </c>
       <c r="G495" t="s">
-        <v>354</v>
+        <v>177</v>
       </c>
       <c r="H495" t="s">
-        <v>355</v>
+        <v>178</v>
       </c>
       <c r="J495" t="s">
         <v>51</v>
@@ -11751,13 +11721,13 @@
     </row>
     <row r="496" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A496" s="1" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
       <c r="G496" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="H496" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="J496" t="s">
         <v>51</v>
@@ -11765,13 +11735,13 @@
     </row>
     <row r="497" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A497" s="1" t="s">
-        <v>892</v>
+        <v>1340</v>
       </c>
       <c r="G497" t="s">
-        <v>426</v>
+        <v>779</v>
       </c>
       <c r="H497" t="s">
-        <v>427</v>
+        <v>1392</v>
       </c>
       <c r="J497" t="s">
         <v>51</v>
@@ -11779,13 +11749,13 @@
     </row>
     <row r="498" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A498" s="1" t="s">
-        <v>891</v>
+        <v>910</v>
       </c>
       <c r="G498" t="s">
-        <v>599</v>
+        <v>413</v>
       </c>
       <c r="H498" t="s">
-        <v>600</v>
+        <v>420</v>
       </c>
       <c r="J498" t="s">
         <v>51</v>
@@ -11793,13 +11763,13 @@
     </row>
     <row r="499" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A499" s="1" t="s">
-        <v>925</v>
+        <v>919</v>
       </c>
       <c r="G499" t="s">
-        <v>177</v>
+        <v>459</v>
       </c>
       <c r="H499" t="s">
-        <v>178</v>
+        <v>460</v>
       </c>
       <c r="J499" t="s">
         <v>51</v>
@@ -11807,13 +11777,13 @@
     </row>
     <row r="500" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A500" s="1" t="s">
-        <v>932</v>
+        <v>923</v>
       </c>
       <c r="G500" t="s">
-        <v>350</v>
+        <v>169</v>
       </c>
       <c r="H500" t="s">
-        <v>351</v>
+        <v>171</v>
       </c>
       <c r="J500" t="s">
         <v>51</v>
@@ -11821,13 +11791,13 @@
     </row>
     <row r="501" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A501" s="1" t="s">
-        <v>1346</v>
+        <v>898</v>
       </c>
       <c r="G501" t="s">
-        <v>780</v>
+        <v>160</v>
       </c>
       <c r="H501" t="s">
-        <v>1399</v>
+        <v>161</v>
       </c>
       <c r="J501" t="s">
         <v>51</v>
@@ -11835,13 +11805,13 @@
     </row>
     <row r="502" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A502" s="1" t="s">
-        <v>911</v>
+        <v>926</v>
       </c>
       <c r="G502" t="s">
-        <v>414</v>
+        <v>175</v>
       </c>
       <c r="H502" t="s">
-        <v>421</v>
+        <v>176</v>
       </c>
       <c r="J502" t="s">
         <v>51</v>
@@ -11849,13 +11819,13 @@
     </row>
     <row r="503" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A503" s="1" t="s">
-        <v>920</v>
+        <v>883</v>
       </c>
       <c r="G503" t="s">
-        <v>460</v>
+        <v>58</v>
       </c>
       <c r="H503" t="s">
-        <v>461</v>
+        <v>59</v>
       </c>
       <c r="J503" t="s">
         <v>51</v>
@@ -11863,13 +11833,13 @@
     </row>
     <row r="504" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A504" s="1" t="s">
-        <v>924</v>
+        <v>949</v>
       </c>
       <c r="G504" t="s">
-        <v>169</v>
+        <v>785</v>
       </c>
       <c r="H504" t="s">
-        <v>171</v>
+        <v>1452</v>
       </c>
       <c r="J504" t="s">
         <v>51</v>
@@ -11877,13 +11847,13 @@
     </row>
     <row r="505" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A505" s="1" t="s">
-        <v>899</v>
+        <v>878</v>
       </c>
       <c r="G505" t="s">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="H505" t="s">
-        <v>161</v>
+        <v>249</v>
       </c>
       <c r="J505" t="s">
         <v>51</v>
@@ -11891,13 +11861,13 @@
     </row>
     <row r="506" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A506" s="1" t="s">
-        <v>927</v>
+        <v>881</v>
       </c>
       <c r="G506" t="s">
-        <v>175</v>
+        <v>52</v>
       </c>
       <c r="H506" t="s">
-        <v>176</v>
+        <v>53</v>
       </c>
       <c r="J506" t="s">
         <v>51</v>
@@ -11905,13 +11875,13 @@
     </row>
     <row r="507" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A507" s="1" t="s">
-        <v>884</v>
+        <v>915</v>
       </c>
       <c r="G507" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="H507" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J507" t="s">
         <v>51</v>
@@ -11919,13 +11889,13 @@
     </row>
     <row r="508" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A508" s="1" t="s">
-        <v>950</v>
+        <v>1341</v>
       </c>
       <c r="G508" t="s">
-        <v>786</v>
+        <v>776</v>
       </c>
       <c r="H508" t="s">
-        <v>1462</v>
+        <v>1393</v>
       </c>
       <c r="J508" t="s">
         <v>51</v>
@@ -11933,13 +11903,13 @@
     </row>
     <row r="509" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A509" s="1" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="G509" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="H509" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="J509" t="s">
         <v>51</v>
@@ -11947,13 +11917,13 @@
     </row>
     <row r="510" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A510" s="1" t="s">
-        <v>882</v>
+        <v>925</v>
       </c>
       <c r="G510" t="s">
-        <v>52</v>
+        <v>169</v>
       </c>
       <c r="H510" t="s">
-        <v>53</v>
+        <v>172</v>
       </c>
       <c r="J510" t="s">
         <v>51</v>
@@ -11961,13 +11931,13 @@
     </row>
     <row r="511" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A511" s="1" t="s">
-        <v>916</v>
+        <v>942</v>
       </c>
       <c r="G511" t="s">
-        <v>52</v>
+        <v>759</v>
       </c>
       <c r="H511" t="s">
-        <v>60</v>
+        <v>1422</v>
       </c>
       <c r="J511" t="s">
         <v>51</v>
@@ -11975,13 +11945,13 @@
     </row>
     <row r="512" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A512" s="1" t="s">
-        <v>1347</v>
+        <v>939</v>
       </c>
       <c r="G512" t="s">
-        <v>777</v>
+        <v>756</v>
       </c>
       <c r="H512" t="s">
-        <v>1400</v>
+        <v>1453</v>
       </c>
       <c r="J512" t="s">
         <v>51</v>
@@ -11989,13 +11959,13 @@
     </row>
     <row r="513" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A513" s="1" t="s">
-        <v>878</v>
+        <v>918</v>
       </c>
       <c r="G513" t="s">
-        <v>248</v>
+        <v>458</v>
       </c>
       <c r="H513" t="s">
-        <v>255</v>
+        <v>461</v>
       </c>
       <c r="J513" t="s">
         <v>51</v>
@@ -12003,13 +11973,13 @@
     </row>
     <row r="514" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A514" s="1" t="s">
-        <v>926</v>
+        <v>913</v>
       </c>
       <c r="G514" t="s">
-        <v>169</v>
+        <v>204</v>
       </c>
       <c r="H514" t="s">
-        <v>172</v>
+        <v>205</v>
       </c>
       <c r="J514" t="s">
         <v>51</v>
@@ -12017,13 +11987,13 @@
     </row>
     <row r="515" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A515" s="1" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
       <c r="G515" t="s">
-        <v>760</v>
+        <v>752</v>
       </c>
       <c r="H515" t="s">
-        <v>1432</v>
+        <v>1454</v>
       </c>
       <c r="J515" t="s">
         <v>51</v>
@@ -12031,13 +12001,13 @@
     </row>
     <row r="516" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A516" s="1" t="s">
-        <v>940</v>
+        <v>1342</v>
       </c>
       <c r="G516" t="s">
-        <v>757</v>
+        <v>346</v>
       </c>
       <c r="H516" t="s">
-        <v>1463</v>
+        <v>1394</v>
       </c>
       <c r="J516" t="s">
         <v>51</v>
@@ -12045,13 +12015,13 @@
     </row>
     <row r="517" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A517" s="1" t="s">
-        <v>919</v>
+        <v>950</v>
       </c>
       <c r="G517" t="s">
-        <v>459</v>
+        <v>1362</v>
       </c>
       <c r="H517" t="s">
-        <v>462</v>
+        <v>1455</v>
       </c>
       <c r="J517" t="s">
         <v>51</v>
@@ -12059,13 +12029,13 @@
     </row>
     <row r="518" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A518" s="1" t="s">
-        <v>914</v>
+        <v>947</v>
       </c>
       <c r="G518" t="s">
-        <v>204</v>
+        <v>782</v>
       </c>
       <c r="H518" t="s">
-        <v>205</v>
+        <v>1456</v>
       </c>
       <c r="J518" t="s">
         <v>51</v>
@@ -12073,13 +12043,13 @@
     </row>
     <row r="519" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A519" s="1" t="s">
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="G519" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="H519" t="s">
-        <v>1464</v>
+        <v>1457</v>
       </c>
       <c r="J519" t="s">
         <v>51</v>
@@ -12087,13 +12057,13 @@
     </row>
     <row r="520" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A520" s="1" t="s">
-        <v>1348</v>
+        <v>941</v>
       </c>
       <c r="G520" t="s">
-        <v>347</v>
+        <v>52</v>
       </c>
       <c r="H520" t="s">
-        <v>1401</v>
+        <v>1458</v>
       </c>
       <c r="J520" t="s">
         <v>51</v>
@@ -12101,13 +12071,13 @@
     </row>
     <row r="521" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A521" s="1" t="s">
-        <v>951</v>
+        <v>879</v>
       </c>
       <c r="G521" t="s">
-        <v>1369</v>
+        <v>250</v>
       </c>
       <c r="H521" t="s">
-        <v>1465</v>
+        <v>251</v>
       </c>
       <c r="J521" t="s">
         <v>51</v>
@@ -12115,13 +12085,13 @@
     </row>
     <row r="522" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A522" s="1" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="G522" t="s">
-        <v>783</v>
+        <v>769</v>
       </c>
       <c r="H522" t="s">
-        <v>1466</v>
+        <v>1459</v>
       </c>
       <c r="J522" t="s">
         <v>51</v>
@@ -12129,13 +12099,13 @@
     </row>
     <row r="523" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A523" s="1" t="s">
-        <v>944</v>
+        <v>884</v>
       </c>
       <c r="G523" t="s">
-        <v>761</v>
+        <v>620</v>
       </c>
       <c r="H523" t="s">
-        <v>1467</v>
+        <v>621</v>
       </c>
       <c r="J523" t="s">
         <v>51</v>
@@ -12143,13 +12113,13 @@
     </row>
     <row r="524" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A524" s="1" t="s">
-        <v>942</v>
+        <v>1343</v>
       </c>
       <c r="G524" t="s">
-        <v>52</v>
+        <v>777</v>
       </c>
       <c r="H524" t="s">
-        <v>1468</v>
+        <v>1395</v>
       </c>
       <c r="J524" t="s">
         <v>51</v>
@@ -12157,13 +12127,13 @@
     </row>
     <row r="525" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A525" s="1" t="s">
-        <v>880</v>
+        <v>944</v>
       </c>
       <c r="G525" t="s">
-        <v>251</v>
+        <v>767</v>
       </c>
       <c r="H525" t="s">
-        <v>252</v>
+        <v>1460</v>
       </c>
       <c r="J525" t="s">
         <v>51</v>
@@ -12171,13 +12141,13 @@
     </row>
     <row r="526" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A526" s="1" t="s">
-        <v>946</v>
+        <v>1344</v>
       </c>
       <c r="G526" t="s">
-        <v>770</v>
+        <v>778</v>
       </c>
       <c r="H526" t="s">
-        <v>1469</v>
+        <v>1396</v>
       </c>
       <c r="J526" t="s">
         <v>51</v>
@@ -12185,13 +12155,13 @@
     </row>
     <row r="527" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A527" s="1" t="s">
-        <v>885</v>
+        <v>937</v>
       </c>
       <c r="G527" t="s">
-        <v>621</v>
+        <v>751</v>
       </c>
       <c r="H527" t="s">
-        <v>622</v>
+        <v>1422</v>
       </c>
       <c r="J527" t="s">
         <v>51</v>
@@ -12199,13 +12169,13 @@
     </row>
     <row r="528" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A528" s="1" t="s">
-        <v>1349</v>
+        <v>916</v>
       </c>
       <c r="G528" t="s">
-        <v>778</v>
+        <v>54</v>
       </c>
       <c r="H528" t="s">
-        <v>1402</v>
+        <v>55</v>
       </c>
       <c r="J528" t="s">
         <v>51</v>
@@ -12213,13 +12183,13 @@
     </row>
     <row r="529" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A529" s="1" t="s">
-        <v>945</v>
+        <v>917</v>
       </c>
       <c r="G529" t="s">
-        <v>768</v>
+        <v>56</v>
       </c>
       <c r="H529" t="s">
-        <v>1470</v>
+        <v>57</v>
       </c>
       <c r="J529" t="s">
         <v>51</v>
@@ -12227,71 +12197,15 @@
     </row>
     <row r="530" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A530" s="1" t="s">
-        <v>1350</v>
+        <v>911</v>
       </c>
       <c r="G530" t="s">
-        <v>779</v>
+        <v>166</v>
       </c>
       <c r="H530" t="s">
-        <v>1403</v>
+        <v>167</v>
       </c>
       <c r="J530" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="531" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A531" s="1" t="s">
-        <v>938</v>
-      </c>
-      <c r="G531" t="s">
-        <v>752</v>
-      </c>
-      <c r="H531" t="s">
-        <v>1432</v>
-      </c>
-      <c r="J531" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="532" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A532" s="1" t="s">
-        <v>917</v>
-      </c>
-      <c r="G532" t="s">
-        <v>54</v>
-      </c>
-      <c r="H532" t="s">
-        <v>55</v>
-      </c>
-      <c r="J532" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="533" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A533" s="1" t="s">
-        <v>918</v>
-      </c>
-      <c r="G533" t="s">
-        <v>56</v>
-      </c>
-      <c r="H533" t="s">
-        <v>57</v>
-      </c>
-      <c r="J533" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="534" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A534" s="1" t="s">
-        <v>912</v>
-      </c>
-      <c r="G534" t="s">
-        <v>166</v>
-      </c>
-      <c r="H534" t="s">
-        <v>167</v>
-      </c>
-      <c r="J534" t="s">
         <v>51</v>
       </c>
     </row>

--- a/input/lista/1 LISTA PDV ENI 2.xlsx
+++ b/input/lista/1 LISTA PDV ENI 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nadir\Desktop\APP TELEPASS\FILE FISSI\lista\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80D1C2A0-0396-4067-AE4B-C399FBEC8622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44333557-B573-4DBF-8793-4E3BA127AB5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{D320C423-4B98-4D55-B6E8-3ABF0EE22191}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2119" uniqueCount="1462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2115" uniqueCount="1459">
   <si>
     <t>ALESSANDRIA</t>
   </si>
@@ -3960,9 +3960,6 @@
     <t>3775</t>
   </si>
   <si>
-    <t>1858</t>
-  </si>
-  <si>
     <t>7224</t>
   </si>
   <si>
@@ -4095,9 +4092,6 @@
     <t>SAN GIOVANNI LUPATOTO</t>
   </si>
   <si>
-    <t>BREGNANO</t>
-  </si>
-  <si>
     <t>PORTO SAN GIORGIO</t>
   </si>
   <si>
@@ -4273,9 +4267,6 @@
   </si>
   <si>
     <t>VIA NOVARA</t>
-  </si>
-  <si>
-    <t>STRADA PROVINC.LE 31</t>
   </si>
   <si>
     <t>Via Casilina, 1423</t>
@@ -4781,7 +4772,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{175EF563-0873-44BA-ACAF-2DC290E6A803}">
-  <dimension ref="A1:J530"/>
+  <dimension ref="A1:J529"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="29.44140625" bestFit="1" customWidth="1"/>
@@ -5077,7 +5068,7 @@
         <v>230</v>
       </c>
       <c r="H21" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="J21" t="s">
         <v>34</v>
@@ -5245,7 +5236,7 @@
         <v>1127</v>
       </c>
       <c r="H33" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="J33" t="s">
         <v>34</v>
@@ -5385,7 +5376,7 @@
         <v>228</v>
       </c>
       <c r="H43" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="J43" t="s">
         <v>34</v>
@@ -5483,7 +5474,7 @@
         <v>330</v>
       </c>
       <c r="H50" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="J50" t="s">
         <v>34</v>
@@ -5525,7 +5516,7 @@
         <v>98</v>
       </c>
       <c r="H53" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="J53" t="s">
         <v>34</v>
@@ -5609,7 +5600,7 @@
         <v>98</v>
       </c>
       <c r="H59" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="J59" t="s">
         <v>34</v>
@@ -5665,7 +5656,7 @@
         <v>757</v>
       </c>
       <c r="H63" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="J63" t="s">
         <v>34</v>
@@ -5721,7 +5712,7 @@
         <v>765</v>
       </c>
       <c r="H67" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="J67" t="s">
         <v>34</v>
@@ -5735,7 +5726,7 @@
         <v>316</v>
       </c>
       <c r="H68" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="J68" t="s">
         <v>34</v>
@@ -5763,7 +5754,7 @@
         <v>612</v>
       </c>
       <c r="H70" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="J70" t="s">
         <v>34</v>
@@ -5777,7 +5768,7 @@
         <v>1131</v>
       </c>
       <c r="H71" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="J71" t="s">
         <v>34</v>
@@ -5791,7 +5782,7 @@
         <v>775</v>
       </c>
       <c r="H72" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="J72" t="s">
         <v>34</v>
@@ -5858,10 +5849,10 @@
         <v>1125</v>
       </c>
       <c r="G77" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H77" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="J77" t="s">
         <v>34</v>
@@ -5875,7 +5866,7 @@
         <v>753</v>
       </c>
       <c r="H78" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="J78" t="s">
         <v>34</v>
@@ -6141,7 +6132,7 @@
         <v>527</v>
       </c>
       <c r="H97" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="J97" t="s">
         <v>31</v>
@@ -6169,7 +6160,7 @@
         <v>1130</v>
       </c>
       <c r="H99" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="J99" t="s">
         <v>31</v>
@@ -6348,10 +6339,10 @@
         <v>870</v>
       </c>
       <c r="G112" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="H112" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="J112" t="s">
         <v>31</v>
@@ -6771,7 +6762,7 @@
         <v>436</v>
       </c>
       <c r="H142" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="J142" t="s">
         <v>31</v>
@@ -6785,7 +6776,7 @@
         <v>655</v>
       </c>
       <c r="H143" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="J143" t="s">
         <v>31</v>
@@ -6852,10 +6843,10 @@
         <v>1301</v>
       </c>
       <c r="G148" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="H148" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="J148" t="s">
         <v>31</v>
@@ -6992,10 +6983,10 @@
         <v>873</v>
       </c>
       <c r="G158" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="H158" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="J158" t="s">
         <v>31</v>
@@ -7107,7 +7098,7 @@
         <v>755</v>
       </c>
       <c r="H166" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="J166" t="s">
         <v>31</v>
@@ -7174,10 +7165,10 @@
         <v>1302</v>
       </c>
       <c r="G171" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="H171" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="J171" t="s">
         <v>31</v>
@@ -7247,7 +7238,7 @@
         <v>772</v>
       </c>
       <c r="H176" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="J176" t="s">
         <v>31</v>
@@ -7275,7 +7266,7 @@
         <v>634</v>
       </c>
       <c r="H178" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="J178" t="s">
         <v>31</v>
@@ -7303,7 +7294,7 @@
         <v>639</v>
       </c>
       <c r="H180" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="J180" t="s">
         <v>31</v>
@@ -7345,7 +7336,7 @@
         <v>784</v>
       </c>
       <c r="H183" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="J183" t="s">
         <v>31</v>
@@ -7359,7 +7350,7 @@
         <v>762</v>
       </c>
       <c r="H184" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="J184" t="s">
         <v>31</v>
@@ -7373,7 +7364,7 @@
         <v>224</v>
       </c>
       <c r="H185" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="J185" t="s">
         <v>31</v>
@@ -7398,10 +7389,10 @@
         <v>1305</v>
       </c>
       <c r="G187" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="H187" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="J187" t="s">
         <v>31</v>
@@ -7426,10 +7417,10 @@
         <v>1306</v>
       </c>
       <c r="G189" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="H189" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="J189" t="s">
         <v>31</v>
@@ -7440,10 +7431,10 @@
         <v>1307</v>
       </c>
       <c r="G190" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="H190" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="J190" t="s">
         <v>31</v>
@@ -7451,27 +7442,27 @@
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A191" s="1" t="s">
-        <v>1308</v>
+        <v>1218</v>
       </c>
       <c r="G191" t="s">
-        <v>1353</v>
+        <v>547</v>
       </c>
       <c r="H191" t="s">
-        <v>1413</v>
+        <v>560</v>
       </c>
       <c r="J191" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
-        <v>1218</v>
+        <v>1209</v>
       </c>
       <c r="G192" t="s">
-        <v>547</v>
+        <v>565</v>
       </c>
       <c r="H192" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="J192" t="s">
         <v>14</v>
@@ -7479,13 +7470,13 @@
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A193" s="1" t="s">
-        <v>1209</v>
+        <v>1228</v>
       </c>
       <c r="G193" t="s">
-        <v>565</v>
+        <v>547</v>
       </c>
       <c r="H193" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="J193" t="s">
         <v>14</v>
@@ -7493,13 +7484,13 @@
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
-        <v>1228</v>
+        <v>1246</v>
       </c>
       <c r="G194" t="s">
-        <v>547</v>
+        <v>188</v>
       </c>
       <c r="H194" t="s">
-        <v>572</v>
+        <v>189</v>
       </c>
       <c r="J194" t="s">
         <v>14</v>
@@ -7507,13 +7498,13 @@
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A195" s="1" t="s">
-        <v>1246</v>
+        <v>1237</v>
       </c>
       <c r="G195" t="s">
-        <v>188</v>
+        <v>484</v>
       </c>
       <c r="H195" t="s">
-        <v>189</v>
+        <v>485</v>
       </c>
       <c r="J195" t="s">
         <v>14</v>
@@ -7521,13 +7512,13 @@
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
-        <v>1237</v>
+        <v>1220</v>
       </c>
       <c r="G196" t="s">
-        <v>484</v>
+        <v>561</v>
       </c>
       <c r="H196" t="s">
-        <v>485</v>
+        <v>562</v>
       </c>
       <c r="J196" t="s">
         <v>14</v>
@@ -7535,13 +7526,13 @@
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="s">
-        <v>1220</v>
+        <v>1258</v>
       </c>
       <c r="G197" t="s">
-        <v>561</v>
+        <v>27</v>
       </c>
       <c r="H197" t="s">
-        <v>562</v>
+        <v>28</v>
       </c>
       <c r="J197" t="s">
         <v>14</v>
@@ -7549,13 +7540,13 @@
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="s">
-        <v>1258</v>
+        <v>1271</v>
       </c>
       <c r="G198" t="s">
-        <v>27</v>
+        <v>225</v>
       </c>
       <c r="H198" t="s">
-        <v>28</v>
+        <v>226</v>
       </c>
       <c r="J198" t="s">
         <v>14</v>
@@ -7563,13 +7554,13 @@
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A199" s="1" t="s">
-        <v>1271</v>
+        <v>1233</v>
       </c>
       <c r="G199" t="s">
-        <v>225</v>
+        <v>547</v>
       </c>
       <c r="H199" t="s">
-        <v>226</v>
+        <v>578</v>
       </c>
       <c r="J199" t="s">
         <v>14</v>
@@ -7577,13 +7568,13 @@
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
-        <v>1233</v>
+        <v>1268</v>
       </c>
       <c r="G200" t="s">
-        <v>547</v>
+        <v>478</v>
       </c>
       <c r="H200" t="s">
-        <v>578</v>
+        <v>479</v>
       </c>
       <c r="J200" t="s">
         <v>14</v>
@@ -7591,13 +7582,13 @@
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A201" s="1" t="s">
-        <v>1268</v>
+        <v>1234</v>
       </c>
       <c r="G201" t="s">
-        <v>478</v>
+        <v>547</v>
       </c>
       <c r="H201" t="s">
-        <v>479</v>
+        <v>580</v>
       </c>
       <c r="J201" t="s">
         <v>14</v>
@@ -7605,13 +7596,13 @@
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
-        <v>1234</v>
+        <v>1210</v>
       </c>
       <c r="G202" t="s">
-        <v>547</v>
+        <v>585</v>
       </c>
       <c r="H202" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="J202" t="s">
         <v>14</v>
@@ -7619,13 +7610,13 @@
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A203" s="1" t="s">
-        <v>1210</v>
+        <v>1219</v>
       </c>
       <c r="G203" t="s">
-        <v>585</v>
+        <v>547</v>
       </c>
       <c r="H203" t="s">
-        <v>586</v>
+        <v>556</v>
       </c>
       <c r="J203" t="s">
         <v>14</v>
@@ -7633,13 +7624,13 @@
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
-        <v>1219</v>
+        <v>1261</v>
       </c>
       <c r="G204" t="s">
-        <v>547</v>
+        <v>23</v>
       </c>
       <c r="H204" t="s">
-        <v>556</v>
+        <v>24</v>
       </c>
       <c r="J204" t="s">
         <v>14</v>
@@ -7647,13 +7638,13 @@
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A205" s="1" t="s">
-        <v>1261</v>
+        <v>1269</v>
       </c>
       <c r="G205" t="s">
-        <v>23</v>
+        <v>335</v>
       </c>
       <c r="H205" t="s">
-        <v>24</v>
+        <v>336</v>
       </c>
       <c r="J205" t="s">
         <v>14</v>
@@ -7661,13 +7652,13 @@
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
-        <v>1269</v>
+        <v>1259</v>
       </c>
       <c r="G206" t="s">
-        <v>335</v>
+        <v>482</v>
       </c>
       <c r="H206" t="s">
-        <v>336</v>
+        <v>483</v>
       </c>
       <c r="J206" t="s">
         <v>14</v>
@@ -7675,13 +7666,13 @@
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A207" s="1" t="s">
-        <v>1259</v>
+        <v>1249</v>
       </c>
       <c r="G207" t="s">
-        <v>482</v>
+        <v>261</v>
       </c>
       <c r="H207" t="s">
-        <v>483</v>
+        <v>262</v>
       </c>
       <c r="J207" t="s">
         <v>14</v>
@@ -7689,13 +7680,13 @@
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
-        <v>1249</v>
+        <v>1243</v>
       </c>
       <c r="G208" t="s">
-        <v>261</v>
+        <v>300</v>
       </c>
       <c r="H208" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="J208" t="s">
         <v>14</v>
@@ -7703,13 +7694,13 @@
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="s">
-        <v>1243</v>
+        <v>1248</v>
       </c>
       <c r="G209" t="s">
-        <v>300</v>
+        <v>154</v>
       </c>
       <c r="H209" t="s">
-        <v>301</v>
+        <v>155</v>
       </c>
       <c r="J209" t="s">
         <v>14</v>
@@ -7717,13 +7708,13 @@
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
-        <v>1248</v>
+        <v>1216</v>
       </c>
       <c r="G210" t="s">
-        <v>154</v>
+        <v>549</v>
       </c>
       <c r="H210" t="s">
-        <v>155</v>
+        <v>550</v>
       </c>
       <c r="J210" t="s">
         <v>14</v>
@@ -7731,13 +7722,13 @@
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A211" s="1" t="s">
-        <v>1216</v>
+        <v>1238</v>
       </c>
       <c r="G211" t="s">
-        <v>549</v>
+        <v>626</v>
       </c>
       <c r="H211" t="s">
-        <v>550</v>
+        <v>627</v>
       </c>
       <c r="J211" t="s">
         <v>14</v>
@@ -7745,13 +7736,13 @@
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="s">
-        <v>1238</v>
+        <v>1250</v>
       </c>
       <c r="G212" t="s">
-        <v>626</v>
+        <v>269</v>
       </c>
       <c r="H212" t="s">
-        <v>627</v>
+        <v>270</v>
       </c>
       <c r="J212" t="s">
         <v>14</v>
@@ -7759,13 +7750,13 @@
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A213" s="1" t="s">
-        <v>1250</v>
+        <v>1239</v>
       </c>
       <c r="G213" t="s">
-        <v>269</v>
+        <v>628</v>
       </c>
       <c r="H213" t="s">
-        <v>270</v>
+        <v>629</v>
       </c>
       <c r="J213" t="s">
         <v>14</v>
@@ -7773,13 +7764,13 @@
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
-        <v>1239</v>
+        <v>1247</v>
       </c>
       <c r="G214" t="s">
-        <v>628</v>
+        <v>186</v>
       </c>
       <c r="H214" t="s">
-        <v>629</v>
+        <v>187</v>
       </c>
       <c r="J214" t="s">
         <v>14</v>
@@ -7787,13 +7778,13 @@
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A215" s="1" t="s">
-        <v>1247</v>
+        <v>1273</v>
       </c>
       <c r="G215" t="s">
-        <v>186</v>
+        <v>334</v>
       </c>
       <c r="H215" t="s">
-        <v>187</v>
+        <v>280</v>
       </c>
       <c r="J215" t="s">
         <v>14</v>
@@ -7801,13 +7792,13 @@
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
-        <v>1273</v>
+        <v>1242</v>
       </c>
       <c r="G216" t="s">
-        <v>334</v>
+        <v>623</v>
       </c>
       <c r="H216" t="s">
-        <v>280</v>
+        <v>624</v>
       </c>
       <c r="J216" t="s">
         <v>14</v>
@@ -7815,13 +7806,13 @@
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A217" s="1" t="s">
-        <v>1242</v>
+        <v>1215</v>
       </c>
       <c r="G217" t="s">
-        <v>623</v>
+        <v>746</v>
       </c>
       <c r="H217" t="s">
-        <v>624</v>
+        <v>747</v>
       </c>
       <c r="J217" t="s">
         <v>14</v>
@@ -7829,13 +7820,13 @@
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
-        <v>1215</v>
+        <v>1241</v>
       </c>
       <c r="G218" t="s">
-        <v>746</v>
+        <v>185</v>
       </c>
       <c r="H218" t="s">
-        <v>747</v>
+        <v>192</v>
       </c>
       <c r="J218" t="s">
         <v>14</v>
@@ -7843,13 +7834,13 @@
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A219" s="1" t="s">
-        <v>1241</v>
+        <v>1224</v>
       </c>
       <c r="G219" t="s">
-        <v>185</v>
+        <v>547</v>
       </c>
       <c r="H219" t="s">
-        <v>192</v>
+        <v>571</v>
       </c>
       <c r="J219" t="s">
         <v>14</v>
@@ -7857,13 +7848,13 @@
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="G220" t="s">
-        <v>547</v>
+        <v>569</v>
       </c>
       <c r="H220" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="J220" t="s">
         <v>14</v>
@@ -7871,13 +7862,13 @@
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A221" s="1" t="s">
-        <v>1223</v>
+        <v>1236</v>
       </c>
       <c r="G221" t="s">
-        <v>569</v>
+        <v>474</v>
       </c>
       <c r="H221" t="s">
-        <v>570</v>
+        <v>477</v>
       </c>
       <c r="J221" t="s">
         <v>14</v>
@@ -7885,13 +7876,13 @@
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="s">
-        <v>1236</v>
+        <v>1222</v>
       </c>
       <c r="G222" t="s">
-        <v>474</v>
+        <v>547</v>
       </c>
       <c r="H222" t="s">
-        <v>477</v>
+        <v>592</v>
       </c>
       <c r="J222" t="s">
         <v>14</v>
@@ -7899,13 +7890,13 @@
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A223" s="1" t="s">
-        <v>1222</v>
+        <v>1244</v>
       </c>
       <c r="G223" t="s">
-        <v>547</v>
+        <v>153</v>
       </c>
       <c r="H223" t="s">
-        <v>592</v>
+        <v>156</v>
       </c>
       <c r="J223" t="s">
         <v>14</v>
@@ -7913,13 +7904,13 @@
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="s">
-        <v>1244</v>
+        <v>1221</v>
       </c>
       <c r="G224" t="s">
-        <v>153</v>
+        <v>547</v>
       </c>
       <c r="H224" t="s">
-        <v>156</v>
+        <v>567</v>
       </c>
       <c r="J224" t="s">
         <v>14</v>
@@ -7927,13 +7918,13 @@
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A225" s="1" t="s">
-        <v>1221</v>
+        <v>1287</v>
       </c>
       <c r="G225" t="s">
         <v>547</v>
       </c>
       <c r="H225" t="s">
-        <v>567</v>
+        <v>1411</v>
       </c>
       <c r="J225" t="s">
         <v>14</v>
@@ -7941,13 +7932,13 @@
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
-        <v>1287</v>
+        <v>1276</v>
       </c>
       <c r="G226" t="s">
-        <v>547</v>
+        <v>1290</v>
       </c>
       <c r="H226" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="J226" t="s">
         <v>14</v>
@@ -7955,13 +7946,13 @@
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="s">
-        <v>1276</v>
+        <v>1240</v>
       </c>
       <c r="G227" t="s">
-        <v>1290</v>
+        <v>622</v>
       </c>
       <c r="H227" t="s">
-        <v>1415</v>
+        <v>625</v>
       </c>
       <c r="J227" t="s">
         <v>14</v>
@@ -7969,13 +7960,13 @@
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
-        <v>1240</v>
+        <v>1260</v>
       </c>
       <c r="G228" t="s">
-        <v>622</v>
+        <v>12</v>
       </c>
       <c r="H228" t="s">
-        <v>625</v>
+        <v>13</v>
       </c>
       <c r="J228" t="s">
         <v>14</v>
@@ -7983,13 +7974,13 @@
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A229" s="1" t="s">
-        <v>1260</v>
+        <v>1245</v>
       </c>
       <c r="G229" t="s">
-        <v>12</v>
+        <v>302</v>
       </c>
       <c r="H229" t="s">
-        <v>13</v>
+        <v>303</v>
       </c>
       <c r="J229" t="s">
         <v>14</v>
@@ -7997,13 +7988,13 @@
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="s">
-        <v>1245</v>
+        <v>1214</v>
       </c>
       <c r="G230" t="s">
-        <v>302</v>
+        <v>573</v>
       </c>
       <c r="H230" t="s">
-        <v>303</v>
+        <v>574</v>
       </c>
       <c r="J230" t="s">
         <v>14</v>
@@ -8011,13 +8002,13 @@
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A231" s="1" t="s">
-        <v>1214</v>
+        <v>1308</v>
       </c>
       <c r="G231" t="s">
-        <v>573</v>
+        <v>547</v>
       </c>
       <c r="H231" t="s">
-        <v>574</v>
+        <v>1375</v>
       </c>
       <c r="J231" t="s">
         <v>14</v>
@@ -8025,13 +8016,13 @@
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="s">
-        <v>1309</v>
+        <v>1254</v>
       </c>
       <c r="G232" t="s">
-        <v>547</v>
+        <v>304</v>
       </c>
       <c r="H232" t="s">
-        <v>1377</v>
+        <v>307</v>
       </c>
       <c r="J232" t="s">
         <v>14</v>
@@ -8039,13 +8030,13 @@
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A233" s="1" t="s">
-        <v>1254</v>
+        <v>1262</v>
       </c>
       <c r="G233" t="s">
-        <v>304</v>
+        <v>17</v>
       </c>
       <c r="H233" t="s">
-        <v>307</v>
+        <v>18</v>
       </c>
       <c r="J233" t="s">
         <v>14</v>
@@ -8053,13 +8044,13 @@
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="s">
-        <v>1262</v>
+        <v>1253</v>
       </c>
       <c r="G234" t="s">
-        <v>17</v>
+        <v>263</v>
       </c>
       <c r="H234" t="s">
-        <v>18</v>
+        <v>264</v>
       </c>
       <c r="J234" t="s">
         <v>14</v>
@@ -8067,13 +8058,13 @@
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A235" s="1" t="s">
-        <v>1253</v>
+        <v>1270</v>
       </c>
       <c r="G235" t="s">
-        <v>263</v>
+        <v>41</v>
       </c>
       <c r="H235" t="s">
-        <v>264</v>
+        <v>42</v>
       </c>
       <c r="J235" t="s">
         <v>14</v>
@@ -8081,13 +8072,13 @@
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="s">
-        <v>1270</v>
+        <v>1212</v>
       </c>
       <c r="G236" t="s">
-        <v>41</v>
+        <v>563</v>
       </c>
       <c r="H236" t="s">
-        <v>42</v>
+        <v>564</v>
       </c>
       <c r="J236" t="s">
         <v>14</v>
@@ -8095,13 +8086,13 @@
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A237" s="1" t="s">
-        <v>1212</v>
+        <v>1274</v>
       </c>
       <c r="G237" t="s">
-        <v>563</v>
+        <v>40</v>
       </c>
       <c r="H237" t="s">
-        <v>564</v>
+        <v>43</v>
       </c>
       <c r="J237" t="s">
         <v>14</v>
@@ -8109,13 +8100,13 @@
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
       <c r="G238" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="H238" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="J238" t="s">
         <v>14</v>
@@ -8123,13 +8114,13 @@
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A239" s="1" t="s">
-        <v>1266</v>
+        <v>1217</v>
       </c>
       <c r="G239" t="s">
-        <v>25</v>
+        <v>748</v>
       </c>
       <c r="H239" t="s">
-        <v>26</v>
+        <v>749</v>
       </c>
       <c r="J239" t="s">
         <v>14</v>
@@ -8137,13 +8128,13 @@
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A240" s="1" t="s">
-        <v>1217</v>
+        <v>1252</v>
       </c>
       <c r="G240" t="s">
-        <v>748</v>
+        <v>265</v>
       </c>
       <c r="H240" t="s">
-        <v>749</v>
+        <v>266</v>
       </c>
       <c r="J240" t="s">
         <v>14</v>
@@ -8151,13 +8142,13 @@
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A241" s="1" t="s">
-        <v>1252</v>
+        <v>1211</v>
       </c>
       <c r="G241" t="s">
-        <v>265</v>
+        <v>547</v>
       </c>
       <c r="H241" t="s">
-        <v>266</v>
+        <v>587</v>
       </c>
       <c r="J241" t="s">
         <v>14</v>
@@ -8165,13 +8156,13 @@
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="s">
-        <v>1211</v>
+        <v>1251</v>
       </c>
       <c r="G242" t="s">
-        <v>547</v>
+        <v>267</v>
       </c>
       <c r="H242" t="s">
-        <v>587</v>
+        <v>268</v>
       </c>
       <c r="J242" t="s">
         <v>14</v>
@@ -8179,13 +8170,13 @@
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A243" s="1" t="s">
-        <v>1251</v>
+        <v>1282</v>
       </c>
       <c r="G243" t="s">
-        <v>267</v>
+        <v>764</v>
       </c>
       <c r="H243" t="s">
-        <v>268</v>
+        <v>1413</v>
       </c>
       <c r="J243" t="s">
         <v>14</v>
@@ -8193,13 +8184,13 @@
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="s">
-        <v>1282</v>
+        <v>1265</v>
       </c>
       <c r="G244" t="s">
-        <v>764</v>
+        <v>19</v>
       </c>
       <c r="H244" t="s">
-        <v>1416</v>
+        <v>20</v>
       </c>
       <c r="J244" t="s">
         <v>14</v>
@@ -8207,13 +8198,13 @@
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A245" s="1" t="s">
-        <v>1265</v>
+        <v>1229</v>
       </c>
       <c r="G245" t="s">
-        <v>19</v>
+        <v>547</v>
       </c>
       <c r="H245" t="s">
-        <v>20</v>
+        <v>589</v>
       </c>
       <c r="J245" t="s">
         <v>14</v>
@@ -8221,13 +8212,13 @@
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="s">
-        <v>1229</v>
+        <v>1264</v>
       </c>
       <c r="G246" t="s">
-        <v>547</v>
+        <v>15</v>
       </c>
       <c r="H246" t="s">
-        <v>589</v>
+        <v>16</v>
       </c>
       <c r="J246" t="s">
         <v>14</v>
@@ -8235,13 +8226,13 @@
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A247" s="1" t="s">
-        <v>1264</v>
+        <v>1309</v>
       </c>
       <c r="G247" t="s">
-        <v>15</v>
+        <v>764</v>
       </c>
       <c r="H247" t="s">
-        <v>16</v>
+        <v>1376</v>
       </c>
       <c r="J247" t="s">
         <v>14</v>
@@ -8249,13 +8240,13 @@
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
-        <v>1310</v>
+        <v>1225</v>
       </c>
       <c r="G248" t="s">
-        <v>764</v>
+        <v>547</v>
       </c>
       <c r="H248" t="s">
-        <v>1378</v>
+        <v>577</v>
       </c>
       <c r="J248" t="s">
         <v>14</v>
@@ -8263,13 +8254,13 @@
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="s">
-        <v>1225</v>
+        <v>1235</v>
       </c>
       <c r="G249" t="s">
         <v>547</v>
       </c>
       <c r="H249" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="J249" t="s">
         <v>14</v>
@@ -8277,13 +8268,13 @@
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
-        <v>1235</v>
+        <v>1263</v>
       </c>
       <c r="G250" t="s">
-        <v>547</v>
+        <v>480</v>
       </c>
       <c r="H250" t="s">
-        <v>581</v>
+        <v>481</v>
       </c>
       <c r="J250" t="s">
         <v>14</v>
@@ -8291,13 +8282,13 @@
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A251" s="1" t="s">
-        <v>1263</v>
+        <v>1272</v>
       </c>
       <c r="G251" t="s">
-        <v>480</v>
+        <v>225</v>
       </c>
       <c r="H251" t="s">
-        <v>481</v>
+        <v>227</v>
       </c>
       <c r="J251" t="s">
         <v>14</v>
@@ -8305,13 +8296,13 @@
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
-        <v>1272</v>
+        <v>1255</v>
       </c>
       <c r="G252" t="s">
-        <v>225</v>
+        <v>632</v>
       </c>
       <c r="H252" t="s">
-        <v>227</v>
+        <v>633</v>
       </c>
       <c r="J252" t="s">
         <v>14</v>
@@ -8319,13 +8310,13 @@
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A253" s="1" t="s">
-        <v>1255</v>
+        <v>1278</v>
       </c>
       <c r="G253" t="s">
-        <v>632</v>
+        <v>547</v>
       </c>
       <c r="H253" t="s">
-        <v>633</v>
+        <v>1414</v>
       </c>
       <c r="J253" t="s">
         <v>14</v>
@@ -8333,13 +8324,13 @@
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
-        <v>1278</v>
+        <v>1227</v>
       </c>
       <c r="G254" t="s">
-        <v>547</v>
+        <v>582</v>
       </c>
       <c r="H254" t="s">
-        <v>1417</v>
+        <v>583</v>
       </c>
       <c r="J254" t="s">
         <v>14</v>
@@ -8347,13 +8338,13 @@
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A255" s="1" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="G255" t="s">
-        <v>582</v>
+        <v>547</v>
       </c>
       <c r="H255" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="J255" t="s">
         <v>14</v>
@@ -8361,13 +8352,13 @@
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
-        <v>1226</v>
+        <v>1285</v>
       </c>
       <c r="G256" t="s">
         <v>547</v>
       </c>
       <c r="H256" t="s">
-        <v>579</v>
+        <v>1415</v>
       </c>
       <c r="J256" t="s">
         <v>14</v>
@@ -8375,13 +8366,13 @@
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A257" s="1" t="s">
-        <v>1285</v>
+        <v>1256</v>
       </c>
       <c r="G257" t="s">
-        <v>547</v>
+        <v>475</v>
       </c>
       <c r="H257" t="s">
-        <v>1418</v>
+        <v>476</v>
       </c>
       <c r="J257" t="s">
         <v>14</v>
@@ -8389,13 +8380,13 @@
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="s">
-        <v>1256</v>
+        <v>1267</v>
       </c>
       <c r="G258" t="s">
-        <v>475</v>
+        <v>21</v>
       </c>
       <c r="H258" t="s">
-        <v>476</v>
+        <v>22</v>
       </c>
       <c r="J258" t="s">
         <v>14</v>
@@ -8403,13 +8394,13 @@
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A259" s="1" t="s">
-        <v>1267</v>
+        <v>1231</v>
       </c>
       <c r="G259" t="s">
-        <v>21</v>
+        <v>547</v>
       </c>
       <c r="H259" t="s">
-        <v>22</v>
+        <v>568</v>
       </c>
       <c r="J259" t="s">
         <v>14</v>
@@ -8417,13 +8408,13 @@
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="s">
-        <v>1231</v>
+        <v>880</v>
       </c>
       <c r="G260" t="s">
-        <v>547</v>
+        <v>252</v>
       </c>
       <c r="H260" t="s">
-        <v>568</v>
+        <v>253</v>
       </c>
       <c r="J260" t="s">
         <v>14</v>
@@ -8431,13 +8422,13 @@
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A261" s="1" t="s">
-        <v>880</v>
+        <v>1280</v>
       </c>
       <c r="G261" t="s">
-        <v>252</v>
+        <v>334</v>
       </c>
       <c r="H261" t="s">
-        <v>253</v>
+        <v>1416</v>
       </c>
       <c r="J261" t="s">
         <v>14</v>
@@ -8445,13 +8436,13 @@
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="s">
-        <v>1280</v>
+        <v>1232</v>
       </c>
       <c r="G262" t="s">
-        <v>334</v>
+        <v>630</v>
       </c>
       <c r="H262" t="s">
-        <v>1419</v>
+        <v>631</v>
       </c>
       <c r="J262" t="s">
         <v>14</v>
@@ -8459,13 +8450,13 @@
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A263" s="1" t="s">
-        <v>1232</v>
+        <v>1257</v>
       </c>
       <c r="G263" t="s">
-        <v>630</v>
+        <v>190</v>
       </c>
       <c r="H263" t="s">
-        <v>631</v>
+        <v>191</v>
       </c>
       <c r="J263" t="s">
         <v>14</v>
@@ -8473,13 +8464,13 @@
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A264" s="1" t="s">
-        <v>1257</v>
+        <v>1283</v>
       </c>
       <c r="G264" t="s">
-        <v>190</v>
+        <v>768</v>
       </c>
       <c r="H264" t="s">
-        <v>191</v>
+        <v>1417</v>
       </c>
       <c r="J264" t="s">
         <v>14</v>
@@ -8487,13 +8478,13 @@
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A265" s="1" t="s">
-        <v>1283</v>
+        <v>1289</v>
       </c>
       <c r="G265" t="s">
-        <v>768</v>
+        <v>1292</v>
       </c>
       <c r="H265" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="J265" t="s">
         <v>14</v>
@@ -8501,13 +8492,13 @@
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A266" s="1" t="s">
-        <v>1289</v>
+        <v>1284</v>
       </c>
       <c r="G266" t="s">
-        <v>1292</v>
+        <v>1352</v>
       </c>
       <c r="H266" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="J266" t="s">
         <v>14</v>
@@ -8515,13 +8506,13 @@
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A267" s="1" t="s">
-        <v>1284</v>
+        <v>1213</v>
       </c>
       <c r="G267" t="s">
-        <v>1354</v>
+        <v>547</v>
       </c>
       <c r="H267" t="s">
-        <v>1422</v>
+        <v>555</v>
       </c>
       <c r="J267" t="s">
         <v>14</v>
@@ -8529,13 +8520,13 @@
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A268" s="1" t="s">
-        <v>1213</v>
+        <v>1288</v>
       </c>
       <c r="G268" t="s">
-        <v>547</v>
+        <v>1291</v>
       </c>
       <c r="H268" t="s">
-        <v>555</v>
+        <v>1420</v>
       </c>
       <c r="J268" t="s">
         <v>14</v>
@@ -8543,13 +8534,13 @@
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A269" s="1" t="s">
-        <v>1288</v>
+        <v>1275</v>
       </c>
       <c r="G269" t="s">
-        <v>1291</v>
+        <v>1353</v>
       </c>
       <c r="H269" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="J269" t="s">
         <v>14</v>
@@ -8557,13 +8548,13 @@
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A270" s="1" t="s">
-        <v>1275</v>
+        <v>1310</v>
       </c>
       <c r="G270" t="s">
-        <v>1355</v>
+        <v>575</v>
       </c>
       <c r="H270" t="s">
-        <v>1424</v>
+        <v>1377</v>
       </c>
       <c r="J270" t="s">
         <v>14</v>
@@ -8571,13 +8562,13 @@
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A271" s="1" t="s">
-        <v>1311</v>
+        <v>1286</v>
       </c>
       <c r="G271" t="s">
-        <v>575</v>
+        <v>547</v>
       </c>
       <c r="H271" t="s">
-        <v>1379</v>
+        <v>1422</v>
       </c>
       <c r="J271" t="s">
         <v>14</v>
@@ -8585,13 +8576,13 @@
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A272" s="1" t="s">
-        <v>1286</v>
+        <v>1311</v>
       </c>
       <c r="G272" t="s">
-        <v>547</v>
+        <v>1293</v>
       </c>
       <c r="H272" t="s">
-        <v>1425</v>
+        <v>1378</v>
       </c>
       <c r="J272" t="s">
         <v>14</v>
@@ -8599,13 +8590,13 @@
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A273" s="1" t="s">
-        <v>1312</v>
+        <v>1277</v>
       </c>
       <c r="G273" t="s">
-        <v>1293</v>
+        <v>547</v>
       </c>
       <c r="H273" t="s">
-        <v>1380</v>
+        <v>1423</v>
       </c>
       <c r="J273" t="s">
         <v>14</v>
@@ -8613,13 +8604,13 @@
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A274" s="1" t="s">
-        <v>1277</v>
+        <v>1281</v>
       </c>
       <c r="G274" t="s">
-        <v>547</v>
+        <v>763</v>
       </c>
       <c r="H274" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
       <c r="J274" t="s">
         <v>14</v>
@@ -8627,13 +8618,13 @@
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A275" s="1" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="G275" t="s">
-        <v>763</v>
+        <v>478</v>
       </c>
       <c r="H275" t="s">
-        <v>1427</v>
+        <v>1419</v>
       </c>
       <c r="J275" t="s">
         <v>14</v>
@@ -8641,13 +8632,13 @@
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A276" s="1" t="s">
-        <v>1279</v>
+        <v>1230</v>
       </c>
       <c r="G276" t="s">
-        <v>478</v>
+        <v>547</v>
       </c>
       <c r="H276" t="s">
-        <v>1422</v>
+        <v>548</v>
       </c>
       <c r="J276" t="s">
         <v>14</v>
@@ -8655,27 +8646,27 @@
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A277" s="1" t="s">
-        <v>1230</v>
+        <v>1154</v>
       </c>
       <c r="G277" t="s">
-        <v>547</v>
+        <v>126</v>
       </c>
       <c r="H277" t="s">
-        <v>548</v>
+        <v>148</v>
       </c>
       <c r="J277" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A278" s="1" t="s">
-        <v>1154</v>
+        <v>1162</v>
       </c>
       <c r="G278" t="s">
         <v>126</v>
       </c>
       <c r="H278" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="J278" t="s">
         <v>3</v>
@@ -8683,13 +8674,13 @@
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A279" s="1" t="s">
-        <v>1162</v>
+        <v>1149</v>
       </c>
       <c r="G279" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="H279" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="J279" t="s">
         <v>3</v>
@@ -8697,13 +8688,13 @@
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A280" s="1" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="G280" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H280" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="J280" t="s">
         <v>3</v>
@@ -8711,13 +8702,13 @@
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A281" s="1" t="s">
-        <v>1148</v>
+        <v>1188</v>
       </c>
       <c r="G281" t="s">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="H281" t="s">
-        <v>147</v>
+        <v>4</v>
       </c>
       <c r="J281" t="s">
         <v>3</v>
@@ -8725,13 +8716,13 @@
     </row>
     <row r="282" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A282" s="1" t="s">
-        <v>1188</v>
+        <v>1170</v>
       </c>
       <c r="G282" t="s">
-        <v>0</v>
+        <v>273</v>
       </c>
       <c r="H282" t="s">
-        <v>4</v>
+        <v>275</v>
       </c>
       <c r="J282" t="s">
         <v>3</v>
@@ -8739,13 +8730,13 @@
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A283" s="1" t="s">
-        <v>1170</v>
+        <v>1155</v>
       </c>
       <c r="G283" t="s">
-        <v>273</v>
+        <v>70</v>
       </c>
       <c r="H283" t="s">
-        <v>275</v>
+        <v>71</v>
       </c>
       <c r="J283" t="s">
         <v>3</v>
@@ -8753,13 +8744,13 @@
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A284" s="1" t="s">
-        <v>1155</v>
+        <v>1133</v>
       </c>
       <c r="G284" t="s">
-        <v>70</v>
+        <v>126</v>
       </c>
       <c r="H284" t="s">
-        <v>71</v>
+        <v>1200</v>
       </c>
       <c r="J284" t="s">
         <v>3</v>
@@ -8767,13 +8758,13 @@
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A285" s="1" t="s">
-        <v>1133</v>
+        <v>1185</v>
       </c>
       <c r="G285" t="s">
-        <v>126</v>
+        <v>220</v>
       </c>
       <c r="H285" t="s">
-        <v>1200</v>
+        <v>221</v>
       </c>
       <c r="J285" t="s">
         <v>3</v>
@@ -8781,69 +8772,69 @@
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="s">
-        <v>1185</v>
+        <v>1189</v>
       </c>
       <c r="G286" t="s">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="H286" t="s">
-        <v>221</v>
+        <v>48</v>
       </c>
       <c r="J286" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A287" s="1" t="s">
-        <v>1189</v>
+        <v>975</v>
       </c>
       <c r="G287" t="s">
-        <v>44</v>
+        <v>505</v>
       </c>
       <c r="H287" t="s">
-        <v>48</v>
+        <v>506</v>
       </c>
       <c r="J287" t="s">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A288" s="1" t="s">
-        <v>975</v>
+        <v>1184</v>
       </c>
       <c r="G288" t="s">
-        <v>505</v>
+        <v>216</v>
       </c>
       <c r="H288" t="s">
-        <v>506</v>
+        <v>217</v>
       </c>
       <c r="J288" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A289" s="1" t="s">
-        <v>1184</v>
+        <v>1159</v>
       </c>
       <c r="G289" t="s">
-        <v>216</v>
+        <v>136</v>
       </c>
       <c r="H289" t="s">
-        <v>217</v>
+        <v>137</v>
       </c>
       <c r="J289" t="s">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="s">
-        <v>1159</v>
+        <v>1134</v>
       </c>
       <c r="G290" t="s">
-        <v>136</v>
+        <v>91</v>
       </c>
       <c r="H290" t="s">
-        <v>137</v>
+        <v>92</v>
       </c>
       <c r="J290" t="s">
         <v>3</v>
@@ -8851,13 +8842,13 @@
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A291" s="1" t="s">
-        <v>1134</v>
+        <v>1158</v>
       </c>
       <c r="G291" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="H291" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="J291" t="s">
         <v>3</v>
@@ -8865,13 +8856,13 @@
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A292" s="1" t="s">
-        <v>1158</v>
+        <v>1132</v>
       </c>
       <c r="G292" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H292" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="J292" t="s">
         <v>3</v>
@@ -8879,13 +8870,13 @@
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A293" s="1" t="s">
-        <v>1132</v>
+        <v>1165</v>
       </c>
       <c r="G293" t="s">
-        <v>87</v>
+        <v>603</v>
       </c>
       <c r="H293" t="s">
-        <v>88</v>
+        <v>608</v>
       </c>
       <c r="J293" t="s">
         <v>3</v>
@@ -8893,13 +8884,13 @@
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="s">
-        <v>1165</v>
+        <v>836</v>
       </c>
       <c r="G294" t="s">
-        <v>603</v>
+        <v>310</v>
       </c>
       <c r="H294" t="s">
-        <v>608</v>
+        <v>311</v>
       </c>
       <c r="J294" t="s">
         <v>3</v>
@@ -8907,13 +8898,13 @@
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A295" s="1" t="s">
-        <v>836</v>
+        <v>1171</v>
       </c>
       <c r="G295" t="s">
-        <v>310</v>
+        <v>273</v>
       </c>
       <c r="H295" t="s">
-        <v>311</v>
+        <v>276</v>
       </c>
       <c r="J295" t="s">
         <v>3</v>
@@ -8921,13 +8912,13 @@
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="s">
-        <v>1171</v>
+        <v>1139</v>
       </c>
       <c r="G296" t="s">
-        <v>273</v>
+        <v>206</v>
       </c>
       <c r="H296" t="s">
-        <v>276</v>
+        <v>209</v>
       </c>
       <c r="J296" t="s">
         <v>3</v>
@@ -8935,13 +8926,13 @@
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A297" s="1" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
       <c r="G297" t="s">
-        <v>206</v>
+        <v>76</v>
       </c>
       <c r="H297" t="s">
-        <v>209</v>
+        <v>77</v>
       </c>
       <c r="J297" t="s">
         <v>3</v>
@@ -8949,13 +8940,13 @@
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A298" s="1" t="s">
-        <v>1135</v>
+        <v>1172</v>
       </c>
       <c r="G298" t="s">
-        <v>76</v>
+        <v>273</v>
       </c>
       <c r="H298" t="s">
-        <v>77</v>
+        <v>274</v>
       </c>
       <c r="J298" t="s">
         <v>3</v>
@@ -8963,13 +8954,13 @@
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A299" s="1" t="s">
-        <v>1172</v>
+        <v>1156</v>
       </c>
       <c r="G299" t="s">
-        <v>273</v>
+        <v>207</v>
       </c>
       <c r="H299" t="s">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="J299" t="s">
         <v>3</v>
@@ -8977,13 +8968,13 @@
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="G300" t="s">
-        <v>207</v>
+        <v>93</v>
       </c>
       <c r="H300" t="s">
-        <v>208</v>
+        <v>94</v>
       </c>
       <c r="J300" t="s">
         <v>3</v>
@@ -8991,13 +8982,13 @@
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A301" s="1" t="s">
-        <v>1157</v>
+        <v>1141</v>
       </c>
       <c r="G301" t="s">
-        <v>93</v>
+        <v>206</v>
       </c>
       <c r="H301" t="s">
-        <v>94</v>
+        <v>215</v>
       </c>
       <c r="J301" t="s">
         <v>3</v>
@@ -9005,13 +8996,13 @@
     </row>
     <row r="302" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A302" s="1" t="s">
-        <v>1141</v>
+        <v>1150</v>
       </c>
       <c r="G302" t="s">
-        <v>206</v>
+        <v>95</v>
       </c>
       <c r="H302" t="s">
-        <v>215</v>
+        <v>96</v>
       </c>
       <c r="J302" t="s">
         <v>3</v>
@@ -9019,13 +9010,13 @@
     </row>
     <row r="303" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A303" s="1" t="s">
-        <v>1150</v>
+        <v>1177</v>
       </c>
       <c r="G303" t="s">
-        <v>95</v>
+        <v>273</v>
       </c>
       <c r="H303" t="s">
-        <v>96</v>
+        <v>277</v>
       </c>
       <c r="J303" t="s">
         <v>3</v>
@@ -9033,13 +9024,13 @@
     </row>
     <row r="304" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A304" s="1" t="s">
-        <v>1177</v>
+        <v>1140</v>
       </c>
       <c r="G304" t="s">
-        <v>273</v>
+        <v>134</v>
       </c>
       <c r="H304" t="s">
-        <v>277</v>
+        <v>135</v>
       </c>
       <c r="J304" t="s">
         <v>3</v>
@@ -9047,13 +9038,13 @@
     </row>
     <row r="305" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A305" s="1" t="s">
-        <v>1140</v>
+        <v>1312</v>
       </c>
       <c r="G305" t="s">
-        <v>134</v>
+        <v>787</v>
       </c>
       <c r="H305" t="s">
-        <v>135</v>
+        <v>1379</v>
       </c>
       <c r="J305" t="s">
         <v>3</v>
@@ -9061,13 +9052,13 @@
     </row>
     <row r="306" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A306" s="1" t="s">
-        <v>1313</v>
+        <v>1174</v>
       </c>
       <c r="G306" t="s">
-        <v>787</v>
+        <v>273</v>
       </c>
       <c r="H306" t="s">
-        <v>1381</v>
+        <v>278</v>
       </c>
       <c r="J306" t="s">
         <v>3</v>
@@ -9075,41 +9066,41 @@
     </row>
     <row r="307" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A307" s="1" t="s">
-        <v>1174</v>
+        <v>1186</v>
       </c>
       <c r="G307" t="s">
-        <v>273</v>
+        <v>218</v>
       </c>
       <c r="H307" t="s">
-        <v>278</v>
+        <v>219</v>
       </c>
       <c r="J307" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="308" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A308" s="1" t="s">
-        <v>1186</v>
+        <v>1313</v>
       </c>
       <c r="G308" t="s">
-        <v>218</v>
+        <v>788</v>
       </c>
       <c r="H308" t="s">
-        <v>219</v>
+        <v>789</v>
       </c>
       <c r="J308" t="s">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="309" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A309" s="1" t="s">
-        <v>1314</v>
+        <v>1173</v>
       </c>
       <c r="G309" t="s">
-        <v>788</v>
+        <v>610</v>
       </c>
       <c r="H309" t="s">
-        <v>789</v>
+        <v>611</v>
       </c>
       <c r="J309" t="s">
         <v>3</v>
@@ -9117,13 +9108,13 @@
     </row>
     <row r="310" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A310" s="1" t="s">
-        <v>1173</v>
+        <v>1191</v>
       </c>
       <c r="G310" t="s">
-        <v>610</v>
+        <v>8</v>
       </c>
       <c r="H310" t="s">
-        <v>611</v>
+        <v>9</v>
       </c>
       <c r="J310" t="s">
         <v>3</v>
@@ -9131,13 +9122,13 @@
     </row>
     <row r="311" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A311" s="1" t="s">
-        <v>1191</v>
+        <v>1164</v>
       </c>
       <c r="G311" t="s">
-        <v>8</v>
+        <v>603</v>
       </c>
       <c r="H311" t="s">
-        <v>9</v>
+        <v>609</v>
       </c>
       <c r="J311" t="s">
         <v>3</v>
@@ -9145,13 +9136,13 @@
     </row>
     <row r="312" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A312" s="1" t="s">
-        <v>1164</v>
+        <v>1160</v>
       </c>
       <c r="G312" t="s">
-        <v>603</v>
+        <v>82</v>
       </c>
       <c r="H312" t="s">
-        <v>609</v>
+        <v>83</v>
       </c>
       <c r="J312" t="s">
         <v>3</v>
@@ -9159,83 +9150,83 @@
     </row>
     <row r="313" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A313" s="1" t="s">
-        <v>1160</v>
+        <v>1192</v>
       </c>
       <c r="G313" t="s">
-        <v>82</v>
+        <v>5</v>
       </c>
       <c r="H313" t="s">
-        <v>83</v>
+        <v>6</v>
       </c>
       <c r="J313" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="314" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A314" s="1" t="s">
-        <v>1192</v>
+        <v>1143</v>
       </c>
       <c r="G314" t="s">
-        <v>5</v>
+        <v>337</v>
       </c>
       <c r="H314" t="s">
-        <v>6</v>
+        <v>342</v>
       </c>
       <c r="J314" t="s">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="315" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A315" s="1" t="s">
-        <v>1143</v>
+        <v>1190</v>
       </c>
       <c r="G315" t="s">
-        <v>337</v>
+        <v>5</v>
       </c>
       <c r="H315" t="s">
-        <v>342</v>
+        <v>7</v>
       </c>
       <c r="J315" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="316" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A316" s="1" t="s">
-        <v>1190</v>
+      <c r="A316">
+        <v>1480</v>
       </c>
       <c r="G316" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="H316" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="J316" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="317" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A317">
-        <v>1480</v>
+      <c r="A317" s="1" t="s">
+        <v>1142</v>
       </c>
       <c r="G317" t="s">
-        <v>44</v>
+        <v>206</v>
       </c>
       <c r="H317" t="s">
-        <v>45</v>
+        <v>210</v>
       </c>
       <c r="J317" t="s">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="318" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A318" s="1" t="s">
-        <v>1142</v>
+        <v>1167</v>
       </c>
       <c r="G318" t="s">
-        <v>206</v>
+        <v>291</v>
       </c>
       <c r="H318" t="s">
-        <v>210</v>
+        <v>292</v>
       </c>
       <c r="J318" t="s">
         <v>3</v>
@@ -9243,13 +9234,13 @@
     </row>
     <row r="319" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A319" s="1" t="s">
-        <v>1167</v>
+        <v>1151</v>
       </c>
       <c r="G319" t="s">
-        <v>291</v>
+        <v>86</v>
       </c>
       <c r="H319" t="s">
-        <v>292</v>
+        <v>1201</v>
       </c>
       <c r="J319" t="s">
         <v>3</v>
@@ -9257,13 +9248,13 @@
     </row>
     <row r="320" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A320" s="1" t="s">
-        <v>1151</v>
+        <v>1182</v>
       </c>
       <c r="G320" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="H320" t="s">
-        <v>1201</v>
+        <v>11</v>
       </c>
       <c r="J320" t="s">
         <v>3</v>
@@ -9271,13 +9262,13 @@
     </row>
     <row r="321" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A321" s="1" t="s">
-        <v>1182</v>
+        <v>1163</v>
       </c>
       <c r="G321" t="s">
-        <v>10</v>
+        <v>126</v>
       </c>
       <c r="H321" t="s">
-        <v>11</v>
+        <v>152</v>
       </c>
       <c r="J321" t="s">
         <v>3</v>
@@ -9285,13 +9276,13 @@
     </row>
     <row r="322" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A322" s="1" t="s">
-        <v>1163</v>
+        <v>1168</v>
       </c>
       <c r="G322" t="s">
-        <v>126</v>
+        <v>604</v>
       </c>
       <c r="H322" t="s">
-        <v>152</v>
+        <v>605</v>
       </c>
       <c r="J322" t="s">
         <v>3</v>
@@ -9299,13 +9290,13 @@
     </row>
     <row r="323" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A323" s="1" t="s">
-        <v>1168</v>
+        <v>1175</v>
       </c>
       <c r="G323" t="s">
-        <v>604</v>
+        <v>273</v>
       </c>
       <c r="H323" t="s">
-        <v>605</v>
+        <v>281</v>
       </c>
       <c r="J323" t="s">
         <v>3</v>
@@ -9313,13 +9304,13 @@
     </row>
     <row r="324" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A324" s="1" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="G324" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="H324" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="J324" t="s">
         <v>3</v>
@@ -9327,13 +9318,13 @@
     </row>
     <row r="325" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A325" s="1" t="s">
-        <v>1176</v>
+        <v>1166</v>
       </c>
       <c r="G325" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="H325" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="J325" t="s">
         <v>3</v>
@@ -9341,41 +9332,41 @@
     </row>
     <row r="326" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A326" s="1" t="s">
-        <v>1166</v>
+        <v>1314</v>
       </c>
       <c r="G326" t="s">
-        <v>290</v>
+        <v>1207</v>
       </c>
       <c r="H326" t="s">
-        <v>293</v>
+        <v>1380</v>
       </c>
       <c r="J326" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="327" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A327" s="1" t="s">
-        <v>1315</v>
+        <v>1144</v>
       </c>
       <c r="G327" t="s">
-        <v>1207</v>
+        <v>340</v>
       </c>
       <c r="H327" t="s">
-        <v>1382</v>
+        <v>341</v>
       </c>
       <c r="J327" t="s">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="328" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A328" s="1" t="s">
-        <v>1144</v>
+        <v>1153</v>
       </c>
       <c r="G328" t="s">
-        <v>340</v>
+        <v>80</v>
       </c>
       <c r="H328" t="s">
-        <v>341</v>
+        <v>81</v>
       </c>
       <c r="J328" t="s">
         <v>3</v>
@@ -9383,13 +9374,13 @@
     </row>
     <row r="329" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A329" s="1" t="s">
-        <v>1153</v>
+        <v>1181</v>
       </c>
       <c r="G329" t="s">
-        <v>80</v>
+        <v>296</v>
       </c>
       <c r="H329" t="s">
-        <v>81</v>
+        <v>297</v>
       </c>
       <c r="J329" t="s">
         <v>3</v>
@@ -9397,13 +9388,13 @@
     </row>
     <row r="330" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A330" s="1" t="s">
-        <v>1181</v>
+        <v>1199</v>
       </c>
       <c r="G330" t="s">
-        <v>296</v>
+        <v>781</v>
       </c>
       <c r="H330" t="s">
-        <v>297</v>
+        <v>1425</v>
       </c>
       <c r="J330" t="s">
         <v>3</v>
@@ -9411,13 +9402,13 @@
     </row>
     <row r="331" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A331" s="1" t="s">
-        <v>1199</v>
+        <v>1146</v>
       </c>
       <c r="G331" t="s">
-        <v>781</v>
+        <v>140</v>
       </c>
       <c r="H331" t="s">
-        <v>1428</v>
+        <v>141</v>
       </c>
       <c r="J331" t="s">
         <v>3</v>
@@ -9425,13 +9416,13 @@
     </row>
     <row r="332" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A332" s="1" t="s">
-        <v>1146</v>
+        <v>1179</v>
       </c>
       <c r="G332" t="s">
-        <v>140</v>
+        <v>279</v>
       </c>
       <c r="H332" t="s">
-        <v>141</v>
+        <v>280</v>
       </c>
       <c r="J332" t="s">
         <v>3</v>
@@ -9439,13 +9430,13 @@
     </row>
     <row r="333" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A333" s="1" t="s">
-        <v>1179</v>
+        <v>1023</v>
       </c>
       <c r="G333" t="s">
-        <v>279</v>
+        <v>786</v>
       </c>
       <c r="H333" t="s">
-        <v>280</v>
+        <v>1426</v>
       </c>
       <c r="J333" t="s">
         <v>3</v>
@@ -9453,13 +9444,13 @@
     </row>
     <row r="334" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A334" s="1" t="s">
-        <v>1023</v>
+        <v>1195</v>
       </c>
       <c r="G334" t="s">
-        <v>786</v>
+        <v>754</v>
       </c>
       <c r="H334" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
       <c r="J334" t="s">
         <v>3</v>
@@ -9467,41 +9458,41 @@
     </row>
     <row r="335" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A335" s="1" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="G335" t="s">
-        <v>754</v>
+        <v>46</v>
       </c>
       <c r="H335" t="s">
-        <v>1430</v>
+        <v>47</v>
       </c>
       <c r="J335" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="336" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A336" s="1" t="s">
-        <v>1193</v>
+        <v>1145</v>
       </c>
       <c r="G336" t="s">
-        <v>46</v>
+        <v>213</v>
       </c>
       <c r="H336" t="s">
-        <v>47</v>
+        <v>214</v>
       </c>
       <c r="J336" t="s">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="337" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A337" s="1" t="s">
-        <v>1145</v>
+        <v>1161</v>
       </c>
       <c r="G337" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="H337" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J337" t="s">
         <v>3</v>
@@ -9509,13 +9500,13 @@
     </row>
     <row r="338" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A338" s="1" t="s">
-        <v>1161</v>
+        <v>1180</v>
       </c>
       <c r="G338" t="s">
-        <v>211</v>
+        <v>294</v>
       </c>
       <c r="H338" t="s">
-        <v>212</v>
+        <v>295</v>
       </c>
       <c r="J338" t="s">
         <v>3</v>
@@ -9523,13 +9514,13 @@
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A339" s="1" t="s">
-        <v>1180</v>
+        <v>1196</v>
       </c>
       <c r="G339" t="s">
-        <v>294</v>
+        <v>1354</v>
       </c>
       <c r="H339" t="s">
-        <v>295</v>
+        <v>1428</v>
       </c>
       <c r="J339" t="s">
         <v>3</v>
@@ -9537,13 +9528,13 @@
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A340" s="1" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="G340" t="s">
-        <v>1356</v>
+        <v>273</v>
       </c>
       <c r="H340" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="J340" t="s">
         <v>3</v>
@@ -9551,41 +9542,41 @@
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A341" s="1" t="s">
-        <v>1197</v>
+        <v>1187</v>
       </c>
       <c r="G341" t="s">
-        <v>273</v>
+        <v>222</v>
       </c>
       <c r="H341" t="s">
-        <v>1432</v>
+        <v>223</v>
       </c>
       <c r="J341" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A342" s="1" t="s">
-        <v>1187</v>
+        <v>1183</v>
       </c>
       <c r="G342" t="s">
-        <v>222</v>
+        <v>298</v>
       </c>
       <c r="H342" t="s">
-        <v>223</v>
+        <v>299</v>
       </c>
       <c r="J342" t="s">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="343" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A343" s="1" t="s">
-        <v>1183</v>
+        <v>1152</v>
       </c>
       <c r="G343" t="s">
-        <v>298</v>
+        <v>84</v>
       </c>
       <c r="H343" t="s">
-        <v>299</v>
+        <v>85</v>
       </c>
       <c r="J343" t="s">
         <v>3</v>
@@ -9593,13 +9584,13 @@
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A344" s="1" t="s">
-        <v>1152</v>
+        <v>1138</v>
       </c>
       <c r="G344" t="s">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="H344" t="s">
-        <v>85</v>
+        <v>127</v>
       </c>
       <c r="J344" t="s">
         <v>3</v>
@@ -9607,13 +9598,13 @@
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A345" s="1" t="s">
-        <v>1138</v>
+        <v>1315</v>
       </c>
       <c r="G345" t="s">
-        <v>126</v>
+        <v>773</v>
       </c>
       <c r="H345" t="s">
-        <v>127</v>
+        <v>1381</v>
       </c>
       <c r="J345" t="s">
         <v>3</v>
@@ -9621,13 +9612,13 @@
     </row>
     <row r="346" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A346" s="1" t="s">
-        <v>1316</v>
+        <v>1198</v>
       </c>
       <c r="G346" t="s">
-        <v>773</v>
+        <v>780</v>
       </c>
       <c r="H346" t="s">
-        <v>1383</v>
+        <v>1430</v>
       </c>
       <c r="J346" t="s">
         <v>3</v>
@@ -9635,13 +9626,13 @@
     </row>
     <row r="347" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A347" s="1" t="s">
-        <v>1198</v>
+        <v>1316</v>
       </c>
       <c r="G347" t="s">
-        <v>780</v>
+        <v>1208</v>
       </c>
       <c r="H347" t="s">
-        <v>1433</v>
+        <v>1382</v>
       </c>
       <c r="J347" t="s">
         <v>3</v>
@@ -9649,13 +9640,13 @@
     </row>
     <row r="348" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A348" s="1" t="s">
-        <v>1317</v>
+        <v>1169</v>
       </c>
       <c r="G348" t="s">
-        <v>1208</v>
+        <v>606</v>
       </c>
       <c r="H348" t="s">
-        <v>1384</v>
+        <v>607</v>
       </c>
       <c r="J348" t="s">
         <v>3</v>
@@ -9663,41 +9654,41 @@
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A349" s="1" t="s">
-        <v>1169</v>
+        <v>1178</v>
       </c>
       <c r="G349" t="s">
-        <v>606</v>
+        <v>1</v>
       </c>
       <c r="H349" t="s">
-        <v>607</v>
+        <v>2</v>
       </c>
       <c r="J349" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A350" s="1" t="s">
-        <v>1178</v>
+        <v>1137</v>
       </c>
       <c r="G350" t="s">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="H350" t="s">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="J350" t="s">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A351" s="1" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="G351" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="H351" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="J351" t="s">
         <v>3</v>
@@ -9705,13 +9696,13 @@
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A352" s="1" t="s">
-        <v>1136</v>
+        <v>1147</v>
       </c>
       <c r="G352" t="s">
-        <v>89</v>
+        <v>338</v>
       </c>
       <c r="H352" t="s">
-        <v>90</v>
+        <v>339</v>
       </c>
       <c r="J352" t="s">
         <v>3</v>
@@ -9719,13 +9710,13 @@
     </row>
     <row r="353" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A353" s="1" t="s">
-        <v>1147</v>
+        <v>1317</v>
       </c>
       <c r="G353" t="s">
-        <v>338</v>
+        <v>1202</v>
       </c>
       <c r="H353" t="s">
-        <v>339</v>
+        <v>1203</v>
       </c>
       <c r="J353" t="s">
         <v>3</v>
@@ -9736,10 +9727,10 @@
         <v>1318</v>
       </c>
       <c r="G354" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="H354" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="J354" t="s">
         <v>3</v>
@@ -9747,13 +9738,13 @@
     </row>
     <row r="355" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A355" s="1" t="s">
-        <v>1319</v>
+        <v>1194</v>
       </c>
       <c r="G355" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="H355" t="s">
-        <v>1205</v>
+        <v>1431</v>
       </c>
       <c r="J355" t="s">
         <v>3</v>
@@ -9761,13 +9752,13 @@
     </row>
     <row r="356" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A356" s="1" t="s">
-        <v>1194</v>
+        <v>1319</v>
       </c>
       <c r="G356" t="s">
-        <v>1206</v>
+        <v>1355</v>
       </c>
       <c r="H356" t="s">
-        <v>1434</v>
+        <v>1383</v>
       </c>
       <c r="J356" t="s">
         <v>3</v>
@@ -9778,13 +9769,13 @@
         <v>1320</v>
       </c>
       <c r="G357" t="s">
-        <v>1357</v>
+        <v>547</v>
       </c>
       <c r="H357" t="s">
-        <v>1385</v>
+        <v>584</v>
       </c>
       <c r="J357" t="s">
-        <v>3</v>
+        <v>553</v>
       </c>
     </row>
     <row r="358" spans="1:10" x14ac:dyDescent="0.3">
@@ -9792,10 +9783,10 @@
         <v>1321</v>
       </c>
       <c r="G358" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="H358" t="s">
-        <v>584</v>
+        <v>552</v>
       </c>
       <c r="J358" t="s">
         <v>553</v>
@@ -9806,10 +9797,10 @@
         <v>1322</v>
       </c>
       <c r="G359" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="H359" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="J359" t="s">
         <v>553</v>
@@ -9820,10 +9811,10 @@
         <v>1323</v>
       </c>
       <c r="G360" t="s">
-        <v>557</v>
+        <v>575</v>
       </c>
       <c r="H360" t="s">
-        <v>558</v>
+        <v>576</v>
       </c>
       <c r="J360" t="s">
         <v>553</v>
@@ -9834,10 +9825,10 @@
         <v>1324</v>
       </c>
       <c r="G361" t="s">
-        <v>575</v>
+        <v>547</v>
       </c>
       <c r="H361" t="s">
-        <v>576</v>
+        <v>559</v>
       </c>
       <c r="J361" t="s">
         <v>553</v>
@@ -9851,7 +9842,7 @@
         <v>547</v>
       </c>
       <c r="H362" t="s">
-        <v>559</v>
+        <v>588</v>
       </c>
       <c r="J362" t="s">
         <v>553</v>
@@ -9862,13 +9853,13 @@
         <v>1326</v>
       </c>
       <c r="G363" t="s">
-        <v>547</v>
+        <v>260</v>
       </c>
       <c r="H363" t="s">
-        <v>588</v>
+        <v>771</v>
       </c>
       <c r="J363" t="s">
-        <v>553</v>
+        <v>272</v>
       </c>
     </row>
     <row r="364" spans="1:10" x14ac:dyDescent="0.3">
@@ -9876,10 +9867,10 @@
         <v>1327</v>
       </c>
       <c r="G364" t="s">
-        <v>260</v>
+        <v>554</v>
       </c>
       <c r="H364" t="s">
-        <v>771</v>
+        <v>1432</v>
       </c>
       <c r="J364" t="s">
         <v>272</v>
@@ -9890,10 +9881,10 @@
         <v>1328</v>
       </c>
       <c r="G365" t="s">
-        <v>554</v>
+        <v>260</v>
       </c>
       <c r="H365" t="s">
-        <v>1435</v>
+        <v>271</v>
       </c>
       <c r="J365" t="s">
         <v>272</v>
@@ -9904,10 +9895,10 @@
         <v>1329</v>
       </c>
       <c r="G366" t="s">
-        <v>260</v>
+        <v>308</v>
       </c>
       <c r="H366" t="s">
-        <v>271</v>
+        <v>309</v>
       </c>
       <c r="J366" t="s">
         <v>272</v>
@@ -9918,10 +9909,10 @@
         <v>1330</v>
       </c>
       <c r="G367" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="H367" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="J367" t="s">
         <v>272</v>
@@ -9932,10 +9923,10 @@
         <v>1331</v>
       </c>
       <c r="G368" t="s">
-        <v>305</v>
+        <v>590</v>
       </c>
       <c r="H368" t="s">
-        <v>306</v>
+        <v>591</v>
       </c>
       <c r="J368" t="s">
         <v>272</v>
@@ -9943,27 +9934,27 @@
     </row>
     <row r="369" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A369" s="1" t="s">
-        <v>1332</v>
+        <v>973</v>
       </c>
       <c r="G369" t="s">
-        <v>590</v>
+        <v>671</v>
       </c>
       <c r="H369" t="s">
-        <v>591</v>
+        <v>672</v>
       </c>
       <c r="J369" t="s">
-        <v>272</v>
+        <v>67</v>
       </c>
     </row>
     <row r="370" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A370" s="1" t="s">
-        <v>973</v>
+        <v>981</v>
       </c>
       <c r="G370" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="H370" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="J370" t="s">
         <v>67</v>
@@ -9971,13 +9962,13 @@
     </row>
     <row r="371" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A371" s="1" t="s">
-        <v>981</v>
+        <v>1008</v>
       </c>
       <c r="G371" t="s">
-        <v>667</v>
+        <v>128</v>
       </c>
       <c r="H371" t="s">
-        <v>668</v>
+        <v>129</v>
       </c>
       <c r="J371" t="s">
         <v>67</v>
@@ -9985,13 +9976,13 @@
     </row>
     <row r="372" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A372" s="1" t="s">
-        <v>1008</v>
+        <v>965</v>
       </c>
       <c r="G372" t="s">
-        <v>128</v>
+        <v>445</v>
       </c>
       <c r="H372" t="s">
-        <v>129</v>
+        <v>446</v>
       </c>
       <c r="J372" t="s">
         <v>67</v>
@@ -9999,13 +9990,13 @@
     </row>
     <row r="373" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A373" s="1" t="s">
-        <v>965</v>
+        <v>952</v>
       </c>
       <c r="G373" t="s">
-        <v>445</v>
+        <v>517</v>
       </c>
       <c r="H373" t="s">
-        <v>446</v>
+        <v>518</v>
       </c>
       <c r="J373" t="s">
         <v>67</v>
@@ -10013,13 +10004,13 @@
     </row>
     <row r="374" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A374" s="1" t="s">
-        <v>952</v>
+        <v>990</v>
       </c>
       <c r="G374" t="s">
-        <v>517</v>
+        <v>228</v>
       </c>
       <c r="H374" t="s">
-        <v>518</v>
+        <v>229</v>
       </c>
       <c r="J374" t="s">
         <v>67</v>
@@ -10027,13 +10018,13 @@
     </row>
     <row r="375" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A375" s="1" t="s">
-        <v>990</v>
+        <v>982</v>
       </c>
       <c r="G375" t="s">
-        <v>228</v>
+        <v>65</v>
       </c>
       <c r="H375" t="s">
-        <v>229</v>
+        <v>66</v>
       </c>
       <c r="J375" t="s">
         <v>67</v>
@@ -10041,13 +10032,13 @@
     </row>
     <row r="376" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A376" s="1" t="s">
-        <v>982</v>
+        <v>991</v>
       </c>
       <c r="G376" t="s">
-        <v>65</v>
+        <v>740</v>
       </c>
       <c r="H376" t="s">
-        <v>66</v>
+        <v>741</v>
       </c>
       <c r="J376" t="s">
         <v>67</v>
@@ -10055,13 +10046,13 @@
     </row>
     <row r="377" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A377" s="1" t="s">
-        <v>991</v>
+        <v>966</v>
       </c>
       <c r="G377" t="s">
-        <v>740</v>
+        <v>593</v>
       </c>
       <c r="H377" t="s">
-        <v>741</v>
+        <v>594</v>
       </c>
       <c r="J377" t="s">
         <v>67</v>
@@ -10069,13 +10060,13 @@
     </row>
     <row r="378" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A378" s="1" t="s">
-        <v>966</v>
+        <v>956</v>
       </c>
       <c r="G378" t="s">
-        <v>593</v>
+        <v>452</v>
       </c>
       <c r="H378" t="s">
-        <v>594</v>
+        <v>453</v>
       </c>
       <c r="J378" t="s">
         <v>67</v>
@@ -10083,13 +10074,13 @@
     </row>
     <row r="379" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A379" s="1" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="G379" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="H379" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="J379" t="s">
         <v>67</v>
@@ -10097,13 +10088,13 @@
     </row>
     <row r="380" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A380" s="1" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="G380" t="s">
         <v>441</v>
       </c>
       <c r="H380" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="J380" t="s">
         <v>67</v>
@@ -10111,13 +10102,13 @@
     </row>
     <row r="381" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A381" s="1" t="s">
-        <v>960</v>
+        <v>977</v>
       </c>
       <c r="G381" t="s">
-        <v>441</v>
+        <v>669</v>
       </c>
       <c r="H381" t="s">
-        <v>448</v>
+        <v>670</v>
       </c>
       <c r="J381" t="s">
         <v>67</v>
@@ -10125,13 +10116,13 @@
     </row>
     <row r="382" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A382" s="1" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="G382" t="s">
-        <v>669</v>
+        <v>505</v>
       </c>
       <c r="H382" t="s">
-        <v>670</v>
+        <v>509</v>
       </c>
       <c r="J382" t="s">
         <v>67</v>
@@ -10139,13 +10130,13 @@
     </row>
     <row r="383" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A383" s="1" t="s">
-        <v>974</v>
+        <v>998</v>
       </c>
       <c r="G383" t="s">
-        <v>505</v>
+        <v>734</v>
       </c>
       <c r="H383" t="s">
-        <v>509</v>
+        <v>735</v>
       </c>
       <c r="J383" t="s">
         <v>67</v>
@@ -10153,13 +10144,13 @@
     </row>
     <row r="384" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A384" s="1" t="s">
-        <v>998</v>
+        <v>984</v>
       </c>
       <c r="G384" t="s">
-        <v>734</v>
+        <v>694</v>
       </c>
       <c r="H384" t="s">
-        <v>735</v>
+        <v>697</v>
       </c>
       <c r="J384" t="s">
         <v>67</v>
@@ -10167,13 +10158,13 @@
     </row>
     <row r="385" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A385" s="1" t="s">
-        <v>984</v>
+        <v>955</v>
       </c>
       <c r="G385" t="s">
-        <v>694</v>
+        <v>441</v>
       </c>
       <c r="H385" t="s">
-        <v>697</v>
+        <v>442</v>
       </c>
       <c r="J385" t="s">
         <v>67</v>
@@ -10181,13 +10172,13 @@
     </row>
     <row r="386" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A386" s="1" t="s">
-        <v>955</v>
+        <v>1332</v>
       </c>
       <c r="G386" t="s">
-        <v>441</v>
+        <v>675</v>
       </c>
       <c r="H386" t="s">
-        <v>442</v>
+        <v>1384</v>
       </c>
       <c r="J386" t="s">
         <v>67</v>
@@ -10195,13 +10186,13 @@
     </row>
     <row r="387" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A387" s="1" t="s">
-        <v>1333</v>
+        <v>997</v>
       </c>
       <c r="G387" t="s">
-        <v>675</v>
+        <v>742</v>
       </c>
       <c r="H387" t="s">
-        <v>1386</v>
+        <v>743</v>
       </c>
       <c r="J387" t="s">
         <v>67</v>
@@ -10209,13 +10200,13 @@
     </row>
     <row r="388" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A388" s="1" t="s">
-        <v>997</v>
+        <v>957</v>
       </c>
       <c r="G388" t="s">
-        <v>742</v>
+        <v>443</v>
       </c>
       <c r="H388" t="s">
-        <v>743</v>
+        <v>444</v>
       </c>
       <c r="J388" t="s">
         <v>67</v>
@@ -10223,13 +10214,13 @@
     </row>
     <row r="389" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A389" s="1" t="s">
-        <v>957</v>
+        <v>1000</v>
       </c>
       <c r="G389" t="s">
-        <v>443</v>
+        <v>716</v>
       </c>
       <c r="H389" t="s">
-        <v>444</v>
+        <v>723</v>
       </c>
       <c r="J389" t="s">
         <v>67</v>
@@ -10237,13 +10228,13 @@
     </row>
     <row r="390" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A390" s="1" t="s">
-        <v>1000</v>
+        <v>993</v>
       </c>
       <c r="G390" t="s">
-        <v>716</v>
+        <v>736</v>
       </c>
       <c r="H390" t="s">
-        <v>723</v>
+        <v>738</v>
       </c>
       <c r="J390" t="s">
         <v>67</v>
@@ -10251,13 +10242,13 @@
     </row>
     <row r="391" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A391" s="1" t="s">
-        <v>993</v>
+        <v>1333</v>
       </c>
       <c r="G391" t="s">
-        <v>736</v>
+        <v>694</v>
       </c>
       <c r="H391" t="s">
-        <v>738</v>
+        <v>1032</v>
       </c>
       <c r="J391" t="s">
         <v>67</v>
@@ -10265,13 +10256,13 @@
     </row>
     <row r="392" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A392" s="1" t="s">
-        <v>1334</v>
+        <v>978</v>
       </c>
       <c r="G392" t="s">
-        <v>694</v>
+        <v>704</v>
       </c>
       <c r="H392" t="s">
-        <v>1032</v>
+        <v>705</v>
       </c>
       <c r="J392" t="s">
         <v>67</v>
@@ -10279,13 +10270,13 @@
     </row>
     <row r="393" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A393" s="1" t="s">
-        <v>978</v>
+        <v>992</v>
       </c>
       <c r="G393" t="s">
-        <v>704</v>
+        <v>736</v>
       </c>
       <c r="H393" t="s">
-        <v>705</v>
+        <v>737</v>
       </c>
       <c r="J393" t="s">
         <v>67</v>
@@ -10293,13 +10284,13 @@
     </row>
     <row r="394" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A394" s="1" t="s">
-        <v>992</v>
+        <v>1334</v>
       </c>
       <c r="G394" t="s">
-        <v>736</v>
+        <v>716</v>
       </c>
       <c r="H394" t="s">
-        <v>737</v>
+        <v>1385</v>
       </c>
       <c r="J394" t="s">
         <v>67</v>
@@ -10307,13 +10298,13 @@
     </row>
     <row r="395" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A395" s="1" t="s">
-        <v>1335</v>
+        <v>959</v>
       </c>
       <c r="G395" t="s">
-        <v>716</v>
+        <v>456</v>
       </c>
       <c r="H395" t="s">
-        <v>1387</v>
+        <v>457</v>
       </c>
       <c r="J395" t="s">
         <v>67</v>
@@ -10321,13 +10312,13 @@
     </row>
     <row r="396" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A396" s="1" t="s">
-        <v>959</v>
+        <v>967</v>
       </c>
       <c r="G396" t="s">
-        <v>456</v>
+        <v>124</v>
       </c>
       <c r="H396" t="s">
-        <v>457</v>
+        <v>125</v>
       </c>
       <c r="J396" t="s">
         <v>67</v>
@@ -10335,13 +10326,13 @@
     </row>
     <row r="397" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A397" s="1" t="s">
-        <v>967</v>
+        <v>996</v>
       </c>
       <c r="G397" t="s">
-        <v>124</v>
+        <v>744</v>
       </c>
       <c r="H397" t="s">
-        <v>125</v>
+        <v>745</v>
       </c>
       <c r="J397" t="s">
         <v>67</v>
@@ -10349,13 +10340,13 @@
     </row>
     <row r="398" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A398" s="1" t="s">
-        <v>996</v>
+        <v>976</v>
       </c>
       <c r="G398" t="s">
-        <v>744</v>
+        <v>673</v>
       </c>
       <c r="H398" t="s">
-        <v>745</v>
+        <v>674</v>
       </c>
       <c r="J398" t="s">
         <v>67</v>
@@ -10363,13 +10354,13 @@
     </row>
     <row r="399" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A399" s="1" t="s">
-        <v>976</v>
+        <v>985</v>
       </c>
       <c r="G399" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="H399" t="s">
-        <v>674</v>
+        <v>699</v>
       </c>
       <c r="J399" t="s">
         <v>67</v>
@@ -10377,13 +10368,13 @@
     </row>
     <row r="400" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A400" s="1" t="s">
-        <v>985</v>
+        <v>1017</v>
       </c>
       <c r="G400" t="s">
-        <v>698</v>
+        <v>750</v>
       </c>
       <c r="H400" t="s">
-        <v>699</v>
+        <v>1433</v>
       </c>
       <c r="J400" t="s">
         <v>67</v>
@@ -10391,13 +10382,13 @@
     </row>
     <row r="401" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A401" s="1" t="s">
-        <v>1017</v>
+        <v>983</v>
       </c>
       <c r="G401" t="s">
-        <v>750</v>
+        <v>700</v>
       </c>
       <c r="H401" t="s">
-        <v>1436</v>
+        <v>701</v>
       </c>
       <c r="J401" t="s">
         <v>67</v>
@@ -10405,13 +10396,13 @@
     </row>
     <row r="402" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A402" s="1" t="s">
-        <v>983</v>
+        <v>962</v>
       </c>
       <c r="G402" t="s">
-        <v>700</v>
+        <v>441</v>
       </c>
       <c r="H402" t="s">
-        <v>701</v>
+        <v>450</v>
       </c>
       <c r="J402" t="s">
         <v>67</v>
@@ -10419,13 +10410,13 @@
     </row>
     <row r="403" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A403" s="1" t="s">
-        <v>962</v>
+        <v>1020</v>
       </c>
       <c r="G403" t="s">
-        <v>441</v>
+        <v>228</v>
       </c>
       <c r="H403" t="s">
-        <v>450</v>
+        <v>1434</v>
       </c>
       <c r="J403" t="s">
         <v>67</v>
@@ -10433,13 +10424,13 @@
     </row>
     <row r="404" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A404" s="1" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="G404" t="s">
-        <v>228</v>
+        <v>517</v>
       </c>
       <c r="H404" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="J404" t="s">
         <v>67</v>
@@ -10447,13 +10438,13 @@
     </row>
     <row r="405" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A405" s="1" t="s">
-        <v>1024</v>
+        <v>999</v>
       </c>
       <c r="G405" t="s">
-        <v>517</v>
+        <v>739</v>
       </c>
       <c r="H405" t="s">
-        <v>1438</v>
+        <v>1031</v>
       </c>
       <c r="J405" t="s">
         <v>67</v>
@@ -10461,13 +10452,13 @@
     </row>
     <row r="406" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A406" s="1" t="s">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="G406" t="s">
-        <v>739</v>
+        <v>716</v>
       </c>
       <c r="H406" t="s">
-        <v>1031</v>
+        <v>724</v>
       </c>
       <c r="J406" t="s">
         <v>67</v>
@@ -10475,13 +10466,13 @@
     </row>
     <row r="407" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A407" s="1" t="s">
-        <v>1003</v>
+        <v>1019</v>
       </c>
       <c r="G407" t="s">
-        <v>716</v>
+        <v>761</v>
       </c>
       <c r="H407" t="s">
-        <v>724</v>
+        <v>1436</v>
       </c>
       <c r="J407" t="s">
         <v>67</v>
@@ -10489,13 +10480,13 @@
     </row>
     <row r="408" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A408" s="1" t="s">
-        <v>1019</v>
+        <v>963</v>
       </c>
       <c r="G408" t="s">
-        <v>761</v>
+        <v>441</v>
       </c>
       <c r="H408" t="s">
-        <v>1439</v>
+        <v>447</v>
       </c>
       <c r="J408" t="s">
         <v>67</v>
@@ -10503,13 +10494,13 @@
     </row>
     <row r="409" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A409" s="1" t="s">
-        <v>963</v>
+        <v>1025</v>
       </c>
       <c r="G409" t="s">
-        <v>441</v>
+        <v>677</v>
       </c>
       <c r="H409" t="s">
-        <v>447</v>
+        <v>1437</v>
       </c>
       <c r="J409" t="s">
         <v>67</v>
@@ -10517,13 +10508,13 @@
     </row>
     <row r="410" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A410" s="1" t="s">
-        <v>1025</v>
+        <v>980</v>
       </c>
       <c r="G410" t="s">
-        <v>677</v>
+        <v>702</v>
       </c>
       <c r="H410" t="s">
-        <v>1440</v>
+        <v>703</v>
       </c>
       <c r="J410" t="s">
         <v>67</v>
@@ -10531,13 +10522,13 @@
     </row>
     <row r="411" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A411" s="1" t="s">
-        <v>980</v>
+        <v>1335</v>
       </c>
       <c r="G411" t="s">
-        <v>702</v>
+        <v>1356</v>
       </c>
       <c r="H411" t="s">
-        <v>703</v>
+        <v>1386</v>
       </c>
       <c r="J411" t="s">
         <v>67</v>
@@ -10545,13 +10536,13 @@
     </row>
     <row r="412" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A412" s="1" t="s">
-        <v>1336</v>
+        <v>961</v>
       </c>
       <c r="G412" t="s">
-        <v>1358</v>
+        <v>441</v>
       </c>
       <c r="H412" t="s">
-        <v>1388</v>
+        <v>451</v>
       </c>
       <c r="J412" t="s">
         <v>67</v>
@@ -10559,13 +10550,13 @@
     </row>
     <row r="413" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A413" s="1" t="s">
-        <v>961</v>
+        <v>979</v>
       </c>
       <c r="G413" t="s">
-        <v>441</v>
+        <v>507</v>
       </c>
       <c r="H413" t="s">
-        <v>451</v>
+        <v>508</v>
       </c>
       <c r="J413" t="s">
         <v>67</v>
@@ -10573,13 +10564,13 @@
     </row>
     <row r="414" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A414" s="1" t="s">
-        <v>979</v>
+        <v>1005</v>
       </c>
       <c r="G414" t="s">
-        <v>507</v>
+        <v>721</v>
       </c>
       <c r="H414" t="s">
-        <v>508</v>
+        <v>722</v>
       </c>
       <c r="J414" t="s">
         <v>67</v>
@@ -10587,13 +10578,13 @@
     </row>
     <row r="415" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A415" s="1" t="s">
-        <v>1005</v>
+        <v>964</v>
       </c>
       <c r="G415" t="s">
-        <v>721</v>
+        <v>454</v>
       </c>
       <c r="H415" t="s">
-        <v>722</v>
+        <v>455</v>
       </c>
       <c r="J415" t="s">
         <v>67</v>
@@ -10601,13 +10592,13 @@
     </row>
     <row r="416" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A416" s="1" t="s">
-        <v>964</v>
+        <v>1015</v>
       </c>
       <c r="G416" t="s">
-        <v>454</v>
+        <v>616</v>
       </c>
       <c r="H416" t="s">
-        <v>455</v>
+        <v>617</v>
       </c>
       <c r="J416" t="s">
         <v>67</v>
@@ -10615,13 +10606,13 @@
     </row>
     <row r="417" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A417" s="1" t="s">
-        <v>1015</v>
+        <v>968</v>
       </c>
       <c r="G417" t="s">
-        <v>616</v>
+        <v>665</v>
       </c>
       <c r="H417" t="s">
-        <v>617</v>
+        <v>666</v>
       </c>
       <c r="J417" t="s">
         <v>67</v>
@@ -10629,13 +10620,13 @@
     </row>
     <row r="418" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A418" s="1" t="s">
-        <v>968</v>
+        <v>1021</v>
       </c>
       <c r="G418" t="s">
-        <v>665</v>
+        <v>783</v>
       </c>
       <c r="H418" t="s">
-        <v>666</v>
+        <v>1438</v>
       </c>
       <c r="J418" t="s">
         <v>67</v>
@@ -10643,13 +10634,13 @@
     </row>
     <row r="419" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A419" s="1" t="s">
-        <v>1021</v>
+        <v>989</v>
       </c>
       <c r="G419" t="s">
-        <v>783</v>
+        <v>284</v>
       </c>
       <c r="H419" t="s">
-        <v>1441</v>
+        <v>285</v>
       </c>
       <c r="J419" t="s">
         <v>67</v>
@@ -10657,13 +10648,13 @@
     </row>
     <row r="420" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A420" s="1" t="s">
-        <v>989</v>
+        <v>1002</v>
       </c>
       <c r="G420" t="s">
-        <v>284</v>
+        <v>717</v>
       </c>
       <c r="H420" t="s">
-        <v>285</v>
+        <v>718</v>
       </c>
       <c r="J420" t="s">
         <v>67</v>
@@ -10671,13 +10662,13 @@
     </row>
     <row r="421" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A421" s="1" t="s">
-        <v>1002</v>
+        <v>953</v>
       </c>
       <c r="G421" t="s">
-        <v>717</v>
+        <v>521</v>
       </c>
       <c r="H421" t="s">
-        <v>718</v>
+        <v>522</v>
       </c>
       <c r="J421" t="s">
         <v>67</v>
@@ -10685,13 +10676,13 @@
     </row>
     <row r="422" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A422" s="1" t="s">
-        <v>953</v>
+        <v>1011</v>
       </c>
       <c r="G422" t="s">
-        <v>521</v>
+        <v>130</v>
       </c>
       <c r="H422" t="s">
-        <v>522</v>
+        <v>131</v>
       </c>
       <c r="J422" t="s">
         <v>67</v>
@@ -10699,13 +10690,13 @@
     </row>
     <row r="423" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A423" s="1" t="s">
-        <v>1011</v>
+        <v>986</v>
       </c>
       <c r="G423" t="s">
-        <v>130</v>
+        <v>695</v>
       </c>
       <c r="H423" t="s">
-        <v>131</v>
+        <v>696</v>
       </c>
       <c r="J423" t="s">
         <v>67</v>
@@ -10713,13 +10704,13 @@
     </row>
     <row r="424" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A424" s="1" t="s">
-        <v>986</v>
+        <v>1014</v>
       </c>
       <c r="G424" t="s">
-        <v>695</v>
+        <v>618</v>
       </c>
       <c r="H424" t="s">
-        <v>696</v>
+        <v>619</v>
       </c>
       <c r="J424" t="s">
         <v>67</v>
@@ -10727,13 +10718,13 @@
     </row>
     <row r="425" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A425" s="1" t="s">
-        <v>1014</v>
+        <v>1336</v>
       </c>
       <c r="G425" t="s">
-        <v>618</v>
+        <v>774</v>
       </c>
       <c r="H425" t="s">
-        <v>619</v>
+        <v>1387</v>
       </c>
       <c r="J425" t="s">
         <v>67</v>
@@ -10741,13 +10732,13 @@
     </row>
     <row r="426" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A426" s="1" t="s">
-        <v>1337</v>
+        <v>994</v>
       </c>
       <c r="G426" t="s">
-        <v>774</v>
+        <v>727</v>
       </c>
       <c r="H426" t="s">
-        <v>1389</v>
+        <v>728</v>
       </c>
       <c r="J426" t="s">
         <v>67</v>
@@ -10755,13 +10746,13 @@
     </row>
     <row r="427" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A427" s="1" t="s">
-        <v>994</v>
+        <v>1029</v>
       </c>
       <c r="G427" t="s">
-        <v>727</v>
+        <v>1357</v>
       </c>
       <c r="H427" t="s">
-        <v>728</v>
+        <v>1439</v>
       </c>
       <c r="J427" t="s">
         <v>67</v>
@@ -10769,13 +10760,13 @@
     </row>
     <row r="428" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A428" s="1" t="s">
-        <v>1029</v>
+        <v>1022</v>
       </c>
       <c r="G428" t="s">
-        <v>1359</v>
+        <v>731</v>
       </c>
       <c r="H428" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
       <c r="J428" t="s">
         <v>67</v>
@@ -10783,13 +10774,13 @@
     </row>
     <row r="429" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A429" s="1" t="s">
-        <v>1022</v>
+        <v>954</v>
       </c>
       <c r="G429" t="s">
-        <v>731</v>
+        <v>517</v>
       </c>
       <c r="H429" t="s">
-        <v>1443</v>
+        <v>1030</v>
       </c>
       <c r="J429" t="s">
         <v>67</v>
@@ -10797,13 +10788,13 @@
     </row>
     <row r="430" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A430" s="1" t="s">
-        <v>954</v>
+        <v>1337</v>
       </c>
       <c r="G430" t="s">
-        <v>517</v>
+        <v>734</v>
       </c>
       <c r="H430" t="s">
-        <v>1030</v>
+        <v>1388</v>
       </c>
       <c r="J430" t="s">
         <v>67</v>
@@ -10811,13 +10802,13 @@
     </row>
     <row r="431" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A431" s="1" t="s">
-        <v>1338</v>
+        <v>1018</v>
       </c>
       <c r="G431" t="s">
-        <v>734</v>
+        <v>716</v>
       </c>
       <c r="H431" t="s">
-        <v>1390</v>
+        <v>1441</v>
       </c>
       <c r="J431" t="s">
         <v>67</v>
@@ -10825,13 +10816,13 @@
     </row>
     <row r="432" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A432" s="1" t="s">
-        <v>1018</v>
+        <v>971</v>
       </c>
       <c r="G432" t="s">
-        <v>716</v>
+        <v>660</v>
       </c>
       <c r="H432" t="s">
-        <v>1444</v>
+        <v>663</v>
       </c>
       <c r="J432" t="s">
         <v>67</v>
@@ -10839,13 +10830,13 @@
     </row>
     <row r="433" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A433" s="1" t="s">
-        <v>971</v>
+        <v>1338</v>
       </c>
       <c r="G433" t="s">
-        <v>660</v>
+        <v>734</v>
       </c>
       <c r="H433" t="s">
-        <v>663</v>
+        <v>1389</v>
       </c>
       <c r="J433" t="s">
         <v>67</v>
@@ -10853,13 +10844,13 @@
     </row>
     <row r="434" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A434" s="1" t="s">
-        <v>1339</v>
+        <v>995</v>
       </c>
       <c r="G434" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="H434" t="s">
-        <v>1391</v>
+        <v>726</v>
       </c>
       <c r="J434" t="s">
         <v>67</v>
@@ -10867,13 +10858,13 @@
     </row>
     <row r="435" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A435" s="1" t="s">
-        <v>995</v>
+        <v>987</v>
       </c>
       <c r="G435" t="s">
-        <v>725</v>
+        <v>677</v>
       </c>
       <c r="H435" t="s">
-        <v>726</v>
+        <v>678</v>
       </c>
       <c r="J435" t="s">
         <v>67</v>
@@ -10881,13 +10872,13 @@
     </row>
     <row r="436" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A436" s="1" t="s">
-        <v>987</v>
+        <v>969</v>
       </c>
       <c r="G436" t="s">
-        <v>677</v>
+        <v>661</v>
       </c>
       <c r="H436" t="s">
-        <v>678</v>
+        <v>662</v>
       </c>
       <c r="J436" t="s">
         <v>67</v>
@@ -10895,13 +10886,13 @@
     </row>
     <row r="437" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A437" s="1" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="G437" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H437" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="J437" t="s">
         <v>67</v>
@@ -10909,13 +10900,13 @@
     </row>
     <row r="438" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A438" s="1" t="s">
-        <v>970</v>
+        <v>1006</v>
       </c>
       <c r="G438" t="s">
-        <v>660</v>
+        <v>719</v>
       </c>
       <c r="H438" t="s">
-        <v>664</v>
+        <v>720</v>
       </c>
       <c r="J438" t="s">
         <v>67</v>
@@ -10923,13 +10914,13 @@
     </row>
     <row r="439" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A439" s="1" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="G439" t="s">
-        <v>719</v>
+        <v>729</v>
       </c>
       <c r="H439" t="s">
-        <v>720</v>
+        <v>730</v>
       </c>
       <c r="J439" t="s">
         <v>67</v>
@@ -10937,13 +10928,13 @@
     </row>
     <row r="440" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A440" s="1" t="s">
-        <v>1004</v>
+        <v>972</v>
       </c>
       <c r="G440" t="s">
-        <v>729</v>
+        <v>510</v>
       </c>
       <c r="H440" t="s">
-        <v>730</v>
+        <v>511</v>
       </c>
       <c r="J440" t="s">
         <v>67</v>
@@ -10951,13 +10942,13 @@
     </row>
     <row r="441" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A441" s="1" t="s">
-        <v>972</v>
+        <v>1001</v>
       </c>
       <c r="G441" t="s">
-        <v>510</v>
+        <v>716</v>
       </c>
       <c r="H441" t="s">
-        <v>511</v>
+        <v>733</v>
       </c>
       <c r="J441" t="s">
         <v>67</v>
@@ -10965,13 +10956,13 @@
     </row>
     <row r="442" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A442" s="1" t="s">
-        <v>1001</v>
+        <v>988</v>
       </c>
       <c r="G442" t="s">
-        <v>716</v>
+        <v>675</v>
       </c>
       <c r="H442" t="s">
-        <v>733</v>
+        <v>676</v>
       </c>
       <c r="J442" t="s">
         <v>67</v>
@@ -10979,13 +10970,13 @@
     </row>
     <row r="443" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A443" s="1" t="s">
-        <v>988</v>
+        <v>1007</v>
       </c>
       <c r="G443" t="s">
-        <v>675</v>
+        <v>731</v>
       </c>
       <c r="H443" t="s">
-        <v>676</v>
+        <v>732</v>
       </c>
       <c r="J443" t="s">
         <v>67</v>
@@ -10993,13 +10984,13 @@
     </row>
     <row r="444" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A444" s="1" t="s">
-        <v>1007</v>
+        <v>1026</v>
       </c>
       <c r="G444" t="s">
-        <v>731</v>
+        <v>1358</v>
       </c>
       <c r="H444" t="s">
-        <v>732</v>
+        <v>1442</v>
       </c>
       <c r="J444" t="s">
         <v>67</v>
@@ -11007,13 +10998,13 @@
     </row>
     <row r="445" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A445" s="1" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="G445" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="H445" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="J445" t="s">
         <v>67</v>
@@ -11021,13 +11012,13 @@
     </row>
     <row r="446" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A446" s="1" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="G446" t="s">
-        <v>1361</v>
+        <v>441</v>
       </c>
       <c r="H446" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="J446" t="s">
         <v>67</v>
@@ -11035,97 +11026,97 @@
     </row>
     <row r="447" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A447" s="1" t="s">
-        <v>1028</v>
+        <v>1009</v>
       </c>
       <c r="G447" t="s">
-        <v>441</v>
+        <v>132</v>
       </c>
       <c r="H447" t="s">
-        <v>1447</v>
+        <v>133</v>
       </c>
       <c r="J447" t="s">
-        <v>67</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="448" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A448" s="1" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="G448" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="H448" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="J448" t="s">
-        <v>1461</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="449" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A449" s="1" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="G449" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="H449" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="J449" t="s">
-        <v>1461</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="450" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A450" s="1" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="G450" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H450" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J450" t="s">
-        <v>1461</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="451" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A451" s="1" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="G451" t="s">
-        <v>142</v>
+        <v>74</v>
       </c>
       <c r="H451" t="s">
-        <v>143</v>
+        <v>75</v>
       </c>
       <c r="J451" t="s">
-        <v>1461</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="452" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A452" s="1" t="s">
-        <v>1016</v>
+        <v>899</v>
       </c>
       <c r="G452" t="s">
-        <v>74</v>
+        <v>157</v>
       </c>
       <c r="H452" t="s">
-        <v>75</v>
+        <v>951</v>
       </c>
       <c r="J452" t="s">
-        <v>1461</v>
+        <v>51</v>
       </c>
     </row>
     <row r="453" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A453" s="1" t="s">
-        <v>899</v>
+        <v>922</v>
       </c>
       <c r="G453" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="H453" t="s">
-        <v>951</v>
+        <v>174</v>
       </c>
       <c r="J453" t="s">
         <v>51</v>
@@ -11133,13 +11124,13 @@
     </row>
     <row r="454" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A454" s="1" t="s">
-        <v>922</v>
+        <v>893</v>
       </c>
       <c r="G454" t="s">
-        <v>173</v>
+        <v>427</v>
       </c>
       <c r="H454" t="s">
-        <v>174</v>
+        <v>428</v>
       </c>
       <c r="J454" t="s">
         <v>51</v>
@@ -11147,13 +11138,13 @@
     </row>
     <row r="455" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A455" s="1" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="G455" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="H455" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="J455" t="s">
         <v>51</v>
@@ -11161,13 +11152,13 @@
     </row>
     <row r="456" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A456" s="1" t="s">
-        <v>886</v>
+        <v>927</v>
       </c>
       <c r="G456" t="s">
-        <v>423</v>
+        <v>351</v>
       </c>
       <c r="H456" t="s">
-        <v>424</v>
+        <v>352</v>
       </c>
       <c r="J456" t="s">
         <v>51</v>
@@ -11175,13 +11166,13 @@
     </row>
     <row r="457" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A457" s="1" t="s">
-        <v>927</v>
+        <v>887</v>
       </c>
       <c r="G457" t="s">
-        <v>351</v>
+        <v>596</v>
       </c>
       <c r="H457" t="s">
-        <v>352</v>
+        <v>597</v>
       </c>
       <c r="J457" t="s">
         <v>51</v>
@@ -11189,13 +11180,13 @@
     </row>
     <row r="458" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A458" s="1" t="s">
-        <v>887</v>
+        <v>892</v>
       </c>
       <c r="G458" t="s">
-        <v>596</v>
+        <v>49</v>
       </c>
       <c r="H458" t="s">
-        <v>597</v>
+        <v>50</v>
       </c>
       <c r="J458" t="s">
         <v>51</v>
@@ -11203,13 +11194,13 @@
     </row>
     <row r="459" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A459" s="1" t="s">
-        <v>892</v>
+        <v>904</v>
       </c>
       <c r="G459" t="s">
-        <v>49</v>
+        <v>416</v>
       </c>
       <c r="H459" t="s">
-        <v>50</v>
+        <v>417</v>
       </c>
       <c r="J459" t="s">
         <v>51</v>
@@ -11217,13 +11208,13 @@
     </row>
     <row r="460" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A460" s="1" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="G460" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="H460" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="J460" t="s">
         <v>51</v>
@@ -11231,13 +11222,13 @@
     </row>
     <row r="461" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A461" s="1" t="s">
-        <v>905</v>
+        <v>888</v>
       </c>
       <c r="G461" t="s">
-        <v>413</v>
+        <v>595</v>
       </c>
       <c r="H461" t="s">
-        <v>414</v>
+        <v>602</v>
       </c>
       <c r="J461" t="s">
         <v>51</v>
@@ -11245,13 +11236,13 @@
     </row>
     <row r="462" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A462" s="1" t="s">
-        <v>888</v>
+        <v>882</v>
       </c>
       <c r="G462" t="s">
-        <v>595</v>
+        <v>61</v>
       </c>
       <c r="H462" t="s">
-        <v>602</v>
+        <v>62</v>
       </c>
       <c r="J462" t="s">
         <v>51</v>
@@ -11259,13 +11250,13 @@
     </row>
     <row r="463" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A463" s="1" t="s">
-        <v>882</v>
+        <v>895</v>
       </c>
       <c r="G463" t="s">
-        <v>61</v>
+        <v>433</v>
       </c>
       <c r="H463" t="s">
-        <v>62</v>
+        <v>434</v>
       </c>
       <c r="J463" t="s">
         <v>51</v>
@@ -11273,13 +11264,13 @@
     </row>
     <row r="464" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A464" s="1" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
       <c r="G464" t="s">
-        <v>433</v>
+        <v>600</v>
       </c>
       <c r="H464" t="s">
-        <v>434</v>
+        <v>601</v>
       </c>
       <c r="J464" t="s">
         <v>51</v>
@@ -11287,13 +11278,13 @@
     </row>
     <row r="465" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A465" s="1" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="G465" t="s">
-        <v>600</v>
+        <v>418</v>
       </c>
       <c r="H465" t="s">
-        <v>601</v>
+        <v>419</v>
       </c>
       <c r="J465" t="s">
         <v>51</v>
@@ -11301,13 +11292,13 @@
     </row>
     <row r="466" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A466" s="1" t="s">
-        <v>885</v>
+        <v>928</v>
       </c>
       <c r="G466" t="s">
-        <v>418</v>
+        <v>355</v>
       </c>
       <c r="H466" t="s">
-        <v>419</v>
+        <v>356</v>
       </c>
       <c r="J466" t="s">
         <v>51</v>
@@ -11315,13 +11306,13 @@
     </row>
     <row r="467" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A467" s="1" t="s">
-        <v>928</v>
+        <v>907</v>
       </c>
       <c r="G467" t="s">
-        <v>355</v>
+        <v>413</v>
       </c>
       <c r="H467" t="s">
-        <v>356</v>
+        <v>432</v>
       </c>
       <c r="J467" t="s">
         <v>51</v>
@@ -11329,13 +11320,13 @@
     </row>
     <row r="468" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A468" s="1" t="s">
-        <v>907</v>
+        <v>921</v>
       </c>
       <c r="G468" t="s">
-        <v>413</v>
+        <v>181</v>
       </c>
       <c r="H468" t="s">
-        <v>432</v>
+        <v>182</v>
       </c>
       <c r="J468" t="s">
         <v>51</v>
@@ -11343,13 +11334,13 @@
     </row>
     <row r="469" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A469" s="1" t="s">
-        <v>921</v>
+        <v>906</v>
       </c>
       <c r="G469" t="s">
-        <v>181</v>
+        <v>413</v>
       </c>
       <c r="H469" t="s">
-        <v>182</v>
+        <v>435</v>
       </c>
       <c r="J469" t="s">
         <v>51</v>
@@ -11357,13 +11348,13 @@
     </row>
     <row r="470" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A470" s="1" t="s">
-        <v>906</v>
+        <v>930</v>
       </c>
       <c r="G470" t="s">
-        <v>413</v>
+        <v>347</v>
       </c>
       <c r="H470" t="s">
-        <v>435</v>
+        <v>348</v>
       </c>
       <c r="J470" t="s">
         <v>51</v>
@@ -11371,13 +11362,13 @@
     </row>
     <row r="471" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A471" s="1" t="s">
-        <v>930</v>
+        <v>920</v>
       </c>
       <c r="G471" t="s">
-        <v>347</v>
+        <v>183</v>
       </c>
       <c r="H471" t="s">
-        <v>348</v>
+        <v>184</v>
       </c>
       <c r="J471" t="s">
         <v>51</v>
@@ -11385,13 +11376,13 @@
     </row>
     <row r="472" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A472" s="1" t="s">
-        <v>920</v>
+        <v>908</v>
       </c>
       <c r="G472" t="s">
-        <v>183</v>
+        <v>413</v>
       </c>
       <c r="H472" t="s">
-        <v>184</v>
+        <v>429</v>
       </c>
       <c r="J472" t="s">
         <v>51</v>
@@ -11399,13 +11390,13 @@
     </row>
     <row r="473" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A473" s="1" t="s">
-        <v>908</v>
+        <v>900</v>
       </c>
       <c r="G473" t="s">
-        <v>413</v>
+        <v>162</v>
       </c>
       <c r="H473" t="s">
-        <v>429</v>
+        <v>163</v>
       </c>
       <c r="J473" t="s">
         <v>51</v>
@@ -11413,13 +11404,13 @@
     </row>
     <row r="474" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A474" s="1" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="G474" t="s">
-        <v>162</v>
+        <v>68</v>
       </c>
       <c r="H474" t="s">
-        <v>163</v>
+        <v>69</v>
       </c>
       <c r="J474" t="s">
         <v>51</v>
@@ -11427,13 +11418,13 @@
     </row>
     <row r="475" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A475" s="1" t="s">
-        <v>897</v>
+        <v>936</v>
       </c>
       <c r="G475" t="s">
-        <v>68</v>
+        <v>458</v>
       </c>
       <c r="H475" t="s">
-        <v>69</v>
+        <v>1445</v>
       </c>
       <c r="J475" t="s">
         <v>51</v>
@@ -11441,13 +11432,13 @@
     </row>
     <row r="476" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A476" s="1" t="s">
-        <v>936</v>
+        <v>894</v>
       </c>
       <c r="G476" t="s">
-        <v>458</v>
+        <v>430</v>
       </c>
       <c r="H476" t="s">
-        <v>1448</v>
+        <v>431</v>
       </c>
       <c r="J476" t="s">
         <v>51</v>
@@ -11455,13 +11446,13 @@
     </row>
     <row r="477" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A477" s="1" t="s">
-        <v>894</v>
+        <v>933</v>
       </c>
       <c r="G477" t="s">
-        <v>430</v>
+        <v>170</v>
       </c>
       <c r="H477" t="s">
-        <v>431</v>
+        <v>129</v>
       </c>
       <c r="J477" t="s">
         <v>51</v>
@@ -11469,13 +11460,13 @@
     </row>
     <row r="478" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A478" s="1" t="s">
-        <v>933</v>
+        <v>901</v>
       </c>
       <c r="G478" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="H478" t="s">
-        <v>129</v>
+        <v>165</v>
       </c>
       <c r="J478" t="s">
         <v>51</v>
@@ -11483,13 +11474,13 @@
     </row>
     <row r="479" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A479" s="1" t="s">
-        <v>901</v>
+        <v>896</v>
       </c>
       <c r="G479" t="s">
-        <v>164</v>
+        <v>421</v>
       </c>
       <c r="H479" t="s">
-        <v>165</v>
+        <v>422</v>
       </c>
       <c r="J479" t="s">
         <v>51</v>
@@ -11497,13 +11488,13 @@
     </row>
     <row r="480" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A480" s="1" t="s">
-        <v>896</v>
+        <v>940</v>
       </c>
       <c r="G480" t="s">
-        <v>421</v>
+        <v>758</v>
       </c>
       <c r="H480" t="s">
-        <v>422</v>
+        <v>1446</v>
       </c>
       <c r="J480" t="s">
         <v>51</v>
@@ -11511,13 +11502,13 @@
     </row>
     <row r="481" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A481" s="1" t="s">
-        <v>940</v>
+        <v>912</v>
       </c>
       <c r="G481" t="s">
-        <v>758</v>
+        <v>512</v>
       </c>
       <c r="H481" t="s">
-        <v>1449</v>
+        <v>513</v>
       </c>
       <c r="J481" t="s">
         <v>51</v>
@@ -11525,13 +11516,13 @@
     </row>
     <row r="482" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A482" s="1" t="s">
-        <v>912</v>
+        <v>902</v>
       </c>
       <c r="G482" t="s">
-        <v>512</v>
+        <v>158</v>
       </c>
       <c r="H482" t="s">
-        <v>513</v>
+        <v>159</v>
       </c>
       <c r="J482" t="s">
         <v>51</v>
@@ -11539,13 +11530,13 @@
     </row>
     <row r="483" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A483" s="1" t="s">
-        <v>902</v>
+        <v>948</v>
       </c>
       <c r="G483" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="H483" t="s">
-        <v>159</v>
+        <v>1447</v>
       </c>
       <c r="J483" t="s">
         <v>51</v>
@@ -11553,13 +11544,13 @@
     </row>
     <row r="484" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A484" s="1" t="s">
-        <v>948</v>
+        <v>909</v>
       </c>
       <c r="G484" t="s">
-        <v>179</v>
+        <v>413</v>
       </c>
       <c r="H484" t="s">
-        <v>1450</v>
+        <v>415</v>
       </c>
       <c r="J484" t="s">
         <v>51</v>
@@ -11567,13 +11558,13 @@
     </row>
     <row r="485" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A485" s="1" t="s">
-        <v>909</v>
+        <v>914</v>
       </c>
       <c r="G485" t="s">
-        <v>413</v>
+        <v>63</v>
       </c>
       <c r="H485" t="s">
-        <v>415</v>
+        <v>64</v>
       </c>
       <c r="J485" t="s">
         <v>51</v>
@@ -11581,13 +11572,13 @@
     </row>
     <row r="486" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A486" s="1" t="s">
-        <v>914</v>
+        <v>932</v>
       </c>
       <c r="G486" t="s">
-        <v>63</v>
+        <v>179</v>
       </c>
       <c r="H486" t="s">
-        <v>64</v>
+        <v>180</v>
       </c>
       <c r="J486" t="s">
         <v>51</v>
@@ -11595,13 +11586,13 @@
     </row>
     <row r="487" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A487" s="1" t="s">
-        <v>932</v>
+        <v>903</v>
       </c>
       <c r="G487" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="H487" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="J487" t="s">
         <v>51</v>
@@ -11609,13 +11600,13 @@
     </row>
     <row r="488" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A488" s="1" t="s">
-        <v>903</v>
+        <v>946</v>
       </c>
       <c r="G488" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="H488" t="s">
-        <v>168</v>
+        <v>1448</v>
       </c>
       <c r="J488" t="s">
         <v>51</v>
@@ -11623,13 +11614,13 @@
     </row>
     <row r="489" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A489" s="1" t="s">
-        <v>946</v>
+        <v>935</v>
       </c>
       <c r="G489" t="s">
-        <v>183</v>
+        <v>346</v>
       </c>
       <c r="H489" t="s">
-        <v>1451</v>
+        <v>358</v>
       </c>
       <c r="J489" t="s">
         <v>51</v>
@@ -11637,13 +11628,13 @@
     </row>
     <row r="490" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A490" s="1" t="s">
-        <v>935</v>
+        <v>929</v>
       </c>
       <c r="G490" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="H490" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="J490" t="s">
         <v>51</v>
@@ -11651,13 +11642,13 @@
     </row>
     <row r="491" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A491" s="1" t="s">
-        <v>929</v>
+        <v>934</v>
       </c>
       <c r="G491" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="H491" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="J491" t="s">
         <v>51</v>
@@ -11665,13 +11656,13 @@
     </row>
     <row r="492" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A492" s="1" t="s">
-        <v>934</v>
+        <v>891</v>
       </c>
       <c r="G492" t="s">
-        <v>346</v>
+        <v>425</v>
       </c>
       <c r="H492" t="s">
-        <v>357</v>
+        <v>426</v>
       </c>
       <c r="J492" t="s">
         <v>51</v>
@@ -11679,13 +11670,13 @@
     </row>
     <row r="493" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A493" s="1" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="G493" t="s">
-        <v>425</v>
+        <v>598</v>
       </c>
       <c r="H493" t="s">
-        <v>426</v>
+        <v>599</v>
       </c>
       <c r="J493" t="s">
         <v>51</v>
@@ -11693,13 +11684,13 @@
     </row>
     <row r="494" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A494" s="1" t="s">
-        <v>890</v>
+        <v>924</v>
       </c>
       <c r="G494" t="s">
-        <v>598</v>
+        <v>177</v>
       </c>
       <c r="H494" t="s">
-        <v>599</v>
+        <v>178</v>
       </c>
       <c r="J494" t="s">
         <v>51</v>
@@ -11707,13 +11698,13 @@
     </row>
     <row r="495" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A495" s="1" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="G495" t="s">
-        <v>177</v>
+        <v>349</v>
       </c>
       <c r="H495" t="s">
-        <v>178</v>
+        <v>350</v>
       </c>
       <c r="J495" t="s">
         <v>51</v>
@@ -11721,13 +11712,13 @@
     </row>
     <row r="496" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A496" s="1" t="s">
-        <v>931</v>
+        <v>1339</v>
       </c>
       <c r="G496" t="s">
-        <v>349</v>
+        <v>779</v>
       </c>
       <c r="H496" t="s">
-        <v>350</v>
+        <v>1390</v>
       </c>
       <c r="J496" t="s">
         <v>51</v>
@@ -11735,13 +11726,13 @@
     </row>
     <row r="497" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A497" s="1" t="s">
-        <v>1340</v>
+        <v>910</v>
       </c>
       <c r="G497" t="s">
-        <v>779</v>
+        <v>413</v>
       </c>
       <c r="H497" t="s">
-        <v>1392</v>
+        <v>420</v>
       </c>
       <c r="J497" t="s">
         <v>51</v>
@@ -11749,13 +11740,13 @@
     </row>
     <row r="498" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A498" s="1" t="s">
-        <v>910</v>
+        <v>919</v>
       </c>
       <c r="G498" t="s">
-        <v>413</v>
+        <v>459</v>
       </c>
       <c r="H498" t="s">
-        <v>420</v>
+        <v>460</v>
       </c>
       <c r="J498" t="s">
         <v>51</v>
@@ -11763,13 +11754,13 @@
     </row>
     <row r="499" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A499" s="1" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="G499" t="s">
-        <v>459</v>
+        <v>169</v>
       </c>
       <c r="H499" t="s">
-        <v>460</v>
+        <v>171</v>
       </c>
       <c r="J499" t="s">
         <v>51</v>
@@ -11777,13 +11768,13 @@
     </row>
     <row r="500" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A500" s="1" t="s">
-        <v>923</v>
+        <v>898</v>
       </c>
       <c r="G500" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="H500" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="J500" t="s">
         <v>51</v>
@@ -11791,13 +11782,13 @@
     </row>
     <row r="501" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A501" s="1" t="s">
-        <v>898</v>
+        <v>926</v>
       </c>
       <c r="G501" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="H501" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="J501" t="s">
         <v>51</v>
@@ -11805,13 +11796,13 @@
     </row>
     <row r="502" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A502" s="1" t="s">
-        <v>926</v>
+        <v>883</v>
       </c>
       <c r="G502" t="s">
-        <v>175</v>
+        <v>58</v>
       </c>
       <c r="H502" t="s">
-        <v>176</v>
+        <v>59</v>
       </c>
       <c r="J502" t="s">
         <v>51</v>
@@ -11819,13 +11810,13 @@
     </row>
     <row r="503" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A503" s="1" t="s">
-        <v>883</v>
+        <v>949</v>
       </c>
       <c r="G503" t="s">
-        <v>58</v>
+        <v>785</v>
       </c>
       <c r="H503" t="s">
-        <v>59</v>
+        <v>1449</v>
       </c>
       <c r="J503" t="s">
         <v>51</v>
@@ -11833,13 +11824,13 @@
     </row>
     <row r="504" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A504" s="1" t="s">
-        <v>949</v>
+        <v>878</v>
       </c>
       <c r="G504" t="s">
-        <v>785</v>
+        <v>248</v>
       </c>
       <c r="H504" t="s">
-        <v>1452</v>
+        <v>249</v>
       </c>
       <c r="J504" t="s">
         <v>51</v>
@@ -11847,13 +11838,13 @@
     </row>
     <row r="505" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A505" s="1" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="G505" t="s">
-        <v>248</v>
+        <v>52</v>
       </c>
       <c r="H505" t="s">
-        <v>249</v>
+        <v>53</v>
       </c>
       <c r="J505" t="s">
         <v>51</v>
@@ -11861,13 +11852,13 @@
     </row>
     <row r="506" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A506" s="1" t="s">
-        <v>881</v>
+        <v>915</v>
       </c>
       <c r="G506" t="s">
         <v>52</v>
       </c>
       <c r="H506" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J506" t="s">
         <v>51</v>
@@ -11875,13 +11866,13 @@
     </row>
     <row r="507" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A507" s="1" t="s">
-        <v>915</v>
+        <v>1340</v>
       </c>
       <c r="G507" t="s">
-        <v>52</v>
+        <v>776</v>
       </c>
       <c r="H507" t="s">
-        <v>60</v>
+        <v>1391</v>
       </c>
       <c r="J507" t="s">
         <v>51</v>
@@ -11889,13 +11880,13 @@
     </row>
     <row r="508" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A508" s="1" t="s">
-        <v>1341</v>
+        <v>877</v>
       </c>
       <c r="G508" t="s">
-        <v>776</v>
+        <v>247</v>
       </c>
       <c r="H508" t="s">
-        <v>1393</v>
+        <v>254</v>
       </c>
       <c r="J508" t="s">
         <v>51</v>
@@ -11903,13 +11894,13 @@
     </row>
     <row r="509" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A509" s="1" t="s">
-        <v>877</v>
+        <v>925</v>
       </c>
       <c r="G509" t="s">
-        <v>247</v>
+        <v>169</v>
       </c>
       <c r="H509" t="s">
-        <v>254</v>
+        <v>172</v>
       </c>
       <c r="J509" t="s">
         <v>51</v>
@@ -11917,13 +11908,13 @@
     </row>
     <row r="510" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A510" s="1" t="s">
-        <v>925</v>
+        <v>942</v>
       </c>
       <c r="G510" t="s">
-        <v>169</v>
+        <v>759</v>
       </c>
       <c r="H510" t="s">
-        <v>172</v>
+        <v>1419</v>
       </c>
       <c r="J510" t="s">
         <v>51</v>
@@ -11931,13 +11922,13 @@
     </row>
     <row r="511" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A511" s="1" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="G511" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="H511" t="s">
-        <v>1422</v>
+        <v>1450</v>
       </c>
       <c r="J511" t="s">
         <v>51</v>
@@ -11945,13 +11936,13 @@
     </row>
     <row r="512" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A512" s="1" t="s">
-        <v>939</v>
+        <v>918</v>
       </c>
       <c r="G512" t="s">
-        <v>756</v>
+        <v>458</v>
       </c>
       <c r="H512" t="s">
-        <v>1453</v>
+        <v>461</v>
       </c>
       <c r="J512" t="s">
         <v>51</v>
@@ -11959,13 +11950,13 @@
     </row>
     <row r="513" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A513" s="1" t="s">
-        <v>918</v>
+        <v>913</v>
       </c>
       <c r="G513" t="s">
-        <v>458</v>
+        <v>204</v>
       </c>
       <c r="H513" t="s">
-        <v>461</v>
+        <v>205</v>
       </c>
       <c r="J513" t="s">
         <v>51</v>
@@ -11973,13 +11964,13 @@
     </row>
     <row r="514" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A514" s="1" t="s">
-        <v>913</v>
+        <v>938</v>
       </c>
       <c r="G514" t="s">
-        <v>204</v>
+        <v>752</v>
       </c>
       <c r="H514" t="s">
-        <v>205</v>
+        <v>1451</v>
       </c>
       <c r="J514" t="s">
         <v>51</v>
@@ -11987,13 +11978,13 @@
     </row>
     <row r="515" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A515" s="1" t="s">
-        <v>938</v>
+        <v>1341</v>
       </c>
       <c r="G515" t="s">
-        <v>752</v>
+        <v>346</v>
       </c>
       <c r="H515" t="s">
-        <v>1454</v>
+        <v>1392</v>
       </c>
       <c r="J515" t="s">
         <v>51</v>
@@ -12001,13 +11992,13 @@
     </row>
     <row r="516" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A516" s="1" t="s">
-        <v>1342</v>
+        <v>950</v>
       </c>
       <c r="G516" t="s">
-        <v>346</v>
+        <v>1360</v>
       </c>
       <c r="H516" t="s">
-        <v>1394</v>
+        <v>1452</v>
       </c>
       <c r="J516" t="s">
         <v>51</v>
@@ -12015,13 +12006,13 @@
     </row>
     <row r="517" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A517" s="1" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="G517" t="s">
-        <v>1362</v>
+        <v>782</v>
       </c>
       <c r="H517" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="J517" t="s">
         <v>51</v>
@@ -12029,13 +12020,13 @@
     </row>
     <row r="518" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A518" s="1" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
       <c r="G518" t="s">
-        <v>782</v>
+        <v>760</v>
       </c>
       <c r="H518" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="J518" t="s">
         <v>51</v>
@@ -12043,13 +12034,13 @@
     </row>
     <row r="519" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A519" s="1" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="G519" t="s">
-        <v>760</v>
+        <v>52</v>
       </c>
       <c r="H519" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="J519" t="s">
         <v>51</v>
@@ -12057,13 +12048,13 @@
     </row>
     <row r="520" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A520" s="1" t="s">
-        <v>941</v>
+        <v>879</v>
       </c>
       <c r="G520" t="s">
-        <v>52</v>
+        <v>250</v>
       </c>
       <c r="H520" t="s">
-        <v>1458</v>
+        <v>251</v>
       </c>
       <c r="J520" t="s">
         <v>51</v>
@@ -12071,13 +12062,13 @@
     </row>
     <row r="521" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A521" s="1" t="s">
-        <v>879</v>
+        <v>945</v>
       </c>
       <c r="G521" t="s">
-        <v>250</v>
+        <v>769</v>
       </c>
       <c r="H521" t="s">
-        <v>251</v>
+        <v>1456</v>
       </c>
       <c r="J521" t="s">
         <v>51</v>
@@ -12085,13 +12076,13 @@
     </row>
     <row r="522" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A522" s="1" t="s">
-        <v>945</v>
+        <v>884</v>
       </c>
       <c r="G522" t="s">
-        <v>769</v>
+        <v>620</v>
       </c>
       <c r="H522" t="s">
-        <v>1459</v>
+        <v>621</v>
       </c>
       <c r="J522" t="s">
         <v>51</v>
@@ -12099,13 +12090,13 @@
     </row>
     <row r="523" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A523" s="1" t="s">
-        <v>884</v>
+        <v>1342</v>
       </c>
       <c r="G523" t="s">
-        <v>620</v>
+        <v>777</v>
       </c>
       <c r="H523" t="s">
-        <v>621</v>
+        <v>1393</v>
       </c>
       <c r="J523" t="s">
         <v>51</v>
@@ -12113,13 +12104,13 @@
     </row>
     <row r="524" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A524" s="1" t="s">
-        <v>1343</v>
+        <v>944</v>
       </c>
       <c r="G524" t="s">
-        <v>777</v>
+        <v>767</v>
       </c>
       <c r="H524" t="s">
-        <v>1395</v>
+        <v>1457</v>
       </c>
       <c r="J524" t="s">
         <v>51</v>
@@ -12127,13 +12118,13 @@
     </row>
     <row r="525" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A525" s="1" t="s">
-        <v>944</v>
+        <v>1343</v>
       </c>
       <c r="G525" t="s">
-        <v>767</v>
+        <v>778</v>
       </c>
       <c r="H525" t="s">
-        <v>1460</v>
+        <v>1394</v>
       </c>
       <c r="J525" t="s">
         <v>51</v>
@@ -12141,13 +12132,13 @@
     </row>
     <row r="526" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A526" s="1" t="s">
-        <v>1344</v>
+        <v>937</v>
       </c>
       <c r="G526" t="s">
-        <v>778</v>
+        <v>751</v>
       </c>
       <c r="H526" t="s">
-        <v>1396</v>
+        <v>1419</v>
       </c>
       <c r="J526" t="s">
         <v>51</v>
@@ -12155,13 +12146,13 @@
     </row>
     <row r="527" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A527" s="1" t="s">
-        <v>937</v>
+        <v>916</v>
       </c>
       <c r="G527" t="s">
-        <v>751</v>
+        <v>54</v>
       </c>
       <c r="H527" t="s">
-        <v>1422</v>
+        <v>55</v>
       </c>
       <c r="J527" t="s">
         <v>51</v>
@@ -12169,13 +12160,13 @@
     </row>
     <row r="528" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A528" s="1" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="G528" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H528" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J528" t="s">
         <v>51</v>
@@ -12183,29 +12174,15 @@
     </row>
     <row r="529" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A529" s="1" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="G529" t="s">
-        <v>56</v>
+        <v>166</v>
       </c>
       <c r="H529" t="s">
-        <v>57</v>
+        <v>167</v>
       </c>
       <c r="J529" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="530" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A530" s="1" t="s">
-        <v>911</v>
-      </c>
-      <c r="G530" t="s">
-        <v>166</v>
-      </c>
-      <c r="H530" t="s">
-        <v>167</v>
-      </c>
-      <c r="J530" t="s">
         <v>51</v>
       </c>
     </row>

--- a/input/lista/1 LISTA PDV ENI 2.xlsx
+++ b/input/lista/1 LISTA PDV ENI 2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nadir\Desktop\APP TELEPASS\FILE FISSI\lista\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF297D08-471F-4F80-AF71-7142D4E99F3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21ECBC85-76B1-4789-988E-B71FBACCB197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-132" yWindow="-132" windowWidth="23304" windowHeight="13224" xr2:uid="{D320C423-4B98-4D55-B6E8-3ABF0EE22191}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{D320C423-4B98-4D55-B6E8-3ABF0EE22191}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="5" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2057" uniqueCount="1414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2057" uniqueCount="1413">
   <si>
     <t>ALESSANDRIA</t>
   </si>
@@ -4075,9 +4075,6 @@
   </si>
   <si>
     <t>A19 Palermo - Catania</t>
-  </si>
-  <si>
-    <t>Emanuele Marcelli</t>
   </si>
   <si>
     <t>03632</t>
@@ -4328,20 +4325,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4659,14 +4653,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{175EF563-0873-44BA-ACAF-2DC290E6A803}">
   <dimension ref="A1:J516"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="7" max="7" width="29.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="50.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="50.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>982</v>
       </c>
@@ -4680,7 +4674,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>983</v>
       </c>
@@ -4694,7 +4688,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>961</v>
       </c>
@@ -4708,7 +4702,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>1024</v>
       </c>
@@ -4722,7 +4716,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>988</v>
       </c>
@@ -4736,7 +4730,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>974</v>
       </c>
@@ -4750,7 +4744,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>1018</v>
       </c>
@@ -4764,7 +4758,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>997</v>
       </c>
@@ -4778,7 +4772,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>1000</v>
       </c>
@@ -4792,7 +4786,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>960</v>
       </c>
@@ -4806,7 +4800,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>1017</v>
       </c>
@@ -4820,7 +4814,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>984</v>
       </c>
@@ -4834,7 +4828,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>978</v>
       </c>
@@ -4848,7 +4842,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>966</v>
       </c>
@@ -4862,7 +4856,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>993</v>
       </c>
@@ -4876,7 +4870,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>1003</v>
       </c>
@@ -4890,7 +4884,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>963</v>
       </c>
@@ -4904,7 +4898,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>1025</v>
       </c>
@@ -4918,7 +4912,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>1004</v>
       </c>
@@ -4932,7 +4926,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>1005</v>
       </c>
@@ -4946,7 +4940,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>1041</v>
       </c>
@@ -4960,7 +4954,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>1016</v>
       </c>
@@ -4974,7 +4968,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>969</v>
       </c>
@@ -4988,7 +4982,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>975</v>
       </c>
@@ -5002,7 +4996,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>998</v>
       </c>
@@ -5016,7 +5010,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>1001</v>
       </c>
@@ -5030,7 +5024,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>1020</v>
       </c>
@@ -5044,7 +5038,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>995</v>
       </c>
@@ -5058,7 +5052,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>964</v>
       </c>
@@ -5072,7 +5066,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>1009</v>
       </c>
@@ -5086,7 +5080,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>979</v>
       </c>
@@ -5100,7 +5094,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>986</v>
       </c>
@@ -5114,7 +5108,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>1049</v>
       </c>
@@ -5128,7 +5122,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>1030</v>
       </c>
@@ -5142,7 +5136,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>1007</v>
       </c>
@@ -5156,7 +5150,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>985</v>
       </c>
@@ -5170,7 +5164,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>1028</v>
       </c>
@@ -5184,7 +5178,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>1002</v>
       </c>
@@ -5198,7 +5192,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>967</v>
       </c>
@@ -5212,7 +5206,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>1031</v>
       </c>
@@ -5226,7 +5220,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>1012</v>
       </c>
@@ -5240,7 +5234,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>980</v>
       </c>
@@ -5254,7 +5248,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>1047</v>
       </c>
@@ -5268,7 +5262,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>989</v>
       </c>
@@ -5282,7 +5276,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>1014</v>
       </c>
@@ -5296,7 +5290,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>970</v>
       </c>
@@ -5310,7 +5304,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>1029</v>
       </c>
@@ -5324,7 +5318,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>977</v>
       </c>
@@ -5338,7 +5332,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>1027</v>
       </c>
@@ -5352,7 +5346,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>1051</v>
       </c>
@@ -5366,7 +5360,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>968</v>
       </c>
@@ -5380,7 +5374,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>1019</v>
       </c>
@@ -5394,7 +5388,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>1044</v>
       </c>
@@ -5408,7 +5402,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>976</v>
       </c>
@@ -5422,7 +5416,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>971</v>
       </c>
@@ -5436,7 +5430,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>1026</v>
       </c>
@@ -5450,7 +5444,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>1010</v>
       </c>
@@ -5464,7 +5458,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>1015</v>
       </c>
@@ -5478,7 +5472,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>1043</v>
       </c>
@@ -5492,7 +5486,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>996</v>
       </c>
@@ -5506,7 +5500,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>973</v>
       </c>
@@ -5520,7 +5514,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>999</v>
       </c>
@@ -5534,7 +5528,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>1042</v>
       </c>
@@ -5548,7 +5542,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>994</v>
       </c>
@@ -5562,7 +5556,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>992</v>
       </c>
@@ -5576,7 +5570,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>972</v>
       </c>
@@ -5590,7 +5584,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>1046</v>
       </c>
@@ -5604,7 +5598,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>1210</v>
       </c>
@@ -5618,7 +5612,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>990</v>
       </c>
@@ -5632,7 +5626,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>1048</v>
       </c>
@@ -5646,7 +5640,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>1211</v>
       </c>
@@ -5660,7 +5654,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>1212</v>
       </c>
@@ -5674,7 +5668,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>1006</v>
       </c>
@@ -5688,7 +5682,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>1022</v>
       </c>
@@ -5702,7 +5696,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>1011</v>
       </c>
@@ -5716,7 +5710,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>991</v>
       </c>
@@ -5730,7 +5724,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>1052</v>
       </c>
@@ -5744,7 +5738,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>1040</v>
       </c>
@@ -5758,7 +5752,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>987</v>
       </c>
@@ -5772,7 +5766,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>965</v>
       </c>
@@ -5786,7 +5780,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>1021</v>
       </c>
@@ -5800,7 +5794,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>1023</v>
       </c>
@@ -5814,7 +5808,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>962</v>
       </c>
@@ -5828,7 +5822,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>1008</v>
       </c>
@@ -5842,7 +5836,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>1013</v>
       </c>
@@ -5856,7 +5850,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>981</v>
       </c>
@@ -5870,7 +5864,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>1213</v>
       </c>
@@ -5884,7 +5878,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>1214</v>
       </c>
@@ -5898,7 +5892,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>1215</v>
       </c>
@@ -5912,7 +5906,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>1038</v>
       </c>
@@ -5926,7 +5920,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>1032</v>
       </c>
@@ -5940,7 +5934,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>1034</v>
       </c>
@@ -5954,7 +5948,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>1035</v>
       </c>
@@ -5968,7 +5962,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>1033</v>
       </c>
@@ -5982,7 +5976,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>1039</v>
       </c>
@@ -5996,7 +5990,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>1036</v>
       </c>
@@ -6010,7 +6004,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>1045</v>
       </c>
@@ -6024,7 +6018,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>1037</v>
       </c>
@@ -6038,7 +6032,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>1050</v>
       </c>
@@ -6052,7 +6046,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>806</v>
       </c>
@@ -6066,7 +6060,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>768</v>
       </c>
@@ -6080,7 +6074,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>807</v>
       </c>
@@ -6094,7 +6088,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>818</v>
       </c>
@@ -6108,7 +6102,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>793</v>
       </c>
@@ -6122,7 +6116,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>769</v>
       </c>
@@ -6136,7 +6130,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>778</v>
       </c>
@@ -6150,7 +6144,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>776</v>
       </c>
@@ -6164,7 +6158,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>784</v>
       </c>
@@ -6178,7 +6172,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>777</v>
       </c>
@@ -6192,7 +6186,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>796</v>
       </c>
@@ -6206,7 +6200,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>836</v>
       </c>
@@ -6220,7 +6214,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>844</v>
       </c>
@@ -6234,7 +6228,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>808</v>
       </c>
@@ -6248,7 +6242,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>770</v>
       </c>
@@ -6262,7 +6256,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>794</v>
       </c>
@@ -6276,7 +6270,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>811</v>
       </c>
@@ -6290,7 +6284,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>771</v>
       </c>
@@ -6304,7 +6298,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>795</v>
       </c>
@@ -6318,7 +6312,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>791</v>
       </c>
@@ -6332,7 +6326,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>820</v>
       </c>
@@ -6346,7 +6340,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
         <v>765</v>
       </c>
@@ -6360,7 +6354,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
         <v>833</v>
       </c>
@@ -6374,7 +6368,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
         <v>812</v>
       </c>
@@ -6388,7 +6382,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
         <v>819</v>
       </c>
@@ -6402,7 +6396,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
         <v>797</v>
       </c>
@@ -6416,7 +6410,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
         <v>809</v>
       </c>
@@ -6430,7 +6424,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
         <v>780</v>
       </c>
@@ -6444,7 +6438,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
         <v>825</v>
       </c>
@@ -6458,7 +6452,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
         <v>775</v>
       </c>
@@ -6472,7 +6466,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
         <v>785</v>
       </c>
@@ -6486,7 +6480,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
         <v>787</v>
       </c>
@@ -6500,7 +6494,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
         <v>773</v>
       </c>
@@ -6514,7 +6508,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
         <v>829</v>
       </c>
@@ -6528,7 +6522,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
         <v>782</v>
       </c>
@@ -6542,7 +6536,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
         <v>766</v>
       </c>
@@ -6556,7 +6550,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
         <v>779</v>
       </c>
@@ -6570,7 +6564,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
         <v>774</v>
       </c>
@@ -6584,7 +6578,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
         <v>772</v>
       </c>
@@ -6598,7 +6592,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
         <v>798</v>
       </c>
@@ -6612,7 +6606,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
         <v>834</v>
       </c>
@@ -6626,7 +6620,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
         <v>828</v>
       </c>
@@ -6640,7 +6634,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
         <v>839</v>
       </c>
@@ -6654,7 +6648,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
         <v>1216</v>
       </c>
@@ -6668,7 +6662,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
         <v>827</v>
       </c>
@@ -6682,7 +6676,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
         <v>789</v>
       </c>
@@ -6696,7 +6690,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
         <v>821</v>
       </c>
@@ -6710,7 +6704,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
         <v>799</v>
       </c>
@@ -6724,7 +6718,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
         <v>1217</v>
       </c>
@@ -6738,7 +6732,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
         <v>783</v>
       </c>
@@ -6752,7 +6746,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
         <v>824</v>
       </c>
@@ -6766,7 +6760,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
         <v>814</v>
       </c>
@@ -6780,7 +6774,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
         <v>781</v>
       </c>
@@ -6794,7 +6788,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
         <v>788</v>
       </c>
@@ -6808,7 +6802,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
         <v>767</v>
       </c>
@@ -6822,7 +6816,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
         <v>822</v>
       </c>
@@ -6836,7 +6830,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
         <v>813</v>
       </c>
@@ -6850,7 +6844,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
         <v>802</v>
       </c>
@@ -6864,7 +6858,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
         <v>847</v>
       </c>
@@ -6878,7 +6872,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
         <v>801</v>
       </c>
@@ -6892,7 +6886,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
         <v>803</v>
       </c>
@@ -6906,7 +6900,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
         <v>800</v>
       </c>
@@ -6920,7 +6914,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
         <v>831</v>
       </c>
@@ -6934,7 +6928,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
         <v>786</v>
       </c>
@@ -6948,7 +6942,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
         <v>830</v>
       </c>
@@ -6962,7 +6956,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
         <v>837</v>
       </c>
@@ -6976,7 +6970,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
         <v>841</v>
       </c>
@@ -6990,7 +6984,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
         <v>843</v>
       </c>
@@ -7004,7 +6998,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
         <v>823</v>
       </c>
@@ -7018,7 +7012,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
         <v>816</v>
       </c>
@@ -7032,7 +7026,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
         <v>832</v>
       </c>
@@ -7046,7 +7040,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
         <v>1218</v>
       </c>
@@ -7060,7 +7054,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
         <v>835</v>
       </c>
@@ -7074,7 +7068,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
         <v>790</v>
       </c>
@@ -7088,7 +7082,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
         <v>815</v>
       </c>
@@ -7102,7 +7096,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
         <v>804</v>
       </c>
@@ -7116,7 +7110,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
         <v>1219</v>
       </c>
@@ -7130,7 +7124,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
         <v>817</v>
       </c>
@@ -7144,7 +7138,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
         <v>840</v>
       </c>
@@ -7158,7 +7152,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
         <v>838</v>
       </c>
@@ -7172,7 +7166,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
         <v>1220</v>
       </c>
@@ -7186,7 +7180,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="s">
         <v>805</v>
       </c>
@@ -7200,7 +7194,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
         <v>826</v>
       </c>
@@ -7214,7 +7208,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="s">
         <v>846</v>
       </c>
@@ -7228,7 +7222,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
         <v>842</v>
       </c>
@@ -7242,7 +7236,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="s">
         <v>845</v>
       </c>
@@ -7256,7 +7250,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
         <v>792</v>
       </c>
@@ -7270,7 +7264,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A187" s="1" t="s">
         <v>1221</v>
       </c>
@@ -7284,7 +7278,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
         <v>764</v>
       </c>
@@ -7298,7 +7292,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A189" s="1" t="s">
         <v>1222</v>
       </c>
@@ -7312,7 +7306,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
         <v>1223</v>
       </c>
@@ -7326,7 +7320,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A191" s="1" t="s">
         <v>1134</v>
       </c>
@@ -7340,7 +7334,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
         <v>1125</v>
       </c>
@@ -7354,7 +7348,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A193" s="1" t="s">
         <v>1144</v>
       </c>
@@ -7368,7 +7362,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
         <v>1162</v>
       </c>
@@ -7382,7 +7376,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A195" s="1" t="s">
         <v>1153</v>
       </c>
@@ -7396,7 +7390,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
         <v>1136</v>
       </c>
@@ -7410,7 +7404,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="s">
         <v>1174</v>
       </c>
@@ -7424,7 +7418,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="s">
         <v>1187</v>
       </c>
@@ -7438,7 +7432,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A199" s="1" t="s">
         <v>1149</v>
       </c>
@@ -7452,7 +7446,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
         <v>1184</v>
       </c>
@@ -7466,7 +7460,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A201" s="1" t="s">
         <v>1150</v>
       </c>
@@ -7480,7 +7474,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
         <v>1126</v>
       </c>
@@ -7494,7 +7488,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A203" s="1" t="s">
         <v>1135</v>
       </c>
@@ -7508,7 +7502,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
         <v>1177</v>
       </c>
@@ -7522,7 +7516,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A205" s="1" t="s">
         <v>1185</v>
       </c>
@@ -7536,7 +7530,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
         <v>1175</v>
       </c>
@@ -7550,7 +7544,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A207" s="1" t="s">
         <v>1165</v>
       </c>
@@ -7564,7 +7558,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
         <v>1159</v>
       </c>
@@ -7578,7 +7572,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="s">
         <v>1164</v>
       </c>
@@ -7592,7 +7586,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
         <v>1132</v>
       </c>
@@ -7606,7 +7600,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A211" s="1" t="s">
         <v>1154</v>
       </c>
@@ -7620,7 +7614,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="s">
         <v>1166</v>
       </c>
@@ -7634,7 +7628,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A213" s="1" t="s">
         <v>1155</v>
       </c>
@@ -7648,7 +7642,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
         <v>1163</v>
       </c>
@@ -7662,7 +7656,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A215" s="1" t="s">
         <v>1189</v>
       </c>
@@ -7676,7 +7670,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
         <v>1158</v>
       </c>
@@ -7690,7 +7684,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A217" s="1" t="s">
         <v>1131</v>
       </c>
@@ -7704,7 +7698,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
         <v>1157</v>
       </c>
@@ -7718,7 +7712,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A219" s="1" t="s">
         <v>1140</v>
       </c>
@@ -7732,7 +7726,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
         <v>1139</v>
       </c>
@@ -7746,7 +7740,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A221" s="1" t="s">
         <v>1152</v>
       </c>
@@ -7760,7 +7754,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="s">
         <v>1138</v>
       </c>
@@ -7774,7 +7768,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A223" s="1" t="s">
         <v>1160</v>
       </c>
@@ -7788,7 +7782,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="s">
         <v>1137</v>
       </c>
@@ -7802,7 +7796,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A225" s="1" t="s">
         <v>1203</v>
       </c>
@@ -7816,7 +7810,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
         <v>1192</v>
       </c>
@@ -7830,7 +7824,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="s">
         <v>1156</v>
       </c>
@@ -7844,7 +7838,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
         <v>1176</v>
       </c>
@@ -7858,7 +7852,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A229" s="1" t="s">
         <v>1161</v>
       </c>
@@ -7872,7 +7866,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="s">
         <v>1130</v>
       </c>
@@ -7886,7 +7880,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A231" s="1" t="s">
         <v>1224</v>
       </c>
@@ -7900,7 +7894,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="s">
         <v>1170</v>
       </c>
@@ -7914,7 +7908,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A233" s="1" t="s">
         <v>1178</v>
       </c>
@@ -7928,7 +7922,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="s">
         <v>1169</v>
       </c>
@@ -7942,7 +7936,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A235" s="1" t="s">
         <v>1186</v>
       </c>
@@ -7956,7 +7950,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="s">
         <v>1128</v>
       </c>
@@ -7970,7 +7964,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A237" s="1" t="s">
         <v>1190</v>
       </c>
@@ -7984,7 +7978,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="s">
         <v>1182</v>
       </c>
@@ -7998,7 +7992,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A239" s="1" t="s">
         <v>1133</v>
       </c>
@@ -8012,7 +8006,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A240" s="1" t="s">
         <v>1168</v>
       </c>
@@ -8026,7 +8020,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A241" s="1" t="s">
         <v>1127</v>
       </c>
@@ -8040,7 +8034,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="s">
         <v>1167</v>
       </c>
@@ -8054,7 +8048,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A243" s="1" t="s">
         <v>1198</v>
       </c>
@@ -8068,7 +8062,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="s">
         <v>1181</v>
       </c>
@@ -8082,7 +8076,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A245" s="1" t="s">
         <v>1145</v>
       </c>
@@ -8096,7 +8090,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="s">
         <v>1180</v>
       </c>
@@ -8110,7 +8104,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A247" s="1" t="s">
         <v>1225</v>
       </c>
@@ -8124,7 +8118,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
         <v>1141</v>
       </c>
@@ -8138,7 +8132,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="s">
         <v>1151</v>
       </c>
@@ -8152,7 +8146,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
         <v>1179</v>
       </c>
@@ -8166,7 +8160,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A251" s="1" t="s">
         <v>1188</v>
       </c>
@@ -8180,7 +8174,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
         <v>1171</v>
       </c>
@@ -8194,7 +8188,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A253" s="1" t="s">
         <v>1194</v>
       </c>
@@ -8208,7 +8202,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
         <v>1143</v>
       </c>
@@ -8222,7 +8216,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A255" s="1" t="s">
         <v>1142</v>
       </c>
@@ -8236,7 +8230,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
         <v>1201</v>
       </c>
@@ -8250,7 +8244,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A257" s="1" t="s">
         <v>1172</v>
       </c>
@@ -8264,7 +8258,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="s">
         <v>1183</v>
       </c>
@@ -8278,7 +8272,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A259" s="1" t="s">
         <v>1147</v>
       </c>
@@ -8292,7 +8286,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="s">
         <v>854</v>
       </c>
@@ -8306,7 +8300,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A261" s="1" t="s">
         <v>1196</v>
       </c>
@@ -8320,7 +8314,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="s">
         <v>1148</v>
       </c>
@@ -8334,7 +8328,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A263" s="1" t="s">
         <v>1173</v>
       </c>
@@ -8348,7 +8342,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A264" s="1" t="s">
         <v>1199</v>
       </c>
@@ -8362,7 +8356,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A265" s="1" t="s">
         <v>1205</v>
       </c>
@@ -8376,7 +8370,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A266" s="1" t="s">
         <v>1200</v>
       </c>
@@ -8390,7 +8384,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="267" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A267" s="1" t="s">
         <v>1129</v>
       </c>
@@ -8404,7 +8398,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A268" s="1" t="s">
         <v>1204</v>
       </c>
@@ -8418,7 +8412,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A269" s="1" t="s">
         <v>1191</v>
       </c>
@@ -8432,7 +8426,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="270" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A270" s="1" t="s">
         <v>1226</v>
       </c>
@@ -8446,7 +8440,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A271" s="1" t="s">
         <v>1202</v>
       </c>
@@ -8460,7 +8454,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="272" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A272" s="1" t="s">
         <v>1227</v>
       </c>
@@ -8474,7 +8468,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A273" s="1" t="s">
         <v>1193</v>
       </c>
@@ -8488,7 +8482,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A274" s="1" t="s">
         <v>1197</v>
       </c>
@@ -8502,7 +8496,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A275" s="1" t="s">
         <v>1195</v>
       </c>
@@ -8516,7 +8510,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A276" s="1" t="s">
         <v>1146</v>
       </c>
@@ -8530,7 +8524,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A277" s="1" t="s">
         <v>1078</v>
       </c>
@@ -8544,7 +8538,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A278" s="1" t="s">
         <v>1086</v>
       </c>
@@ -8558,7 +8552,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A279" s="1" t="s">
         <v>1073</v>
       </c>
@@ -8572,7 +8566,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A280" s="1" t="s">
         <v>1072</v>
       </c>
@@ -8586,7 +8580,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A281" s="1" t="s">
         <v>1111</v>
       </c>
@@ -8600,7 +8594,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A282" s="1" t="s">
         <v>1093</v>
       </c>
@@ -8614,7 +8608,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A283" s="1" t="s">
         <v>1079</v>
       </c>
@@ -8628,7 +8622,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A284" s="1" t="s">
         <v>1060</v>
       </c>
@@ -8642,7 +8636,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A285" s="1" t="s">
         <v>1108</v>
       </c>
@@ -8656,7 +8650,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="s">
         <v>1112</v>
       </c>
@@ -8670,7 +8664,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A287" s="1" t="s">
         <v>1107</v>
       </c>
@@ -8684,7 +8678,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A288" s="1" t="s">
         <v>1083</v>
       </c>
@@ -8698,7 +8692,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A289" s="1" t="s">
         <v>1061</v>
       </c>
@@ -8712,7 +8706,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="s">
         <v>1082</v>
       </c>
@@ -8726,7 +8720,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A291" s="1" t="s">
         <v>1059</v>
       </c>
@@ -8740,7 +8734,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A292" s="1" t="s">
         <v>1089</v>
       </c>
@@ -8754,7 +8748,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A293" s="1" t="s">
         <v>810</v>
       </c>
@@ -8768,7 +8762,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="s">
         <v>1094</v>
       </c>
@@ -8782,7 +8776,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A295" s="1" t="s">
         <v>1064</v>
       </c>
@@ -8796,7 +8790,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="s">
         <v>1062</v>
       </c>
@@ -8810,7 +8804,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A297" s="1" t="s">
         <v>1095</v>
       </c>
@@ -8824,7 +8818,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A298" s="1" t="s">
         <v>1080</v>
       </c>
@@ -8838,7 +8832,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A299" s="1" t="s">
         <v>1081</v>
       </c>
@@ -8852,7 +8846,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="s">
         <v>1066</v>
       </c>
@@ -8866,7 +8860,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A301" s="1" t="s">
         <v>1074</v>
       </c>
@@ -8880,7 +8874,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A302" s="1" t="s">
         <v>1100</v>
       </c>
@@ -8894,7 +8888,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="303" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A303" s="1" t="s">
         <v>1065</v>
       </c>
@@ -8908,7 +8902,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="304" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A304" s="1" t="s">
         <v>1228</v>
       </c>
@@ -8922,7 +8916,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A305" s="1" t="s">
         <v>1097</v>
       </c>
@@ -8936,7 +8930,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A306" s="1" t="s">
         <v>1109</v>
       </c>
@@ -8950,7 +8944,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="307" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A307" s="1" t="s">
         <v>1229</v>
       </c>
@@ -8964,7 +8958,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A308" s="1" t="s">
         <v>1096</v>
       </c>
@@ -8978,7 +8972,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="309" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A309" s="1" t="s">
         <v>1114</v>
       </c>
@@ -8992,7 +8986,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="310" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A310" s="1" t="s">
         <v>1088</v>
       </c>
@@ -9006,7 +9000,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="311" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A311" s="1" t="s">
         <v>1084</v>
       </c>
@@ -9020,7 +9014,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A312" s="1" t="s">
         <v>1115</v>
       </c>
@@ -9034,7 +9028,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A313" s="1" t="s">
         <v>1068</v>
       </c>
@@ -9048,7 +9042,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="314" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A314" s="1" t="s">
         <v>1113</v>
       </c>
@@ -9062,7 +9056,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="315" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>1480</v>
       </c>
@@ -9076,7 +9070,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="316" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A316" s="1" t="s">
         <v>1067</v>
       </c>
@@ -9090,7 +9084,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A317" s="1" t="s">
         <v>1091</v>
       </c>
@@ -9104,7 +9098,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="318" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A318" s="1" t="s">
         <v>1075</v>
       </c>
@@ -9118,7 +9112,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="319" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A319" s="1" t="s">
         <v>1105</v>
       </c>
@@ -9132,7 +9126,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="320" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A320" s="1" t="s">
         <v>1087</v>
       </c>
@@ -9146,7 +9140,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="321" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A321" s="1" t="s">
         <v>1092</v>
       </c>
@@ -9160,7 +9154,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="322" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A322" s="1" t="s">
         <v>1098</v>
       </c>
@@ -9174,7 +9168,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="323" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A323" s="1" t="s">
         <v>1099</v>
       </c>
@@ -9188,7 +9182,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="324" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A324" s="1" t="s">
         <v>1090</v>
       </c>
@@ -9202,7 +9196,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="325" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A325" s="1" t="s">
         <v>1230</v>
       </c>
@@ -9216,7 +9210,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="326" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A326" s="1" t="s">
         <v>1069</v>
       </c>
@@ -9230,7 +9224,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A327" s="1" t="s">
         <v>1077</v>
       </c>
@@ -9244,7 +9238,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="328" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A328" s="1" t="s">
         <v>1104</v>
       </c>
@@ -9258,7 +9252,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="329" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A329" s="1" t="s">
         <v>1121</v>
       </c>
@@ -9272,7 +9266,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="330" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A330" s="1" t="s">
         <v>1071</v>
       </c>
@@ -9286,7 +9280,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="331" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A331" s="1" t="s">
         <v>1102</v>
       </c>
@@ -9300,7 +9294,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="332" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A332" s="1" t="s">
         <v>955</v>
       </c>
@@ -9314,7 +9308,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="333" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A333" s="1" t="s">
         <v>1117</v>
       </c>
@@ -9328,7 +9322,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="334" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A334" s="1" t="s">
         <v>1116</v>
       </c>
@@ -9342,7 +9336,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="335" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A335" s="1" t="s">
         <v>1070</v>
       </c>
@@ -9356,7 +9350,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="336" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A336" s="1" t="s">
         <v>1085</v>
       </c>
@@ -9370,7 +9364,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="337" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A337" s="1" t="s">
         <v>1103</v>
       </c>
@@ -9384,7 +9378,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="338" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A338" s="1" t="s">
         <v>1118</v>
       </c>
@@ -9398,7 +9392,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="339" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A339" s="1" t="s">
         <v>1119</v>
       </c>
@@ -9412,7 +9406,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="340" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A340" s="1" t="s">
         <v>1110</v>
       </c>
@@ -9426,7 +9420,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="341" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A341" s="1" t="s">
         <v>1106</v>
       </c>
@@ -9440,7 +9434,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="342" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A342" s="1" t="s">
         <v>1076</v>
       </c>
@@ -9454,7 +9448,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="343" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A343" s="1" t="s">
         <v>1063</v>
       </c>
@@ -9468,7 +9462,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="344" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A344" s="1" t="s">
         <v>1231</v>
       </c>
@@ -9482,7 +9476,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="345" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A345" s="1" t="s">
         <v>1120</v>
       </c>
@@ -9496,7 +9490,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="346" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A346" s="1" t="s">
         <v>1101</v>
       </c>
@@ -9510,7 +9504,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="347" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A347" s="1" t="s">
         <v>1232</v>
       </c>
@@ -9524,7 +9518,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="348" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A348" s="1" t="s">
         <v>1233</v>
       </c>
@@ -9538,7 +9532,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="349" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A349" s="1" t="s">
         <v>1234</v>
       </c>
@@ -9552,7 +9546,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="350" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A350" s="1" t="s">
         <v>1235</v>
       </c>
@@ -9566,7 +9560,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="351" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A351" s="1" t="s">
         <v>1236</v>
       </c>
@@ -9580,7 +9574,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="352" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A352" s="1" t="s">
         <v>1237</v>
       </c>
@@ -9594,7 +9588,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="353" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A353" s="1" t="s">
         <v>1238</v>
       </c>
@@ -9608,7 +9602,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="354" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A354" s="1" t="s">
         <v>1239</v>
       </c>
@@ -9622,7 +9616,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="355" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A355" s="1" t="s">
         <v>1240</v>
       </c>
@@ -9636,7 +9630,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="356" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A356" s="1" t="s">
         <v>1241</v>
       </c>
@@ -9650,7 +9644,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="357" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A357" s="1" t="s">
         <v>1242</v>
       </c>
@@ -9664,7 +9658,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="358" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A358" s="1" t="s">
         <v>1243</v>
       </c>
@@ -9678,7 +9672,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="359" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A359" s="1" t="s">
         <v>1244</v>
       </c>
@@ -9692,7 +9686,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="360" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A360" s="1" t="s">
         <v>946</v>
       </c>
@@ -9703,10 +9697,10 @@
         <v>129</v>
       </c>
       <c r="J360" t="s">
-        <v>1346</v>
-      </c>
-    </row>
-    <row r="361" spans="1:10" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="361" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A361" s="1" t="s">
         <v>948</v>
       </c>
@@ -9717,10 +9711,10 @@
         <v>146</v>
       </c>
       <c r="J361" t="s">
-        <v>1346</v>
-      </c>
-    </row>
-    <row r="362" spans="1:10" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="362" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A362" s="1" t="s">
         <v>947</v>
       </c>
@@ -9731,10 +9725,10 @@
         <v>141</v>
       </c>
       <c r="J362" t="s">
-        <v>1346</v>
-      </c>
-    </row>
-    <row r="363" spans="1:10" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="363" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A363" s="1" t="s">
         <v>949</v>
       </c>
@@ -9745,10 +9739,10 @@
         <v>139</v>
       </c>
       <c r="J363" t="s">
-        <v>1346</v>
-      </c>
-    </row>
-    <row r="364" spans="1:10" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="364" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A364" s="1" t="s">
         <v>951</v>
       </c>
@@ -9759,10 +9753,10 @@
         <v>73</v>
       </c>
       <c r="J364" t="s">
-        <v>1346</v>
-      </c>
-    </row>
-    <row r="365" spans="1:10" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="365" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A365" s="1" t="s">
         <v>873</v>
       </c>
@@ -9776,7 +9770,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="366" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A366" s="1" t="s">
         <v>896</v>
       </c>
@@ -9790,7 +9784,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="367" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A367" s="1" t="s">
         <v>867</v>
       </c>
@@ -9804,7 +9798,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="368" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A368" s="1" t="s">
         <v>860</v>
       </c>
@@ -9818,7 +9812,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="369" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A369" s="1" t="s">
         <v>901</v>
       </c>
@@ -9832,7 +9826,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="370" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A370" s="1" t="s">
         <v>861</v>
       </c>
@@ -9846,7 +9840,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="371" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A371" s="1" t="s">
         <v>866</v>
       </c>
@@ -9860,7 +9854,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="372" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A372" s="1" t="s">
         <v>878</v>
       </c>
@@ -9874,7 +9868,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="373" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A373" s="1" t="s">
         <v>879</v>
       </c>
@@ -9888,7 +9882,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="374" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A374" s="1" t="s">
         <v>862</v>
       </c>
@@ -9902,7 +9896,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="375" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A375" s="1" t="s">
         <v>856</v>
       </c>
@@ -9916,7 +9910,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="376" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A376" s="1" t="s">
         <v>869</v>
       </c>
@@ -9930,7 +9924,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="377" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A377" s="1" t="s">
         <v>863</v>
       </c>
@@ -9944,7 +9938,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="378" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A378" s="1" t="s">
         <v>859</v>
       </c>
@@ -9958,7 +9952,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="379" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A379" s="1" t="s">
         <v>902</v>
       </c>
@@ -9972,7 +9966,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="380" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A380" s="1" t="s">
         <v>881</v>
       </c>
@@ -9986,7 +9980,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="381" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A381" s="1" t="s">
         <v>895</v>
       </c>
@@ -10000,7 +9994,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="382" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A382" s="1" t="s">
         <v>880</v>
       </c>
@@ -10014,7 +10008,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="383" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A383" s="1" t="s">
         <v>904</v>
       </c>
@@ -10028,7 +10022,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="384" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A384" s="1" t="s">
         <v>894</v>
       </c>
@@ -10042,7 +10036,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="385" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A385" s="1" t="s">
         <v>882</v>
       </c>
@@ -10056,7 +10050,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="386" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A386" s="1" t="s">
         <v>874</v>
       </c>
@@ -10070,7 +10064,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="387" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A387" s="1" t="s">
         <v>871</v>
       </c>
@@ -10084,7 +10078,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="388" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A388" s="1" t="s">
         <v>910</v>
       </c>
@@ -10098,7 +10092,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="389" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A389" s="1" t="s">
         <v>868</v>
       </c>
@@ -10112,7 +10106,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="390" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A390" s="1" t="s">
         <v>907</v>
       </c>
@@ -10126,7 +10120,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="391" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A391" s="1" t="s">
         <v>875</v>
       </c>
@@ -10140,7 +10134,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="392" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A392" s="1" t="s">
         <v>870</v>
       </c>
@@ -10154,7 +10148,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="393" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A393" s="1" t="s">
         <v>914</v>
       </c>
@@ -10168,7 +10162,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="394" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A394" s="1" t="s">
         <v>886</v>
       </c>
@@ -10182,7 +10176,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="395" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A395" s="1" t="s">
         <v>876</v>
       </c>
@@ -10196,7 +10190,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="396" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A396" s="1" t="s">
         <v>922</v>
       </c>
@@ -10210,7 +10204,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="397" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A397" s="1" t="s">
         <v>883</v>
       </c>
@@ -10224,7 +10218,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="398" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A398" s="1" t="s">
         <v>888</v>
       </c>
@@ -10238,7 +10232,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="399" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A399" s="1" t="s">
         <v>906</v>
       </c>
@@ -10252,7 +10246,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="400" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A400" s="1" t="s">
         <v>877</v>
       </c>
@@ -10266,7 +10260,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="401" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A401" s="1" t="s">
         <v>920</v>
       </c>
@@ -10280,7 +10274,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="402" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A402" s="1" t="s">
         <v>909</v>
       </c>
@@ -10294,7 +10288,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="403" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A403" s="1" t="s">
         <v>903</v>
       </c>
@@ -10308,7 +10302,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="404" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A404" s="1" t="s">
         <v>908</v>
       </c>
@@ -10322,7 +10316,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="405" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A405" s="1" t="s">
         <v>865</v>
       </c>
@@ -10336,7 +10330,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="406" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A406" s="1" t="s">
         <v>864</v>
       </c>
@@ -10350,7 +10344,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="407" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A407" s="1" t="s">
         <v>898</v>
       </c>
@@ -10364,7 +10358,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="408" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A408" s="1" t="s">
         <v>905</v>
       </c>
@@ -10378,7 +10372,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="409" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A409" s="1" t="s">
         <v>1245</v>
       </c>
@@ -10392,7 +10386,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="410" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A410" s="1" t="s">
         <v>884</v>
       </c>
@@ -10406,7 +10400,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="411" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A411" s="1" t="s">
         <v>893</v>
       </c>
@@ -10420,7 +10414,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="412" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A412" s="1" t="s">
         <v>897</v>
       </c>
@@ -10434,7 +10428,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="413" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A413" s="1" t="s">
         <v>872</v>
       </c>
@@ -10448,7 +10442,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="414" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A414" s="1" t="s">
         <v>900</v>
       </c>
@@ -10462,7 +10456,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="415" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A415" s="1" t="s">
         <v>857</v>
       </c>
@@ -10476,7 +10470,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="416" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A416" s="1" t="s">
         <v>923</v>
       </c>
@@ -10490,7 +10484,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="417" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A417" s="1" t="s">
         <v>852</v>
       </c>
@@ -10504,7 +10498,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="418" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A418" s="1" t="s">
         <v>855</v>
       </c>
@@ -10518,7 +10512,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="419" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A419" s="1" t="s">
         <v>889</v>
       </c>
@@ -10532,7 +10526,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="420" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A420" s="1" t="s">
         <v>1246</v>
       </c>
@@ -10546,7 +10540,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="421" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A421" s="1" t="s">
         <v>851</v>
       </c>
@@ -10560,7 +10554,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="422" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A422" s="1" t="s">
         <v>899</v>
       </c>
@@ -10574,7 +10568,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="423" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A423" s="1" t="s">
         <v>916</v>
       </c>
@@ -10588,7 +10582,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="424" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A424" s="1" t="s">
         <v>913</v>
       </c>
@@ -10602,7 +10596,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="425" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A425" s="1" t="s">
         <v>892</v>
       </c>
@@ -10616,7 +10610,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="426" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A426" s="1" t="s">
         <v>887</v>
       </c>
@@ -10630,7 +10624,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="427" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A427" s="1" t="s">
         <v>912</v>
       </c>
@@ -10644,7 +10638,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="428" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A428" s="1" t="s">
         <v>1247</v>
       </c>
@@ -10658,7 +10652,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="429" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A429" s="1" t="s">
         <v>924</v>
       </c>
@@ -10672,7 +10666,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="430" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A430" s="1" t="s">
         <v>921</v>
       </c>
@@ -10686,7 +10680,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="431" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A431" s="1" t="s">
         <v>917</v>
       </c>
@@ -10700,7 +10694,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="432" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A432" s="1" t="s">
         <v>915</v>
       </c>
@@ -10714,7 +10708,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="433" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A433" s="1" t="s">
         <v>853</v>
       </c>
@@ -10728,7 +10722,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="434" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A434" s="1" t="s">
         <v>919</v>
       </c>
@@ -10742,7 +10736,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="435" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A435" s="1" t="s">
         <v>858</v>
       </c>
@@ -10756,7 +10750,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="436" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A436" s="1" t="s">
         <v>1248</v>
       </c>
@@ -10770,7 +10764,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="437" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A437" s="1" t="s">
         <v>918</v>
       </c>
@@ -10784,7 +10778,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="438" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A438" s="1" t="s">
         <v>1249</v>
       </c>
@@ -10798,7 +10792,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="439" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A439" s="1" t="s">
         <v>911</v>
       </c>
@@ -10812,7 +10806,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="440" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A440" s="1" t="s">
         <v>890</v>
       </c>
@@ -10826,7 +10820,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="441" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A441" s="1" t="s">
         <v>891</v>
       </c>
@@ -10840,7 +10834,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="442" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A442" s="1" t="s">
         <v>885</v>
       </c>
@@ -10854,7 +10848,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="443" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>932</v>
       </c>
@@ -10868,9 +10862,9 @@
         <v>67</v>
       </c>
     </row>
-    <row r="444" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="G444" s="2" t="s">
         <v>650</v>
@@ -10882,9 +10876,9 @@
         <v>67</v>
       </c>
     </row>
-    <row r="445" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="G445" s="2" t="s">
         <v>124</v>
@@ -10896,9 +10890,9 @@
         <v>67</v>
       </c>
     </row>
-    <row r="446" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="G446" s="2" t="s">
         <v>499</v>
@@ -10910,9 +10904,9 @@
         <v>67</v>
       </c>
     </row>
-    <row r="447" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="G447" s="2" t="s">
         <v>439</v>
@@ -10924,9 +10918,9 @@
         <v>67</v>
       </c>
     </row>
-    <row r="448" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="G448" s="2" t="s">
         <v>224</v>
@@ -10938,7 +10932,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="449" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>938</v>
       </c>
@@ -10952,7 +10946,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="450" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>941</v>
       </c>
@@ -10966,9 +10960,9 @@
         <v>67</v>
       </c>
     </row>
-    <row r="451" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="G451" s="2" t="s">
         <v>581</v>
@@ -10980,7 +10974,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="452" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
         <v>935</v>
       </c>
@@ -10994,7 +10988,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="453" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>926</v>
       </c>
@@ -11008,9 +11002,9 @@
         <v>67</v>
       </c>
     </row>
-    <row r="454" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="G454" s="2" t="s">
         <v>435</v>
@@ -11022,9 +11016,9 @@
         <v>67</v>
       </c>
     </row>
-    <row r="455" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="G455" s="2" t="s">
         <v>435</v>
@@ -11036,7 +11030,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="456" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>933</v>
       </c>
@@ -11050,9 +11044,9 @@
         <v>67</v>
       </c>
     </row>
-    <row r="457" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="G457" s="2" t="s">
         <v>708</v>
@@ -11064,7 +11058,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="458" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
         <v>944</v>
       </c>
@@ -11078,9 +11072,9 @@
         <v>67</v>
       </c>
     </row>
-    <row r="459" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="G459" s="2" t="s">
         <v>676</v>
@@ -11092,9 +11086,9 @@
         <v>67</v>
       </c>
     </row>
-    <row r="460" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="G460" s="2" t="s">
         <v>435</v>
@@ -11106,23 +11100,23 @@
         <v>67</v>
       </c>
     </row>
-    <row r="461" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="G461" s="2" t="s">
         <v>658</v>
       </c>
       <c r="H461" s="2" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="J461" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="462" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="G462" s="2" t="s">
         <v>437</v>
@@ -11134,9 +11128,9 @@
         <v>67</v>
       </c>
     </row>
-    <row r="463" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="G463" s="2" t="s">
         <v>710</v>
@@ -11148,9 +11142,9 @@
         <v>67</v>
       </c>
     </row>
-    <row r="464" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="G464" s="2" t="s">
         <v>698</v>
@@ -11162,7 +11156,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="465" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
         <v>936</v>
       </c>
@@ -11176,9 +11170,9 @@
         <v>67</v>
       </c>
     </row>
-    <row r="466" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="G466" s="2" t="s">
         <v>676</v>
@@ -11190,9 +11184,9 @@
         <v>67</v>
       </c>
     </row>
-    <row r="467" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="G467" s="2" t="s">
         <v>710</v>
@@ -11204,9 +11198,9 @@
         <v>67</v>
       </c>
     </row>
-    <row r="468" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="G468" s="2" t="s">
         <v>698</v>
@@ -11218,7 +11212,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="469" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
         <v>934</v>
       </c>
@@ -11232,7 +11226,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="470" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
         <v>927</v>
       </c>
@@ -11246,7 +11240,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="471" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
         <v>943</v>
       </c>
@@ -11260,7 +11254,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="472" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
         <v>931</v>
       </c>
@@ -11274,9 +11268,9 @@
         <v>67</v>
       </c>
     </row>
-    <row r="473" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="G473" s="2" t="s">
         <v>680</v>
@@ -11288,35 +11282,35 @@
         <v>67</v>
       </c>
     </row>
-    <row r="474" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="G474" s="2" t="s">
         <v>724</v>
       </c>
       <c r="H474" s="2" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="J474" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="475" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="G475" s="2" t="s">
         <v>224</v>
       </c>
       <c r="H475" s="2" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J475" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="476" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
         <v>929</v>
       </c>
@@ -11330,7 +11324,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="477" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
         <v>939</v>
       </c>
@@ -11344,7 +11338,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="478" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
         <v>945</v>
       </c>
@@ -11358,9 +11352,9 @@
         <v>67</v>
       </c>
     </row>
-    <row r="479" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="G479" s="2" t="s">
         <v>698</v>
@@ -11372,21 +11366,21 @@
         <v>67</v>
       </c>
     </row>
-    <row r="480" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="G480" s="2" t="s">
         <v>224</v>
       </c>
       <c r="H480" s="2" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="J480" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="481" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
         <v>937</v>
       </c>
@@ -11400,7 +11394,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="482" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
         <v>952</v>
       </c>
@@ -11408,13 +11402,13 @@
         <v>735</v>
       </c>
       <c r="H482" s="2" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="J482" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="483" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
         <v>956</v>
       </c>
@@ -11422,15 +11416,15 @@
         <v>659</v>
       </c>
       <c r="H483" s="2" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="J483" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="484" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="G484" s="2" t="s">
         <v>435</v>
@@ -11442,7 +11436,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="485" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
         <v>928</v>
       </c>
@@ -11456,9 +11450,9 @@
         <v>67</v>
       </c>
     </row>
-    <row r="486" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="G486" s="2" t="s">
         <v>501</v>
@@ -11470,23 +11464,23 @@
         <v>67</v>
       </c>
     </row>
-    <row r="487" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="G487" s="2" t="s">
         <v>1262</v>
       </c>
       <c r="H487" s="2" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="J487" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="488" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="G488" s="2" t="s">
         <v>602</v>
@@ -11498,7 +11492,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="489" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
         <v>930</v>
       </c>
@@ -11512,9 +11506,9 @@
         <v>67</v>
       </c>
     </row>
-    <row r="490" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="G490" s="2" t="s">
         <v>701</v>
@@ -11526,9 +11520,9 @@
         <v>67</v>
       </c>
     </row>
-    <row r="491" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="G491" s="2" t="s">
         <v>699</v>
@@ -11540,9 +11534,9 @@
         <v>67</v>
       </c>
     </row>
-    <row r="492" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="G492" s="2" t="s">
         <v>648</v>
@@ -11554,7 +11548,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="493" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
         <v>953</v>
       </c>
@@ -11562,29 +11556,29 @@
         <v>757</v>
       </c>
       <c r="H493" s="2" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="J493" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="494" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="G494" s="2" t="s">
         <v>760</v>
       </c>
       <c r="H494" s="2" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="J494" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="495" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="G495" s="2" t="s">
         <v>280</v>
@@ -11596,9 +11590,9 @@
         <v>67</v>
       </c>
     </row>
-    <row r="496" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="G496" s="2" t="s">
         <v>126</v>
@@ -11610,23 +11604,23 @@
         <v>67</v>
       </c>
     </row>
-    <row r="497" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="G497" s="2" t="s">
         <v>1257</v>
       </c>
       <c r="H497" s="2" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="J497" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="498" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="G498" s="2" t="s">
         <v>677</v>
@@ -11638,7 +11632,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="499" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
         <v>950</v>
       </c>
@@ -11652,9 +11646,9 @@
         <v>67</v>
       </c>
     </row>
-    <row r="500" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="G500" s="2" t="s">
         <v>748</v>
@@ -11666,7 +11660,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="501" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
         <v>942</v>
       </c>
@@ -11680,7 +11674,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="502" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
         <v>954</v>
       </c>
@@ -11688,13 +11682,13 @@
         <v>707</v>
       </c>
       <c r="H502" s="2" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="J502" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="503" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
         <v>957</v>
       </c>
@@ -11702,29 +11696,29 @@
         <v>1263</v>
       </c>
       <c r="H503" s="2" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="J503" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="504" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="G504" s="2" t="s">
         <v>698</v>
       </c>
       <c r="H504" s="2" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="J504" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="505" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="G505" s="2" t="s">
         <v>708</v>
@@ -11736,7 +11730,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="506" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
         <v>940</v>
       </c>
@@ -11750,9 +11744,9 @@
         <v>67</v>
       </c>
     </row>
-    <row r="507" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="G507" s="2" t="s">
         <v>646</v>
@@ -11764,35 +11758,35 @@
         <v>67</v>
       </c>
     </row>
-    <row r="508" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="G508" s="2" t="s">
         <v>708</v>
       </c>
       <c r="H508" s="2" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="J508" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="509" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="G509" s="2" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H509" s="2" t="s">
         <v>1403</v>
-      </c>
-      <c r="H509" s="2" t="s">
-        <v>1404</v>
       </c>
       <c r="J509" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="510" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A510" s="4">
         <v>14289</v>
       </c>
@@ -11800,13 +11794,13 @@
         <v>1264</v>
       </c>
       <c r="H510" s="2" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="J510" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="511" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A511" s="4">
         <v>23973</v>
       </c>
@@ -11814,13 +11808,13 @@
         <v>1265</v>
       </c>
       <c r="H511" s="2" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="J511" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="512" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A512" s="4">
         <v>53921</v>
       </c>
@@ -11828,63 +11822,63 @@
         <v>435</v>
       </c>
       <c r="H512" s="2" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="J512" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="513" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="G513" s="2" t="s">
+        <v>1407</v>
+      </c>
+      <c r="H513" s="2" t="s">
         <v>1408</v>
-      </c>
-      <c r="H513" s="2" t="s">
-        <v>1409</v>
       </c>
       <c r="J513" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="514" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A514" s="4">
         <v>22973</v>
       </c>
-      <c r="G514" s="5" t="s">
+      <c r="G514" s="2" t="s">
+        <v>1409</v>
+      </c>
+      <c r="H514" s="2" t="s">
         <v>1410</v>
-      </c>
-      <c r="H514" s="5" t="s">
-        <v>1411</v>
       </c>
       <c r="J514" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="515" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A515" s="4">
         <v>16435</v>
       </c>
-      <c r="G515" s="5" t="s">
+      <c r="G515" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="H515" s="5" t="s">
-        <v>1412</v>
+      <c r="H515" s="2" t="s">
+        <v>1411</v>
       </c>
       <c r="J515" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="516" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A516" s="4">
         <v>2667</v>
       </c>
-      <c r="G516" s="5" t="s">
+      <c r="G516" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="H516" s="5" t="s">
-        <v>1413</v>
+      <c r="H516" s="2" t="s">
+        <v>1412</v>
       </c>
       <c r="J516" t="s">
         <v>31</v>

--- a/input/lista/1 LISTA PDV ENI 2.xlsx
+++ b/input/lista/1 LISTA PDV ENI 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nadir\Desktop\APP TELEPASS\FILE FISSI\lista\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21ECBC85-76B1-4789-988E-B71FBACCB197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6435A2DB-3245-4862-84BC-A308402F66E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{D320C423-4B98-4D55-B6E8-3ABF0EE22191}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Foglio1" sheetId="5" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Foglio1!$A$1:$J$442</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Foglio1!$A$1:$J$441</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2057" uniqueCount="1413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2053" uniqueCount="1410">
   <si>
     <t>ALESSANDRIA</t>
   </si>
@@ -1128,9 +1128,6 @@
     <t>PACE</t>
   </si>
   <si>
-    <t>SETTALA</t>
-  </si>
-  <si>
     <t>PESCHIERA BORROMEO</t>
   </si>
   <si>
@@ -2487,9 +2484,6 @@
     <t>12416</t>
   </si>
   <si>
-    <t>2414</t>
-  </si>
-  <si>
     <t>51919</t>
   </si>
   <si>
@@ -2587,9 +2581,6 @@
   </si>
   <si>
     <t>VIA GIUSEPPE  MAZZINI SNC</t>
-  </si>
-  <si>
-    <t>VIA CERCA  FRAZ.CALEPPIO 21</t>
   </si>
   <si>
     <t>9298</t>
@@ -4652,7 +4643,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{175EF563-0873-44BA-ACAF-2DC290E6A803}">
-  <dimension ref="A1:J516"/>
+  <dimension ref="A1:J515"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="29.44140625" bestFit="1" customWidth="1"/>
@@ -4662,13 +4653,13 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="G1" t="s">
+        <v>505</v>
+      </c>
+      <c r="H1" t="s">
         <v>506</v>
-      </c>
-      <c r="H1" t="s">
-        <v>507</v>
       </c>
       <c r="J1" t="s">
         <v>34</v>
@@ -4676,13 +4667,13 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="G2" t="s">
+        <v>495</v>
+      </c>
+      <c r="H2" t="s">
         <v>496</v>
-      </c>
-      <c r="H2" t="s">
-        <v>497</v>
       </c>
       <c r="J2" t="s">
         <v>34</v>
@@ -4690,7 +4681,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="G3" t="s">
         <v>227</v>
@@ -4704,7 +4695,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="G4" t="s">
         <v>94</v>
@@ -4718,7 +4709,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="G5" t="s">
         <v>324</v>
@@ -4732,7 +4723,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="G6" t="s">
         <v>232</v>
@@ -4746,13 +4737,13 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="G7" t="s">
+        <v>392</v>
+      </c>
+      <c r="H7" t="s">
         <v>393</v>
-      </c>
-      <c r="H7" t="s">
-        <v>394</v>
       </c>
       <c r="J7" t="s">
         <v>34</v>
@@ -4760,13 +4751,13 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="G8" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H8" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="J8" t="s">
         <v>34</v>
@@ -4774,13 +4765,13 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="G9" t="s">
+        <v>528</v>
+      </c>
+      <c r="H9" t="s">
         <v>529</v>
-      </c>
-      <c r="H9" t="s">
-        <v>530</v>
       </c>
       <c r="J9" t="s">
         <v>34</v>
@@ -4788,13 +4779,13 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="G10" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H10" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="J10" t="s">
         <v>34</v>
@@ -4802,13 +4793,13 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="G11" t="s">
+        <v>389</v>
+      </c>
+      <c r="H11" t="s">
         <v>390</v>
-      </c>
-      <c r="H11" t="s">
-        <v>391</v>
       </c>
       <c r="J11" t="s">
         <v>34</v>
@@ -4816,13 +4807,13 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="G12" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H12" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="J12" t="s">
         <v>34</v>
@@ -4830,7 +4821,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
       <c r="G13" t="s">
         <v>310</v>
@@ -4844,7 +4835,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="G14" t="s">
         <v>239</v>
@@ -4858,13 +4849,13 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="G15" t="s">
+        <v>488</v>
+      </c>
+      <c r="H15" t="s">
         <v>489</v>
-      </c>
-      <c r="H15" t="s">
-        <v>490</v>
       </c>
       <c r="J15" t="s">
         <v>34</v>
@@ -4872,13 +4863,13 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="G16" t="s">
+        <v>508</v>
+      </c>
+      <c r="H16" t="s">
         <v>509</v>
-      </c>
-      <c r="H16" t="s">
-        <v>510</v>
       </c>
       <c r="J16" t="s">
         <v>34</v>
@@ -4886,7 +4877,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="G17" t="s">
         <v>226</v>
@@ -4900,7 +4891,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="G18" t="s">
         <v>94</v>
@@ -4914,13 +4905,13 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="G19" t="s">
+        <v>531</v>
+      </c>
+      <c r="H19" t="s">
         <v>532</v>
-      </c>
-      <c r="H19" t="s">
-        <v>533</v>
       </c>
       <c r="J19" t="s">
         <v>34</v>
@@ -4928,7 +4919,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="G20" t="s">
         <v>251</v>
@@ -4942,13 +4933,13 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="G21" t="s">
         <v>226</v>
       </c>
       <c r="H21" t="s">
-        <v>1296</v>
+        <v>1293</v>
       </c>
       <c r="J21" t="s">
         <v>34</v>
@@ -4956,7 +4947,7 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="G22" t="s">
         <v>104</v>
@@ -4970,7 +4961,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="G23" t="s">
         <v>35</v>
@@ -4984,7 +4975,7 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="G24" t="s">
         <v>241</v>
@@ -4998,13 +4989,13 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="G25" t="s">
+        <v>526</v>
+      </c>
+      <c r="H25" t="s">
         <v>527</v>
-      </c>
-      <c r="H25" t="s">
-        <v>528</v>
       </c>
       <c r="J25" t="s">
         <v>34</v>
@@ -5012,7 +5003,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="G26" t="s">
         <v>251</v>
@@ -5026,13 +5017,13 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="G27" t="s">
+        <v>387</v>
+      </c>
+      <c r="H27" t="s">
         <v>388</v>
-      </c>
-      <c r="H27" t="s">
-        <v>389</v>
       </c>
       <c r="J27" t="s">
         <v>34</v>
@@ -5040,13 +5031,13 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="G28" t="s">
+        <v>486</v>
+      </c>
+      <c r="H28" t="s">
         <v>487</v>
-      </c>
-      <c r="H28" t="s">
-        <v>488</v>
       </c>
       <c r="J28" t="s">
         <v>34</v>
@@ -5054,7 +5045,7 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="G29" t="s">
         <v>226</v>
@@ -5068,7 +5059,7 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="G30" t="s">
         <v>94</v>
@@ -5082,7 +5073,7 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="G31" t="s">
         <v>314</v>
@@ -5096,13 +5087,13 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="G32" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H32" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="J32" t="s">
         <v>34</v>
@@ -5110,13 +5101,13 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="G33" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="H33" t="s">
-        <v>1297</v>
+        <v>1294</v>
       </c>
       <c r="J33" t="s">
         <v>34</v>
@@ -5124,7 +5115,7 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="G34" t="s">
         <v>100</v>
@@ -5138,7 +5129,7 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="G35" t="s">
         <v>94</v>
@@ -5152,7 +5143,7 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="G36" t="s">
         <v>338</v>
@@ -5166,7 +5157,7 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="G37" t="s">
         <v>97</v>
@@ -5180,7 +5171,7 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="G38" t="s">
         <v>253</v>
@@ -5194,7 +5185,7 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="G39" t="s">
         <v>236</v>
@@ -5208,13 +5199,13 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="G40" t="s">
+        <v>397</v>
+      </c>
+      <c r="H40" t="s">
         <v>398</v>
-      </c>
-      <c r="H40" t="s">
-        <v>399</v>
       </c>
       <c r="J40" t="s">
         <v>34</v>
@@ -5222,7 +5213,7 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="G41" t="s">
         <v>94</v>
@@ -5236,7 +5227,7 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="G42" t="s">
         <v>282</v>
@@ -5250,13 +5241,13 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="G43" t="s">
         <v>224</v>
       </c>
       <c r="H43" t="s">
-        <v>1298</v>
+        <v>1295</v>
       </c>
       <c r="J43" t="s">
         <v>34</v>
@@ -5264,13 +5255,13 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="G44" t="s">
+        <v>490</v>
+      </c>
+      <c r="H44" t="s">
         <v>491</v>
-      </c>
-      <c r="H44" t="s">
-        <v>492</v>
       </c>
       <c r="J44" t="s">
         <v>34</v>
@@ -5278,7 +5269,7 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="G45" t="s">
         <v>94</v>
@@ -5292,13 +5283,13 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="G46" t="s">
         <v>32</v>
       </c>
       <c r="H46" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="J46" t="s">
         <v>34</v>
@@ -5306,7 +5297,7 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="G47" t="s">
         <v>94</v>
@@ -5320,13 +5311,13 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="G48" t="s">
+        <v>598</v>
+      </c>
+      <c r="H48" t="s">
         <v>599</v>
-      </c>
-      <c r="H48" t="s">
-        <v>600</v>
       </c>
       <c r="J48" t="s">
         <v>34</v>
@@ -5334,13 +5325,13 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="G49" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H49" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="J49" t="s">
         <v>34</v>
@@ -5348,13 +5339,13 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="G50" t="s">
         <v>326</v>
       </c>
       <c r="H50" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
       <c r="J50" t="s">
         <v>34</v>
@@ -5362,7 +5353,7 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="G51" t="s">
         <v>226</v>
@@ -5376,13 +5367,13 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="G52" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H52" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="J52" t="s">
         <v>34</v>
@@ -5390,13 +5381,13 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="G53" t="s">
         <v>94</v>
       </c>
       <c r="H53" t="s">
-        <v>1299</v>
+        <v>1296</v>
       </c>
       <c r="J53" t="s">
         <v>34</v>
@@ -5404,13 +5395,13 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="G54" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H54" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J54" t="s">
         <v>34</v>
@@ -5418,7 +5409,7 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="G55" t="s">
         <v>37</v>
@@ -5432,7 +5423,7 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="G56" t="s">
         <v>94</v>
@@ -5446,7 +5437,7 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="G57" t="s">
         <v>102</v>
@@ -5460,7 +5451,7 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="G58" t="s">
         <v>115</v>
@@ -5474,13 +5465,13 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="G59" t="s">
         <v>94</v>
       </c>
       <c r="H59" t="s">
-        <v>1300</v>
+        <v>1297</v>
       </c>
       <c r="J59" t="s">
         <v>34</v>
@@ -5488,13 +5479,13 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="G60" t="s">
+        <v>493</v>
+      </c>
+      <c r="H60" t="s">
         <v>494</v>
-      </c>
-      <c r="H60" t="s">
-        <v>495</v>
       </c>
       <c r="J60" t="s">
         <v>34</v>
@@ -5502,7 +5493,7 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="G61" t="s">
         <v>32</v>
@@ -5516,13 +5507,13 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="G62" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H62" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="J62" t="s">
         <v>34</v>
@@ -5530,13 +5521,13 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="G63" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H63" t="s">
-        <v>1301</v>
+        <v>1298</v>
       </c>
       <c r="J63" t="s">
         <v>34</v>
@@ -5544,7 +5535,7 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="G64" t="s">
         <v>316</v>
@@ -5558,7 +5549,7 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="G65" t="s">
         <v>312</v>
@@ -5572,7 +5563,7 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="G66" t="s">
         <v>32</v>
@@ -5586,13 +5577,13 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="G67" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H67" t="s">
-        <v>1302</v>
+        <v>1299</v>
       </c>
       <c r="J67" t="s">
         <v>34</v>
@@ -5600,13 +5591,13 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="G68" t="s">
         <v>312</v>
       </c>
       <c r="H68" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
       <c r="J68" t="s">
         <v>34</v>
@@ -5614,7 +5605,7 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="G69" t="s">
         <v>328</v>
@@ -5628,13 +5619,13 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="G70" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H70" t="s">
-        <v>1303</v>
+        <v>1300</v>
       </c>
       <c r="J70" t="s">
         <v>34</v>
@@ -5642,13 +5633,13 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="G71" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="H71" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="J71" t="s">
         <v>34</v>
@@ -5656,13 +5647,13 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="G72" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H72" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
       <c r="J72" t="s">
         <v>34</v>
@@ -5670,7 +5661,7 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="G73" t="s">
         <v>110</v>
@@ -5684,13 +5675,13 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="G74" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H74" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J74" t="s">
         <v>34</v>
@@ -5698,7 +5689,7 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="G75" t="s">
         <v>95</v>
@@ -5712,7 +5703,7 @@
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
       <c r="G76" t="s">
         <v>326</v>
@@ -5726,13 +5717,13 @@
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
       <c r="G77" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="H77" t="s">
-        <v>1301</v>
+        <v>1298</v>
       </c>
       <c r="J77" t="s">
         <v>34</v>
@@ -5740,13 +5731,13 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="G78" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H78" t="s">
-        <v>1301</v>
+        <v>1298</v>
       </c>
       <c r="J78" t="s">
         <v>34</v>
@@ -5754,7 +5745,7 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="G79" t="s">
         <v>312</v>
@@ -5768,7 +5759,7 @@
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="G80" t="s">
         <v>230</v>
@@ -5782,13 +5773,13 @@
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="G81" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H81" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="J81" t="s">
         <v>34</v>
@@ -5796,13 +5787,13 @@
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="G82" t="s">
+        <v>512</v>
+      </c>
+      <c r="H82" t="s">
         <v>513</v>
-      </c>
-      <c r="H82" t="s">
-        <v>514</v>
       </c>
       <c r="J82" t="s">
         <v>34</v>
@@ -5810,7 +5801,7 @@
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="G83" t="s">
         <v>226</v>
@@ -5824,7 +5815,7 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="G84" t="s">
         <v>104</v>
@@ -5838,7 +5829,7 @@
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="G85" t="s">
         <v>107</v>
@@ -5852,7 +5843,7 @@
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="G86" t="s">
         <v>284</v>
@@ -5866,13 +5857,13 @@
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
-        <v>1213</v>
+        <v>1210</v>
       </c>
       <c r="G87" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="H87" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="J87" t="s">
         <v>34</v>
@@ -5880,41 +5871,41 @@
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="G88" t="s">
+        <v>521</v>
+      </c>
+      <c r="H88" t="s">
         <v>522</v>
       </c>
-      <c r="H88" t="s">
+      <c r="J88" t="s">
         <v>523</v>
-      </c>
-      <c r="J88" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="G89" t="s">
+        <v>524</v>
+      </c>
+      <c r="H89" t="s">
         <v>525</v>
       </c>
-      <c r="H89" t="s">
-        <v>526</v>
-      </c>
       <c r="J89" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>1038</v>
+        <v>1035</v>
       </c>
       <c r="G90" t="s">
+        <v>455</v>
+      </c>
+      <c r="H90" t="s">
         <v>456</v>
-      </c>
-      <c r="H90" t="s">
-        <v>457</v>
       </c>
       <c r="J90" t="s">
         <v>31</v>
@@ -5922,13 +5913,13 @@
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="G91" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H91" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="J91" t="s">
         <v>31</v>
@@ -5936,13 +5927,13 @@
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="G92" t="s">
+        <v>514</v>
+      </c>
+      <c r="H92" t="s">
         <v>515</v>
-      </c>
-      <c r="H92" t="s">
-        <v>516</v>
       </c>
       <c r="J92" t="s">
         <v>31</v>
@@ -5950,13 +5941,13 @@
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="G93" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H93" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J93" t="s">
         <v>31</v>
@@ -5964,13 +5955,13 @@
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="G94" t="s">
+        <v>510</v>
+      </c>
+      <c r="H94" t="s">
         <v>511</v>
-      </c>
-      <c r="H94" t="s">
-        <v>512</v>
       </c>
       <c r="J94" t="s">
         <v>31</v>
@@ -5978,13 +5969,13 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="G95" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H95" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J95" t="s">
         <v>31</v>
@@ -5992,13 +5983,13 @@
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="G96" t="s">
+        <v>518</v>
+      </c>
+      <c r="H96" t="s">
         <v>519</v>
-      </c>
-      <c r="H96" t="s">
-        <v>520</v>
       </c>
       <c r="J96" t="s">
         <v>31</v>
@@ -6006,13 +5997,13 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="G97" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H97" t="s">
-        <v>1304</v>
+        <v>1301</v>
       </c>
       <c r="J97" t="s">
         <v>31</v>
@@ -6020,13 +6011,13 @@
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
       <c r="G98" t="s">
+        <v>516</v>
+      </c>
+      <c r="H98" t="s">
         <v>517</v>
-      </c>
-      <c r="H98" t="s">
-        <v>518</v>
       </c>
       <c r="J98" t="s">
         <v>31</v>
@@ -6034,13 +6025,13 @@
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="G99" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="H99" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="J99" t="s">
         <v>31</v>
@@ -6048,13 +6039,13 @@
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="G100" t="s">
+        <v>399</v>
+      </c>
+      <c r="H100" t="s">
         <v>400</v>
-      </c>
-      <c r="H100" t="s">
-        <v>401</v>
       </c>
       <c r="J100" t="s">
         <v>31</v>
@@ -6062,13 +6053,13 @@
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="G101" t="s">
+        <v>673</v>
+      </c>
+      <c r="H101" t="s">
         <v>674</v>
-      </c>
-      <c r="H101" t="s">
-        <v>675</v>
       </c>
       <c r="J101" t="s">
         <v>31</v>
@@ -6076,13 +6067,13 @@
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="G102" t="s">
+        <v>402</v>
+      </c>
+      <c r="H102" t="s">
         <v>403</v>
-      </c>
-      <c r="H102" t="s">
-        <v>404</v>
       </c>
       <c r="J102" t="s">
         <v>31</v>
@@ -6090,13 +6081,13 @@
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="G103" t="s">
+        <v>463</v>
+      </c>
+      <c r="H103" t="s">
         <v>464</v>
-      </c>
-      <c r="H103" t="s">
-        <v>465</v>
       </c>
       <c r="J103" t="s">
         <v>31</v>
@@ -6104,7 +6095,7 @@
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="G104" t="s">
         <v>190</v>
@@ -6118,13 +6109,13 @@
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="G105" t="s">
+        <v>666</v>
+      </c>
+      <c r="H105" t="s">
         <v>667</v>
-      </c>
-      <c r="H105" t="s">
-        <v>668</v>
       </c>
       <c r="J105" t="s">
         <v>31</v>
@@ -6132,13 +6123,13 @@
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G106" t="s">
+        <v>384</v>
+      </c>
+      <c r="H106" t="s">
         <v>385</v>
-      </c>
-      <c r="H106" t="s">
-        <v>386</v>
       </c>
       <c r="J106" t="s">
         <v>31</v>
@@ -6146,7 +6137,7 @@
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="G107" t="s">
         <v>357</v>
@@ -6160,13 +6151,13 @@
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="G108" t="s">
+        <v>689</v>
+      </c>
+      <c r="H108" t="s">
         <v>690</v>
-      </c>
-      <c r="H108" t="s">
-        <v>691</v>
       </c>
       <c r="J108" t="s">
         <v>31</v>
@@ -6174,7 +6165,7 @@
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="G109" t="s">
         <v>355</v>
@@ -6188,7 +6179,7 @@
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="G110" t="s">
         <v>192</v>
@@ -6202,13 +6193,13 @@
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="G111" t="s">
+        <v>629</v>
+      </c>
+      <c r="H111" t="s">
         <v>630</v>
-      </c>
-      <c r="H111" t="s">
-        <v>631</v>
       </c>
       <c r="J111" t="s">
         <v>31</v>
@@ -6216,13 +6207,13 @@
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="G112" t="s">
-        <v>1251</v>
+        <v>1248</v>
       </c>
       <c r="H112" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
       <c r="J112" t="s">
         <v>31</v>
@@ -6230,10 +6221,10 @@
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="G113" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H113" t="s">
         <v>353</v>
@@ -6244,13 +6235,13 @@
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="G114" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H114" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="J114" t="s">
         <v>31</v>
@@ -6258,7 +6249,7 @@
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="G115" t="s">
         <v>197</v>
@@ -6272,7 +6263,7 @@
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="G116" t="s">
         <v>359</v>
@@ -6286,13 +6277,13 @@
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="G117" t="s">
+        <v>664</v>
+      </c>
+      <c r="H117" t="s">
         <v>665</v>
-      </c>
-      <c r="H117" t="s">
-        <v>666</v>
       </c>
       <c r="J117" t="s">
         <v>31</v>
@@ -6300,7 +6291,7 @@
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="G118" t="s">
         <v>189</v>
@@ -6314,13 +6305,13 @@
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="G119" t="s">
         <v>93</v>
       </c>
       <c r="H119" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="J119" t="s">
         <v>31</v>
@@ -6328,13 +6319,13 @@
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="G120" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H120" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="J120" t="s">
         <v>31</v>
@@ -6342,13 +6333,13 @@
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="G121" t="s">
+        <v>483</v>
+      </c>
+      <c r="H121" t="s">
         <v>484</v>
-      </c>
-      <c r="H121" t="s">
-        <v>485</v>
       </c>
       <c r="J121" t="s">
         <v>31</v>
@@ -6356,13 +6347,13 @@
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="G122" t="s">
+        <v>642</v>
+      </c>
+      <c r="H122" t="s">
         <v>643</v>
-      </c>
-      <c r="H122" t="s">
-        <v>644</v>
       </c>
       <c r="J122" t="s">
         <v>31</v>
@@ -6370,13 +6361,13 @@
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="G123" t="s">
         <v>353</v>
       </c>
       <c r="H123" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="J123" t="s">
         <v>31</v>
@@ -6384,7 +6375,7 @@
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="G124" t="s">
         <v>318</v>
@@ -6398,13 +6389,13 @@
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="G125" t="s">
+        <v>404</v>
+      </c>
+      <c r="H125" t="s">
         <v>405</v>
-      </c>
-      <c r="H125" t="s">
-        <v>406</v>
       </c>
       <c r="J125" t="s">
         <v>31</v>
@@ -6412,7 +6403,7 @@
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="G126" t="s">
         <v>308</v>
@@ -6426,13 +6417,13 @@
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="G127" t="s">
         <v>353</v>
       </c>
       <c r="H127" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="J127" t="s">
         <v>31</v>
@@ -6440,13 +6431,13 @@
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="G128" t="s">
+        <v>625</v>
+      </c>
+      <c r="H128" t="s">
         <v>626</v>
-      </c>
-      <c r="H128" t="s">
-        <v>627</v>
       </c>
       <c r="J128" t="s">
         <v>31</v>
@@ -6454,13 +6445,13 @@
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="G129" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H129" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="J129" t="s">
         <v>31</v>
@@ -6468,13 +6459,13 @@
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="G130" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H130" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="J130" t="s">
         <v>31</v>
@@ -6482,13 +6473,13 @@
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="G131" t="s">
+        <v>687</v>
+      </c>
+      <c r="H131" t="s">
         <v>688</v>
-      </c>
-      <c r="H131" t="s">
-        <v>689</v>
       </c>
       <c r="J131" t="s">
         <v>31</v>
@@ -6496,13 +6487,13 @@
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="G132" t="s">
+        <v>671</v>
+      </c>
+      <c r="H132" t="s">
         <v>672</v>
-      </c>
-      <c r="H132" t="s">
-        <v>673</v>
       </c>
       <c r="J132" t="s">
         <v>31</v>
@@ -6510,13 +6501,13 @@
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="G133" t="s">
+        <v>640</v>
+      </c>
+      <c r="H133" t="s">
         <v>641</v>
-      </c>
-      <c r="H133" t="s">
-        <v>642</v>
       </c>
       <c r="J133" t="s">
         <v>31</v>
@@ -6524,7 +6515,7 @@
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="G134" t="s">
         <v>361</v>
@@ -6538,13 +6529,13 @@
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="G135" t="s">
+        <v>480</v>
+      </c>
+      <c r="H135" t="s">
         <v>481</v>
-      </c>
-      <c r="H135" t="s">
-        <v>482</v>
       </c>
       <c r="J135" t="s">
         <v>31</v>
@@ -6552,13 +6543,13 @@
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="G136" t="s">
+        <v>382</v>
+      </c>
+      <c r="H136" t="s">
         <v>383</v>
-      </c>
-      <c r="H136" t="s">
-        <v>384</v>
       </c>
       <c r="J136" t="s">
         <v>31</v>
@@ -6566,13 +6557,13 @@
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="G137" t="s">
+        <v>661</v>
+      </c>
+      <c r="H137" t="s">
         <v>662</v>
-      </c>
-      <c r="H137" t="s">
-        <v>663</v>
       </c>
       <c r="J137" t="s">
         <v>31</v>
@@ -6580,13 +6571,13 @@
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="G138" t="s">
+        <v>668</v>
+      </c>
+      <c r="H138" t="s">
         <v>669</v>
-      </c>
-      <c r="H138" t="s">
-        <v>670</v>
       </c>
       <c r="J138" t="s">
         <v>31</v>
@@ -6594,7 +6585,7 @@
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="G139" t="s">
         <v>189</v>
@@ -6608,13 +6599,13 @@
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="G140" t="s">
+        <v>621</v>
+      </c>
+      <c r="H140" t="s">
         <v>622</v>
-      </c>
-      <c r="H140" t="s">
-        <v>623</v>
       </c>
       <c r="J140" t="s">
         <v>31</v>
@@ -6622,13 +6613,13 @@
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="G141" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="H141" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="J141" t="s">
         <v>31</v>
@@ -6636,13 +6627,13 @@
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="G142" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H142" t="s">
-        <v>1305</v>
+        <v>1302</v>
       </c>
       <c r="J142" t="s">
         <v>31</v>
@@ -6650,13 +6641,13 @@
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="G143" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H143" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
       <c r="J143" t="s">
         <v>31</v>
@@ -6664,13 +6655,13 @@
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="G144" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H144" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="J144" t="s">
         <v>31</v>
@@ -6678,13 +6669,13 @@
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="G145" t="s">
+        <v>430</v>
+      </c>
+      <c r="H145" t="s">
         <v>431</v>
-      </c>
-      <c r="H145" t="s">
-        <v>432</v>
       </c>
       <c r="J145" t="s">
         <v>31</v>
@@ -6692,7 +6683,7 @@
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="G146" t="s">
         <v>321</v>
@@ -6706,13 +6697,13 @@
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="G147" t="s">
         <v>353</v>
       </c>
       <c r="H147" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="J147" t="s">
         <v>31</v>
@@ -6720,13 +6711,13 @@
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="G148" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
       <c r="H148" t="s">
-        <v>1273</v>
+        <v>1270</v>
       </c>
       <c r="J148" t="s">
         <v>31</v>
@@ -6734,13 +6725,13 @@
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="G149" t="s">
+        <v>377</v>
+      </c>
+      <c r="H149" t="s">
         <v>378</v>
-      </c>
-      <c r="H149" t="s">
-        <v>379</v>
       </c>
       <c r="J149" t="s">
         <v>31</v>
@@ -6748,7 +6739,7 @@
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="G150" t="s">
         <v>319</v>
@@ -6762,13 +6753,13 @@
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="G151" t="s">
+        <v>369</v>
+      </c>
+      <c r="H151" t="s">
         <v>370</v>
-      </c>
-      <c r="H151" t="s">
-        <v>371</v>
       </c>
       <c r="J151" t="s">
         <v>31</v>
@@ -6776,13 +6767,13 @@
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="G152" t="s">
+        <v>375</v>
+      </c>
+      <c r="H152" t="s">
         <v>376</v>
-      </c>
-      <c r="H152" t="s">
-        <v>377</v>
       </c>
       <c r="J152" t="s">
         <v>31</v>
@@ -6790,13 +6781,13 @@
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="G153" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H153" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="J153" t="s">
         <v>31</v>
@@ -6804,13 +6795,13 @@
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="G154" t="s">
+        <v>635</v>
+      </c>
+      <c r="H154" t="s">
         <v>636</v>
-      </c>
-      <c r="H154" t="s">
-        <v>637</v>
       </c>
       <c r="J154" t="s">
         <v>31</v>
@@ -6818,13 +6809,13 @@
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="G155" t="s">
+        <v>460</v>
+      </c>
+      <c r="H155" t="s">
         <v>461</v>
-      </c>
-      <c r="H155" t="s">
-        <v>462</v>
       </c>
       <c r="J155" t="s">
         <v>31</v>
@@ -6832,13 +6823,13 @@
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="G156" t="s">
+        <v>363</v>
+      </c>
+      <c r="H156" t="s">
         <v>364</v>
-      </c>
-      <c r="H156" t="s">
-        <v>365</v>
       </c>
       <c r="J156" t="s">
         <v>31</v>
@@ -6846,13 +6837,13 @@
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="G157" t="s">
         <v>353</v>
       </c>
       <c r="H157" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="J157" t="s">
         <v>31</v>
@@ -6860,13 +6851,13 @@
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="G158" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="H158" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="J158" t="s">
         <v>31</v>
@@ -6874,7 +6865,7 @@
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="G159" t="s">
         <v>194</v>
@@ -6888,7 +6879,7 @@
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="G160" t="s">
         <v>353</v>
@@ -6902,13 +6893,13 @@
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="G161" t="s">
         <v>353</v>
       </c>
       <c r="H161" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J161" t="s">
         <v>31</v>
@@ -6916,13 +6907,13 @@
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="G162" t="s">
+        <v>627</v>
+      </c>
+      <c r="H162" t="s">
         <v>628</v>
-      </c>
-      <c r="H162" t="s">
-        <v>629</v>
       </c>
       <c r="J162" t="s">
         <v>31</v>
@@ -6930,13 +6921,13 @@
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="G163" t="s">
+        <v>693</v>
+      </c>
+      <c r="H163" t="s">
         <v>694</v>
-      </c>
-      <c r="H163" t="s">
-        <v>695</v>
       </c>
       <c r="J163" t="s">
         <v>31</v>
@@ -6944,13 +6935,13 @@
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="G164" t="s">
+        <v>619</v>
+      </c>
+      <c r="H164" t="s">
         <v>620</v>
-      </c>
-      <c r="H164" t="s">
-        <v>621</v>
       </c>
       <c r="J164" t="s">
         <v>31</v>
@@ -6958,13 +6949,13 @@
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="G165" t="s">
+        <v>637</v>
+      </c>
+      <c r="H165" t="s">
         <v>638</v>
-      </c>
-      <c r="H165" t="s">
-        <v>639</v>
       </c>
       <c r="J165" t="s">
         <v>31</v>
@@ -6972,13 +6963,13 @@
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="G166" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H166" t="s">
-        <v>1306</v>
+        <v>1303</v>
       </c>
       <c r="J166" t="s">
         <v>31</v>
@@ -6986,13 +6977,13 @@
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="G167" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H167" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="J167" t="s">
         <v>31</v>
@@ -7000,13 +6991,13 @@
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="G168" t="s">
+        <v>465</v>
+      </c>
+      <c r="H168" t="s">
         <v>466</v>
-      </c>
-      <c r="H168" t="s">
-        <v>467</v>
       </c>
       <c r="J168" t="s">
         <v>31</v>
@@ -7014,13 +7005,13 @@
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
-        <v>816</v>
+        <v>830</v>
       </c>
       <c r="G169" t="s">
-        <v>363</v>
+        <v>633</v>
       </c>
       <c r="H169" t="s">
-        <v>850</v>
+        <v>634</v>
       </c>
       <c r="J169" t="s">
         <v>31</v>
@@ -7028,13 +7019,13 @@
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
-        <v>832</v>
+        <v>1215</v>
       </c>
       <c r="G170" t="s">
-        <v>634</v>
+        <v>1251</v>
       </c>
       <c r="H170" t="s">
-        <v>635</v>
+        <v>1272</v>
       </c>
       <c r="J170" t="s">
         <v>31</v>
@@ -7042,13 +7033,13 @@
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
-        <v>1218</v>
+        <v>833</v>
       </c>
       <c r="G171" t="s">
-        <v>1254</v>
+        <v>631</v>
       </c>
       <c r="H171" t="s">
-        <v>1275</v>
+        <v>632</v>
       </c>
       <c r="J171" t="s">
         <v>31</v>
@@ -7056,13 +7047,13 @@
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
-        <v>835</v>
+        <v>789</v>
       </c>
       <c r="G172" t="s">
-        <v>632</v>
+        <v>691</v>
       </c>
       <c r="H172" t="s">
-        <v>633</v>
+        <v>692</v>
       </c>
       <c r="J172" t="s">
         <v>31</v>
@@ -7070,13 +7061,13 @@
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
-        <v>790</v>
+        <v>814</v>
       </c>
       <c r="G173" t="s">
-        <v>692</v>
+        <v>367</v>
       </c>
       <c r="H173" t="s">
-        <v>693</v>
+        <v>368</v>
       </c>
       <c r="J173" t="s">
         <v>31</v>
@@ -7084,13 +7075,13 @@
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
-        <v>815</v>
+        <v>803</v>
       </c>
       <c r="G174" t="s">
-        <v>368</v>
+        <v>353</v>
       </c>
       <c r="H174" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="J174" t="s">
         <v>31</v>
@@ -7098,13 +7089,13 @@
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
-        <v>804</v>
+        <v>1216</v>
       </c>
       <c r="G175" t="s">
-        <v>353</v>
+        <v>745</v>
       </c>
       <c r="H175" t="s">
-        <v>375</v>
+        <v>1273</v>
       </c>
       <c r="J175" t="s">
         <v>31</v>
@@ -7112,13 +7103,13 @@
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
-        <v>1219</v>
+        <v>815</v>
       </c>
       <c r="G176" t="s">
-        <v>746</v>
+        <v>371</v>
       </c>
       <c r="H176" t="s">
-        <v>1276</v>
+        <v>372</v>
       </c>
       <c r="J176" t="s">
         <v>31</v>
@@ -7126,13 +7117,13 @@
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
-        <v>817</v>
+        <v>838</v>
       </c>
       <c r="G177" t="s">
-        <v>372</v>
+        <v>619</v>
       </c>
       <c r="H177" t="s">
-        <v>373</v>
+        <v>1304</v>
       </c>
       <c r="J177" t="s">
         <v>31</v>
@@ -7140,13 +7131,13 @@
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="G178" t="s">
-        <v>620</v>
+        <v>29</v>
       </c>
       <c r="H178" t="s">
-        <v>1307</v>
+        <v>30</v>
       </c>
       <c r="J178" t="s">
         <v>31</v>
@@ -7154,13 +7145,13 @@
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
-        <v>838</v>
+        <v>1217</v>
       </c>
       <c r="G179" t="s">
-        <v>29</v>
+        <v>624</v>
       </c>
       <c r="H179" t="s">
-        <v>30</v>
+        <v>1274</v>
       </c>
       <c r="J179" t="s">
         <v>31</v>
@@ -7168,13 +7159,13 @@
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
-        <v>1220</v>
+        <v>804</v>
       </c>
       <c r="G180" t="s">
-        <v>625</v>
+        <v>353</v>
       </c>
       <c r="H180" t="s">
-        <v>1277</v>
+        <v>373</v>
       </c>
       <c r="J180" t="s">
         <v>31</v>
@@ -7182,13 +7173,13 @@
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="s">
-        <v>805</v>
+        <v>824</v>
       </c>
       <c r="G181" t="s">
-        <v>353</v>
+        <v>619</v>
       </c>
       <c r="H181" t="s">
-        <v>374</v>
+        <v>644</v>
       </c>
       <c r="J181" t="s">
         <v>31</v>
@@ -7196,13 +7187,13 @@
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
-        <v>826</v>
+        <v>844</v>
       </c>
       <c r="G182" t="s">
-        <v>620</v>
+        <v>757</v>
       </c>
       <c r="H182" t="s">
-        <v>645</v>
+        <v>1305</v>
       </c>
       <c r="J182" t="s">
         <v>31</v>
@@ -7210,13 +7201,13 @@
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="s">
-        <v>846</v>
+        <v>840</v>
       </c>
       <c r="G183" t="s">
-        <v>758</v>
+        <v>735</v>
       </c>
       <c r="H183" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="J183" t="s">
         <v>31</v>
@@ -7224,13 +7215,13 @@
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="G184" t="s">
-        <v>736</v>
+        <v>220</v>
       </c>
       <c r="H184" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="J184" t="s">
         <v>31</v>
@@ -7238,13 +7229,13 @@
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="s">
-        <v>845</v>
+        <v>791</v>
       </c>
       <c r="G185" t="s">
-        <v>220</v>
+        <v>695</v>
       </c>
       <c r="H185" t="s">
-        <v>1310</v>
+        <v>696</v>
       </c>
       <c r="J185" t="s">
         <v>31</v>
@@ -7252,13 +7243,13 @@
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
-        <v>792</v>
+        <v>1218</v>
       </c>
       <c r="G186" t="s">
-        <v>696</v>
+        <v>1252</v>
       </c>
       <c r="H186" t="s">
-        <v>697</v>
+        <v>1275</v>
       </c>
       <c r="J186" t="s">
         <v>31</v>
@@ -7266,13 +7257,13 @@
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A187" s="1" t="s">
-        <v>1221</v>
+        <v>763</v>
       </c>
       <c r="G187" t="s">
-        <v>1255</v>
+        <v>479</v>
       </c>
       <c r="H187" t="s">
-        <v>1278</v>
+        <v>482</v>
       </c>
       <c r="J187" t="s">
         <v>31</v>
@@ -7280,13 +7271,13 @@
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
-        <v>764</v>
+        <v>1219</v>
       </c>
       <c r="G188" t="s">
-        <v>480</v>
+        <v>1253</v>
       </c>
       <c r="H188" t="s">
-        <v>483</v>
+        <v>1308</v>
       </c>
       <c r="J188" t="s">
         <v>31</v>
@@ -7294,13 +7285,13 @@
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A189" s="1" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="G189" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="H189" t="s">
-        <v>1311</v>
+        <v>1276</v>
       </c>
       <c r="J189" t="s">
         <v>31</v>
@@ -7308,27 +7299,27 @@
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
-        <v>1223</v>
+        <v>1131</v>
       </c>
       <c r="G190" t="s">
-        <v>1257</v>
+        <v>534</v>
       </c>
       <c r="H190" t="s">
-        <v>1279</v>
+        <v>547</v>
       </c>
       <c r="J190" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A191" s="1" t="s">
-        <v>1134</v>
+        <v>1122</v>
       </c>
       <c r="G191" t="s">
-        <v>535</v>
+        <v>552</v>
       </c>
       <c r="H191" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="J191" t="s">
         <v>14</v>
@@ -7336,13 +7327,13 @@
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
-        <v>1125</v>
+        <v>1141</v>
       </c>
       <c r="G192" t="s">
-        <v>553</v>
+        <v>534</v>
       </c>
       <c r="H192" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="J192" t="s">
         <v>14</v>
@@ -7350,13 +7341,13 @@
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A193" s="1" t="s">
-        <v>1144</v>
+        <v>1159</v>
       </c>
       <c r="G193" t="s">
-        <v>535</v>
+        <v>184</v>
       </c>
       <c r="H193" t="s">
-        <v>560</v>
+        <v>185</v>
       </c>
       <c r="J193" t="s">
         <v>14</v>
@@ -7364,13 +7355,13 @@
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
-        <v>1162</v>
+        <v>1150</v>
       </c>
       <c r="G194" t="s">
-        <v>184</v>
+        <v>477</v>
       </c>
       <c r="H194" t="s">
-        <v>185</v>
+        <v>478</v>
       </c>
       <c r="J194" t="s">
         <v>14</v>
@@ -7378,13 +7369,13 @@
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A195" s="1" t="s">
-        <v>1153</v>
+        <v>1133</v>
       </c>
       <c r="G195" t="s">
-        <v>478</v>
+        <v>548</v>
       </c>
       <c r="H195" t="s">
-        <v>479</v>
+        <v>549</v>
       </c>
       <c r="J195" t="s">
         <v>14</v>
@@ -7392,13 +7383,13 @@
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
-        <v>1136</v>
+        <v>1171</v>
       </c>
       <c r="G196" t="s">
-        <v>549</v>
+        <v>27</v>
       </c>
       <c r="H196" t="s">
-        <v>550</v>
+        <v>28</v>
       </c>
       <c r="J196" t="s">
         <v>14</v>
@@ -7406,13 +7397,13 @@
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="s">
-        <v>1174</v>
+        <v>1184</v>
       </c>
       <c r="G197" t="s">
-        <v>27</v>
+        <v>221</v>
       </c>
       <c r="H197" t="s">
-        <v>28</v>
+        <v>222</v>
       </c>
       <c r="J197" t="s">
         <v>14</v>
@@ -7420,13 +7411,13 @@
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="s">
-        <v>1187</v>
+        <v>1146</v>
       </c>
       <c r="G198" t="s">
-        <v>221</v>
+        <v>534</v>
       </c>
       <c r="H198" t="s">
-        <v>222</v>
+        <v>565</v>
       </c>
       <c r="J198" t="s">
         <v>14</v>
@@ -7434,13 +7425,13 @@
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A199" s="1" t="s">
-        <v>1149</v>
+        <v>1181</v>
       </c>
       <c r="G199" t="s">
-        <v>535</v>
+        <v>471</v>
       </c>
       <c r="H199" t="s">
-        <v>566</v>
+        <v>472</v>
       </c>
       <c r="J199" t="s">
         <v>14</v>
@@ -7448,13 +7439,13 @@
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
-        <v>1184</v>
+        <v>1147</v>
       </c>
       <c r="G200" t="s">
-        <v>472</v>
+        <v>534</v>
       </c>
       <c r="H200" t="s">
-        <v>473</v>
+        <v>567</v>
       </c>
       <c r="J200" t="s">
         <v>14</v>
@@ -7462,13 +7453,13 @@
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A201" s="1" t="s">
-        <v>1150</v>
+        <v>1123</v>
       </c>
       <c r="G201" t="s">
-        <v>535</v>
+        <v>572</v>
       </c>
       <c r="H201" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="J201" t="s">
         <v>14</v>
@@ -7476,13 +7467,13 @@
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
-        <v>1126</v>
+        <v>1132</v>
       </c>
       <c r="G202" t="s">
-        <v>573</v>
+        <v>534</v>
       </c>
       <c r="H202" t="s">
-        <v>574</v>
+        <v>543</v>
       </c>
       <c r="J202" t="s">
         <v>14</v>
@@ -7490,13 +7481,13 @@
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A203" s="1" t="s">
-        <v>1135</v>
+        <v>1174</v>
       </c>
       <c r="G203" t="s">
-        <v>535</v>
+        <v>23</v>
       </c>
       <c r="H203" t="s">
-        <v>544</v>
+        <v>24</v>
       </c>
       <c r="J203" t="s">
         <v>14</v>
@@ -7504,13 +7495,13 @@
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
-        <v>1177</v>
+        <v>1182</v>
       </c>
       <c r="G204" t="s">
-        <v>23</v>
+        <v>331</v>
       </c>
       <c r="H204" t="s">
-        <v>24</v>
+        <v>332</v>
       </c>
       <c r="J204" t="s">
         <v>14</v>
@@ -7518,13 +7509,13 @@
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A205" s="1" t="s">
-        <v>1185</v>
+        <v>1172</v>
       </c>
       <c r="G205" t="s">
-        <v>331</v>
+        <v>475</v>
       </c>
       <c r="H205" t="s">
-        <v>332</v>
+        <v>476</v>
       </c>
       <c r="J205" t="s">
         <v>14</v>
@@ -7532,13 +7523,13 @@
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
-        <v>1175</v>
+        <v>1162</v>
       </c>
       <c r="G206" t="s">
-        <v>476</v>
+        <v>257</v>
       </c>
       <c r="H206" t="s">
-        <v>477</v>
+        <v>258</v>
       </c>
       <c r="J206" t="s">
         <v>14</v>
@@ -7546,13 +7537,13 @@
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A207" s="1" t="s">
-        <v>1165</v>
+        <v>1156</v>
       </c>
       <c r="G207" t="s">
-        <v>257</v>
+        <v>296</v>
       </c>
       <c r="H207" t="s">
-        <v>258</v>
+        <v>297</v>
       </c>
       <c r="J207" t="s">
         <v>14</v>
@@ -7560,13 +7551,13 @@
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="G208" t="s">
-        <v>296</v>
+        <v>150</v>
       </c>
       <c r="H208" t="s">
-        <v>297</v>
+        <v>151</v>
       </c>
       <c r="J208" t="s">
         <v>14</v>
@@ -7574,13 +7565,13 @@
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="s">
-        <v>1164</v>
+        <v>1129</v>
       </c>
       <c r="G209" t="s">
-        <v>150</v>
+        <v>536</v>
       </c>
       <c r="H209" t="s">
-        <v>151</v>
+        <v>537</v>
       </c>
       <c r="J209" t="s">
         <v>14</v>
@@ -7588,13 +7579,13 @@
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
-        <v>1132</v>
+        <v>1151</v>
       </c>
       <c r="G210" t="s">
-        <v>537</v>
+        <v>611</v>
       </c>
       <c r="H210" t="s">
-        <v>538</v>
+        <v>612</v>
       </c>
       <c r="J210" t="s">
         <v>14</v>
@@ -7602,13 +7593,13 @@
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A211" s="1" t="s">
-        <v>1154</v>
+        <v>1163</v>
       </c>
       <c r="G211" t="s">
-        <v>612</v>
+        <v>265</v>
       </c>
       <c r="H211" t="s">
-        <v>613</v>
+        <v>266</v>
       </c>
       <c r="J211" t="s">
         <v>14</v>
@@ -7616,13 +7607,13 @@
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="s">
-        <v>1166</v>
+        <v>1152</v>
       </c>
       <c r="G212" t="s">
-        <v>265</v>
+        <v>613</v>
       </c>
       <c r="H212" t="s">
-        <v>266</v>
+        <v>614</v>
       </c>
       <c r="J212" t="s">
         <v>14</v>
@@ -7630,13 +7621,13 @@
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A213" s="1" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
       <c r="G213" t="s">
-        <v>614</v>
+        <v>182</v>
       </c>
       <c r="H213" t="s">
-        <v>615</v>
+        <v>183</v>
       </c>
       <c r="J213" t="s">
         <v>14</v>
@@ -7644,13 +7635,13 @@
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
-        <v>1163</v>
+        <v>1186</v>
       </c>
       <c r="G214" t="s">
-        <v>182</v>
+        <v>330</v>
       </c>
       <c r="H214" t="s">
-        <v>183</v>
+        <v>276</v>
       </c>
       <c r="J214" t="s">
         <v>14</v>
@@ -7658,13 +7649,13 @@
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A215" s="1" t="s">
-        <v>1189</v>
+        <v>1155</v>
       </c>
       <c r="G215" t="s">
-        <v>330</v>
+        <v>608</v>
       </c>
       <c r="H215" t="s">
-        <v>276</v>
+        <v>609</v>
       </c>
       <c r="J215" t="s">
         <v>14</v>
@@ -7672,13 +7663,13 @@
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
-        <v>1158</v>
+        <v>1128</v>
       </c>
       <c r="G216" t="s">
-        <v>609</v>
+        <v>719</v>
       </c>
       <c r="H216" t="s">
-        <v>610</v>
+        <v>720</v>
       </c>
       <c r="J216" t="s">
         <v>14</v>
@@ -7686,13 +7677,13 @@
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A217" s="1" t="s">
-        <v>1131</v>
+        <v>1154</v>
       </c>
       <c r="G217" t="s">
-        <v>720</v>
+        <v>181</v>
       </c>
       <c r="H217" t="s">
-        <v>721</v>
+        <v>188</v>
       </c>
       <c r="J217" t="s">
         <v>14</v>
@@ -7700,13 +7691,13 @@
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
-        <v>1157</v>
+        <v>1137</v>
       </c>
       <c r="G218" t="s">
-        <v>181</v>
+        <v>534</v>
       </c>
       <c r="H218" t="s">
-        <v>188</v>
+        <v>558</v>
       </c>
       <c r="J218" t="s">
         <v>14</v>
@@ -7714,13 +7705,13 @@
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A219" s="1" t="s">
-        <v>1140</v>
+        <v>1136</v>
       </c>
       <c r="G219" t="s">
-        <v>535</v>
+        <v>556</v>
       </c>
       <c r="H219" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="J219" t="s">
         <v>14</v>
@@ -7728,13 +7719,13 @@
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
-        <v>1139</v>
+        <v>1149</v>
       </c>
       <c r="G220" t="s">
-        <v>557</v>
+        <v>467</v>
       </c>
       <c r="H220" t="s">
-        <v>558</v>
+        <v>470</v>
       </c>
       <c r="J220" t="s">
         <v>14</v>
@@ -7742,13 +7733,13 @@
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A221" s="1" t="s">
-        <v>1152</v>
+        <v>1135</v>
       </c>
       <c r="G221" t="s">
-        <v>468</v>
+        <v>534</v>
       </c>
       <c r="H221" t="s">
-        <v>471</v>
+        <v>579</v>
       </c>
       <c r="J221" t="s">
         <v>14</v>
@@ -7756,13 +7747,13 @@
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="s">
-        <v>1138</v>
+        <v>1157</v>
       </c>
       <c r="G222" t="s">
-        <v>535</v>
+        <v>149</v>
       </c>
       <c r="H222" t="s">
-        <v>580</v>
+        <v>152</v>
       </c>
       <c r="J222" t="s">
         <v>14</v>
@@ -7770,13 +7761,13 @@
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A223" s="1" t="s">
-        <v>1160</v>
+        <v>1134</v>
       </c>
       <c r="G223" t="s">
-        <v>149</v>
+        <v>534</v>
       </c>
       <c r="H223" t="s">
-        <v>152</v>
+        <v>554</v>
       </c>
       <c r="J223" t="s">
         <v>14</v>
@@ -7784,13 +7775,13 @@
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="s">
-        <v>1137</v>
+        <v>1200</v>
       </c>
       <c r="G224" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H224" t="s">
-        <v>555</v>
+        <v>1309</v>
       </c>
       <c r="J224" t="s">
         <v>14</v>
@@ -7798,13 +7789,13 @@
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A225" s="1" t="s">
+        <v>1189</v>
+      </c>
+      <c r="G225" t="s">
         <v>1203</v>
       </c>
-      <c r="G225" t="s">
-        <v>535</v>
-      </c>
       <c r="H225" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="J225" t="s">
         <v>14</v>
@@ -7812,13 +7803,13 @@
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
-        <v>1192</v>
+        <v>1153</v>
       </c>
       <c r="G226" t="s">
-        <v>1206</v>
+        <v>607</v>
       </c>
       <c r="H226" t="s">
-        <v>1313</v>
+        <v>610</v>
       </c>
       <c r="J226" t="s">
         <v>14</v>
@@ -7826,13 +7817,13 @@
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="s">
-        <v>1156</v>
+        <v>1173</v>
       </c>
       <c r="G227" t="s">
-        <v>608</v>
+        <v>12</v>
       </c>
       <c r="H227" t="s">
-        <v>611</v>
+        <v>13</v>
       </c>
       <c r="J227" t="s">
         <v>14</v>
@@ -7840,13 +7831,13 @@
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
-        <v>1176</v>
+        <v>1158</v>
       </c>
       <c r="G228" t="s">
-        <v>12</v>
+        <v>298</v>
       </c>
       <c r="H228" t="s">
-        <v>13</v>
+        <v>299</v>
       </c>
       <c r="J228" t="s">
         <v>14</v>
@@ -7854,13 +7845,13 @@
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A229" s="1" t="s">
-        <v>1161</v>
+        <v>1127</v>
       </c>
       <c r="G229" t="s">
-        <v>298</v>
+        <v>560</v>
       </c>
       <c r="H229" t="s">
-        <v>299</v>
+        <v>561</v>
       </c>
       <c r="J229" t="s">
         <v>14</v>
@@ -7868,13 +7859,13 @@
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="s">
-        <v>1130</v>
+        <v>1221</v>
       </c>
       <c r="G230" t="s">
-        <v>561</v>
+        <v>534</v>
       </c>
       <c r="H230" t="s">
-        <v>562</v>
+        <v>1277</v>
       </c>
       <c r="J230" t="s">
         <v>14</v>
@@ -7882,13 +7873,13 @@
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A231" s="1" t="s">
-        <v>1224</v>
+        <v>1167</v>
       </c>
       <c r="G231" t="s">
-        <v>535</v>
+        <v>300</v>
       </c>
       <c r="H231" t="s">
-        <v>1280</v>
+        <v>303</v>
       </c>
       <c r="J231" t="s">
         <v>14</v>
@@ -7896,13 +7887,13 @@
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="s">
-        <v>1170</v>
+        <v>1175</v>
       </c>
       <c r="G232" t="s">
-        <v>300</v>
+        <v>17</v>
       </c>
       <c r="H232" t="s">
-        <v>303</v>
+        <v>18</v>
       </c>
       <c r="J232" t="s">
         <v>14</v>
@@ -7910,13 +7901,13 @@
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A233" s="1" t="s">
-        <v>1178</v>
+        <v>1166</v>
       </c>
       <c r="G233" t="s">
-        <v>17</v>
+        <v>259</v>
       </c>
       <c r="H233" t="s">
-        <v>18</v>
+        <v>260</v>
       </c>
       <c r="J233" t="s">
         <v>14</v>
@@ -7924,13 +7915,13 @@
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="s">
-        <v>1169</v>
+        <v>1183</v>
       </c>
       <c r="G234" t="s">
-        <v>259</v>
+        <v>41</v>
       </c>
       <c r="H234" t="s">
-        <v>260</v>
+        <v>42</v>
       </c>
       <c r="J234" t="s">
         <v>14</v>
@@ -7938,13 +7929,13 @@
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A235" s="1" t="s">
-        <v>1186</v>
+        <v>1125</v>
       </c>
       <c r="G235" t="s">
-        <v>41</v>
+        <v>550</v>
       </c>
       <c r="H235" t="s">
-        <v>42</v>
+        <v>551</v>
       </c>
       <c r="J235" t="s">
         <v>14</v>
@@ -7952,13 +7943,13 @@
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="s">
-        <v>1128</v>
+        <v>1187</v>
       </c>
       <c r="G236" t="s">
-        <v>551</v>
+        <v>40</v>
       </c>
       <c r="H236" t="s">
-        <v>552</v>
+        <v>43</v>
       </c>
       <c r="J236" t="s">
         <v>14</v>
@@ -7966,13 +7957,13 @@
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A237" s="1" t="s">
-        <v>1190</v>
+        <v>1179</v>
       </c>
       <c r="G237" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="H237" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="J237" t="s">
         <v>14</v>
@@ -7980,13 +7971,13 @@
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="s">
-        <v>1182</v>
+        <v>1130</v>
       </c>
       <c r="G238" t="s">
-        <v>25</v>
+        <v>721</v>
       </c>
       <c r="H238" t="s">
-        <v>26</v>
+        <v>722</v>
       </c>
       <c r="J238" t="s">
         <v>14</v>
@@ -7994,13 +7985,13 @@
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A239" s="1" t="s">
-        <v>1133</v>
+        <v>1165</v>
       </c>
       <c r="G239" t="s">
-        <v>722</v>
+        <v>261</v>
       </c>
       <c r="H239" t="s">
-        <v>723</v>
+        <v>262</v>
       </c>
       <c r="J239" t="s">
         <v>14</v>
@@ -8008,13 +7999,13 @@
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A240" s="1" t="s">
-        <v>1168</v>
+        <v>1124</v>
       </c>
       <c r="G240" t="s">
-        <v>261</v>
+        <v>534</v>
       </c>
       <c r="H240" t="s">
-        <v>262</v>
+        <v>574</v>
       </c>
       <c r="J240" t="s">
         <v>14</v>
@@ -8022,13 +8013,13 @@
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A241" s="1" t="s">
-        <v>1127</v>
+        <v>1164</v>
       </c>
       <c r="G241" t="s">
-        <v>535</v>
+        <v>263</v>
       </c>
       <c r="H241" t="s">
-        <v>575</v>
+        <v>264</v>
       </c>
       <c r="J241" t="s">
         <v>14</v>
@@ -8036,13 +8027,13 @@
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="s">
-        <v>1167</v>
+        <v>1195</v>
       </c>
       <c r="G242" t="s">
-        <v>263</v>
+        <v>737</v>
       </c>
       <c r="H242" t="s">
-        <v>264</v>
+        <v>1311</v>
       </c>
       <c r="J242" t="s">
         <v>14</v>
@@ -8050,13 +8041,13 @@
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A243" s="1" t="s">
-        <v>1198</v>
+        <v>1178</v>
       </c>
       <c r="G243" t="s">
-        <v>738</v>
+        <v>19</v>
       </c>
       <c r="H243" t="s">
-        <v>1314</v>
+        <v>20</v>
       </c>
       <c r="J243" t="s">
         <v>14</v>
@@ -8064,13 +8055,13 @@
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="s">
-        <v>1181</v>
+        <v>1142</v>
       </c>
       <c r="G244" t="s">
-        <v>19</v>
+        <v>534</v>
       </c>
       <c r="H244" t="s">
-        <v>20</v>
+        <v>576</v>
       </c>
       <c r="J244" t="s">
         <v>14</v>
@@ -8078,13 +8069,13 @@
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A245" s="1" t="s">
-        <v>1145</v>
+        <v>1177</v>
       </c>
       <c r="G245" t="s">
-        <v>535</v>
+        <v>15</v>
       </c>
       <c r="H245" t="s">
-        <v>577</v>
+        <v>16</v>
       </c>
       <c r="J245" t="s">
         <v>14</v>
@@ -8092,13 +8083,13 @@
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="s">
-        <v>1180</v>
+        <v>1222</v>
       </c>
       <c r="G246" t="s">
-        <v>15</v>
+        <v>737</v>
       </c>
       <c r="H246" t="s">
-        <v>16</v>
+        <v>1278</v>
       </c>
       <c r="J246" t="s">
         <v>14</v>
@@ -8106,13 +8097,13 @@
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A247" s="1" t="s">
-        <v>1225</v>
+        <v>1138</v>
       </c>
       <c r="G247" t="s">
-        <v>738</v>
+        <v>534</v>
       </c>
       <c r="H247" t="s">
-        <v>1281</v>
+        <v>564</v>
       </c>
       <c r="J247" t="s">
         <v>14</v>
@@ -8120,13 +8111,13 @@
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
-        <v>1141</v>
+        <v>1148</v>
       </c>
       <c r="G248" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H248" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="J248" t="s">
         <v>14</v>
@@ -8134,13 +8125,13 @@
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="s">
-        <v>1151</v>
+        <v>1176</v>
       </c>
       <c r="G249" t="s">
-        <v>535</v>
+        <v>473</v>
       </c>
       <c r="H249" t="s">
-        <v>569</v>
+        <v>474</v>
       </c>
       <c r="J249" t="s">
         <v>14</v>
@@ -8148,13 +8139,13 @@
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
-        <v>1179</v>
+        <v>1185</v>
       </c>
       <c r="G250" t="s">
-        <v>474</v>
+        <v>221</v>
       </c>
       <c r="H250" t="s">
-        <v>475</v>
+        <v>223</v>
       </c>
       <c r="J250" t="s">
         <v>14</v>
@@ -8162,13 +8153,13 @@
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A251" s="1" t="s">
-        <v>1188</v>
+        <v>1168</v>
       </c>
       <c r="G251" t="s">
-        <v>221</v>
+        <v>617</v>
       </c>
       <c r="H251" t="s">
-        <v>223</v>
+        <v>618</v>
       </c>
       <c r="J251" t="s">
         <v>14</v>
@@ -8176,13 +8167,13 @@
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
-        <v>1171</v>
+        <v>1191</v>
       </c>
       <c r="G252" t="s">
-        <v>618</v>
+        <v>534</v>
       </c>
       <c r="H252" t="s">
-        <v>619</v>
+        <v>1312</v>
       </c>
       <c r="J252" t="s">
         <v>14</v>
@@ -8190,13 +8181,13 @@
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A253" s="1" t="s">
-        <v>1194</v>
+        <v>1140</v>
       </c>
       <c r="G253" t="s">
-        <v>535</v>
+        <v>569</v>
       </c>
       <c r="H253" t="s">
-        <v>1315</v>
+        <v>570</v>
       </c>
       <c r="J253" t="s">
         <v>14</v>
@@ -8204,13 +8195,13 @@
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
-        <v>1143</v>
+        <v>1139</v>
       </c>
       <c r="G254" t="s">
-        <v>570</v>
+        <v>534</v>
       </c>
       <c r="H254" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="J254" t="s">
         <v>14</v>
@@ -8218,13 +8209,13 @@
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A255" s="1" t="s">
-        <v>1142</v>
+        <v>1198</v>
       </c>
       <c r="G255" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H255" t="s">
-        <v>567</v>
+        <v>1313</v>
       </c>
       <c r="J255" t="s">
         <v>14</v>
@@ -8232,13 +8223,13 @@
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
-        <v>1201</v>
+        <v>1169</v>
       </c>
       <c r="G256" t="s">
-        <v>535</v>
+        <v>468</v>
       </c>
       <c r="H256" t="s">
-        <v>1316</v>
+        <v>469</v>
       </c>
       <c r="J256" t="s">
         <v>14</v>
@@ -8246,13 +8237,13 @@
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A257" s="1" t="s">
-        <v>1172</v>
+        <v>1180</v>
       </c>
       <c r="G257" t="s">
-        <v>469</v>
+        <v>21</v>
       </c>
       <c r="H257" t="s">
-        <v>470</v>
+        <v>22</v>
       </c>
       <c r="J257" t="s">
         <v>14</v>
@@ -8260,13 +8251,13 @@
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="s">
-        <v>1183</v>
+        <v>1144</v>
       </c>
       <c r="G258" t="s">
-        <v>21</v>
+        <v>534</v>
       </c>
       <c r="H258" t="s">
-        <v>22</v>
+        <v>555</v>
       </c>
       <c r="J258" t="s">
         <v>14</v>
@@ -8274,13 +8265,13 @@
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A259" s="1" t="s">
-        <v>1147</v>
+        <v>851</v>
       </c>
       <c r="G259" t="s">
-        <v>535</v>
+        <v>248</v>
       </c>
       <c r="H259" t="s">
-        <v>556</v>
+        <v>249</v>
       </c>
       <c r="J259" t="s">
         <v>14</v>
@@ -8288,13 +8279,13 @@
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="s">
-        <v>854</v>
+        <v>1193</v>
       </c>
       <c r="G260" t="s">
-        <v>248</v>
+        <v>330</v>
       </c>
       <c r="H260" t="s">
-        <v>249</v>
+        <v>1314</v>
       </c>
       <c r="J260" t="s">
         <v>14</v>
@@ -8302,13 +8293,13 @@
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A261" s="1" t="s">
-        <v>1196</v>
+        <v>1145</v>
       </c>
       <c r="G261" t="s">
-        <v>330</v>
+        <v>615</v>
       </c>
       <c r="H261" t="s">
-        <v>1317</v>
+        <v>616</v>
       </c>
       <c r="J261" t="s">
         <v>14</v>
@@ -8316,13 +8307,13 @@
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="G262" t="s">
-        <v>616</v>
+        <v>186</v>
       </c>
       <c r="H262" t="s">
-        <v>617</v>
+        <v>187</v>
       </c>
       <c r="J262" t="s">
         <v>14</v>
@@ -8330,13 +8321,13 @@
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A263" s="1" t="s">
-        <v>1173</v>
+        <v>1196</v>
       </c>
       <c r="G263" t="s">
-        <v>186</v>
+        <v>741</v>
       </c>
       <c r="H263" t="s">
-        <v>187</v>
+        <v>1315</v>
       </c>
       <c r="J263" t="s">
         <v>14</v>
@@ -8344,13 +8335,13 @@
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A264" s="1" t="s">
-        <v>1199</v>
+        <v>1202</v>
       </c>
       <c r="G264" t="s">
-        <v>742</v>
+        <v>1205</v>
       </c>
       <c r="H264" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="J264" t="s">
         <v>14</v>
@@ -8358,13 +8349,13 @@
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A265" s="1" t="s">
-        <v>1205</v>
+        <v>1197</v>
       </c>
       <c r="G265" t="s">
-        <v>1208</v>
+        <v>1255</v>
       </c>
       <c r="H265" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="J265" t="s">
         <v>14</v>
@@ -8372,13 +8363,13 @@
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A266" s="1" t="s">
-        <v>1200</v>
+        <v>1126</v>
       </c>
       <c r="G266" t="s">
-        <v>1258</v>
+        <v>534</v>
       </c>
       <c r="H266" t="s">
-        <v>1320</v>
+        <v>542</v>
       </c>
       <c r="J266" t="s">
         <v>14</v>
@@ -8386,13 +8377,13 @@
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A267" s="1" t="s">
-        <v>1129</v>
+        <v>1201</v>
       </c>
       <c r="G267" t="s">
-        <v>535</v>
+        <v>1204</v>
       </c>
       <c r="H267" t="s">
-        <v>543</v>
+        <v>1318</v>
       </c>
       <c r="J267" t="s">
         <v>14</v>
@@ -8400,13 +8391,13 @@
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A268" s="1" t="s">
-        <v>1204</v>
+        <v>1188</v>
       </c>
       <c r="G268" t="s">
-        <v>1207</v>
+        <v>1256</v>
       </c>
       <c r="H268" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="J268" t="s">
         <v>14</v>
@@ -8414,13 +8405,13 @@
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A269" s="1" t="s">
-        <v>1191</v>
+        <v>1223</v>
       </c>
       <c r="G269" t="s">
-        <v>1259</v>
+        <v>562</v>
       </c>
       <c r="H269" t="s">
-        <v>1322</v>
+        <v>1279</v>
       </c>
       <c r="J269" t="s">
         <v>14</v>
@@ -8428,13 +8419,13 @@
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A270" s="1" t="s">
-        <v>1226</v>
+        <v>1199</v>
       </c>
       <c r="G270" t="s">
-        <v>563</v>
+        <v>534</v>
       </c>
       <c r="H270" t="s">
-        <v>1282</v>
+        <v>1320</v>
       </c>
       <c r="J270" t="s">
         <v>14</v>
@@ -8442,13 +8433,13 @@
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A271" s="1" t="s">
-        <v>1202</v>
+        <v>1224</v>
       </c>
       <c r="G271" t="s">
-        <v>535</v>
+        <v>1206</v>
       </c>
       <c r="H271" t="s">
-        <v>1323</v>
+        <v>1280</v>
       </c>
       <c r="J271" t="s">
         <v>14</v>
@@ -8456,13 +8447,13 @@
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A272" s="1" t="s">
-        <v>1227</v>
+        <v>1190</v>
       </c>
       <c r="G272" t="s">
-        <v>1209</v>
+        <v>534</v>
       </c>
       <c r="H272" t="s">
-        <v>1283</v>
+        <v>1321</v>
       </c>
       <c r="J272" t="s">
         <v>14</v>
@@ -8470,13 +8461,13 @@
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A273" s="1" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="G273" t="s">
-        <v>535</v>
+        <v>736</v>
       </c>
       <c r="H273" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="J273" t="s">
         <v>14</v>
@@ -8484,13 +8475,13 @@
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A274" s="1" t="s">
-        <v>1197</v>
+        <v>1192</v>
       </c>
       <c r="G274" t="s">
-        <v>737</v>
+        <v>471</v>
       </c>
       <c r="H274" t="s">
-        <v>1325</v>
+        <v>1317</v>
       </c>
       <c r="J274" t="s">
         <v>14</v>
@@ -8498,13 +8489,13 @@
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A275" s="1" t="s">
-        <v>1195</v>
+        <v>1143</v>
       </c>
       <c r="G275" t="s">
-        <v>472</v>
+        <v>534</v>
       </c>
       <c r="H275" t="s">
-        <v>1320</v>
+        <v>535</v>
       </c>
       <c r="J275" t="s">
         <v>14</v>
@@ -8512,27 +8503,27 @@
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A276" s="1" t="s">
-        <v>1146</v>
+        <v>1075</v>
       </c>
       <c r="G276" t="s">
-        <v>535</v>
+        <v>122</v>
       </c>
       <c r="H276" t="s">
-        <v>536</v>
+        <v>144</v>
       </c>
       <c r="J276" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A277" s="1" t="s">
-        <v>1078</v>
+        <v>1083</v>
       </c>
       <c r="G277" t="s">
         <v>122</v>
       </c>
       <c r="H277" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="J277" t="s">
         <v>3</v>
@@ -8540,13 +8531,13 @@
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A278" s="1" t="s">
-        <v>1086</v>
+        <v>1070</v>
       </c>
       <c r="G278" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="H278" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="J278" t="s">
         <v>3</v>
@@ -8554,13 +8545,13 @@
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A279" s="1" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
       <c r="G279" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="H279" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="J279" t="s">
         <v>3</v>
@@ -8568,13 +8559,13 @@
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A280" s="1" t="s">
-        <v>1072</v>
+        <v>1108</v>
       </c>
       <c r="G280" t="s">
-        <v>142</v>
+        <v>0</v>
       </c>
       <c r="H280" t="s">
-        <v>143</v>
+        <v>4</v>
       </c>
       <c r="J280" t="s">
         <v>3</v>
@@ -8582,13 +8573,13 @@
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A281" s="1" t="s">
-        <v>1111</v>
+        <v>1090</v>
       </c>
       <c r="G281" t="s">
-        <v>0</v>
+        <v>269</v>
       </c>
       <c r="H281" t="s">
-        <v>4</v>
+        <v>271</v>
       </c>
       <c r="J281" t="s">
         <v>3</v>
@@ -8596,13 +8587,13 @@
     </row>
     <row r="282" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A282" s="1" t="s">
-        <v>1093</v>
+        <v>1076</v>
       </c>
       <c r="G282" t="s">
-        <v>269</v>
+        <v>70</v>
       </c>
       <c r="H282" t="s">
-        <v>271</v>
+        <v>71</v>
       </c>
       <c r="J282" t="s">
         <v>3</v>
@@ -8610,13 +8601,13 @@
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A283" s="1" t="s">
-        <v>1079</v>
+        <v>1057</v>
       </c>
       <c r="G283" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="H283" t="s">
-        <v>71</v>
+        <v>1119</v>
       </c>
       <c r="J283" t="s">
         <v>3</v>
@@ -8624,13 +8615,13 @@
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A284" s="1" t="s">
-        <v>1060</v>
+        <v>1105</v>
       </c>
       <c r="G284" t="s">
-        <v>122</v>
+        <v>216</v>
       </c>
       <c r="H284" t="s">
-        <v>1122</v>
+        <v>217</v>
       </c>
       <c r="J284" t="s">
         <v>3</v>
@@ -8638,27 +8629,27 @@
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A285" s="1" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="G285" t="s">
-        <v>216</v>
+        <v>44</v>
       </c>
       <c r="H285" t="s">
-        <v>217</v>
+        <v>48</v>
       </c>
       <c r="J285" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="s">
-        <v>1112</v>
+        <v>1104</v>
       </c>
       <c r="G286" t="s">
-        <v>44</v>
+        <v>212</v>
       </c>
       <c r="H286" t="s">
-        <v>48</v>
+        <v>213</v>
       </c>
       <c r="J286" t="s">
         <v>31</v>
@@ -8666,27 +8657,27 @@
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A287" s="1" t="s">
-        <v>1107</v>
+        <v>1080</v>
       </c>
       <c r="G287" t="s">
-        <v>212</v>
+        <v>132</v>
       </c>
       <c r="H287" t="s">
-        <v>213</v>
+        <v>133</v>
       </c>
       <c r="J287" t="s">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A288" s="1" t="s">
-        <v>1083</v>
+        <v>1058</v>
       </c>
       <c r="G288" t="s">
-        <v>132</v>
+        <v>87</v>
       </c>
       <c r="H288" t="s">
-        <v>133</v>
+        <v>88</v>
       </c>
       <c r="J288" t="s">
         <v>3</v>
@@ -8694,13 +8685,13 @@
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A289" s="1" t="s">
-        <v>1061</v>
+        <v>1079</v>
       </c>
       <c r="G289" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="H289" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J289" t="s">
         <v>3</v>
@@ -8708,13 +8699,13 @@
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="s">
-        <v>1082</v>
+        <v>1056</v>
       </c>
       <c r="G290" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H290" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="J290" t="s">
         <v>3</v>
@@ -8722,13 +8713,13 @@
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A291" s="1" t="s">
-        <v>1059</v>
+        <v>1086</v>
       </c>
       <c r="G291" t="s">
-        <v>85</v>
+        <v>590</v>
       </c>
       <c r="H291" t="s">
-        <v>86</v>
+        <v>593</v>
       </c>
       <c r="J291" t="s">
         <v>3</v>
@@ -8736,41 +8727,41 @@
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A292" s="1" t="s">
-        <v>1089</v>
+        <v>809</v>
       </c>
       <c r="G292" t="s">
-        <v>591</v>
+        <v>306</v>
       </c>
       <c r="H292" t="s">
-        <v>594</v>
+        <v>307</v>
       </c>
       <c r="J292" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A293" s="1" t="s">
-        <v>810</v>
+        <v>1091</v>
       </c>
       <c r="G293" t="s">
-        <v>306</v>
+        <v>269</v>
       </c>
       <c r="H293" t="s">
-        <v>307</v>
+        <v>272</v>
       </c>
       <c r="J293" t="s">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="s">
-        <v>1094</v>
+        <v>1061</v>
       </c>
       <c r="G294" t="s">
-        <v>269</v>
+        <v>202</v>
       </c>
       <c r="H294" t="s">
-        <v>272</v>
+        <v>205</v>
       </c>
       <c r="J294" t="s">
         <v>3</v>
@@ -8778,13 +8769,13 @@
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A295" s="1" t="s">
-        <v>1064</v>
+        <v>1059</v>
       </c>
       <c r="G295" t="s">
-        <v>202</v>
+        <v>74</v>
       </c>
       <c r="H295" t="s">
-        <v>205</v>
+        <v>75</v>
       </c>
       <c r="J295" t="s">
         <v>3</v>
@@ -8792,13 +8783,13 @@
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="s">
-        <v>1062</v>
+        <v>1092</v>
       </c>
       <c r="G296" t="s">
-        <v>74</v>
+        <v>269</v>
       </c>
       <c r="H296" t="s">
-        <v>75</v>
+        <v>270</v>
       </c>
       <c r="J296" t="s">
         <v>3</v>
@@ -8806,13 +8797,13 @@
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A297" s="1" t="s">
-        <v>1095</v>
+        <v>1077</v>
       </c>
       <c r="G297" t="s">
-        <v>269</v>
+        <v>203</v>
       </c>
       <c r="H297" t="s">
-        <v>270</v>
+        <v>204</v>
       </c>
       <c r="J297" t="s">
         <v>3</v>
@@ -8820,13 +8811,13 @@
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A298" s="1" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="G298" t="s">
-        <v>203</v>
+        <v>89</v>
       </c>
       <c r="H298" t="s">
-        <v>204</v>
+        <v>90</v>
       </c>
       <c r="J298" t="s">
         <v>3</v>
@@ -8834,13 +8825,13 @@
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A299" s="1" t="s">
-        <v>1081</v>
+        <v>1063</v>
       </c>
       <c r="G299" t="s">
-        <v>89</v>
+        <v>202</v>
       </c>
       <c r="H299" t="s">
-        <v>90</v>
+        <v>211</v>
       </c>
       <c r="J299" t="s">
         <v>3</v>
@@ -8848,13 +8839,13 @@
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="s">
-        <v>1066</v>
+        <v>1071</v>
       </c>
       <c r="G300" t="s">
-        <v>202</v>
+        <v>91</v>
       </c>
       <c r="H300" t="s">
-        <v>211</v>
+        <v>92</v>
       </c>
       <c r="J300" t="s">
         <v>3</v>
@@ -8862,13 +8853,13 @@
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A301" s="1" t="s">
-        <v>1074</v>
+        <v>1097</v>
       </c>
       <c r="G301" t="s">
-        <v>91</v>
+        <v>269</v>
       </c>
       <c r="H301" t="s">
-        <v>92</v>
+        <v>273</v>
       </c>
       <c r="J301" t="s">
         <v>3</v>
@@ -8876,13 +8867,13 @@
     </row>
     <row r="302" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A302" s="1" t="s">
-        <v>1100</v>
+        <v>1062</v>
       </c>
       <c r="G302" t="s">
-        <v>269</v>
+        <v>130</v>
       </c>
       <c r="H302" t="s">
-        <v>273</v>
+        <v>131</v>
       </c>
       <c r="J302" t="s">
         <v>3</v>
@@ -8890,13 +8881,13 @@
     </row>
     <row r="303" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A303" s="1" t="s">
-        <v>1065</v>
+        <v>1225</v>
       </c>
       <c r="G303" t="s">
-        <v>130</v>
+        <v>760</v>
       </c>
       <c r="H303" t="s">
-        <v>131</v>
+        <v>1281</v>
       </c>
       <c r="J303" t="s">
         <v>3</v>
@@ -8904,13 +8895,13 @@
     </row>
     <row r="304" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A304" s="1" t="s">
-        <v>1228</v>
+        <v>1094</v>
       </c>
       <c r="G304" t="s">
-        <v>761</v>
+        <v>269</v>
       </c>
       <c r="H304" t="s">
-        <v>1284</v>
+        <v>274</v>
       </c>
       <c r="J304" t="s">
         <v>3</v>
@@ -8918,41 +8909,41 @@
     </row>
     <row r="305" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A305" s="1" t="s">
-        <v>1097</v>
+        <v>1106</v>
       </c>
       <c r="G305" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
       <c r="H305" t="s">
-        <v>274</v>
+        <v>215</v>
       </c>
       <c r="J305" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="306" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A306" s="1" t="s">
-        <v>1109</v>
+        <v>1226</v>
       </c>
       <c r="G306" t="s">
-        <v>214</v>
+        <v>761</v>
       </c>
       <c r="H306" t="s">
-        <v>215</v>
+        <v>762</v>
       </c>
       <c r="J306" t="s">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="307" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A307" s="1" t="s">
-        <v>1229</v>
+        <v>1093</v>
       </c>
       <c r="G307" t="s">
-        <v>762</v>
+        <v>595</v>
       </c>
       <c r="H307" t="s">
-        <v>763</v>
+        <v>596</v>
       </c>
       <c r="J307" t="s">
         <v>3</v>
@@ -8960,13 +8951,13 @@
     </row>
     <row r="308" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A308" s="1" t="s">
-        <v>1096</v>
+        <v>1111</v>
       </c>
       <c r="G308" t="s">
-        <v>596</v>
+        <v>8</v>
       </c>
       <c r="H308" t="s">
-        <v>597</v>
+        <v>9</v>
       </c>
       <c r="J308" t="s">
         <v>3</v>
@@ -8974,13 +8965,13 @@
     </row>
     <row r="309" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A309" s="1" t="s">
-        <v>1114</v>
+        <v>1085</v>
       </c>
       <c r="G309" t="s">
-        <v>8</v>
+        <v>590</v>
       </c>
       <c r="H309" t="s">
-        <v>9</v>
+        <v>594</v>
       </c>
       <c r="J309" t="s">
         <v>3</v>
@@ -8988,13 +8979,13 @@
     </row>
     <row r="310" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A310" s="1" t="s">
-        <v>1088</v>
+        <v>1081</v>
       </c>
       <c r="G310" t="s">
-        <v>591</v>
+        <v>80</v>
       </c>
       <c r="H310" t="s">
-        <v>595</v>
+        <v>81</v>
       </c>
       <c r="J310" t="s">
         <v>3</v>
@@ -9002,83 +8993,83 @@
     </row>
     <row r="311" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A311" s="1" t="s">
-        <v>1084</v>
+        <v>1112</v>
       </c>
       <c r="G311" t="s">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="H311" t="s">
-        <v>81</v>
+        <v>6</v>
       </c>
       <c r="J311" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="312" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A312" s="1" t="s">
-        <v>1115</v>
+        <v>1065</v>
       </c>
       <c r="G312" t="s">
-        <v>5</v>
+        <v>333</v>
       </c>
       <c r="H312" t="s">
-        <v>6</v>
+        <v>336</v>
       </c>
       <c r="J312" t="s">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="313" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A313" s="1" t="s">
-        <v>1068</v>
+        <v>1110</v>
       </c>
       <c r="G313" t="s">
-        <v>333</v>
+        <v>5</v>
       </c>
       <c r="H313" t="s">
-        <v>336</v>
+        <v>7</v>
       </c>
       <c r="J313" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="314" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A314" s="1" t="s">
-        <v>1113</v>
+      <c r="A314">
+        <v>1480</v>
       </c>
       <c r="G314" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="H314" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="J314" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="315" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A315">
-        <v>1480</v>
+      <c r="A315" s="1" t="s">
+        <v>1064</v>
       </c>
       <c r="G315" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="H315" t="s">
-        <v>45</v>
+        <v>206</v>
       </c>
       <c r="J315" t="s">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="316" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A316" s="1" t="s">
-        <v>1067</v>
+        <v>1088</v>
       </c>
       <c r="G316" t="s">
-        <v>202</v>
+        <v>287</v>
       </c>
       <c r="H316" t="s">
-        <v>206</v>
+        <v>288</v>
       </c>
       <c r="J316" t="s">
         <v>3</v>
@@ -9086,13 +9077,13 @@
     </row>
     <row r="317" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A317" s="1" t="s">
-        <v>1091</v>
+        <v>1072</v>
       </c>
       <c r="G317" t="s">
-        <v>287</v>
+        <v>84</v>
       </c>
       <c r="H317" t="s">
-        <v>288</v>
+        <v>1120</v>
       </c>
       <c r="J317" t="s">
         <v>3</v>
@@ -9100,13 +9091,13 @@
     </row>
     <row r="318" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A318" s="1" t="s">
-        <v>1075</v>
+        <v>1102</v>
       </c>
       <c r="G318" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="H318" t="s">
-        <v>1123</v>
+        <v>11</v>
       </c>
       <c r="J318" t="s">
         <v>3</v>
@@ -9114,13 +9105,13 @@
     </row>
     <row r="319" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A319" s="1" t="s">
-        <v>1105</v>
+        <v>1084</v>
       </c>
       <c r="G319" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="H319" t="s">
-        <v>11</v>
+        <v>148</v>
       </c>
       <c r="J319" t="s">
         <v>3</v>
@@ -9128,13 +9119,13 @@
     </row>
     <row r="320" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A320" s="1" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="G320" t="s">
-        <v>122</v>
+        <v>591</v>
       </c>
       <c r="H320" t="s">
-        <v>148</v>
+        <v>592</v>
       </c>
       <c r="J320" t="s">
         <v>3</v>
@@ -9142,13 +9133,13 @@
     </row>
     <row r="321" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A321" s="1" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
       <c r="G321" t="s">
-        <v>592</v>
+        <v>269</v>
       </c>
       <c r="H321" t="s">
-        <v>593</v>
+        <v>277</v>
       </c>
       <c r="J321" t="s">
         <v>3</v>
@@ -9156,13 +9147,13 @@
     </row>
     <row r="322" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A322" s="1" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="G322" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="H322" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="J322" t="s">
         <v>3</v>
@@ -9170,13 +9161,13 @@
     </row>
     <row r="323" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A323" s="1" t="s">
-        <v>1099</v>
+        <v>1087</v>
       </c>
       <c r="G323" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="H323" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="J323" t="s">
         <v>3</v>
@@ -9184,41 +9175,41 @@
     </row>
     <row r="324" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A324" s="1" t="s">
-        <v>1090</v>
+        <v>1227</v>
       </c>
       <c r="G324" t="s">
-        <v>286</v>
+        <v>1121</v>
       </c>
       <c r="H324" t="s">
-        <v>289</v>
+        <v>1282</v>
       </c>
       <c r="J324" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="325" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A325" s="1" t="s">
-        <v>1230</v>
+        <v>1066</v>
       </c>
       <c r="G325" t="s">
-        <v>1124</v>
+        <v>334</v>
       </c>
       <c r="H325" t="s">
-        <v>1285</v>
+        <v>335</v>
       </c>
       <c r="J325" t="s">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="326" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A326" s="1" t="s">
-        <v>1069</v>
+        <v>1074</v>
       </c>
       <c r="G326" t="s">
-        <v>334</v>
+        <v>78</v>
       </c>
       <c r="H326" t="s">
-        <v>335</v>
+        <v>79</v>
       </c>
       <c r="J326" t="s">
         <v>3</v>
@@ -9226,13 +9217,13 @@
     </row>
     <row r="327" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A327" s="1" t="s">
-        <v>1077</v>
+        <v>1101</v>
       </c>
       <c r="G327" t="s">
-        <v>78</v>
+        <v>292</v>
       </c>
       <c r="H327" t="s">
-        <v>79</v>
+        <v>293</v>
       </c>
       <c r="J327" t="s">
         <v>3</v>
@@ -9240,13 +9231,13 @@
     </row>
     <row r="328" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A328" s="1" t="s">
-        <v>1104</v>
+        <v>1118</v>
       </c>
       <c r="G328" t="s">
-        <v>292</v>
+        <v>754</v>
       </c>
       <c r="H328" t="s">
-        <v>293</v>
+        <v>1323</v>
       </c>
       <c r="J328" t="s">
         <v>3</v>
@@ -9254,13 +9245,13 @@
     </row>
     <row r="329" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A329" s="1" t="s">
-        <v>1121</v>
+        <v>1068</v>
       </c>
       <c r="G329" t="s">
-        <v>755</v>
+        <v>136</v>
       </c>
       <c r="H329" t="s">
-        <v>1326</v>
+        <v>137</v>
       </c>
       <c r="J329" t="s">
         <v>3</v>
@@ -9268,13 +9259,13 @@
     </row>
     <row r="330" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A330" s="1" t="s">
-        <v>1071</v>
+        <v>1099</v>
       </c>
       <c r="G330" t="s">
-        <v>136</v>
+        <v>275</v>
       </c>
       <c r="H330" t="s">
-        <v>137</v>
+        <v>276</v>
       </c>
       <c r="J330" t="s">
         <v>3</v>
@@ -9282,13 +9273,13 @@
     </row>
     <row r="331" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A331" s="1" t="s">
-        <v>1102</v>
+        <v>952</v>
       </c>
       <c r="G331" t="s">
-        <v>275</v>
+        <v>759</v>
       </c>
       <c r="H331" t="s">
-        <v>276</v>
+        <v>1324</v>
       </c>
       <c r="J331" t="s">
         <v>3</v>
@@ -9296,13 +9287,13 @@
     </row>
     <row r="332" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A332" s="1" t="s">
-        <v>955</v>
+        <v>1114</v>
       </c>
       <c r="G332" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="H332" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="J332" t="s">
         <v>3</v>
@@ -9310,41 +9301,41 @@
     </row>
     <row r="333" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A333" s="1" t="s">
-        <v>1117</v>
+        <v>1113</v>
       </c>
       <c r="G333" t="s">
-        <v>728</v>
+        <v>46</v>
       </c>
       <c r="H333" t="s">
-        <v>1328</v>
+        <v>47</v>
       </c>
       <c r="J333" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="334" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A334" s="1" t="s">
-        <v>1116</v>
+        <v>1067</v>
       </c>
       <c r="G334" t="s">
-        <v>46</v>
+        <v>209</v>
       </c>
       <c r="H334" t="s">
-        <v>47</v>
+        <v>210</v>
       </c>
       <c r="J334" t="s">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="335" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A335" s="1" t="s">
-        <v>1070</v>
+        <v>1082</v>
       </c>
       <c r="G335" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H335" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J335" t="s">
         <v>3</v>
@@ -9352,13 +9343,13 @@
     </row>
     <row r="336" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A336" s="1" t="s">
-        <v>1085</v>
+        <v>1100</v>
       </c>
       <c r="G336" t="s">
-        <v>207</v>
+        <v>290</v>
       </c>
       <c r="H336" t="s">
-        <v>208</v>
+        <v>291</v>
       </c>
       <c r="J336" t="s">
         <v>3</v>
@@ -9366,13 +9357,13 @@
     </row>
     <row r="337" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A337" s="1" t="s">
-        <v>1103</v>
+        <v>1115</v>
       </c>
       <c r="G337" t="s">
-        <v>290</v>
+        <v>1257</v>
       </c>
       <c r="H337" t="s">
-        <v>291</v>
+        <v>1326</v>
       </c>
       <c r="J337" t="s">
         <v>3</v>
@@ -9380,13 +9371,13 @@
     </row>
     <row r="338" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A338" s="1" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="G338" t="s">
-        <v>1260</v>
+        <v>269</v>
       </c>
       <c r="H338" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="J338" t="s">
         <v>3</v>
@@ -9394,41 +9385,41 @@
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A339" s="1" t="s">
-        <v>1119</v>
+        <v>1107</v>
       </c>
       <c r="G339" t="s">
-        <v>269</v>
+        <v>218</v>
       </c>
       <c r="H339" t="s">
-        <v>1330</v>
+        <v>219</v>
       </c>
       <c r="J339" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A340" s="1" t="s">
-        <v>1110</v>
+        <v>1103</v>
       </c>
       <c r="G340" t="s">
-        <v>218</v>
+        <v>294</v>
       </c>
       <c r="H340" t="s">
-        <v>219</v>
+        <v>295</v>
       </c>
       <c r="J340" t="s">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A341" s="1" t="s">
-        <v>1106</v>
+        <v>1073</v>
       </c>
       <c r="G341" t="s">
-        <v>294</v>
+        <v>82</v>
       </c>
       <c r="H341" t="s">
-        <v>295</v>
+        <v>83</v>
       </c>
       <c r="J341" t="s">
         <v>3</v>
@@ -9436,13 +9427,13 @@
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A342" s="1" t="s">
-        <v>1076</v>
+        <v>1060</v>
       </c>
       <c r="G342" t="s">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="H342" t="s">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="J342" t="s">
         <v>3</v>
@@ -9450,13 +9441,13 @@
     </row>
     <row r="343" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A343" s="1" t="s">
-        <v>1063</v>
+        <v>1228</v>
       </c>
       <c r="G343" t="s">
-        <v>122</v>
+        <v>746</v>
       </c>
       <c r="H343" t="s">
-        <v>123</v>
+        <v>1283</v>
       </c>
       <c r="J343" t="s">
         <v>3</v>
@@ -9464,13 +9455,13 @@
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A344" s="1" t="s">
-        <v>1231</v>
+        <v>1117</v>
       </c>
       <c r="G344" t="s">
-        <v>747</v>
+        <v>753</v>
       </c>
       <c r="H344" t="s">
-        <v>1286</v>
+        <v>1328</v>
       </c>
       <c r="J344" t="s">
         <v>3</v>
@@ -9478,139 +9469,139 @@
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A345" s="1" t="s">
-        <v>1120</v>
+        <v>1098</v>
       </c>
       <c r="G345" t="s">
-        <v>754</v>
+        <v>1</v>
       </c>
       <c r="H345" t="s">
-        <v>1331</v>
+        <v>2</v>
       </c>
       <c r="J345" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="346" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A346" s="1" t="s">
-        <v>1101</v>
+        <v>1229</v>
       </c>
       <c r="G346" t="s">
-        <v>1</v>
+        <v>1258</v>
       </c>
       <c r="H346" t="s">
-        <v>2</v>
+        <v>1284</v>
       </c>
       <c r="J346" t="s">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="347" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A347" s="1" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="G347" t="s">
-        <v>1261</v>
+        <v>534</v>
       </c>
       <c r="H347" t="s">
-        <v>1287</v>
+        <v>571</v>
       </c>
       <c r="J347" t="s">
-        <v>3</v>
+        <v>540</v>
       </c>
     </row>
     <row r="348" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A348" s="1" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="G348" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="H348" t="s">
-        <v>572</v>
+        <v>539</v>
       </c>
       <c r="J348" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A349" s="1" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="G349" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="H349" t="s">
+        <v>545</v>
+      </c>
+      <c r="J349" t="s">
         <v>540</v>
-      </c>
-      <c r="J349" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A350" s="1" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="G350" t="s">
-        <v>545</v>
+        <v>562</v>
       </c>
       <c r="H350" t="s">
-        <v>546</v>
+        <v>563</v>
       </c>
       <c r="J350" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A351" s="1" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="G351" t="s">
-        <v>563</v>
+        <v>534</v>
       </c>
       <c r="H351" t="s">
-        <v>564</v>
+        <v>546</v>
       </c>
       <c r="J351" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A352" s="1" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="G352" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H352" t="s">
-        <v>547</v>
+        <v>575</v>
       </c>
       <c r="J352" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="353" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A353" s="1" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="G353" t="s">
-        <v>535</v>
+        <v>256</v>
       </c>
       <c r="H353" t="s">
-        <v>576</v>
+        <v>744</v>
       </c>
       <c r="J353" t="s">
-        <v>541</v>
+        <v>268</v>
       </c>
     </row>
     <row r="354" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A354" s="1" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="G354" t="s">
-        <v>256</v>
+        <v>541</v>
       </c>
       <c r="H354" t="s">
-        <v>745</v>
+        <v>1329</v>
       </c>
       <c r="J354" t="s">
         <v>268</v>
@@ -9618,13 +9609,13 @@
     </row>
     <row r="355" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A355" s="1" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="G355" t="s">
-        <v>542</v>
+        <v>256</v>
       </c>
       <c r="H355" t="s">
-        <v>1332</v>
+        <v>267</v>
       </c>
       <c r="J355" t="s">
         <v>268</v>
@@ -9632,13 +9623,13 @@
     </row>
     <row r="356" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A356" s="1" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="G356" t="s">
-        <v>256</v>
+        <v>304</v>
       </c>
       <c r="H356" t="s">
-        <v>267</v>
+        <v>305</v>
       </c>
       <c r="J356" t="s">
         <v>268</v>
@@ -9646,13 +9637,13 @@
     </row>
     <row r="357" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A357" s="1" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="G357" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="H357" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="J357" t="s">
         <v>268</v>
@@ -9660,13 +9651,13 @@
     </row>
     <row r="358" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A358" s="1" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="G358" t="s">
-        <v>301</v>
+        <v>577</v>
       </c>
       <c r="H358" t="s">
-        <v>302</v>
+        <v>578</v>
       </c>
       <c r="J358" t="s">
         <v>268</v>
@@ -9674,27 +9665,27 @@
     </row>
     <row r="359" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A359" s="1" t="s">
-        <v>1244</v>
+        <v>943</v>
       </c>
       <c r="G359" t="s">
-        <v>578</v>
+        <v>128</v>
       </c>
       <c r="H359" t="s">
-        <v>579</v>
+        <v>129</v>
       </c>
       <c r="J359" t="s">
-        <v>268</v>
+        <v>3</v>
       </c>
     </row>
     <row r="360" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A360" s="1" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="G360" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="H360" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="J360" t="s">
         <v>3</v>
@@ -9702,13 +9693,13 @@
     </row>
     <row r="361" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A361" s="1" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="G361" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H361" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="J361" t="s">
         <v>3</v>
@@ -9716,13 +9707,13 @@
     </row>
     <row r="362" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A362" s="1" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="G362" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H362" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J362" t="s">
         <v>3</v>
@@ -9730,13 +9721,13 @@
     </row>
     <row r="363" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A363" s="1" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="G363" t="s">
-        <v>138</v>
+        <v>72</v>
       </c>
       <c r="H363" t="s">
-        <v>139</v>
+        <v>73</v>
       </c>
       <c r="J363" t="s">
         <v>3</v>
@@ -9744,27 +9735,27 @@
     </row>
     <row r="364" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A364" s="1" t="s">
-        <v>951</v>
+        <v>870</v>
       </c>
       <c r="G364" t="s">
-        <v>72</v>
+        <v>153</v>
       </c>
       <c r="H364" t="s">
-        <v>73</v>
+        <v>922</v>
       </c>
       <c r="J364" t="s">
-        <v>3</v>
+        <v>51</v>
       </c>
     </row>
     <row r="365" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A365" s="1" t="s">
-        <v>873</v>
+        <v>893</v>
       </c>
       <c r="G365" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="H365" t="s">
-        <v>925</v>
+        <v>170</v>
       </c>
       <c r="J365" t="s">
         <v>51</v>
@@ -9772,13 +9763,13 @@
     </row>
     <row r="366" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A366" s="1" t="s">
-        <v>896</v>
+        <v>864</v>
       </c>
       <c r="G366" t="s">
-        <v>169</v>
+        <v>420</v>
       </c>
       <c r="H366" t="s">
-        <v>170</v>
+        <v>421</v>
       </c>
       <c r="J366" t="s">
         <v>51</v>
@@ -9786,13 +9777,13 @@
     </row>
     <row r="367" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A367" s="1" t="s">
-        <v>867</v>
+        <v>857</v>
       </c>
       <c r="G367" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="H367" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="J367" t="s">
         <v>51</v>
@@ -9800,13 +9791,13 @@
     </row>
     <row r="368" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A368" s="1" t="s">
-        <v>860</v>
+        <v>898</v>
       </c>
       <c r="G368" t="s">
-        <v>417</v>
+        <v>345</v>
       </c>
       <c r="H368" t="s">
-        <v>418</v>
+        <v>346</v>
       </c>
       <c r="J368" t="s">
         <v>51</v>
@@ -9814,13 +9805,13 @@
     </row>
     <row r="369" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A369" s="1" t="s">
-        <v>901</v>
+        <v>858</v>
       </c>
       <c r="G369" t="s">
-        <v>345</v>
+        <v>583</v>
       </c>
       <c r="H369" t="s">
-        <v>346</v>
+        <v>584</v>
       </c>
       <c r="J369" t="s">
         <v>51</v>
@@ -9828,13 +9819,13 @@
     </row>
     <row r="370" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A370" s="1" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="G370" t="s">
-        <v>584</v>
+        <v>49</v>
       </c>
       <c r="H370" t="s">
-        <v>585</v>
+        <v>50</v>
       </c>
       <c r="J370" t="s">
         <v>51</v>
@@ -9842,13 +9833,13 @@
     </row>
     <row r="371" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A371" s="1" t="s">
-        <v>866</v>
+        <v>875</v>
       </c>
       <c r="G371" t="s">
-        <v>49</v>
+        <v>409</v>
       </c>
       <c r="H371" t="s">
-        <v>50</v>
+        <v>410</v>
       </c>
       <c r="J371" t="s">
         <v>51</v>
@@ -9856,13 +9847,13 @@
     </row>
     <row r="372" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A372" s="1" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="G372" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="H372" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="J372" t="s">
         <v>51</v>
@@ -9870,13 +9861,13 @@
     </row>
     <row r="373" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A373" s="1" t="s">
-        <v>879</v>
+        <v>859</v>
       </c>
       <c r="G373" t="s">
-        <v>407</v>
+        <v>582</v>
       </c>
       <c r="H373" t="s">
-        <v>408</v>
+        <v>589</v>
       </c>
       <c r="J373" t="s">
         <v>51</v>
@@ -9884,13 +9875,13 @@
     </row>
     <row r="374" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A374" s="1" t="s">
-        <v>862</v>
+        <v>853</v>
       </c>
       <c r="G374" t="s">
-        <v>583</v>
+        <v>61</v>
       </c>
       <c r="H374" t="s">
-        <v>590</v>
+        <v>62</v>
       </c>
       <c r="J374" t="s">
         <v>51</v>
@@ -9898,13 +9889,13 @@
     </row>
     <row r="375" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A375" s="1" t="s">
-        <v>856</v>
+        <v>866</v>
       </c>
       <c r="G375" t="s">
-        <v>61</v>
+        <v>426</v>
       </c>
       <c r="H375" t="s">
-        <v>62</v>
+        <v>427</v>
       </c>
       <c r="J375" t="s">
         <v>51</v>
@@ -9912,13 +9903,13 @@
     </row>
     <row r="376" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A376" s="1" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="G376" t="s">
-        <v>427</v>
+        <v>587</v>
       </c>
       <c r="H376" t="s">
-        <v>428</v>
+        <v>588</v>
       </c>
       <c r="J376" t="s">
         <v>51</v>
@@ -9926,13 +9917,13 @@
     </row>
     <row r="377" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A377" s="1" t="s">
-        <v>863</v>
+        <v>856</v>
       </c>
       <c r="G377" t="s">
-        <v>588</v>
+        <v>411</v>
       </c>
       <c r="H377" t="s">
-        <v>589</v>
+        <v>412</v>
       </c>
       <c r="J377" t="s">
         <v>51</v>
@@ -9940,13 +9931,13 @@
     </row>
     <row r="378" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A378" s="1" t="s">
-        <v>859</v>
+        <v>899</v>
       </c>
       <c r="G378" t="s">
-        <v>412</v>
+        <v>349</v>
       </c>
       <c r="H378" t="s">
-        <v>413</v>
+        <v>350</v>
       </c>
       <c r="J378" t="s">
         <v>51</v>
@@ -9954,13 +9945,13 @@
     </row>
     <row r="379" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A379" s="1" t="s">
-        <v>902</v>
+        <v>878</v>
       </c>
       <c r="G379" t="s">
-        <v>349</v>
+        <v>406</v>
       </c>
       <c r="H379" t="s">
-        <v>350</v>
+        <v>425</v>
       </c>
       <c r="J379" t="s">
         <v>51</v>
@@ -9968,13 +9959,13 @@
     </row>
     <row r="380" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A380" s="1" t="s">
-        <v>881</v>
+        <v>892</v>
       </c>
       <c r="G380" t="s">
-        <v>407</v>
+        <v>177</v>
       </c>
       <c r="H380" t="s">
-        <v>426</v>
+        <v>178</v>
       </c>
       <c r="J380" t="s">
         <v>51</v>
@@ -9982,13 +9973,13 @@
     </row>
     <row r="381" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A381" s="1" t="s">
-        <v>895</v>
+        <v>877</v>
       </c>
       <c r="G381" t="s">
-        <v>177</v>
+        <v>406</v>
       </c>
       <c r="H381" t="s">
-        <v>178</v>
+        <v>428</v>
       </c>
       <c r="J381" t="s">
         <v>51</v>
@@ -9996,13 +9987,13 @@
     </row>
     <row r="382" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A382" s="1" t="s">
-        <v>880</v>
+        <v>901</v>
       </c>
       <c r="G382" t="s">
-        <v>407</v>
+        <v>341</v>
       </c>
       <c r="H382" t="s">
-        <v>429</v>
+        <v>342</v>
       </c>
       <c r="J382" t="s">
         <v>51</v>
@@ -10010,13 +10001,13 @@
     </row>
     <row r="383" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A383" s="1" t="s">
-        <v>904</v>
+        <v>891</v>
       </c>
       <c r="G383" t="s">
-        <v>341</v>
+        <v>179</v>
       </c>
       <c r="H383" t="s">
-        <v>342</v>
+        <v>180</v>
       </c>
       <c r="J383" t="s">
         <v>51</v>
@@ -10024,13 +10015,13 @@
     </row>
     <row r="384" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A384" s="1" t="s">
-        <v>894</v>
+        <v>879</v>
       </c>
       <c r="G384" t="s">
-        <v>179</v>
+        <v>406</v>
       </c>
       <c r="H384" t="s">
-        <v>180</v>
+        <v>422</v>
       </c>
       <c r="J384" t="s">
         <v>51</v>
@@ -10038,13 +10029,13 @@
     </row>
     <row r="385" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A385" s="1" t="s">
-        <v>882</v>
+        <v>871</v>
       </c>
       <c r="G385" t="s">
-        <v>407</v>
+        <v>158</v>
       </c>
       <c r="H385" t="s">
-        <v>423</v>
+        <v>159</v>
       </c>
       <c r="J385" t="s">
         <v>51</v>
@@ -10052,13 +10043,13 @@
     </row>
     <row r="386" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A386" s="1" t="s">
-        <v>874</v>
+        <v>868</v>
       </c>
       <c r="G386" t="s">
-        <v>158</v>
+        <v>68</v>
       </c>
       <c r="H386" t="s">
-        <v>159</v>
+        <v>69</v>
       </c>
       <c r="J386" t="s">
         <v>51</v>
@@ -10066,13 +10057,13 @@
     </row>
     <row r="387" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A387" s="1" t="s">
-        <v>871</v>
+        <v>907</v>
       </c>
       <c r="G387" t="s">
-        <v>68</v>
+        <v>451</v>
       </c>
       <c r="H387" t="s">
-        <v>69</v>
+        <v>1330</v>
       </c>
       <c r="J387" t="s">
         <v>51</v>
@@ -10080,13 +10071,13 @@
     </row>
     <row r="388" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A388" s="1" t="s">
-        <v>910</v>
+        <v>865</v>
       </c>
       <c r="G388" t="s">
-        <v>452</v>
+        <v>423</v>
       </c>
       <c r="H388" t="s">
-        <v>1333</v>
+        <v>424</v>
       </c>
       <c r="J388" t="s">
         <v>51</v>
@@ -10094,13 +10085,13 @@
     </row>
     <row r="389" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A389" s="1" t="s">
-        <v>868</v>
+        <v>904</v>
       </c>
       <c r="G389" t="s">
-        <v>424</v>
+        <v>166</v>
       </c>
       <c r="H389" t="s">
-        <v>425</v>
+        <v>125</v>
       </c>
       <c r="J389" t="s">
         <v>51</v>
@@ -10108,13 +10099,13 @@
     </row>
     <row r="390" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A390" s="1" t="s">
-        <v>907</v>
+        <v>872</v>
       </c>
       <c r="G390" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="H390" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="J390" t="s">
         <v>51</v>
@@ -10122,13 +10113,13 @@
     </row>
     <row r="391" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A391" s="1" t="s">
-        <v>875</v>
+        <v>867</v>
       </c>
       <c r="G391" t="s">
-        <v>160</v>
+        <v>414</v>
       </c>
       <c r="H391" t="s">
-        <v>161</v>
+        <v>415</v>
       </c>
       <c r="J391" t="s">
         <v>51</v>
@@ -10136,13 +10127,13 @@
     </row>
     <row r="392" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A392" s="1" t="s">
-        <v>870</v>
+        <v>911</v>
       </c>
       <c r="G392" t="s">
-        <v>415</v>
+        <v>731</v>
       </c>
       <c r="H392" t="s">
-        <v>416</v>
+        <v>1331</v>
       </c>
       <c r="J392" t="s">
         <v>51</v>
@@ -10150,13 +10141,13 @@
     </row>
     <row r="393" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A393" s="1" t="s">
-        <v>914</v>
+        <v>883</v>
       </c>
       <c r="G393" t="s">
-        <v>732</v>
+        <v>503</v>
       </c>
       <c r="H393" t="s">
-        <v>1334</v>
+        <v>504</v>
       </c>
       <c r="J393" t="s">
         <v>51</v>
@@ -10164,13 +10155,13 @@
     </row>
     <row r="394" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A394" s="1" t="s">
-        <v>886</v>
+        <v>873</v>
       </c>
       <c r="G394" t="s">
-        <v>504</v>
+        <v>154</v>
       </c>
       <c r="H394" t="s">
-        <v>505</v>
+        <v>155</v>
       </c>
       <c r="J394" t="s">
         <v>51</v>
@@ -10178,13 +10169,13 @@
     </row>
     <row r="395" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A395" s="1" t="s">
-        <v>876</v>
+        <v>919</v>
       </c>
       <c r="G395" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="H395" t="s">
-        <v>155</v>
+        <v>1332</v>
       </c>
       <c r="J395" t="s">
         <v>51</v>
@@ -10192,13 +10183,13 @@
     </row>
     <row r="396" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A396" s="1" t="s">
-        <v>922</v>
+        <v>880</v>
       </c>
       <c r="G396" t="s">
-        <v>175</v>
+        <v>406</v>
       </c>
       <c r="H396" t="s">
-        <v>1335</v>
+        <v>408</v>
       </c>
       <c r="J396" t="s">
         <v>51</v>
@@ -10206,13 +10197,13 @@
     </row>
     <row r="397" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A397" s="1" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="G397" t="s">
-        <v>407</v>
+        <v>63</v>
       </c>
       <c r="H397" t="s">
-        <v>409</v>
+        <v>64</v>
       </c>
       <c r="J397" t="s">
         <v>51</v>
@@ -10220,13 +10211,13 @@
     </row>
     <row r="398" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A398" s="1" t="s">
-        <v>888</v>
+        <v>903</v>
       </c>
       <c r="G398" t="s">
-        <v>63</v>
+        <v>175</v>
       </c>
       <c r="H398" t="s">
-        <v>64</v>
+        <v>176</v>
       </c>
       <c r="J398" t="s">
         <v>51</v>
@@ -10234,13 +10225,13 @@
     </row>
     <row r="399" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A399" s="1" t="s">
-        <v>906</v>
+        <v>874</v>
       </c>
       <c r="G399" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="H399" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="J399" t="s">
         <v>51</v>
@@ -10248,13 +10239,13 @@
     </row>
     <row r="400" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A400" s="1" t="s">
-        <v>877</v>
+        <v>917</v>
       </c>
       <c r="G400" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="H400" t="s">
-        <v>164</v>
+        <v>1333</v>
       </c>
       <c r="J400" t="s">
         <v>51</v>
@@ -10262,13 +10253,13 @@
     </row>
     <row r="401" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A401" s="1" t="s">
-        <v>920</v>
+        <v>906</v>
       </c>
       <c r="G401" t="s">
-        <v>179</v>
+        <v>340</v>
       </c>
       <c r="H401" t="s">
-        <v>1336</v>
+        <v>352</v>
       </c>
       <c r="J401" t="s">
         <v>51</v>
@@ -10276,13 +10267,13 @@
     </row>
     <row r="402" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A402" s="1" t="s">
-        <v>909</v>
+        <v>900</v>
       </c>
       <c r="G402" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="H402" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="J402" t="s">
         <v>51</v>
@@ -10290,13 +10281,13 @@
     </row>
     <row r="403" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A403" s="1" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="G403" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="H403" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="J403" t="s">
         <v>51</v>
@@ -10304,13 +10295,13 @@
     </row>
     <row r="404" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A404" s="1" t="s">
-        <v>908</v>
+        <v>862</v>
       </c>
       <c r="G404" t="s">
-        <v>340</v>
+        <v>418</v>
       </c>
       <c r="H404" t="s">
-        <v>351</v>
+        <v>419</v>
       </c>
       <c r="J404" t="s">
         <v>51</v>
@@ -10318,13 +10309,13 @@
     </row>
     <row r="405" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A405" s="1" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="G405" t="s">
-        <v>419</v>
+        <v>585</v>
       </c>
       <c r="H405" t="s">
-        <v>420</v>
+        <v>586</v>
       </c>
       <c r="J405" t="s">
         <v>51</v>
@@ -10332,13 +10323,13 @@
     </row>
     <row r="406" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A406" s="1" t="s">
-        <v>864</v>
+        <v>895</v>
       </c>
       <c r="G406" t="s">
-        <v>586</v>
+        <v>173</v>
       </c>
       <c r="H406" t="s">
-        <v>587</v>
+        <v>174</v>
       </c>
       <c r="J406" t="s">
         <v>51</v>
@@ -10346,13 +10337,13 @@
     </row>
     <row r="407" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A407" s="1" t="s">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="G407" t="s">
-        <v>173</v>
+        <v>343</v>
       </c>
       <c r="H407" t="s">
-        <v>174</v>
+        <v>344</v>
       </c>
       <c r="J407" t="s">
         <v>51</v>
@@ -10360,13 +10351,13 @@
     </row>
     <row r="408" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A408" s="1" t="s">
-        <v>905</v>
+        <v>1242</v>
       </c>
       <c r="G408" t="s">
-        <v>343</v>
+        <v>752</v>
       </c>
       <c r="H408" t="s">
-        <v>344</v>
+        <v>1288</v>
       </c>
       <c r="J408" t="s">
         <v>51</v>
@@ -10374,13 +10365,13 @@
     </row>
     <row r="409" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A409" s="1" t="s">
-        <v>1245</v>
+        <v>881</v>
       </c>
       <c r="G409" t="s">
-        <v>753</v>
+        <v>406</v>
       </c>
       <c r="H409" t="s">
-        <v>1291</v>
+        <v>413</v>
       </c>
       <c r="J409" t="s">
         <v>51</v>
@@ -10388,13 +10379,13 @@
     </row>
     <row r="410" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A410" s="1" t="s">
-        <v>884</v>
+        <v>890</v>
       </c>
       <c r="G410" t="s">
-        <v>407</v>
+        <v>452</v>
       </c>
       <c r="H410" t="s">
-        <v>414</v>
+        <v>453</v>
       </c>
       <c r="J410" t="s">
         <v>51</v>
@@ -10402,13 +10393,13 @@
     </row>
     <row r="411" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A411" s="1" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="G411" t="s">
-        <v>453</v>
+        <v>165</v>
       </c>
       <c r="H411" t="s">
-        <v>454</v>
+        <v>167</v>
       </c>
       <c r="J411" t="s">
         <v>51</v>
@@ -10416,13 +10407,13 @@
     </row>
     <row r="412" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A412" s="1" t="s">
-        <v>897</v>
+        <v>869</v>
       </c>
       <c r="G412" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="H412" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="J412" t="s">
         <v>51</v>
@@ -10430,13 +10421,13 @@
     </row>
     <row r="413" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A413" s="1" t="s">
-        <v>872</v>
+        <v>897</v>
       </c>
       <c r="G413" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="H413" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J413" t="s">
         <v>51</v>
@@ -10444,13 +10435,13 @@
     </row>
     <row r="414" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A414" s="1" t="s">
-        <v>900</v>
+        <v>854</v>
       </c>
       <c r="G414" t="s">
-        <v>171</v>
+        <v>58</v>
       </c>
       <c r="H414" t="s">
-        <v>172</v>
+        <v>59</v>
       </c>
       <c r="J414" t="s">
         <v>51</v>
@@ -10458,13 +10449,13 @@
     </row>
     <row r="415" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A415" s="1" t="s">
-        <v>857</v>
+        <v>920</v>
       </c>
       <c r="G415" t="s">
-        <v>58</v>
+        <v>758</v>
       </c>
       <c r="H415" t="s">
-        <v>59</v>
+        <v>1334</v>
       </c>
       <c r="J415" t="s">
         <v>51</v>
@@ -10472,13 +10463,13 @@
     </row>
     <row r="416" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A416" s="1" t="s">
-        <v>923</v>
+        <v>849</v>
       </c>
       <c r="G416" t="s">
-        <v>759</v>
+        <v>244</v>
       </c>
       <c r="H416" t="s">
-        <v>1337</v>
+        <v>245</v>
       </c>
       <c r="J416" t="s">
         <v>51</v>
@@ -10489,10 +10480,10 @@
         <v>852</v>
       </c>
       <c r="G417" t="s">
-        <v>244</v>
+        <v>52</v>
       </c>
       <c r="H417" t="s">
-        <v>245</v>
+        <v>53</v>
       </c>
       <c r="J417" t="s">
         <v>51</v>
@@ -10500,13 +10491,13 @@
     </row>
     <row r="418" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A418" s="1" t="s">
-        <v>855</v>
+        <v>886</v>
       </c>
       <c r="G418" t="s">
         <v>52</v>
       </c>
       <c r="H418" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J418" t="s">
         <v>51</v>
@@ -10514,13 +10505,13 @@
     </row>
     <row r="419" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A419" s="1" t="s">
-        <v>889</v>
+        <v>1243</v>
       </c>
       <c r="G419" t="s">
-        <v>52</v>
+        <v>749</v>
       </c>
       <c r="H419" t="s">
-        <v>60</v>
+        <v>1289</v>
       </c>
       <c r="J419" t="s">
         <v>51</v>
@@ -10528,13 +10519,13 @@
     </row>
     <row r="420" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A420" s="1" t="s">
-        <v>1246</v>
+        <v>848</v>
       </c>
       <c r="G420" t="s">
-        <v>750</v>
+        <v>243</v>
       </c>
       <c r="H420" t="s">
-        <v>1292</v>
+        <v>250</v>
       </c>
       <c r="J420" t="s">
         <v>51</v>
@@ -10542,13 +10533,13 @@
     </row>
     <row r="421" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A421" s="1" t="s">
-        <v>851</v>
+        <v>896</v>
       </c>
       <c r="G421" t="s">
-        <v>243</v>
+        <v>165</v>
       </c>
       <c r="H421" t="s">
-        <v>250</v>
+        <v>168</v>
       </c>
       <c r="J421" t="s">
         <v>51</v>
@@ -10556,13 +10547,13 @@
     </row>
     <row r="422" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A422" s="1" t="s">
-        <v>899</v>
+        <v>913</v>
       </c>
       <c r="G422" t="s">
-        <v>165</v>
+        <v>732</v>
       </c>
       <c r="H422" t="s">
-        <v>168</v>
+        <v>1317</v>
       </c>
       <c r="J422" t="s">
         <v>51</v>
@@ -10570,13 +10561,13 @@
     </row>
     <row r="423" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A423" s="1" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="G423" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="H423" t="s">
-        <v>1320</v>
+        <v>1335</v>
       </c>
       <c r="J423" t="s">
         <v>51</v>
@@ -10584,13 +10575,13 @@
     </row>
     <row r="424" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A424" s="1" t="s">
-        <v>913</v>
+        <v>889</v>
       </c>
       <c r="G424" t="s">
-        <v>730</v>
+        <v>451</v>
       </c>
       <c r="H424" t="s">
-        <v>1338</v>
+        <v>454</v>
       </c>
       <c r="J424" t="s">
         <v>51</v>
@@ -10598,13 +10589,13 @@
     </row>
     <row r="425" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A425" s="1" t="s">
-        <v>892</v>
+        <v>884</v>
       </c>
       <c r="G425" t="s">
-        <v>452</v>
+        <v>200</v>
       </c>
       <c r="H425" t="s">
-        <v>455</v>
+        <v>201</v>
       </c>
       <c r="J425" t="s">
         <v>51</v>
@@ -10612,13 +10603,13 @@
     </row>
     <row r="426" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A426" s="1" t="s">
-        <v>887</v>
+        <v>909</v>
       </c>
       <c r="G426" t="s">
-        <v>200</v>
+        <v>725</v>
       </c>
       <c r="H426" t="s">
-        <v>201</v>
+        <v>1336</v>
       </c>
       <c r="J426" t="s">
         <v>51</v>
@@ -10626,13 +10617,13 @@
     </row>
     <row r="427" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A427" s="1" t="s">
-        <v>912</v>
+        <v>1244</v>
       </c>
       <c r="G427" t="s">
-        <v>726</v>
+        <v>340</v>
       </c>
       <c r="H427" t="s">
-        <v>1339</v>
+        <v>1290</v>
       </c>
       <c r="J427" t="s">
         <v>51</v>
@@ -10640,13 +10631,13 @@
     </row>
     <row r="428" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A428" s="1" t="s">
-        <v>1247</v>
+        <v>921</v>
       </c>
       <c r="G428" t="s">
-        <v>340</v>
+        <v>165</v>
       </c>
       <c r="H428" t="s">
-        <v>1293</v>
+        <v>1337</v>
       </c>
       <c r="J428" t="s">
         <v>51</v>
@@ -10654,13 +10645,13 @@
     </row>
     <row r="429" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A429" s="1" t="s">
-        <v>924</v>
+        <v>918</v>
       </c>
       <c r="G429" t="s">
-        <v>165</v>
+        <v>755</v>
       </c>
       <c r="H429" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="J429" t="s">
         <v>51</v>
@@ -10668,13 +10659,13 @@
     </row>
     <row r="430" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A430" s="1" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="G430" t="s">
-        <v>756</v>
+        <v>733</v>
       </c>
       <c r="H430" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="J430" t="s">
         <v>51</v>
@@ -10682,13 +10673,13 @@
     </row>
     <row r="431" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A431" s="1" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="G431" t="s">
-        <v>734</v>
+        <v>52</v>
       </c>
       <c r="H431" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="J431" t="s">
         <v>51</v>
@@ -10696,13 +10687,13 @@
     </row>
     <row r="432" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A432" s="1" t="s">
-        <v>915</v>
+        <v>850</v>
       </c>
       <c r="G432" t="s">
-        <v>52</v>
+        <v>246</v>
       </c>
       <c r="H432" t="s">
-        <v>1343</v>
+        <v>247</v>
       </c>
       <c r="J432" t="s">
         <v>51</v>
@@ -10710,13 +10701,13 @@
     </row>
     <row r="433" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A433" s="1" t="s">
-        <v>853</v>
+        <v>916</v>
       </c>
       <c r="G433" t="s">
-        <v>246</v>
+        <v>742</v>
       </c>
       <c r="H433" t="s">
-        <v>247</v>
+        <v>1341</v>
       </c>
       <c r="J433" t="s">
         <v>51</v>
@@ -10724,13 +10715,13 @@
     </row>
     <row r="434" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A434" s="1" t="s">
-        <v>919</v>
+        <v>855</v>
       </c>
       <c r="G434" t="s">
-        <v>743</v>
+        <v>605</v>
       </c>
       <c r="H434" t="s">
-        <v>1344</v>
+        <v>606</v>
       </c>
       <c r="J434" t="s">
         <v>51</v>
@@ -10738,13 +10729,13 @@
     </row>
     <row r="435" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A435" s="1" t="s">
-        <v>858</v>
+        <v>1245</v>
       </c>
       <c r="G435" t="s">
-        <v>606</v>
+        <v>750</v>
       </c>
       <c r="H435" t="s">
-        <v>607</v>
+        <v>1291</v>
       </c>
       <c r="J435" t="s">
         <v>51</v>
@@ -10752,13 +10743,13 @@
     </row>
     <row r="436" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A436" s="1" t="s">
-        <v>1248</v>
+        <v>915</v>
       </c>
       <c r="G436" t="s">
-        <v>751</v>
+        <v>740</v>
       </c>
       <c r="H436" t="s">
-        <v>1294</v>
+        <v>1342</v>
       </c>
       <c r="J436" t="s">
         <v>51</v>
@@ -10766,13 +10757,13 @@
     </row>
     <row r="437" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A437" s="1" t="s">
-        <v>918</v>
+        <v>1246</v>
       </c>
       <c r="G437" t="s">
-        <v>741</v>
+        <v>751</v>
       </c>
       <c r="H437" t="s">
-        <v>1345</v>
+        <v>1292</v>
       </c>
       <c r="J437" t="s">
         <v>51</v>
@@ -10780,13 +10771,13 @@
     </row>
     <row r="438" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A438" s="1" t="s">
-        <v>1249</v>
+        <v>908</v>
       </c>
       <c r="G438" t="s">
-        <v>752</v>
+        <v>724</v>
       </c>
       <c r="H438" t="s">
-        <v>1295</v>
+        <v>1317</v>
       </c>
       <c r="J438" t="s">
         <v>51</v>
@@ -10794,13 +10785,13 @@
     </row>
     <row r="439" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A439" s="1" t="s">
-        <v>911</v>
+        <v>887</v>
       </c>
       <c r="G439" t="s">
-        <v>725</v>
+        <v>54</v>
       </c>
       <c r="H439" t="s">
-        <v>1320</v>
+        <v>55</v>
       </c>
       <c r="J439" t="s">
         <v>51</v>
@@ -10808,13 +10799,13 @@
     </row>
     <row r="440" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A440" s="1" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="G440" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H440" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J440" t="s">
         <v>51</v>
@@ -10822,41 +10813,41 @@
     </row>
     <row r="441" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A441" s="1" t="s">
-        <v>891</v>
+        <v>882</v>
       </c>
       <c r="G441" t="s">
-        <v>56</v>
+        <v>162</v>
       </c>
       <c r="H441" t="s">
-        <v>57</v>
+        <v>163</v>
       </c>
       <c r="J441" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="442" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A442" s="1" t="s">
-        <v>885</v>
-      </c>
-      <c r="G442" t="s">
-        <v>162</v>
-      </c>
-      <c r="H442" t="s">
-        <v>163</v>
+      <c r="A442" t="s">
+        <v>929</v>
+      </c>
+      <c r="G442" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="H442" s="2" t="s">
+        <v>654</v>
       </c>
       <c r="J442" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
     </row>
     <row r="443" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
-        <v>932</v>
+        <v>1343</v>
       </c>
       <c r="G443" s="2" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="H443" s="2" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="J443" t="s">
         <v>67</v>
@@ -10864,13 +10855,13 @@
     </row>
     <row r="444" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="G444" s="2" t="s">
-        <v>650</v>
+        <v>124</v>
       </c>
       <c r="H444" s="2" t="s">
-        <v>651</v>
+        <v>125</v>
       </c>
       <c r="J444" t="s">
         <v>67</v>
@@ -10878,13 +10869,13 @@
     </row>
     <row r="445" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="G445" s="2" t="s">
-        <v>124</v>
+        <v>498</v>
       </c>
       <c r="H445" s="2" t="s">
-        <v>125</v>
+        <v>499</v>
       </c>
       <c r="J445" t="s">
         <v>67</v>
@@ -10892,13 +10883,13 @@
     </row>
     <row r="446" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
       <c r="G446" s="2" t="s">
-        <v>499</v>
+        <v>438</v>
       </c>
       <c r="H446" s="2" t="s">
-        <v>500</v>
+        <v>439</v>
       </c>
       <c r="J446" t="s">
         <v>67</v>
@@ -10906,13 +10897,13 @@
     </row>
     <row r="447" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="G447" s="2" t="s">
-        <v>439</v>
+        <v>224</v>
       </c>
       <c r="H447" s="2" t="s">
-        <v>440</v>
+        <v>225</v>
       </c>
       <c r="J447" t="s">
         <v>67</v>
@@ -10920,13 +10911,13 @@
     </row>
     <row r="448" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
-        <v>1350</v>
+        <v>935</v>
       </c>
       <c r="G448" s="2" t="s">
-        <v>224</v>
+        <v>65</v>
       </c>
       <c r="H448" s="2" t="s">
-        <v>225</v>
+        <v>66</v>
       </c>
       <c r="J448" t="s">
         <v>67</v>
@@ -10937,10 +10928,10 @@
         <v>938</v>
       </c>
       <c r="G449" s="2" t="s">
-        <v>65</v>
+        <v>713</v>
       </c>
       <c r="H449" s="2" t="s">
-        <v>66</v>
+        <v>714</v>
       </c>
       <c r="J449" t="s">
         <v>67</v>
@@ -10948,13 +10939,13 @@
     </row>
     <row r="450" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
-        <v>941</v>
+        <v>1348</v>
       </c>
       <c r="G450" s="2" t="s">
-        <v>714</v>
+        <v>580</v>
       </c>
       <c r="H450" s="2" t="s">
-        <v>715</v>
+        <v>581</v>
       </c>
       <c r="J450" t="s">
         <v>67</v>
@@ -10962,13 +10953,13 @@
     </row>
     <row r="451" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
-        <v>1351</v>
+        <v>932</v>
       </c>
       <c r="G451" s="2" t="s">
-        <v>581</v>
+        <v>651</v>
       </c>
       <c r="H451" s="2" t="s">
-        <v>582</v>
+        <v>652</v>
       </c>
       <c r="J451" t="s">
         <v>67</v>
@@ -10976,13 +10967,13 @@
     </row>
     <row r="452" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
-        <v>935</v>
+        <v>923</v>
       </c>
       <c r="G452" s="2" t="s">
-        <v>652</v>
+        <v>445</v>
       </c>
       <c r="H452" s="2" t="s">
-        <v>653</v>
+        <v>446</v>
       </c>
       <c r="J452" t="s">
         <v>67</v>
@@ -10990,13 +10981,13 @@
     </row>
     <row r="453" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
-        <v>926</v>
+        <v>1349</v>
       </c>
       <c r="G453" s="2" t="s">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="H453" s="2" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="J453" t="s">
         <v>67</v>
@@ -11004,13 +10995,13 @@
     </row>
     <row r="454" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="G454" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H454" s="2" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="J454" t="s">
         <v>67</v>
@@ -11018,13 +11009,13 @@
     </row>
     <row r="455" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
-        <v>1353</v>
+        <v>930</v>
       </c>
       <c r="G455" s="2" t="s">
-        <v>435</v>
+        <v>498</v>
       </c>
       <c r="H455" s="2" t="s">
-        <v>442</v>
+        <v>502</v>
       </c>
       <c r="J455" t="s">
         <v>67</v>
@@ -11032,13 +11023,13 @@
     </row>
     <row r="456" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
-        <v>933</v>
+        <v>1351</v>
       </c>
       <c r="G456" s="2" t="s">
-        <v>499</v>
+        <v>707</v>
       </c>
       <c r="H456" s="2" t="s">
-        <v>503</v>
+        <v>708</v>
       </c>
       <c r="J456" t="s">
         <v>67</v>
@@ -11046,13 +11037,13 @@
     </row>
     <row r="457" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
-        <v>1354</v>
+        <v>941</v>
       </c>
       <c r="G457" s="2" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="H457" s="2" t="s">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="J457" t="s">
         <v>67</v>
@@ -11060,13 +11051,13 @@
     </row>
     <row r="458" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
-        <v>944</v>
+        <v>1352</v>
       </c>
       <c r="G458" s="2" t="s">
-        <v>716</v>
+        <v>675</v>
       </c>
       <c r="H458" s="2" t="s">
-        <v>717</v>
+        <v>678</v>
       </c>
       <c r="J458" t="s">
         <v>67</v>
@@ -11074,13 +11065,13 @@
     </row>
     <row r="459" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="G459" s="2" t="s">
-        <v>676</v>
+        <v>434</v>
       </c>
       <c r="H459" s="2" t="s">
-        <v>679</v>
+        <v>435</v>
       </c>
       <c r="J459" t="s">
         <v>67</v>
@@ -11088,13 +11079,13 @@
     </row>
     <row r="460" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="G460" s="2" t="s">
-        <v>435</v>
+        <v>657</v>
       </c>
       <c r="H460" s="2" t="s">
-        <v>436</v>
+        <v>1385</v>
       </c>
       <c r="J460" t="s">
         <v>67</v>
@@ -11102,13 +11093,13 @@
     </row>
     <row r="461" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="G461" s="2" t="s">
-        <v>658</v>
+        <v>436</v>
       </c>
       <c r="H461" s="2" t="s">
-        <v>1388</v>
+        <v>437</v>
       </c>
       <c r="J461" t="s">
         <v>67</v>
@@ -11116,13 +11107,13 @@
     </row>
     <row r="462" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="G462" s="2" t="s">
-        <v>437</v>
+        <v>709</v>
       </c>
       <c r="H462" s="2" t="s">
-        <v>438</v>
+        <v>711</v>
       </c>
       <c r="J462" t="s">
         <v>67</v>
@@ -11130,13 +11121,13 @@
     </row>
     <row r="463" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="G463" s="2" t="s">
-        <v>710</v>
+        <v>697</v>
       </c>
       <c r="H463" s="2" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="J463" t="s">
         <v>67</v>
@@ -11144,13 +11135,13 @@
     </row>
     <row r="464" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
-        <v>1360</v>
+        <v>933</v>
       </c>
       <c r="G464" s="2" t="s">
-        <v>698</v>
+        <v>685</v>
       </c>
       <c r="H464" s="2" t="s">
-        <v>703</v>
+        <v>686</v>
       </c>
       <c r="J464" t="s">
         <v>67</v>
@@ -11158,13 +11149,13 @@
     </row>
     <row r="465" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
-        <v>936</v>
+        <v>1358</v>
       </c>
       <c r="G465" s="2" t="s">
-        <v>686</v>
+        <v>675</v>
       </c>
       <c r="H465" s="2" t="s">
-        <v>687</v>
+        <v>956</v>
       </c>
       <c r="J465" t="s">
         <v>67</v>
@@ -11172,13 +11163,13 @@
     </row>
     <row r="466" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="G466" s="2" t="s">
-        <v>676</v>
+        <v>709</v>
       </c>
       <c r="H466" s="2" t="s">
-        <v>959</v>
+        <v>710</v>
       </c>
       <c r="J466" t="s">
         <v>67</v>
@@ -11186,13 +11177,13 @@
     </row>
     <row r="467" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="G467" s="2" t="s">
-        <v>710</v>
+        <v>697</v>
       </c>
       <c r="H467" s="2" t="s">
-        <v>711</v>
+        <v>1285</v>
       </c>
       <c r="J467" t="s">
         <v>67</v>
@@ -11200,13 +11191,13 @@
     </row>
     <row r="468" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
-        <v>1363</v>
+        <v>931</v>
       </c>
       <c r="G468" s="2" t="s">
-        <v>698</v>
+        <v>655</v>
       </c>
       <c r="H468" s="2" t="s">
-        <v>1288</v>
+        <v>656</v>
       </c>
       <c r="J468" t="s">
         <v>67</v>
@@ -11214,13 +11205,13 @@
     </row>
     <row r="469" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
-        <v>934</v>
+        <v>924</v>
       </c>
       <c r="G469" s="2" t="s">
-        <v>656</v>
+        <v>449</v>
       </c>
       <c r="H469" s="2" t="s">
-        <v>657</v>
+        <v>450</v>
       </c>
       <c r="J469" t="s">
         <v>67</v>
@@ -11228,13 +11219,13 @@
     </row>
     <row r="470" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
-        <v>927</v>
+        <v>940</v>
       </c>
       <c r="G470" s="2" t="s">
-        <v>450</v>
+        <v>717</v>
       </c>
       <c r="H470" s="2" t="s">
-        <v>451</v>
+        <v>718</v>
       </c>
       <c r="J470" t="s">
         <v>67</v>
@@ -11242,13 +11233,13 @@
     </row>
     <row r="471" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
-        <v>943</v>
+        <v>928</v>
       </c>
       <c r="G471" s="2" t="s">
-        <v>718</v>
+        <v>120</v>
       </c>
       <c r="H471" s="2" t="s">
-        <v>719</v>
+        <v>121</v>
       </c>
       <c r="J471" t="s">
         <v>67</v>
@@ -11256,13 +11247,13 @@
     </row>
     <row r="472" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
-        <v>931</v>
+        <v>1361</v>
       </c>
       <c r="G472" s="2" t="s">
-        <v>120</v>
+        <v>679</v>
       </c>
       <c r="H472" s="2" t="s">
-        <v>121</v>
+        <v>680</v>
       </c>
       <c r="J472" t="s">
         <v>67</v>
@@ -11270,13 +11261,13 @@
     </row>
     <row r="473" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="G473" s="2" t="s">
-        <v>680</v>
+        <v>723</v>
       </c>
       <c r="H473" s="2" t="s">
-        <v>681</v>
+        <v>1386</v>
       </c>
       <c r="J473" t="s">
         <v>67</v>
@@ -11284,13 +11275,13 @@
     </row>
     <row r="474" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="G474" s="2" t="s">
-        <v>724</v>
+        <v>224</v>
       </c>
       <c r="H474" s="2" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="J474" t="s">
         <v>67</v>
@@ -11298,13 +11289,13 @@
     </row>
     <row r="475" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
-        <v>1366</v>
+        <v>926</v>
       </c>
       <c r="G475" s="2" t="s">
-        <v>224</v>
+        <v>434</v>
       </c>
       <c r="H475" s="2" t="s">
-        <v>1390</v>
+        <v>443</v>
       </c>
       <c r="J475" t="s">
         <v>67</v>
@@ -11312,13 +11303,13 @@
     </row>
     <row r="476" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
-        <v>929</v>
+        <v>936</v>
       </c>
       <c r="G476" s="2" t="s">
-        <v>435</v>
+        <v>681</v>
       </c>
       <c r="H476" s="2" t="s">
-        <v>444</v>
+        <v>682</v>
       </c>
       <c r="J476" t="s">
         <v>67</v>
@@ -11326,13 +11317,13 @@
     </row>
     <row r="477" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="G477" s="2" t="s">
-        <v>682</v>
+        <v>712</v>
       </c>
       <c r="H477" s="2" t="s">
-        <v>683</v>
+        <v>955</v>
       </c>
       <c r="J477" t="s">
         <v>67</v>
@@ -11340,13 +11331,13 @@
     </row>
     <row r="478" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
-        <v>945</v>
+        <v>1364</v>
       </c>
       <c r="G478" s="2" t="s">
-        <v>713</v>
+        <v>697</v>
       </c>
       <c r="H478" s="2" t="s">
-        <v>958</v>
+        <v>703</v>
       </c>
       <c r="J478" t="s">
         <v>67</v>
@@ -11354,13 +11345,13 @@
     </row>
     <row r="479" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="G479" s="2" t="s">
-        <v>698</v>
+        <v>224</v>
       </c>
       <c r="H479" s="2" t="s">
-        <v>704</v>
+        <v>1388</v>
       </c>
       <c r="J479" t="s">
         <v>67</v>
@@ -11368,13 +11359,13 @@
     </row>
     <row r="480" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
-        <v>1368</v>
+        <v>934</v>
       </c>
       <c r="G480" s="2" t="s">
-        <v>224</v>
+        <v>683</v>
       </c>
       <c r="H480" s="2" t="s">
-        <v>1391</v>
+        <v>684</v>
       </c>
       <c r="J480" t="s">
         <v>67</v>
@@ -11382,13 +11373,13 @@
     </row>
     <row r="481" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
-        <v>937</v>
+        <v>949</v>
       </c>
       <c r="G481" s="2" t="s">
-        <v>684</v>
+        <v>734</v>
       </c>
       <c r="H481" s="2" t="s">
-        <v>685</v>
+        <v>1389</v>
       </c>
       <c r="J481" t="s">
         <v>67</v>
@@ -11396,13 +11387,13 @@
     </row>
     <row r="482" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="G482" s="2" t="s">
-        <v>735</v>
+        <v>658</v>
       </c>
       <c r="H482" s="2" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="J482" t="s">
         <v>67</v>
@@ -11410,13 +11401,13 @@
     </row>
     <row r="483" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
-        <v>956</v>
+        <v>1366</v>
       </c>
       <c r="G483" s="2" t="s">
-        <v>659</v>
+        <v>434</v>
       </c>
       <c r="H483" s="2" t="s">
-        <v>1393</v>
+        <v>440</v>
       </c>
       <c r="J483" t="s">
         <v>67</v>
@@ -11424,13 +11415,13 @@
     </row>
     <row r="484" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
-        <v>1369</v>
+        <v>925</v>
       </c>
       <c r="G484" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H484" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="J484" t="s">
         <v>67</v>
@@ -11438,13 +11429,13 @@
     </row>
     <row r="485" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
-        <v>928</v>
+        <v>1367</v>
       </c>
       <c r="G485" s="2" t="s">
-        <v>435</v>
+        <v>500</v>
       </c>
       <c r="H485" s="2" t="s">
-        <v>445</v>
+        <v>501</v>
       </c>
       <c r="J485" t="s">
         <v>67</v>
@@ -11452,13 +11443,13 @@
     </row>
     <row r="486" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="G486" s="2" t="s">
-        <v>501</v>
+        <v>1259</v>
       </c>
       <c r="H486" s="2" t="s">
-        <v>502</v>
+        <v>1391</v>
       </c>
       <c r="J486" t="s">
         <v>67</v>
@@ -11466,13 +11457,13 @@
     </row>
     <row r="487" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="G487" s="2" t="s">
-        <v>1262</v>
+        <v>601</v>
       </c>
       <c r="H487" s="2" t="s">
-        <v>1394</v>
+        <v>602</v>
       </c>
       <c r="J487" t="s">
         <v>67</v>
@@ -11480,13 +11471,13 @@
     </row>
     <row r="488" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
-        <v>1372</v>
+        <v>927</v>
       </c>
       <c r="G488" s="2" t="s">
-        <v>602</v>
+        <v>447</v>
       </c>
       <c r="H488" s="2" t="s">
-        <v>603</v>
+        <v>448</v>
       </c>
       <c r="J488" t="s">
         <v>67</v>
@@ -11494,13 +11485,13 @@
     </row>
     <row r="489" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
-        <v>930</v>
+        <v>1370</v>
       </c>
       <c r="G489" s="2" t="s">
-        <v>448</v>
+        <v>700</v>
       </c>
       <c r="H489" s="2" t="s">
-        <v>449</v>
+        <v>701</v>
       </c>
       <c r="J489" t="s">
         <v>67</v>
@@ -11508,13 +11499,13 @@
     </row>
     <row r="490" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="G490" s="2" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="H490" s="2" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="J490" t="s">
         <v>67</v>
@@ -11522,13 +11513,13 @@
     </row>
     <row r="491" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="G491" s="2" t="s">
-        <v>699</v>
+        <v>647</v>
       </c>
       <c r="H491" s="2" t="s">
-        <v>700</v>
+        <v>648</v>
       </c>
       <c r="J491" t="s">
         <v>67</v>
@@ -11536,13 +11527,13 @@
     </row>
     <row r="492" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
-        <v>1375</v>
+        <v>950</v>
       </c>
       <c r="G492" s="2" t="s">
-        <v>648</v>
+        <v>756</v>
       </c>
       <c r="H492" s="2" t="s">
-        <v>649</v>
+        <v>1392</v>
       </c>
       <c r="J492" t="s">
         <v>67</v>
@@ -11550,13 +11541,13 @@
     </row>
     <row r="493" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
-        <v>953</v>
+        <v>1373</v>
       </c>
       <c r="G493" s="2" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="H493" s="2" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="J493" t="s">
         <v>67</v>
@@ -11564,13 +11555,13 @@
     </row>
     <row r="494" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="G494" s="2" t="s">
-        <v>760</v>
+        <v>280</v>
       </c>
       <c r="H494" s="2" t="s">
-        <v>1396</v>
+        <v>281</v>
       </c>
       <c r="J494" t="s">
         <v>67</v>
@@ -11578,13 +11569,13 @@
     </row>
     <row r="495" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="G495" s="2" t="s">
-        <v>280</v>
+        <v>126</v>
       </c>
       <c r="H495" s="2" t="s">
-        <v>281</v>
+        <v>127</v>
       </c>
       <c r="J495" t="s">
         <v>67</v>
@@ -11592,13 +11583,13 @@
     </row>
     <row r="496" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="G496" s="2" t="s">
-        <v>126</v>
+        <v>1254</v>
       </c>
       <c r="H496" s="2" t="s">
-        <v>127</v>
+        <v>1394</v>
       </c>
       <c r="J496" t="s">
         <v>67</v>
@@ -11606,13 +11597,13 @@
     </row>
     <row r="497" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="G497" s="2" t="s">
-        <v>1257</v>
+        <v>676</v>
       </c>
       <c r="H497" s="2" t="s">
-        <v>1397</v>
+        <v>677</v>
       </c>
       <c r="J497" t="s">
         <v>67</v>
@@ -11620,13 +11611,13 @@
     </row>
     <row r="498" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
-        <v>1380</v>
+        <v>947</v>
       </c>
       <c r="G498" s="2" t="s">
-        <v>677</v>
+        <v>603</v>
       </c>
       <c r="H498" s="2" t="s">
-        <v>678</v>
+        <v>604</v>
       </c>
       <c r="J498" t="s">
         <v>67</v>
@@ -11634,13 +11625,13 @@
     </row>
     <row r="499" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
-        <v>950</v>
+        <v>1378</v>
       </c>
       <c r="G499" s="2" t="s">
-        <v>604</v>
+        <v>747</v>
       </c>
       <c r="H499" s="2" t="s">
-        <v>605</v>
+        <v>1286</v>
       </c>
       <c r="J499" t="s">
         <v>67</v>
@@ -11648,13 +11639,13 @@
     </row>
     <row r="500" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
-        <v>1381</v>
+        <v>939</v>
       </c>
       <c r="G500" s="2" t="s">
-        <v>748</v>
+        <v>704</v>
       </c>
       <c r="H500" s="2" t="s">
-        <v>1289</v>
+        <v>705</v>
       </c>
       <c r="J500" t="s">
         <v>67</v>
@@ -11662,13 +11653,13 @@
     </row>
     <row r="501" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
-        <v>942</v>
+        <v>951</v>
       </c>
       <c r="G501" s="2" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H501" s="2" t="s">
-        <v>706</v>
+        <v>1395</v>
       </c>
       <c r="J501" t="s">
         <v>67</v>
@@ -11679,10 +11670,10 @@
         <v>954</v>
       </c>
       <c r="G502" s="2" t="s">
-        <v>707</v>
+        <v>1260</v>
       </c>
       <c r="H502" s="2" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="J502" t="s">
         <v>67</v>
@@ -11690,13 +11681,13 @@
     </row>
     <row r="503" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
-        <v>957</v>
+        <v>1379</v>
       </c>
       <c r="G503" s="2" t="s">
-        <v>1263</v>
+        <v>697</v>
       </c>
       <c r="H503" s="2" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="J503" t="s">
         <v>67</v>
@@ -11704,13 +11695,13 @@
     </row>
     <row r="504" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="G504" s="2" t="s">
-        <v>698</v>
+        <v>707</v>
       </c>
       <c r="H504" s="2" t="s">
-        <v>1400</v>
+        <v>1287</v>
       </c>
       <c r="J504" t="s">
         <v>67</v>
@@ -11718,13 +11709,13 @@
     </row>
     <row r="505" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
-        <v>1383</v>
+        <v>937</v>
       </c>
       <c r="G505" s="2" t="s">
-        <v>708</v>
+        <v>658</v>
       </c>
       <c r="H505" s="2" t="s">
-        <v>1290</v>
+        <v>659</v>
       </c>
       <c r="J505" t="s">
         <v>67</v>
@@ -11732,13 +11723,13 @@
     </row>
     <row r="506" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
-        <v>940</v>
+        <v>1381</v>
       </c>
       <c r="G506" s="2" t="s">
-        <v>659</v>
+        <v>645</v>
       </c>
       <c r="H506" s="2" t="s">
-        <v>660</v>
+        <v>646</v>
       </c>
       <c r="J506" t="s">
         <v>67</v>
@@ -11746,13 +11737,13 @@
     </row>
     <row r="507" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="G507" s="2" t="s">
-        <v>646</v>
+        <v>707</v>
       </c>
       <c r="H507" s="2" t="s">
-        <v>647</v>
+        <v>1398</v>
       </c>
       <c r="J507" t="s">
         <v>67</v>
@@ -11760,27 +11751,27 @@
     </row>
     <row r="508" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="G508" s="2" t="s">
-        <v>708</v>
+        <v>1399</v>
       </c>
       <c r="H508" s="2" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="J508" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="509" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A509" t="s">
-        <v>1386</v>
+      <c r="A509" s="4">
+        <v>14289</v>
       </c>
       <c r="G509" s="2" t="s">
-        <v>1402</v>
+        <v>1261</v>
       </c>
       <c r="H509" s="2" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="J509" t="s">
         <v>67</v>
@@ -11788,13 +11779,13 @@
     </row>
     <row r="510" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A510" s="4">
-        <v>14289</v>
-      </c>
-      <c r="G510" s="2" t="s">
-        <v>1264</v>
+        <v>23973</v>
+      </c>
+      <c r="G510" s="3" t="s">
+        <v>1262</v>
       </c>
       <c r="H510" s="2" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="J510" t="s">
         <v>67</v>
@@ -11802,55 +11793,55 @@
     </row>
     <row r="511" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A511" s="4">
-        <v>23973</v>
+        <v>53921</v>
       </c>
       <c r="G511" s="3" t="s">
-        <v>1265</v>
+        <v>434</v>
       </c>
       <c r="H511" s="2" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="J511" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="512" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A512" s="4">
-        <v>53921</v>
-      </c>
-      <c r="G512" s="3" t="s">
-        <v>435</v>
+      <c r="A512" t="s">
+        <v>1384</v>
+      </c>
+      <c r="G512" s="2" t="s">
+        <v>1404</v>
       </c>
       <c r="H512" s="2" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="J512" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="513" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A513" t="s">
-        <v>1387</v>
+      <c r="A513" s="4">
+        <v>22973</v>
       </c>
       <c r="G513" s="2" t="s">
+        <v>1406</v>
+      </c>
+      <c r="H513" s="2" t="s">
         <v>1407</v>
       </c>
-      <c r="H513" s="2" t="s">
-        <v>1408</v>
-      </c>
       <c r="J513" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
     </row>
     <row r="514" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A514" s="4">
-        <v>22973</v>
+        <v>16435</v>
       </c>
       <c r="G514" s="2" t="s">
-        <v>1409</v>
+        <v>512</v>
       </c>
       <c r="H514" s="2" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="J514" t="s">
         <v>31</v>
@@ -11858,29 +11849,15 @@
     </row>
     <row r="515" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A515" s="4">
-        <v>16435</v>
+        <v>2667</v>
       </c>
       <c r="G515" s="2" t="s">
-        <v>513</v>
+        <v>479</v>
       </c>
       <c r="H515" s="2" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="J515" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="516" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A516" s="4">
-        <v>2667</v>
-      </c>
-      <c r="G516" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="H516" s="2" t="s">
-        <v>1412</v>
-      </c>
-      <c r="J516" t="s">
         <v>31</v>
       </c>
     </row>
